--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G8">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G17">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G27">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G44">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G57">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G60">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G82">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G90">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G120">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G139">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.84</v>
+        <v>2.37</v>
       </c>
       <c r="O142">
-        <v>4.27</v>
+        <v>4.06</v>
       </c>
       <c r="P142">
-        <v>4.21</v>
+        <v>2.88</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23500,10 +23500,10 @@
         <v>0</v>
       </c>
       <c r="AC142">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD142">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="O143">
-        <v>4.06</v>
+        <v>4.36</v>
       </c>
       <c r="P143">
-        <v>2.88</v>
+        <v>4.36</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23663,10 +23663,10 @@
         <v>0</v>
       </c>
       <c r="AC143">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD143">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O144">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="P144">
-        <v>4.36</v>
+        <v>4.21</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>3.21</v>
+        <v>1.47</v>
       </c>
       <c r="O146">
-        <v>3.64</v>
+        <v>4.93</v>
       </c>
       <c r="P146">
-        <v>2.33</v>
+        <v>7.6</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="AA146">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB146">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AC146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.47</v>
+        <v>3.21</v>
       </c>
       <c r="O147">
-        <v>4.93</v>
+        <v>3.64</v>
       </c>
       <c r="P147">
-        <v>7.6</v>
+        <v>2.33</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24309,10 +24309,10 @@
         <v>0</v>
       </c>
       <c r="AA147">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB147">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AC147">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G152">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G168">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30340,10 +30340,10 @@
         <v>0</v>
       </c>
       <c r="AA184">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB184">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC184">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O185">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P185">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30503,10 +30503,10 @@
         <v>0</v>
       </c>
       <c r="AA185">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB185">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G186">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,10 +30829,10 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O188">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P188">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -30992,10 +30992,10 @@
         <v>0</v>
       </c>
       <c r="AA188">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB188">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G189">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G197">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G206">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="G207">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G208">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G241">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G242">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G243">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G244">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G245">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G300">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G301">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G302">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G303">
@@ -61402,12 +61402,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G375">
@@ -61728,12 +61728,12 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G377">
@@ -63032,12 +63032,12 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G385">
@@ -63195,12 +63195,12 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G386">
@@ -64010,12 +64010,12 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G391">
@@ -64173,12 +64173,12 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G392">
@@ -64499,12 +64499,12 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G394">
@@ -64662,12 +64662,12 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G395">

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G55">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="O143">
-        <v>3.84</v>
+        <v>4.06</v>
       </c>
       <c r="P143">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23657,16 +23657,16 @@
         <v>0</v>
       </c>
       <c r="AA143">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB143">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="O144">
-        <v>4.06</v>
+        <v>4.36</v>
       </c>
       <c r="P144">
-        <v>2.88</v>
+        <v>4.36</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23826,10 +23826,10 @@
         <v>0</v>
       </c>
       <c r="AC144">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD144">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O145">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="P145">
-        <v>4.36</v>
+        <v>4.21</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.84</v>
+        <v>1.33</v>
       </c>
       <c r="O146">
-        <v>4.27</v>
+        <v>6.49</v>
       </c>
       <c r="P146">
-        <v>4.21</v>
+        <v>9.1</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24152,10 +24152,10 @@
         <v>0</v>
       </c>
       <c r="AC146">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AD146">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AE146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.33</v>
+        <v>2.29</v>
       </c>
       <c r="O147">
-        <v>6.49</v>
+        <v>3.84</v>
       </c>
       <c r="P147">
-        <v>9.1</v>
+        <v>3.14</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24309,16 +24309,16 @@
         <v>0</v>
       </c>
       <c r="AA147">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC147">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD147">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE147">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G171">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G206">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G207">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G208">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G209">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G245">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G246">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G247">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G248">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G249">
@@ -64010,12 +64010,12 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G391">
@@ -64173,12 +64173,12 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G392">
@@ -64499,12 +64499,12 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G394">
@@ -64662,12 +64662,12 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G395">
@@ -64825,12 +64825,12 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G396">

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G27">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9645,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9808,10 +9808,10 @@
         <v>0</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE58">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22679,10 +22679,10 @@
         <v>0</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC137">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O160">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26428,10 +26428,10 @@
         <v>0</v>
       </c>
       <c r="AA160">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB160">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC160">
         <v>0</v>
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>7.27</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29531,10 +29531,10 @@
         <v>0</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30183,10 +30183,10 @@
         <v>0</v>
       </c>
       <c r="AC183">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD183">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -30992,10 +30992,10 @@
         <v>0</v>
       </c>
       <c r="AA188">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB188">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC188">
         <v>0</v>
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O200">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q200">
         <v>0</v>
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O205">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O208">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41587,10 +41587,10 @@
         <v>0</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC253">
         <v>0</v>
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O258">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P258">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q258">
         <v>0</v>
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O315">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P315">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -51693,10 +51693,10 @@
         <v>0</v>
       </c>
       <c r="AA315">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB315">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC315">
         <v>0</v>
@@ -64368,13 +64368,13 @@
         </is>
       </c>
       <c r="N393">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O393">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P393">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q393">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU398"/>
+  <dimension ref="A1:AU399"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,22 +21946,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,22 +22109,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O134">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P134">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>3.35</v>
+        <v>1.45</v>
       </c>
       <c r="O135">
-        <v>3.13</v>
+        <v>5.1</v>
       </c>
       <c r="P135">
-        <v>2.52</v>
+        <v>7.6</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22430,12 +22430,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fanja</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-10-24 10:10:00</t>
+          <t>2026-10-24 10:00:00</t>
         </is>
       </c>
     </row>
@@ -22593,12 +22593,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Fanja</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O137">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P137">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22679,10 +22679,10 @@
         <v>0</v>
       </c>
       <c r="AA137">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB137">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC137">
         <v>0</v>
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-10-24 10:30:00</t>
+          <t>2026-10-24 10:10:00</t>
         </is>
       </c>
     </row>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="O138">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="P138">
-        <v>2.28</v>
+        <v>2.89</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22842,10 +22842,10 @@
         <v>0</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O140">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P140">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O141">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="P141">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O142">
-        <v>3.34</v>
+        <v>3.89</v>
       </c>
       <c r="P142">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="O143">
-        <v>4.06</v>
+        <v>3.34</v>
       </c>
       <c r="P143">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23663,10 +23663,10 @@
         <v>0</v>
       </c>
       <c r="AC143">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD143">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="O144">
-        <v>4.36</v>
+        <v>4.06</v>
       </c>
       <c r="P144">
-        <v>4.36</v>
+        <v>2.88</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23826,10 +23826,10 @@
         <v>0</v>
       </c>
       <c r="AC144">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD144">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O145">
-        <v>4.27</v>
+        <v>4.36</v>
       </c>
       <c r="P145">
-        <v>4.21</v>
+        <v>4.36</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.33</v>
+        <v>1.84</v>
       </c>
       <c r="O146">
-        <v>6.49</v>
+        <v>4.27</v>
       </c>
       <c r="P146">
-        <v>9.1</v>
+        <v>4.21</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24152,10 +24152,10 @@
         <v>0</v>
       </c>
       <c r="AC146">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AD146">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AE146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="O147">
-        <v>3.84</v>
+        <v>6.49</v>
       </c>
       <c r="P147">
-        <v>3.14</v>
+        <v>9.1</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24309,16 +24309,16 @@
         <v>0</v>
       </c>
       <c r="AA147">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB147">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC147">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD147">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE147">
         <v>0</v>
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.47</v>
+        <v>2.29</v>
       </c>
       <c r="O148">
-        <v>4.93</v>
+        <v>3.84</v>
       </c>
       <c r="P148">
-        <v>7.6</v>
+        <v>3.14</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-10-24 11:00:00</t>
+          <t>2026-10-24 10:30:00</t>
         </is>
       </c>
     </row>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>3.21</v>
+        <v>1.47</v>
       </c>
       <c r="O149">
-        <v>3.64</v>
+        <v>4.93</v>
       </c>
       <c r="P149">
-        <v>2.33</v>
+        <v>7.6</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24635,10 +24635,10 @@
         <v>0</v>
       </c>
       <c r="AA149">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB149">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AC149">
         <v>0</v>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24798,10 +24798,10 @@
         <v>0</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC150">
         <v>0</v>
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G151">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G155">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O158">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P158">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>5.06</v>
+        <v>2.35</v>
       </c>
       <c r="O159">
-        <v>3.7</v>
+        <v>3.06</v>
       </c>
       <c r="P159">
-        <v>1.65</v>
+        <v>2.73</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.31</v>
+        <v>5.06</v>
       </c>
       <c r="O160">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P160">
-        <v>8.300000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26428,10 +26428,10 @@
         <v>0</v>
       </c>
       <c r="AA160">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB160">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="O161">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P161">
-        <v>7.27</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26591,10 +26591,10 @@
         <v>0</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>7.27</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O163">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P163">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,22 +28303,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G172">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G173">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G175">
@@ -28955,22 +28955,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,22 +29281,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O179">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P179">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29531,10 +29531,10 @@
         <v>0</v>
       </c>
       <c r="AC179">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD179">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE179">
         <v>0</v>
@@ -30422,22 +30422,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30509,10 +30509,10 @@
         <v>0</v>
       </c>
       <c r="AC185">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD185">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O186">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P186">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB186">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>3</v>
+        <v>3.41</v>
       </c>
       <c r="O187">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="P187">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,10 +30829,10 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB187">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AC187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O188">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P188">
-        <v>2.81</v>
+        <v>2.37</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -30992,10 +30992,10 @@
         <v>0</v>
       </c>
       <c r="AA188">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB188">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AC188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="O189">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="P189">
-        <v>2.22</v>
+        <v>2.81</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AB189">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.37</v>
+        <v>3.05</v>
       </c>
       <c r="O190">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P190">
-        <v>2.9</v>
+        <v>2.22</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB190">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.56</v>
+        <v>2.37</v>
       </c>
       <c r="O191">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P191">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31481,10 +31481,10 @@
         <v>0</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.65</v>
+        <v>2.56</v>
       </c>
       <c r="O192">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="P192">
-        <v>4.35</v>
+        <v>2.69</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,7 +32052,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O195">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P195">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="O196">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="P196">
-        <v>3.98</v>
+        <v>9.6</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="O197">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="P197">
-        <v>3.35</v>
+        <v>3.98</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="O198">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P198">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O200">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P200">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="O201">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P201">
-        <v>2.89</v>
+        <v>2.42</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="O202">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P202">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="O203">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P203">
-        <v>4.14</v>
+        <v>2.94</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.65</v>
+        <v>1.71</v>
       </c>
       <c r="O204">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P204">
-        <v>2.33</v>
+        <v>4.14</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O205">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P205">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O206">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P206">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="O207">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P207">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="O208">
         <v>3.3</v>
       </c>
       <c r="P208">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O209">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P209">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O210">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P210">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="O211">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P211">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O212">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P212">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -34981,12 +34981,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="O213">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="P213">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35067,10 +35067,10 @@
         <v>0</v>
       </c>
       <c r="AA213">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB213">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC213">
         <v>0</v>
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-10-24 11:15:00</t>
+          <t>2026-10-24 11:00:00</t>
         </is>
       </c>
     </row>
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O215">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="P215">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -35470,12 +35470,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35621,7 +35621,7 @@
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>2026-10-24 11:30:00</t>
+          <t>2026-10-24 11:15:00</t>
         </is>
       </c>
     </row>
@@ -35638,22 +35638,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,22 +35801,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O219">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P219">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36045,10 +36045,10 @@
         <v>0</v>
       </c>
       <c r="AA219">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB219">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC219">
         <v>0</v>
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -36208,10 +36208,10 @@
         <v>0</v>
       </c>
       <c r="AA220">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB220">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC220">
         <v>0</v>
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O222">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="P222">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36616,7 +36616,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.69</v>
+        <v>2.99</v>
       </c>
       <c r="O223">
-        <v>4.34</v>
+        <v>3.67</v>
       </c>
       <c r="P223">
-        <v>4.54</v>
+        <v>2.13</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O224">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36937,12 +36937,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G225">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>2026-10-24 12:00:00</t>
+          <t>2026-10-24 11:30:00</t>
         </is>
       </c>
     </row>
@@ -37105,22 +37105,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,22 +37268,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G227">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="G228">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G229">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="G230">
@@ -37920,22 +37920,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G231">
@@ -38083,22 +38083,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O235">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P235">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38653,10 +38653,10 @@
         <v>0</v>
       </c>
       <c r="AA235">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB235">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC235">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="O236">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P236">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38816,10 +38816,10 @@
         <v>0</v>
       </c>
       <c r="AA236">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB236">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC236">
         <v>0</v>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="G238">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O239">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P239">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G242">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G243">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G245">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G246">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G247">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G248">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G249">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G250">
@@ -41175,12 +41175,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G251">
@@ -41326,7 +41326,7 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>2026-10-24 12:05:00</t>
+          <t>2026-10-24 12:00:00</t>
         </is>
       </c>
     </row>
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G252">
@@ -41501,12 +41501,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O253">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P253">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41587,10 +41587,10 @@
         <v>0</v>
       </c>
       <c r="AA253">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB253">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC253">
         <v>0</v>
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-10-24 12:15:00</t>
+          <t>2026-10-24 12:05:00</t>
         </is>
       </c>
     </row>
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G254">
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="O254">
-        <v>4.42</v>
+        <v>3.4</v>
       </c>
       <c r="P254">
-        <v>5.44</v>
+        <v>3.1</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41750,10 +41750,10 @@
         <v>0</v>
       </c>
       <c r="AA254">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB254">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC254">
         <v>0</v>
@@ -41827,12 +41827,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G255">
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O255">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="P255">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -41978,7 +41978,7 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>2026-10-24 12:30:00</t>
+          <t>2026-10-24 12:15:00</t>
         </is>
       </c>
     </row>
@@ -41995,22 +41995,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,22 +42158,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G258">
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O258">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P258">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="Q258">
         <v>0</v>
@@ -42484,22 +42484,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O259">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P259">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="P260">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42810,22 +42810,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P261">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G262">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G263">
@@ -43294,12 +43294,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G264">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>2026-10-24 12:45:00</t>
+          <t>2026-10-24 12:30:00</t>
         </is>
       </c>
     </row>
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G265">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G266">
@@ -43783,12 +43783,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-10-24 13:00:00</t>
+          <t>2026-10-24 12:45:00</t>
         </is>
       </c>
     </row>
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G268">
@@ -44114,7 +44114,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O269">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P269">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -44201,10 +44201,10 @@
         <v>0</v>
       </c>
       <c r="AC269">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD269">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="O270">
         <v>4</v>
       </c>
       <c r="P270">
-        <v>3.79</v>
+        <v>2.4</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -44364,10 +44364,10 @@
         <v>0</v>
       </c>
       <c r="AC270">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD270">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE270">
         <v>0</v>
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O271">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P271">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G272">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G273">
@@ -44929,22 +44929,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,22 +45092,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.63</v>
+        <v>4.35</v>
       </c>
       <c r="O275">
-        <v>3.14</v>
+        <v>4.14</v>
       </c>
       <c r="P275">
-        <v>2.66</v>
+        <v>1.74</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O276">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P276">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="G277">
@@ -45581,7 +45581,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G278">
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G279">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G280">
@@ -46070,7 +46070,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G281">
@@ -46233,7 +46233,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G282">
@@ -46396,7 +46396,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G283">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G284">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G285">
@@ -46885,7 +46885,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G286">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O287">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P287">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47129,10 +47129,10 @@
         <v>0</v>
       </c>
       <c r="AA287">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB287">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC287">
         <v>0</v>
@@ -47206,12 +47206,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47292,10 +47292,10 @@
         <v>0</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC288">
         <v>0</v>
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-10-24 13:15:00</t>
+          <t>2026-10-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -47374,7 +47374,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G289">
@@ -47537,7 +47537,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G290">
@@ -47695,12 +47695,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O291">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="P291">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47781,10 +47781,10 @@
         <v>0</v>
       </c>
       <c r="AA291">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB291">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC291">
         <v>0</v>
@@ -47846,7 +47846,7 @@
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>2026-10-24 13:30:00</t>
+          <t>2026-10-24 13:15:00</t>
         </is>
       </c>
     </row>
@@ -47863,7 +47863,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O292">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="P292">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q292">
         <v>0</v>
@@ -47944,10 +47944,10 @@
         <v>0</v>
       </c>
       <c r="AA292">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB292">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC292">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G293">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O294">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P294">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -48352,22 +48352,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G295">
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O295">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P295">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48515,22 +48515,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G296">
@@ -48678,7 +48678,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G297">
@@ -48841,7 +48841,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G298">
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O298">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P298">
-        <v>7.07</v>
+        <v>0</v>
       </c>
       <c r="Q298">
         <v>0</v>
@@ -49004,7 +49004,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O299">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P299">
-        <v>0</v>
+        <v>7.07</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49167,7 +49167,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G300">
@@ -49330,7 +49330,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="G301">
@@ -49493,7 +49493,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O302">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="P302">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49580,10 +49580,10 @@
         <v>0</v>
       </c>
       <c r="AC302">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD302">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE302">
         <v>0</v>
@@ -49651,12 +49651,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O303">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="P303">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49743,10 +49743,10 @@
         <v>0</v>
       </c>
       <c r="AC303">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD303">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE303">
         <v>0</v>
@@ -49802,7 +49802,7 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45:00</t>
+          <t>2026-10-24 13:30:00</t>
         </is>
       </c>
     </row>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G304">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G305">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G306">
@@ -50308,7 +50308,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Lusail City</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G307">
@@ -50471,7 +50471,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Lusail City</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O308">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P308">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50629,12 +50629,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O309">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P309">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q309">
         <v>0</v>
@@ -50780,7 +50780,7 @@
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>2026-10-24 14:00:00</t>
+          <t>2026-10-24 13:45:00</t>
         </is>
       </c>
     </row>
@@ -50797,7 +50797,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G310">
@@ -50960,7 +50960,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G311">
@@ -51002,13 +51002,13 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O311">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P311">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q311">
         <v>0</v>
@@ -51123,7 +51123,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,13 +51165,13 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.18</v>
+        <v>1.87</v>
       </c>
       <c r="O312">
-        <v>6.3</v>
+        <v>3.34</v>
       </c>
       <c r="P312">
-        <v>15</v>
+        <v>4.07</v>
       </c>
       <c r="Q312">
         <v>0</v>
@@ -51286,7 +51286,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q313">
         <v>0</v>
@@ -51449,7 +51449,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="G314">
@@ -51491,13 +51491,13 @@
         </is>
       </c>
       <c r="N314">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O314">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P314">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q314">
         <v>0</v>
@@ -51530,10 +51530,10 @@
         <v>0</v>
       </c>
       <c r="AA314">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB314">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC314">
         <v>0</v>
@@ -51607,12 +51607,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G315">
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>2.85</v>
+        <v>2.26</v>
       </c>
       <c r="O315">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="P315">
-        <v>2.45</v>
+        <v>3.28</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -51693,10 +51693,10 @@
         <v>0</v>
       </c>
       <c r="AA315">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB315">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC315">
         <v>0</v>
@@ -51758,7 +51758,7 @@
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>2026-10-24 14:30:00</t>
+          <t>2026-10-24 14:00:00</t>
         </is>
       </c>
     </row>
@@ -51775,7 +51775,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G316">
@@ -51817,13 +51817,13 @@
         </is>
       </c>
       <c r="N316">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O316">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P316">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q316">
         <v>0</v>
@@ -51856,10 +51856,10 @@
         <v>0</v>
       </c>
       <c r="AA316">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB316">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC316">
         <v>0</v>
@@ -51938,7 +51938,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G317">
@@ -51980,13 +51980,13 @@
         </is>
       </c>
       <c r="N317">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="O317">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P317">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Q317">
         <v>0</v>
@@ -52101,22 +52101,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G318">
@@ -52143,13 +52143,13 @@
         </is>
       </c>
       <c r="N318">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O318">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P318">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q318">
         <v>0</v>
@@ -52259,27 +52259,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G319">
@@ -52410,7 +52410,7 @@
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>2026-10-24 15:00:00</t>
+          <t>2026-10-24 14:30:00</t>
         </is>
       </c>
     </row>
@@ -52427,7 +52427,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G320">
@@ -52590,7 +52590,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G321">
@@ -52753,7 +52753,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G322">
@@ -52916,7 +52916,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O323">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P323">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -53074,12 +53074,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,13 +53121,13 @@
         </is>
       </c>
       <c r="N324">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O324">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P324">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q324">
         <v>0</v>
@@ -53225,7 +53225,7 @@
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>2026-10-24 15:15:00</t>
+          <t>2026-10-24 15:00:00</t>
         </is>
       </c>
     </row>
@@ -53237,12 +53237,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="N325">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O325">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P325">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="Q325">
         <v>0</v>
@@ -53388,7 +53388,7 @@
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>2026-10-24 15:30:00</t>
+          <t>2026-10-24 15:15:00</t>
         </is>
       </c>
     </row>
@@ -53405,22 +53405,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,13 +53447,13 @@
         </is>
       </c>
       <c r="N326">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O326">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P326">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="Q326">
         <v>0</v>
@@ -53568,22 +53568,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G327">
@@ -53731,7 +53731,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G328">
@@ -53894,7 +53894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G329">
@@ -54052,12 +54052,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G330">
@@ -54099,13 +54099,13 @@
         </is>
       </c>
       <c r="N330">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O330">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="P330">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="Q330">
         <v>0</v>
@@ -54203,7 +54203,7 @@
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>2026-10-24 15:45:00</t>
+          <t>2026-10-24 15:30:00</t>
         </is>
       </c>
     </row>
@@ -54220,7 +54220,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G331">
@@ -54262,13 +54262,13 @@
         </is>
       </c>
       <c r="N331">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="O331">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="P331">
-        <v>6.53</v>
+        <v>3.39</v>
       </c>
       <c r="Q331">
         <v>0</v>
@@ -54301,10 +54301,10 @@
         <v>0</v>
       </c>
       <c r="AA331">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB331">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC331">
         <v>0</v>
@@ -54383,7 +54383,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G332">
@@ -54425,13 +54425,13 @@
         </is>
       </c>
       <c r="N332">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O332">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="P332">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="Q332">
         <v>0</v>
@@ -54464,10 +54464,10 @@
         <v>0</v>
       </c>
       <c r="AA332">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB332">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC332">
         <v>0</v>
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G333">
@@ -54704,12 +54704,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G334">
@@ -54855,7 +54855,7 @@
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>2026-10-24 16:00:00</t>
+          <t>2026-10-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -54872,22 +54872,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G335">
@@ -55035,7 +55035,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G336">
@@ -55198,22 +55198,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G337">
@@ -55361,7 +55361,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G338">
@@ -55524,7 +55524,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G339">
@@ -55687,22 +55687,22 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O340">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P340">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -55850,22 +55850,22 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G341">
@@ -56008,27 +56008,27 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="O342">
-        <v>3.33</v>
+        <v>3.97</v>
       </c>
       <c r="P342">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q342">
         <v>0</v>
@@ -56159,7 +56159,7 @@
       </c>
       <c r="AU342" t="inlineStr">
         <is>
-          <t>2026-10-24 16:30:00</t>
+          <t>2026-10-24 16:00:00</t>
         </is>
       </c>
     </row>
@@ -56171,12 +56171,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G343">
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O343">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="P343">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q343">
         <v>0</v>
@@ -56257,10 +56257,10 @@
         <v>0</v>
       </c>
       <c r="AA343">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB343">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC343">
         <v>0</v>
@@ -56322,7 +56322,7 @@
       </c>
       <c r="AU343" t="inlineStr">
         <is>
-          <t>2026-10-24 16:30:00</t>
+          <t>2026-10-24 16:00:00</t>
         </is>
       </c>
     </row>
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G344">
@@ -56381,13 +56381,13 @@
         </is>
       </c>
       <c r="N344">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="O344">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="P344">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q344">
         <v>0</v>
@@ -56420,10 +56420,10 @@
         <v>0</v>
       </c>
       <c r="AA344">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB344">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC344">
         <v>0</v>
@@ -56502,7 +56502,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G345">
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O345">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P345">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q345">
         <v>0</v>
@@ -56583,10 +56583,10 @@
         <v>0</v>
       </c>
       <c r="AA345">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB345">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC345">
         <v>0</v>
@@ -56665,22 +56665,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G346">
@@ -56707,13 +56707,13 @@
         </is>
       </c>
       <c r="N346">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="O346">
-        <v>4.43</v>
+        <v>3.55</v>
       </c>
       <c r="P346">
-        <v>1.48</v>
+        <v>3.53</v>
       </c>
       <c r="Q346">
         <v>0</v>
@@ -56746,10 +56746,10 @@
         <v>0</v>
       </c>
       <c r="AA346">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AB346">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AC346">
         <v>0</v>
@@ -56828,7 +56828,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G347">
@@ -56991,22 +56991,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O348">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P348">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q348">
         <v>0</v>
@@ -57072,10 +57072,10 @@
         <v>0</v>
       </c>
       <c r="AA348">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB348">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC348">
         <v>0</v>
@@ -57149,12 +57149,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G349">
@@ -57300,7 +57300,7 @@
       </c>
       <c r="AU349" t="inlineStr">
         <is>
-          <t>2026-10-24 17:00:00</t>
+          <t>2026-10-24 16:30:00</t>
         </is>
       </c>
     </row>
@@ -57312,12 +57312,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G350">
@@ -57463,7 +57463,7 @@
       </c>
       <c r="AU350" t="inlineStr">
         <is>
-          <t>2026-10-24 17:00:00</t>
+          <t>2026-10-24 16:30:00</t>
         </is>
       </c>
     </row>
@@ -57480,7 +57480,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G351">
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G352">
@@ -57801,12 +57801,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G353">
@@ -57952,7 +57952,7 @@
       </c>
       <c r="AU353" t="inlineStr">
         <is>
-          <t>2026-10-24 17:30:00</t>
+          <t>2026-10-24 17:00:00</t>
         </is>
       </c>
     </row>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G354">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G355">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G356">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G357">
@@ -58616,12 +58616,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G358">
@@ -58767,7 +58767,7 @@
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>2026-10-24 18:00:00</t>
+          <t>2026-10-24 17:30:00</t>
         </is>
       </c>
     </row>
@@ -58779,12 +58779,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G359">
@@ -58930,7 +58930,7 @@
       </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>2026-10-24 18:15:00</t>
+          <t>2026-10-24 18:00:00</t>
         </is>
       </c>
     </row>
@@ -58942,12 +58942,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G360">
@@ -58989,13 +58989,13 @@
         </is>
       </c>
       <c r="N360">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O360">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="P360">
-        <v>5.98</v>
+        <v>0</v>
       </c>
       <c r="Q360">
         <v>0</v>
@@ -59028,10 +59028,10 @@
         <v>0</v>
       </c>
       <c r="AA360">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB360">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC360">
         <v>0</v>
@@ -59093,7 +59093,7 @@
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>2026-10-24 18:30:00</t>
+          <t>2026-10-24 18:15:00</t>
         </is>
       </c>
     </row>
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G361">
@@ -59152,13 +59152,13 @@
         </is>
       </c>
       <c r="N361">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="O361">
-        <v>3.61</v>
+        <v>4.08</v>
       </c>
       <c r="P361">
-        <v>4.17</v>
+        <v>5.98</v>
       </c>
       <c r="Q361">
         <v>0</v>
@@ -59191,10 +59191,10 @@
         <v>0</v>
       </c>
       <c r="AA361">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AB361">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AC361">
         <v>0</v>
@@ -59273,7 +59273,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G362">
@@ -59315,13 +59315,13 @@
         </is>
       </c>
       <c r="N362">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O362">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P362">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q362">
         <v>0</v>
@@ -59354,10 +59354,10 @@
         <v>0</v>
       </c>
       <c r="AA362">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB362">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC362">
         <v>0</v>
@@ -59436,7 +59436,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G363">
@@ -59599,7 +59599,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G364">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G365">
@@ -59920,12 +59920,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G366">
@@ -60071,7 +60071,7 @@
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>2026-10-24 19:00:00</t>
+          <t>2026-10-24 18:30:00</t>
         </is>
       </c>
     </row>
@@ -60088,7 +60088,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G367">
@@ -60246,12 +60246,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G368">
@@ -60293,13 +60293,13 @@
         </is>
       </c>
       <c r="N368">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O368">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P368">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q368">
         <v>0</v>
@@ -60332,10 +60332,10 @@
         <v>0</v>
       </c>
       <c r="AA368">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB368">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC368">
         <v>0</v>
@@ -60397,7 +60397,7 @@
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>2026-10-24 19:30:00</t>
+          <t>2026-10-24 19:00:00</t>
         </is>
       </c>
     </row>
@@ -60414,7 +60414,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G369">
@@ -60456,13 +60456,13 @@
         </is>
       </c>
       <c r="N369">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O369">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P369">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q369">
         <v>0</v>
@@ -60495,10 +60495,10 @@
         <v>0</v>
       </c>
       <c r="AA369">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB369">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC369">
         <v>0</v>
@@ -60572,12 +60572,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G370">
@@ -60723,7 +60723,7 @@
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00:00</t>
+          <t>2026-10-24 19:30:00</t>
         </is>
       </c>
     </row>
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G371">
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G372">
@@ -61066,7 +61066,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G373">
@@ -61229,7 +61229,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -61239,12 +61239,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G374">
@@ -61387,12 +61387,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -61402,12 +61402,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G375">
@@ -61538,7 +61538,7 @@
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>2026-10-24 20:30:00</t>
+          <t>2026-10-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -61555,7 +61555,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -61565,12 +61565,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G376">
@@ -61718,7 +61718,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -61728,12 +61728,12 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G377">
@@ -61891,12 +61891,12 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G378">
@@ -62054,12 +62054,12 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G379">
@@ -62217,12 +62217,12 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G380">
@@ -62365,27 +62365,27 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G381">
@@ -62516,7 +62516,7 @@
       </c>
       <c r="AU381" t="inlineStr">
         <is>
-          <t>2026-10-24 21:00:00</t>
+          <t>2026-10-24 20:30:00</t>
         </is>
       </c>
     </row>
@@ -62533,22 +62533,22 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G382">
@@ -62575,13 +62575,13 @@
         </is>
       </c>
       <c r="N382">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O382">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P382">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q382">
         <v>0</v>
@@ -62696,7 +62696,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -62706,12 +62706,12 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G383">
@@ -62738,13 +62738,13 @@
         </is>
       </c>
       <c r="N383">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O383">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P383">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q383">
         <v>0</v>
@@ -62854,12 +62854,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -62869,12 +62869,12 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G384">
@@ -63005,7 +63005,7 @@
       </c>
       <c r="AU384" t="inlineStr">
         <is>
-          <t>2026-10-24 21:30:00</t>
+          <t>2026-10-24 21:00:00</t>
         </is>
       </c>
     </row>
@@ -63022,7 +63022,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -63032,12 +63032,12 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G385">
@@ -63195,12 +63195,12 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G386">
@@ -63358,12 +63358,12 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G387">
@@ -63521,12 +63521,12 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G388">
@@ -63684,12 +63684,12 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G389">
@@ -63832,12 +63832,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -63847,12 +63847,12 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G390">
@@ -63983,7 +63983,7 @@
       </c>
       <c r="AU390" t="inlineStr">
         <is>
-          <t>2026-10-24 21:45:00</t>
+          <t>2026-10-24 21:30:00</t>
         </is>
       </c>
     </row>
@@ -63995,12 +63995,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -64010,12 +64010,12 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G391">
@@ -64146,7 +64146,7 @@
       </c>
       <c r="AU391" t="inlineStr">
         <is>
-          <t>2026-10-24 22:00:00</t>
+          <t>2026-10-24 21:45:00</t>
         </is>
       </c>
     </row>
@@ -64173,12 +64173,12 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G392">
@@ -64321,27 +64321,27 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G393">
@@ -64368,13 +64368,13 @@
         </is>
       </c>
       <c r="N393">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O393">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P393">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q393">
         <v>0</v>
@@ -64472,7 +64472,7 @@
       </c>
       <c r="AU393" t="inlineStr">
         <is>
-          <t>2026-10-24 23:00:00</t>
+          <t>2026-10-24 22:00:00</t>
         </is>
       </c>
     </row>
@@ -64489,22 +64489,22 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="G394">
@@ -64531,13 +64531,13 @@
         </is>
       </c>
       <c r="N394">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O394">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P394">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q394">
         <v>0</v>
@@ -64662,12 +64662,12 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G395">
@@ -64825,12 +64825,12 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G396">
@@ -64973,12 +64973,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -64988,12 +64988,12 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G397">
@@ -65124,7 +65124,7 @@
       </c>
       <c r="AU397" t="inlineStr">
         <is>
-          <t>2026-10-24 23:30:00</t>
+          <t>2026-10-24 23:00:00</t>
         </is>
       </c>
     </row>
@@ -65151,141 +65151,304 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="G398">
+        <v>0</v>
+      </c>
+      <c r="H398">
+        <v>0</v>
+      </c>
+      <c r="I398">
+        <v>0</v>
+      </c>
+      <c r="J398">
+        <v>0</v>
+      </c>
+      <c r="K398">
+        <v>0</v>
+      </c>
+      <c r="L398">
+        <v>0</v>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N398">
+        <v>0</v>
+      </c>
+      <c r="O398">
+        <v>0</v>
+      </c>
+      <c r="P398">
+        <v>0</v>
+      </c>
+      <c r="Q398">
+        <v>0</v>
+      </c>
+      <c r="R398">
+        <v>0</v>
+      </c>
+      <c r="S398">
+        <v>0</v>
+      </c>
+      <c r="T398">
+        <v>0</v>
+      </c>
+      <c r="U398">
+        <v>0</v>
+      </c>
+      <c r="V398">
+        <v>0</v>
+      </c>
+      <c r="W398">
+        <v>0</v>
+      </c>
+      <c r="X398">
+        <v>0</v>
+      </c>
+      <c r="Y398">
+        <v>0</v>
+      </c>
+      <c r="Z398">
+        <v>0</v>
+      </c>
+      <c r="AA398">
+        <v>0</v>
+      </c>
+      <c r="AB398">
+        <v>0</v>
+      </c>
+      <c r="AC398">
+        <v>0</v>
+      </c>
+      <c r="AD398">
+        <v>0</v>
+      </c>
+      <c r="AE398">
+        <v>0</v>
+      </c>
+      <c r="AF398">
+        <v>0</v>
+      </c>
+      <c r="AG398">
+        <v>0</v>
+      </c>
+      <c r="AH398" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI398" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ398">
+        <v>0</v>
+      </c>
+      <c r="AK398">
+        <v>0</v>
+      </c>
+      <c r="AL398">
+        <v>0</v>
+      </c>
+      <c r="AM398">
+        <v>-1</v>
+      </c>
+      <c r="AN398">
+        <v>-1</v>
+      </c>
+      <c r="AO398">
+        <v>-1</v>
+      </c>
+      <c r="AP398">
+        <v>-1</v>
+      </c>
+      <c r="AQ398">
+        <v>0</v>
+      </c>
+      <c r="AR398">
+        <v>0</v>
+      </c>
+      <c r="AS398">
+        <v>0</v>
+      </c>
+      <c r="AT398">
+        <v>0</v>
+      </c>
+      <c r="AU398" t="inlineStr">
+        <is>
+          <t>2026-10-24 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr">
+      <c r="F399" t="inlineStr">
         <is>
           <t>Seattle Sounders</t>
         </is>
       </c>
-      <c r="G398">
-        <v>0</v>
-      </c>
-      <c r="H398">
-        <v>0</v>
-      </c>
-      <c r="I398">
-        <v>0</v>
-      </c>
-      <c r="J398">
-        <v>0</v>
-      </c>
-      <c r="K398">
-        <v>0</v>
-      </c>
-      <c r="L398">
-        <v>0</v>
-      </c>
-      <c r="M398" t="inlineStr">
+      <c r="G399">
+        <v>0</v>
+      </c>
+      <c r="H399">
+        <v>0</v>
+      </c>
+      <c r="I399">
+        <v>0</v>
+      </c>
+      <c r="J399">
+        <v>0</v>
+      </c>
+      <c r="K399">
+        <v>0</v>
+      </c>
+      <c r="L399">
+        <v>0</v>
+      </c>
+      <c r="M399" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N398">
-        <v>0</v>
-      </c>
-      <c r="O398">
-        <v>0</v>
-      </c>
-      <c r="P398">
-        <v>0</v>
-      </c>
-      <c r="Q398">
-        <v>0</v>
-      </c>
-      <c r="R398">
-        <v>0</v>
-      </c>
-      <c r="S398">
-        <v>0</v>
-      </c>
-      <c r="T398">
-        <v>0</v>
-      </c>
-      <c r="U398">
-        <v>0</v>
-      </c>
-      <c r="V398">
-        <v>0</v>
-      </c>
-      <c r="W398">
-        <v>0</v>
-      </c>
-      <c r="X398">
-        <v>0</v>
-      </c>
-      <c r="Y398">
-        <v>0</v>
-      </c>
-      <c r="Z398">
-        <v>0</v>
-      </c>
-      <c r="AA398">
-        <v>0</v>
-      </c>
-      <c r="AB398">
-        <v>0</v>
-      </c>
-      <c r="AC398">
-        <v>0</v>
-      </c>
-      <c r="AD398">
-        <v>0</v>
-      </c>
-      <c r="AE398">
-        <v>0</v>
-      </c>
-      <c r="AF398">
-        <v>0</v>
-      </c>
-      <c r="AG398">
-        <v>0</v>
-      </c>
-      <c r="AH398" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI398" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ398">
-        <v>0</v>
-      </c>
-      <c r="AK398">
-        <v>0</v>
-      </c>
-      <c r="AL398">
-        <v>0</v>
-      </c>
-      <c r="AM398">
-        <v>-1</v>
-      </c>
-      <c r="AN398">
-        <v>-1</v>
-      </c>
-      <c r="AO398">
-        <v>-1</v>
-      </c>
-      <c r="AP398">
-        <v>-1</v>
-      </c>
-      <c r="AQ398">
-        <v>0</v>
-      </c>
-      <c r="AR398">
-        <v>0</v>
-      </c>
-      <c r="AS398">
-        <v>0</v>
-      </c>
-      <c r="AT398">
-        <v>0</v>
-      </c>
-      <c r="AU398" t="inlineStr">
+      <c r="N399">
+        <v>0</v>
+      </c>
+      <c r="O399">
+        <v>0</v>
+      </c>
+      <c r="P399">
+        <v>0</v>
+      </c>
+      <c r="Q399">
+        <v>0</v>
+      </c>
+      <c r="R399">
+        <v>0</v>
+      </c>
+      <c r="S399">
+        <v>0</v>
+      </c>
+      <c r="T399">
+        <v>0</v>
+      </c>
+      <c r="U399">
+        <v>0</v>
+      </c>
+      <c r="V399">
+        <v>0</v>
+      </c>
+      <c r="W399">
+        <v>0</v>
+      </c>
+      <c r="X399">
+        <v>0</v>
+      </c>
+      <c r="Y399">
+        <v>0</v>
+      </c>
+      <c r="Z399">
+        <v>0</v>
+      </c>
+      <c r="AA399">
+        <v>0</v>
+      </c>
+      <c r="AB399">
+        <v>0</v>
+      </c>
+      <c r="AC399">
+        <v>0</v>
+      </c>
+      <c r="AD399">
+        <v>0</v>
+      </c>
+      <c r="AE399">
+        <v>0</v>
+      </c>
+      <c r="AF399">
+        <v>0</v>
+      </c>
+      <c r="AG399">
+        <v>0</v>
+      </c>
+      <c r="AH399" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI399" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ399">
+        <v>0</v>
+      </c>
+      <c r="AK399">
+        <v>0</v>
+      </c>
+      <c r="AL399">
+        <v>0</v>
+      </c>
+      <c r="AM399">
+        <v>-1</v>
+      </c>
+      <c r="AN399">
+        <v>-1</v>
+      </c>
+      <c r="AO399">
+        <v>-1</v>
+      </c>
+      <c r="AP399">
+        <v>-1</v>
+      </c>
+      <c r="AQ399">
+        <v>0</v>
+      </c>
+      <c r="AR399">
+        <v>0</v>
+      </c>
+      <c r="AS399">
+        <v>0</v>
+      </c>
+      <c r="AT399">
+        <v>0</v>
+      </c>
+      <c r="AU399" t="inlineStr">
         <is>
           <t>2026-10-24 23:30:00</t>
         </is>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC20">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC170">
         <v>0</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O171">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB172">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O180">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P180">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30020,10 +30020,10 @@
         <v>0</v>
       </c>
       <c r="AC182">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD182">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="O183">
-        <v>3.96</v>
+        <v>3.72</v>
       </c>
       <c r="P183">
-        <v>3.77</v>
+        <v>3.52</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30183,10 +30183,10 @@
         <v>0</v>
       </c>
       <c r="AC183">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD183">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AE183">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="O185">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="P185">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30509,10 +30509,10 @@
         <v>0</v>
       </c>
       <c r="AC185">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD185">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE185">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O267">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P267">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O291">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P291">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47781,10 +47781,10 @@
         <v>0</v>
       </c>
       <c r="AA291">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB291">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC291">
         <v>0</v>
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O293">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P293">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q293">
         <v>0</v>
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O322">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P322">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q322">
         <v>0</v>
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O323">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P323">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="N325">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O325">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P325">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q325">
         <v>0</v>
@@ -53773,13 +53773,13 @@
         </is>
       </c>
       <c r="N328">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O328">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P328">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q328">
         <v>0</v>
@@ -53812,10 +53812,10 @@
         <v>0</v>
       </c>
       <c r="AA328">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB328">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC328">
         <v>0</v>
@@ -54588,13 +54588,13 @@
         </is>
       </c>
       <c r="N333">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O333">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P333">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q333">
         <v>0</v>
@@ -54627,10 +54627,10 @@
         <v>0</v>
       </c>
       <c r="AA333">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB333">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC333">
         <v>0</v>
@@ -54751,13 +54751,13 @@
         </is>
       </c>
       <c r="N334">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O334">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P334">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q334">
         <v>0</v>
@@ -54796,10 +54796,10 @@
         <v>0</v>
       </c>
       <c r="AC334">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD334">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE334">
         <v>0</v>
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O339">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P339">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -57522,13 +57522,13 @@
         </is>
       </c>
       <c r="N351">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O351">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P351">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q351">
         <v>0</v>
@@ -59478,13 +59478,13 @@
         </is>
       </c>
       <c r="N363">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O363">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P363">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q363">
         <v>0</v>
@@ -59517,10 +59517,10 @@
         <v>0</v>
       </c>
       <c r="AA363">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB363">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC363">
         <v>0</v>
@@ -59641,13 +59641,13 @@
         </is>
       </c>
       <c r="N364">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O364">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P364">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q364">
         <v>0</v>
@@ -59686,10 +59686,10 @@
         <v>0</v>
       </c>
       <c r="AC364">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD364">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE364">
         <v>0</v>
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G365">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G366">
@@ -59967,13 +59967,13 @@
         </is>
       </c>
       <c r="N366">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O366">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P366">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q366">
         <v>0</v>
@@ -60006,10 +60006,10 @@
         <v>0</v>
       </c>
       <c r="AA366">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB366">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC366">
         <v>0</v>
@@ -60130,13 +60130,13 @@
         </is>
       </c>
       <c r="N367">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O367">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P367">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q367">
         <v>0</v>
@@ -60619,13 +60619,13 @@
         </is>
       </c>
       <c r="N370">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O370">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="P370">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q370">
         <v>0</v>
@@ -61108,13 +61108,13 @@
         </is>
       </c>
       <c r="N373">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O373">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P373">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q373">
         <v>0</v>
@@ -61147,10 +61147,10 @@
         <v>0</v>
       </c>
       <c r="AA373">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB373">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC373">
         <v>0</v>
@@ -62086,13 +62086,13 @@
         </is>
       </c>
       <c r="N379">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O379">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P379">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q379">
         <v>0</v>
@@ -62131,10 +62131,10 @@
         <v>0</v>
       </c>
       <c r="AC379">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD379">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE379">
         <v>0</v>
@@ -62249,13 +62249,13 @@
         </is>
       </c>
       <c r="N380">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O380">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P380">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q380">
         <v>0</v>
@@ -62294,10 +62294,10 @@
         <v>0</v>
       </c>
       <c r="AC380">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD380">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE380">
         <v>0</v>
@@ -62412,13 +62412,13 @@
         </is>
       </c>
       <c r="N381">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O381">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P381">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="Q381">
         <v>0</v>
@@ -62457,10 +62457,10 @@
         <v>0</v>
       </c>
       <c r="AC381">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD381">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE381">
         <v>0</v>
@@ -63390,13 +63390,13 @@
         </is>
       </c>
       <c r="N387">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O387">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P387">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q387">
         <v>0</v>
@@ -63435,10 +63435,10 @@
         <v>0</v>
       </c>
       <c r="AC387">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD387">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE387">
         <v>0</v>
@@ -63521,12 +63521,12 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G388">
@@ -63684,12 +63684,12 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G389">
@@ -63716,13 +63716,13 @@
         </is>
       </c>
       <c r="N389">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O389">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P389">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q389">
         <v>0</v>
@@ -63761,10 +63761,10 @@
         <v>0</v>
       </c>
       <c r="AC389">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD389">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE389">
         <v>0</v>
@@ -63847,12 +63847,12 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G390">
@@ -63879,13 +63879,13 @@
         </is>
       </c>
       <c r="N390">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O390">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P390">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q390">
         <v>0</v>
@@ -63918,10 +63918,10 @@
         <v>0</v>
       </c>
       <c r="AA390">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB390">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC390">
         <v>0</v>
@@ -64368,13 +64368,13 @@
         </is>
       </c>
       <c r="N393">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O393">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P393">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q393">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G133">

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G244">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G245">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G248">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G250">
@@ -62054,12 +62054,12 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G379">
@@ -62086,13 +62086,13 @@
         </is>
       </c>
       <c r="N379">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O379">
-        <v>3.82</v>
+        <v>4.03</v>
       </c>
       <c r="P379">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="Q379">
         <v>0</v>
@@ -62131,10 +62131,10 @@
         <v>0</v>
       </c>
       <c r="AC379">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD379">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE379">
         <v>0</v>
@@ -62217,12 +62217,12 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G380">
@@ -62249,13 +62249,13 @@
         </is>
       </c>
       <c r="N380">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="O380">
-        <v>4.03</v>
+        <v>4.55</v>
       </c>
       <c r="P380">
-        <v>2.74</v>
+        <v>4.86</v>
       </c>
       <c r="Q380">
         <v>0</v>
@@ -62294,10 +62294,10 @@
         <v>0</v>
       </c>
       <c r="AC380">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AD380">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE380">
         <v>0</v>
@@ -62380,12 +62380,12 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G381">
@@ -62412,13 +62412,13 @@
         </is>
       </c>
       <c r="N381">
-        <v>1.65</v>
+        <v>2.44</v>
       </c>
       <c r="O381">
-        <v>4.55</v>
+        <v>3.82</v>
       </c>
       <c r="P381">
-        <v>4.86</v>
+        <v>2.79</v>
       </c>
       <c r="Q381">
         <v>0</v>
@@ -62457,10 +62457,10 @@
         <v>0</v>
       </c>
       <c r="AC381">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD381">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE381">
         <v>0</v>
@@ -64662,12 +64662,12 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G395">
@@ -64825,12 +64825,12 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G396">
@@ -64988,12 +64988,12 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G397">

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13068,10 +13068,10 @@
         <v>0</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE78">
         <v>0</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19745,10 +19745,10 @@
         <v>0</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC119">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.45</v>
+        <v>3.35</v>
       </c>
       <c r="O135">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="P135">
-        <v>7.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>3.35</v>
+        <v>1.45</v>
       </c>
       <c r="O136">
-        <v>3.13</v>
+        <v>5.1</v>
       </c>
       <c r="P136">
-        <v>2.52</v>
+        <v>7.6</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="O145">
-        <v>4.36</v>
+        <v>3.84</v>
       </c>
       <c r="P145">
-        <v>4.36</v>
+        <v>3.14</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -23983,16 +23983,16 @@
         <v>0</v>
       </c>
       <c r="AA145">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC145">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD145">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O146">
-        <v>4.27</v>
+        <v>4.36</v>
       </c>
       <c r="P146">
-        <v>4.21</v>
+        <v>4.36</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.33</v>
+        <v>1.84</v>
       </c>
       <c r="O147">
-        <v>6.49</v>
+        <v>4.27</v>
       </c>
       <c r="P147">
-        <v>9.1</v>
+        <v>4.21</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24315,10 +24315,10 @@
         <v>0</v>
       </c>
       <c r="AC147">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AD147">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AE147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="O148">
-        <v>3.84</v>
+        <v>6.49</v>
       </c>
       <c r="P148">
-        <v>3.14</v>
+        <v>9.1</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24472,16 +24472,16 @@
         <v>0</v>
       </c>
       <c r="AA148">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB148">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC148">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD148">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE148">
         <v>0</v>
@@ -64988,12 +64988,12 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G397">
@@ -65151,12 +65151,12 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G398">
@@ -65314,12 +65314,12 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G399">

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3940,10 +3940,10 @@
         <v>0</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.63</v>
+        <v>2.47</v>
       </c>
       <c r="O111">
-        <v>3.98</v>
+        <v>3.15</v>
       </c>
       <c r="P111">
-        <v>4.89</v>
+        <v>2.83</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB111">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="AC111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="O112">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P112">
-        <v>3.27</v>
+        <v>4.18</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB112">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="O113">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="P113">
-        <v>4.18</v>
+        <v>3.27</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB113">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.47</v>
+        <v>1.63</v>
       </c>
       <c r="O114">
-        <v>3.15</v>
+        <v>3.98</v>
       </c>
       <c r="P114">
-        <v>2.83</v>
+        <v>4.89</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AB114">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G125">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O141">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="P141">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O142">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="P142">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="O192">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P192">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB192">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="O194">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P194">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -31970,10 +31970,10 @@
         <v>0</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC194">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="O202">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P202">
-        <v>2.42</v>
+        <v>2.89</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="O203">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P203">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="O204">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P204">
-        <v>2.94</v>
+        <v>4.14</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.71</v>
+        <v>2.65</v>
       </c>
       <c r="O205">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P205">
-        <v>4.14</v>
+        <v>2.33</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
+        <v>2.5</v>
+      </c>
+      <c r="O206">
+        <v>3.1</v>
+      </c>
+      <c r="P206">
         <v>2.65</v>
-      </c>
-      <c r="O206">
-        <v>3.4</v>
-      </c>
-      <c r="P206">
-        <v>2.33</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="O207">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="P207">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34089,10 +34089,10 @@
         <v>0</v>
       </c>
       <c r="AA207">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB207">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="O208">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P208">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="O209">
         <v>3.3</v>
       </c>
       <c r="P209">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="O210">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P210">
-        <v>2.02</v>
+        <v>2.43</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -52632,13 +52632,13 @@
         </is>
       </c>
       <c r="N321">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O321">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="P321">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q321">
         <v>0</v>
@@ -52677,10 +52677,10 @@
         <v>0</v>
       </c>
       <c r="AC321">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD321">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE321">
         <v>0</v>
@@ -63390,13 +63390,13 @@
         </is>
       </c>
       <c r="N387">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O387">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P387">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q387">
         <v>0</v>
@@ -63429,10 +63429,10 @@
         <v>0</v>
       </c>
       <c r="AA387">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB387">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC387">
         <v>0</v>
@@ -63553,13 +63553,13 @@
         </is>
       </c>
       <c r="N388">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O388">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P388">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q388">
         <v>0</v>
@@ -63592,10 +63592,10 @@
         <v>0</v>
       </c>
       <c r="AA388">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB388">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC388">
         <v>0</v>
@@ -63879,13 +63879,13 @@
         </is>
       </c>
       <c r="N390">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O390">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="P390">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q390">
         <v>0</v>
@@ -63924,10 +63924,10 @@
         <v>0</v>
       </c>
       <c r="AC390">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD390">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE390">
         <v>0</v>
@@ -65020,13 +65020,13 @@
         </is>
       </c>
       <c r="N397">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O397">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P397">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q397">
         <v>0</v>
@@ -65183,13 +65183,13 @@
         </is>
       </c>
       <c r="N398">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O398">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P398">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q398">
         <v>0</v>
@@ -65346,13 +65346,13 @@
         </is>
       </c>
       <c r="N399">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O399">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P399">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="Q399">
         <v>0</v>
@@ -65385,10 +65385,10 @@
         <v>0</v>
       </c>
       <c r="AA399">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB399">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC399">
         <v>0</v>
@@ -65509,13 +65509,13 @@
         </is>
       </c>
       <c r="N400">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O400">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="P400">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q400">
         <v>0</v>
@@ -65554,10 +65554,10 @@
         <v>0</v>
       </c>
       <c r="AC400">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD400">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE400">
         <v>0</v>
@@ -65672,13 +65672,13 @@
         </is>
       </c>
       <c r="N401">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O401">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P401">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q401">
         <v>0</v>
@@ -65717,10 +65717,10 @@
         <v>0</v>
       </c>
       <c r="AC401">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD401">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE401">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.19</v>
+        <v>1.63</v>
       </c>
       <c r="O113">
-        <v>3.25</v>
+        <v>3.98</v>
       </c>
       <c r="P113">
-        <v>3.27</v>
+        <v>4.89</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AB113">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.63</v>
+        <v>2.19</v>
       </c>
       <c r="O114">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="P114">
-        <v>4.89</v>
+        <v>3.27</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB114">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AC114">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="O3">
-        <v>3.13</v>
+        <v>3.42</v>
       </c>
       <c r="P3">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.18</v>
+        <v>3.31</v>
       </c>
       <c r="O4">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.14</v>
+        <v>2.11</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.31</v>
+        <v>2</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="P5">
-        <v>2.11</v>
+        <v>3.44</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="O6">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>3.44</v>
+        <v>4.13</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>3.81</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="P7">
-        <v>4.13</v>
+        <v>1.9</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.81</v>
+        <v>2.35</v>
       </c>
       <c r="O8">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="P8">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="O112">
-        <v>3.54</v>
+        <v>3.98</v>
       </c>
       <c r="P112">
-        <v>4.18</v>
+        <v>4.89</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AB112">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.63</v>
+        <v>2.19</v>
       </c>
       <c r="O113">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="P113">
-        <v>4.89</v>
+        <v>3.27</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB113">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="O114">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P114">
-        <v>3.27</v>
+        <v>4.18</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB114">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G125">
@@ -53936,13 +53936,13 @@
         </is>
       </c>
       <c r="N329">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O329">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P329">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q329">
         <v>0</v>
@@ -53969,10 +53969,10 @@
         <v>0</v>
       </c>
       <c r="Y329">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z329">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA329">
         <v>0</v>
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O345">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P345">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q345">
         <v>0</v>
@@ -56583,10 +56583,10 @@
         <v>0</v>
       </c>
       <c r="AA345">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB345">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC345">
         <v>0</v>
@@ -57196,13 +57196,13 @@
         </is>
       </c>
       <c r="N349">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O349">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="P349">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q349">
         <v>0</v>
@@ -57241,10 +57241,10 @@
         <v>0</v>
       </c>
       <c r="AC349">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD349">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE349">
         <v>0</v>
@@ -57522,13 +57522,13 @@
         </is>
       </c>
       <c r="N351">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O351">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P351">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q351">
         <v>0</v>
@@ -57685,13 +57685,13 @@
         </is>
       </c>
       <c r="N352">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O352">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P352">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q352">
         <v>0</v>
@@ -57724,10 +57724,10 @@
         <v>0</v>
       </c>
       <c r="AA352">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB352">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC352">
         <v>0</v>
@@ -60619,13 +60619,13 @@
         </is>
       </c>
       <c r="N370">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O370">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P370">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q370">
         <v>0</v>
@@ -60658,10 +60658,10 @@
         <v>0</v>
       </c>
       <c r="AA370">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB370">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC370">
         <v>0</v>
@@ -61760,13 +61760,13 @@
         </is>
       </c>
       <c r="N377">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O377">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P377">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q377">
         <v>0</v>
@@ -61793,10 +61793,10 @@
         <v>0</v>
       </c>
       <c r="Y377">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z377">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA377">
         <v>0</v>
@@ -63227,13 +63227,13 @@
         </is>
       </c>
       <c r="N386">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O386">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P386">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q386">
         <v>0</v>
@@ -64368,13 +64368,13 @@
         </is>
       </c>
       <c r="N393">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O393">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P393">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q393">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU401"/>
+  <dimension ref="A1:AU399"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.81</v>
+        <v>2.35</v>
       </c>
       <c r="O7">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="P7">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.35</v>
+        <v>3.81</v>
       </c>
       <c r="O8">
-        <v>3.13</v>
+        <v>3.56</v>
       </c>
       <c r="P8">
-        <v>3.09</v>
+        <v>1.9</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G125">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32296,10 +32296,10 @@
         <v>0</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC196">
         <v>0</v>
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O298">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P298">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q298">
         <v>0</v>
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O339">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P339">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -55605,10 +55605,10 @@
         <v>0</v>
       </c>
       <c r="AA339">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB339">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC339">
         <v>0</v>
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O340">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P340">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -55762,10 +55762,10 @@
         <v>0</v>
       </c>
       <c r="Y340">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z340">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA340">
         <v>0</v>
@@ -57964,12 +57964,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G354">
@@ -58115,7 +58115,7 @@
       </c>
       <c r="AU354" t="inlineStr">
         <is>
-          <t>2026-10-24 17:00:00</t>
+          <t>2026-10-24 17:30:00</t>
         </is>
       </c>
     </row>
@@ -58127,12 +58127,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G355">
@@ -58278,7 +58278,7 @@
       </c>
       <c r="AU355" t="inlineStr">
         <is>
-          <t>2026-10-24 17:00:00</t>
+          <t>2026-10-24 17:30:00</t>
         </is>
       </c>
     </row>
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G356">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G357">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G358">
@@ -58779,12 +58779,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G359">
@@ -58930,7 +58930,7 @@
       </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>2026-10-24 17:30:00</t>
+          <t>2026-10-24 18:00:00</t>
         </is>
       </c>
     </row>
@@ -58942,12 +58942,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G360">
@@ -59093,7 +59093,7 @@
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>2026-10-24 17:30:00</t>
+          <t>2026-10-24 18:15:00</t>
         </is>
       </c>
     </row>
@@ -59105,12 +59105,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G361">
@@ -59152,13 +59152,13 @@
         </is>
       </c>
       <c r="N361">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O361">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P361">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="Q361">
         <v>0</v>
@@ -59191,10 +59191,10 @@
         <v>0</v>
       </c>
       <c r="AA361">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB361">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC361">
         <v>0</v>
@@ -59256,7 +59256,7 @@
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>2026-10-24 18:00:00</t>
+          <t>2026-10-24 18:30:00</t>
         </is>
       </c>
     </row>
@@ -59268,12 +59268,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G362">
@@ -59315,13 +59315,13 @@
         </is>
       </c>
       <c r="N362">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O362">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P362">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q362">
         <v>0</v>
@@ -59354,10 +59354,10 @@
         <v>0</v>
       </c>
       <c r="AA362">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB362">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC362">
         <v>0</v>
@@ -59419,7 +59419,7 @@
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>2026-10-24 18:15:00</t>
+          <t>2026-10-24 18:30:00</t>
         </is>
       </c>
     </row>
@@ -59436,7 +59436,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G363">
@@ -59478,13 +59478,13 @@
         </is>
       </c>
       <c r="N363">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="O363">
-        <v>4.08</v>
+        <v>3.71</v>
       </c>
       <c r="P363">
-        <v>5.98</v>
+        <v>4.81</v>
       </c>
       <c r="Q363">
         <v>0</v>
@@ -59517,10 +59517,10 @@
         <v>0</v>
       </c>
       <c r="AA363">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB363">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AC363">
         <v>0</v>
@@ -59599,7 +59599,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G364">
@@ -59641,13 +59641,13 @@
         </is>
       </c>
       <c r="N364">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="O364">
-        <v>3.61</v>
+        <v>4.43</v>
       </c>
       <c r="P364">
-        <v>4.17</v>
+        <v>1.96</v>
       </c>
       <c r="Q364">
         <v>0</v>
@@ -59680,16 +59680,16 @@
         <v>0</v>
       </c>
       <c r="AA364">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB364">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC364">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD364">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE364">
         <v>0</v>
@@ -59762,7 +59762,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G365">
@@ -59804,13 +59804,13 @@
         </is>
       </c>
       <c r="N365">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O365">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P365">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="Q365">
         <v>0</v>
@@ -59843,10 +59843,10 @@
         <v>0</v>
       </c>
       <c r="AA365">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB365">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC365">
         <v>0</v>
@@ -59925,7 +59925,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G366">
@@ -59967,13 +59967,13 @@
         </is>
       </c>
       <c r="N366">
-        <v>3.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O366">
-        <v>4.43</v>
+        <v>4.75</v>
       </c>
       <c r="P366">
-        <v>1.96</v>
+        <v>1.33</v>
       </c>
       <c r="Q366">
         <v>0</v>
@@ -60006,16 +60006,16 @@
         <v>0</v>
       </c>
       <c r="AA366">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB366">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC366">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD366">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE366">
         <v>0</v>
@@ -60083,12 +60083,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G367">
@@ -60130,13 +60130,13 @@
         </is>
       </c>
       <c r="N367">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O367">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P367">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q367">
         <v>0</v>
@@ -60234,7 +60234,7 @@
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>2026-10-24 18:30:00</t>
+          <t>2026-10-24 19:00:00</t>
         </is>
       </c>
     </row>
@@ -60246,12 +60246,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G368">
@@ -60293,13 +60293,13 @@
         </is>
       </c>
       <c r="N368">
-        <v>8.550000000000001</v>
+        <v>1.61</v>
       </c>
       <c r="O368">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="P368">
-        <v>1.33</v>
+        <v>5.5</v>
       </c>
       <c r="Q368">
         <v>0</v>
@@ -60332,10 +60332,10 @@
         <v>0</v>
       </c>
       <c r="AA368">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB368">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AC368">
         <v>0</v>
@@ -60397,7 +60397,7 @@
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>2026-10-24 18:30:00</t>
+          <t>2026-10-24 19:00:00</t>
         </is>
       </c>
     </row>
@@ -60409,12 +60409,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G369">
@@ -60456,13 +60456,13 @@
         </is>
       </c>
       <c r="N369">
-        <v>1.47</v>
+        <v>4.22</v>
       </c>
       <c r="O369">
-        <v>4.2</v>
+        <v>3.61</v>
       </c>
       <c r="P369">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="Q369">
         <v>0</v>
@@ -60495,10 +60495,10 @@
         <v>0</v>
       </c>
       <c r="AA369">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB369">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC369">
         <v>0</v>
@@ -60560,7 +60560,7 @@
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>2026-10-24 19:00:00</t>
+          <t>2026-10-24 19:30:00</t>
         </is>
       </c>
     </row>
@@ -60572,12 +60572,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G370">
@@ -60619,13 +60619,13 @@
         </is>
       </c>
       <c r="N370">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="O370">
-        <v>3.4</v>
+        <v>4.77</v>
       </c>
       <c r="P370">
-        <v>5.5</v>
+        <v>5.36</v>
       </c>
       <c r="Q370">
         <v>0</v>
@@ -60658,10 +60658,10 @@
         <v>0</v>
       </c>
       <c r="AA370">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB370">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC370">
         <v>0</v>
@@ -60723,7 +60723,7 @@
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>2026-10-24 19:00:00</t>
+          <t>2026-10-24 19:30:00</t>
         </is>
       </c>
     </row>
@@ -60735,12 +60735,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G371">
@@ -60782,13 +60782,13 @@
         </is>
       </c>
       <c r="N371">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O371">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P371">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q371">
         <v>0</v>
@@ -60821,10 +60821,10 @@
         <v>0</v>
       </c>
       <c r="AA371">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB371">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC371">
         <v>0</v>
@@ -60886,7 +60886,7 @@
       </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>2026-10-24 19:30:00</t>
+          <t>2026-10-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -60898,12 +60898,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G372">
@@ -60945,13 +60945,13 @@
         </is>
       </c>
       <c r="N372">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O372">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="P372">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="Q372">
         <v>0</v>
@@ -61049,7 +61049,7 @@
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>2026-10-24 19:30:00</t>
+          <t>2026-10-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G373">
@@ -61108,13 +61108,13 @@
         </is>
       </c>
       <c r="N373">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O373">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P373">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q373">
         <v>0</v>
@@ -61147,10 +61147,10 @@
         <v>0</v>
       </c>
       <c r="AA373">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB373">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC373">
         <v>0</v>
@@ -61229,7 +61229,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -61239,12 +61239,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G374">
@@ -61392,7 +61392,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -61402,12 +61402,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G375">
@@ -61434,13 +61434,13 @@
         </is>
       </c>
       <c r="N375">
-        <v>2.83</v>
+        <v>1.78</v>
       </c>
       <c r="O375">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="P375">
-        <v>2.36</v>
+        <v>4.6</v>
       </c>
       <c r="Q375">
         <v>0</v>
@@ -61467,16 +61467,16 @@
         <v>0</v>
       </c>
       <c r="Y375">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z375">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA375">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB375">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC375">
         <v>0</v>
@@ -61550,12 +61550,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -61565,12 +61565,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G376">
@@ -61701,7 +61701,7 @@
       </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00:00</t>
+          <t>2026-10-24 20:30:00</t>
         </is>
       </c>
     </row>
@@ -61713,12 +61713,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -61728,12 +61728,12 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G377">
@@ -61760,13 +61760,13 @@
         </is>
       </c>
       <c r="N377">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O377">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P377">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q377">
         <v>0</v>
@@ -61793,10 +61793,10 @@
         <v>0</v>
       </c>
       <c r="Y377">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z377">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA377">
         <v>0</v>
@@ -61864,7 +61864,7 @@
       </c>
       <c r="AU377" t="inlineStr">
         <is>
-          <t>2026-10-24 20:00:00</t>
+          <t>2026-10-24 20:30:00</t>
         </is>
       </c>
     </row>
@@ -61881,7 +61881,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -61891,12 +61891,12 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G378">
@@ -62044,7 +62044,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -62054,12 +62054,12 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G379">
@@ -62086,13 +62086,13 @@
         </is>
       </c>
       <c r="N379">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O379">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P379">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q379">
         <v>0</v>
@@ -62131,10 +62131,10 @@
         <v>0</v>
       </c>
       <c r="AC379">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD379">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE379">
         <v>0</v>
@@ -62217,12 +62217,12 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G380">
@@ -62249,13 +62249,13 @@
         </is>
       </c>
       <c r="N380">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O380">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P380">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q380">
         <v>0</v>
@@ -62294,10 +62294,10 @@
         <v>0</v>
       </c>
       <c r="AC380">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD380">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE380">
         <v>0</v>
@@ -62380,12 +62380,12 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G381">
@@ -62412,13 +62412,13 @@
         </is>
       </c>
       <c r="N381">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="O381">
-        <v>4.03</v>
+        <v>4.55</v>
       </c>
       <c r="P381">
-        <v>2.74</v>
+        <v>4.86</v>
       </c>
       <c r="Q381">
         <v>0</v>
@@ -62457,10 +62457,10 @@
         <v>0</v>
       </c>
       <c r="AC381">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AD381">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE381">
         <v>0</v>
@@ -62528,27 +62528,27 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G382">
@@ -62575,13 +62575,13 @@
         </is>
       </c>
       <c r="N382">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O382">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P382">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q382">
         <v>0</v>
@@ -62620,10 +62620,10 @@
         <v>0</v>
       </c>
       <c r="AC382">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD382">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE382">
         <v>0</v>
@@ -62679,7 +62679,7 @@
       </c>
       <c r="AU382" t="inlineStr">
         <is>
-          <t>2026-10-24 20:30:00</t>
+          <t>2026-10-24 21:00:00</t>
         </is>
       </c>
     </row>
@@ -62691,12 +62691,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -62706,12 +62706,12 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G383">
@@ -62738,13 +62738,13 @@
         </is>
       </c>
       <c r="N383">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="O383">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="P383">
-        <v>4.86</v>
+        <v>3</v>
       </c>
       <c r="Q383">
         <v>0</v>
@@ -62783,10 +62783,10 @@
         <v>0</v>
       </c>
       <c r="AC383">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD383">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE383">
         <v>0</v>
@@ -62842,7 +62842,7 @@
       </c>
       <c r="AU383" t="inlineStr">
         <is>
-          <t>2026-10-24 20:30:00</t>
+          <t>2026-10-24 21:00:00</t>
         </is>
       </c>
     </row>
@@ -62859,22 +62859,22 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G384">
@@ -62901,13 +62901,13 @@
         </is>
       </c>
       <c r="N384">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O384">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P384">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q384">
         <v>0</v>
@@ -63017,12 +63017,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -63032,12 +63032,12 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G385">
@@ -63064,13 +63064,13 @@
         </is>
       </c>
       <c r="N385">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="O385">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="P385">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="Q385">
         <v>0</v>
@@ -63103,10 +63103,10 @@
         <v>0</v>
       </c>
       <c r="AA385">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB385">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC385">
         <v>0</v>
@@ -63168,7 +63168,7 @@
       </c>
       <c r="AU385" t="inlineStr">
         <is>
-          <t>2026-10-24 21:00:00</t>
+          <t>2026-10-24 21:30:00</t>
         </is>
       </c>
     </row>
@@ -63180,12 +63180,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -63195,12 +63195,12 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G386">
@@ -63227,13 +63227,13 @@
         </is>
       </c>
       <c r="N386">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O386">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="P386">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q386">
         <v>0</v>
@@ -63266,10 +63266,10 @@
         <v>0</v>
       </c>
       <c r="AA386">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB386">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC386">
         <v>0</v>
@@ -63331,7 +63331,7 @@
       </c>
       <c r="AU386" t="inlineStr">
         <is>
-          <t>2026-10-24 21:00:00</t>
+          <t>2026-10-24 21:30:00</t>
         </is>
       </c>
     </row>
@@ -63348,7 +63348,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -63358,12 +63358,12 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G387">
@@ -63390,55 +63390,55 @@
         </is>
       </c>
       <c r="N387">
+        <v>2.45</v>
+      </c>
+      <c r="O387">
+        <v>3.8</v>
+      </c>
+      <c r="P387">
+        <v>2.5</v>
+      </c>
+      <c r="Q387">
+        <v>0</v>
+      </c>
+      <c r="R387">
+        <v>0</v>
+      </c>
+      <c r="S387">
+        <v>0</v>
+      </c>
+      <c r="T387">
+        <v>0</v>
+      </c>
+      <c r="U387">
+        <v>0</v>
+      </c>
+      <c r="V387">
+        <v>0</v>
+      </c>
+      <c r="W387">
+        <v>0</v>
+      </c>
+      <c r="X387">
+        <v>0</v>
+      </c>
+      <c r="Y387">
+        <v>0</v>
+      </c>
+      <c r="Z387">
+        <v>0</v>
+      </c>
+      <c r="AA387">
+        <v>0</v>
+      </c>
+      <c r="AB387">
+        <v>0</v>
+      </c>
+      <c r="AC387">
+        <v>2.2</v>
+      </c>
+      <c r="AD387">
         <v>1.58</v>
-      </c>
-      <c r="O387">
-        <v>3.72</v>
-      </c>
-      <c r="P387">
-        <v>4.9</v>
-      </c>
-      <c r="Q387">
-        <v>0</v>
-      </c>
-      <c r="R387">
-        <v>0</v>
-      </c>
-      <c r="S387">
-        <v>0</v>
-      </c>
-      <c r="T387">
-        <v>0</v>
-      </c>
-      <c r="U387">
-        <v>0</v>
-      </c>
-      <c r="V387">
-        <v>0</v>
-      </c>
-      <c r="W387">
-        <v>0</v>
-      </c>
-      <c r="X387">
-        <v>0</v>
-      </c>
-      <c r="Y387">
-        <v>0</v>
-      </c>
-      <c r="Z387">
-        <v>0</v>
-      </c>
-      <c r="AA387">
-        <v>1.83</v>
-      </c>
-      <c r="AB387">
-        <v>1.93</v>
-      </c>
-      <c r="AC387">
-        <v>0</v>
-      </c>
-      <c r="AD387">
-        <v>0</v>
       </c>
       <c r="AE387">
         <v>0</v>
@@ -63521,12 +63521,12 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G388">
@@ -63553,13 +63553,13 @@
         </is>
       </c>
       <c r="N388">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="O388">
-        <v>3.6</v>
+        <v>4.13</v>
       </c>
       <c r="P388">
-        <v>2.2</v>
+        <v>3.86</v>
       </c>
       <c r="Q388">
         <v>0</v>
@@ -63592,16 +63592,16 @@
         <v>0</v>
       </c>
       <c r="AA388">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB388">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC388">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD388">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE388">
         <v>0</v>
@@ -63684,12 +63684,12 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G389">
@@ -63716,13 +63716,13 @@
         </is>
       </c>
       <c r="N389">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="O389">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P389">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q389">
         <v>0</v>
@@ -63761,10 +63761,10 @@
         <v>0</v>
       </c>
       <c r="AC389">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD389">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AE389">
         <v>0</v>
@@ -63847,12 +63847,12 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G390">
@@ -63879,13 +63879,13 @@
         </is>
       </c>
       <c r="N390">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="O390">
-        <v>4.13</v>
+        <v>3.8</v>
       </c>
       <c r="P390">
-        <v>3.86</v>
+        <v>3.3</v>
       </c>
       <c r="Q390">
         <v>0</v>
@@ -63918,16 +63918,16 @@
         <v>0</v>
       </c>
       <c r="AA390">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB390">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC390">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD390">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE390">
         <v>0</v>
@@ -63995,12 +63995,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -64010,12 +64010,12 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G391">
@@ -64042,13 +64042,13 @@
         </is>
       </c>
       <c r="N391">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="O391">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P391">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="Q391">
         <v>0</v>
@@ -64087,10 +64087,10 @@
         <v>0</v>
       </c>
       <c r="AC391">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD391">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE391">
         <v>0</v>
@@ -64146,7 +64146,7 @@
       </c>
       <c r="AU391" t="inlineStr">
         <is>
-          <t>2026-10-24 21:30:00</t>
+          <t>2026-10-24 21:45:00</t>
         </is>
       </c>
     </row>
@@ -64158,12 +64158,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -64173,12 +64173,12 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G392">
@@ -64205,13 +64205,13 @@
         </is>
       </c>
       <c r="N392">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O392">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P392">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q392">
         <v>0</v>
@@ -64244,10 +64244,10 @@
         <v>0</v>
       </c>
       <c r="AA392">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB392">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC392">
         <v>0</v>
@@ -64309,7 +64309,7 @@
       </c>
       <c r="AU392" t="inlineStr">
         <is>
-          <t>2026-10-24 21:30:00</t>
+          <t>2026-10-24 22:00:00</t>
         </is>
       </c>
     </row>
@@ -64321,12 +64321,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -64336,12 +64336,12 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G393">
@@ -64368,10 +64368,10 @@
         </is>
       </c>
       <c r="N393">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O393">
-        <v>3.6</v>
+        <v>4.02</v>
       </c>
       <c r="P393">
         <v>3.58</v>
@@ -64472,7 +64472,7 @@
       </c>
       <c r="AU393" t="inlineStr">
         <is>
-          <t>2026-10-24 21:45:00</t>
+          <t>2026-10-24 22:00:00</t>
         </is>
       </c>
     </row>
@@ -64484,27 +64484,27 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="G394">
@@ -64531,13 +64531,13 @@
         </is>
       </c>
       <c r="N394">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O394">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P394">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q394">
         <v>0</v>
@@ -64635,7 +64635,7 @@
       </c>
       <c r="AU394" t="inlineStr">
         <is>
-          <t>2026-10-24 22:00:00</t>
+          <t>2026-10-24 23:00:00</t>
         </is>
       </c>
     </row>
@@ -64647,7 +64647,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -64662,12 +64662,12 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G395">
@@ -64694,13 +64694,13 @@
         </is>
       </c>
       <c r="N395">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="O395">
-        <v>4.02</v>
+        <v>3.48</v>
       </c>
       <c r="P395">
-        <v>3.58</v>
+        <v>2.32</v>
       </c>
       <c r="Q395">
         <v>0</v>
@@ -64798,7 +64798,7 @@
       </c>
       <c r="AU395" t="inlineStr">
         <is>
-          <t>2026-10-24 22:00:00</t>
+          <t>2026-10-24 23:00:00</t>
         </is>
       </c>
     </row>
@@ -64815,22 +64815,22 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Central Coast Mariners</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G396">
@@ -64857,13 +64857,13 @@
         </is>
       </c>
       <c r="N396">
-        <v>1.87</v>
+        <v>2.41</v>
       </c>
       <c r="O396">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="P396">
-        <v>4.05</v>
+        <v>2.39</v>
       </c>
       <c r="Q396">
         <v>0</v>
@@ -64988,12 +64988,12 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G397">
@@ -65020,13 +65020,13 @@
         </is>
       </c>
       <c r="N397">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="O397">
-        <v>3.48</v>
+        <v>3.96</v>
       </c>
       <c r="P397">
-        <v>2.32</v>
+        <v>5.91</v>
       </c>
       <c r="Q397">
         <v>0</v>
@@ -65059,10 +65059,10 @@
         <v>0</v>
       </c>
       <c r="AA397">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB397">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC397">
         <v>0</v>
@@ -65136,12 +65136,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -65151,12 +65151,12 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G398">
@@ -65183,13 +65183,13 @@
         </is>
       </c>
       <c r="N398">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="O398">
-        <v>3.5</v>
+        <v>4.22</v>
       </c>
       <c r="P398">
-        <v>2.39</v>
+        <v>3.34</v>
       </c>
       <c r="Q398">
         <v>0</v>
@@ -65228,10 +65228,10 @@
         <v>0</v>
       </c>
       <c r="AC398">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD398">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE398">
         <v>0</v>
@@ -65287,7 +65287,7 @@
       </c>
       <c r="AU398" t="inlineStr">
         <is>
-          <t>2026-10-24 23:00:00</t>
+          <t>2026-10-24 23:30:00</t>
         </is>
       </c>
     </row>
@@ -65299,12 +65299,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -65314,12 +65314,12 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G399">
@@ -65346,13 +65346,13 @@
         </is>
       </c>
       <c r="N399">
-        <v>1.46</v>
+        <v>2.25</v>
       </c>
       <c r="O399">
-        <v>3.96</v>
+        <v>4.03</v>
       </c>
       <c r="P399">
-        <v>5.91</v>
+        <v>2.95</v>
       </c>
       <c r="Q399">
         <v>0</v>
@@ -65385,16 +65385,16 @@
         <v>0</v>
       </c>
       <c r="AA399">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB399">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC399">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD399">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE399">
         <v>0</v>
@@ -65449,332 +65449,6 @@
         <v>0</v>
       </c>
       <c r="AU399" t="inlineStr">
-        <is>
-          <t>2026-10-24 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="G400">
-        <v>0</v>
-      </c>
-      <c r="H400">
-        <v>0</v>
-      </c>
-      <c r="I400">
-        <v>0</v>
-      </c>
-      <c r="J400">
-        <v>0</v>
-      </c>
-      <c r="K400">
-        <v>0</v>
-      </c>
-      <c r="L400">
-        <v>0</v>
-      </c>
-      <c r="M400" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N400">
-        <v>2.02</v>
-      </c>
-      <c r="O400">
-        <v>4.22</v>
-      </c>
-      <c r="P400">
-        <v>3.34</v>
-      </c>
-      <c r="Q400">
-        <v>0</v>
-      </c>
-      <c r="R400">
-        <v>0</v>
-      </c>
-      <c r="S400">
-        <v>0</v>
-      </c>
-      <c r="T400">
-        <v>0</v>
-      </c>
-      <c r="U400">
-        <v>0</v>
-      </c>
-      <c r="V400">
-        <v>0</v>
-      </c>
-      <c r="W400">
-        <v>0</v>
-      </c>
-      <c r="X400">
-        <v>0</v>
-      </c>
-      <c r="Y400">
-        <v>0</v>
-      </c>
-      <c r="Z400">
-        <v>0</v>
-      </c>
-      <c r="AA400">
-        <v>0</v>
-      </c>
-      <c r="AB400">
-        <v>0</v>
-      </c>
-      <c r="AC400">
-        <v>1.8</v>
-      </c>
-      <c r="AD400">
-        <v>1.88</v>
-      </c>
-      <c r="AE400">
-        <v>0</v>
-      </c>
-      <c r="AF400">
-        <v>0</v>
-      </c>
-      <c r="AG400">
-        <v>0</v>
-      </c>
-      <c r="AH400" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI400" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ400">
-        <v>0</v>
-      </c>
-      <c r="AK400">
-        <v>0</v>
-      </c>
-      <c r="AL400">
-        <v>0</v>
-      </c>
-      <c r="AM400">
-        <v>-1</v>
-      </c>
-      <c r="AN400">
-        <v>-1</v>
-      </c>
-      <c r="AO400">
-        <v>-1</v>
-      </c>
-      <c r="AP400">
-        <v>-1</v>
-      </c>
-      <c r="AQ400">
-        <v>0</v>
-      </c>
-      <c r="AR400">
-        <v>0</v>
-      </c>
-      <c r="AS400">
-        <v>0</v>
-      </c>
-      <c r="AT400">
-        <v>0</v>
-      </c>
-      <c r="AU400" t="inlineStr">
-        <is>
-          <t>2026-10-24 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="G401">
-        <v>0</v>
-      </c>
-      <c r="H401">
-        <v>0</v>
-      </c>
-      <c r="I401">
-        <v>0</v>
-      </c>
-      <c r="J401">
-        <v>0</v>
-      </c>
-      <c r="K401">
-        <v>0</v>
-      </c>
-      <c r="L401">
-        <v>0</v>
-      </c>
-      <c r="M401" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N401">
-        <v>2.25</v>
-      </c>
-      <c r="O401">
-        <v>4.03</v>
-      </c>
-      <c r="P401">
-        <v>2.95</v>
-      </c>
-      <c r="Q401">
-        <v>0</v>
-      </c>
-      <c r="R401">
-        <v>0</v>
-      </c>
-      <c r="S401">
-        <v>0</v>
-      </c>
-      <c r="T401">
-        <v>0</v>
-      </c>
-      <c r="U401">
-        <v>0</v>
-      </c>
-      <c r="V401">
-        <v>0</v>
-      </c>
-      <c r="W401">
-        <v>0</v>
-      </c>
-      <c r="X401">
-        <v>0</v>
-      </c>
-      <c r="Y401">
-        <v>0</v>
-      </c>
-      <c r="Z401">
-        <v>0</v>
-      </c>
-      <c r="AA401">
-        <v>0</v>
-      </c>
-      <c r="AB401">
-        <v>0</v>
-      </c>
-      <c r="AC401">
-        <v>1.98</v>
-      </c>
-      <c r="AD401">
-        <v>1.73</v>
-      </c>
-      <c r="AE401">
-        <v>0</v>
-      </c>
-      <c r="AF401">
-        <v>0</v>
-      </c>
-      <c r="AG401">
-        <v>0</v>
-      </c>
-      <c r="AH401" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI401" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ401">
-        <v>0</v>
-      </c>
-      <c r="AK401">
-        <v>0</v>
-      </c>
-      <c r="AL401">
-        <v>0</v>
-      </c>
-      <c r="AM401">
-        <v>-1</v>
-      </c>
-      <c r="AN401">
-        <v>-1</v>
-      </c>
-      <c r="AO401">
-        <v>-1</v>
-      </c>
-      <c r="AP401">
-        <v>-1</v>
-      </c>
-      <c r="AQ401">
-        <v>0</v>
-      </c>
-      <c r="AR401">
-        <v>0</v>
-      </c>
-      <c r="AS401">
-        <v>0</v>
-      </c>
-      <c r="AT401">
-        <v>0</v>
-      </c>
-      <c r="AU401" t="inlineStr">
         <is>
           <t>2026-10-24 23:30:00</t>
         </is>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="O271">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P271">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q271">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.31</v>
+        <v>2.35</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="P3">
-        <v>2.11</v>
+        <v>3.09</v>
       </c>
       <c r="Q3">
-        <v>4.07</v>
+        <v>3.04</v>
       </c>
       <c r="R3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="U3">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="Z3">
-        <v>3.48</v>
+        <v>2.99</v>
       </c>
       <c r="AA3">
-        <v>1.84</v>
+        <v>2.27</v>
       </c>
       <c r="AB3">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>3.03</v>
+        <v>4.14</v>
       </c>
       <c r="AD3">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG3">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.35</v>
+        <v>3.81</v>
       </c>
       <c r="O4">
-        <v>3.13</v>
+        <v>3.56</v>
       </c>
       <c r="P4">
+        <v>1.9</v>
+      </c>
+      <c r="Q4">
+        <v>4.54</v>
+      </c>
+      <c r="R4">
+        <v>2.31</v>
+      </c>
+      <c r="S4">
+        <v>1.34</v>
+      </c>
+      <c r="T4">
+        <v>3.1</v>
+      </c>
+      <c r="U4">
+        <v>2.74</v>
+      </c>
+      <c r="V4">
+        <v>1.42</v>
+      </c>
+      <c r="W4">
+        <v>1.1</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1.23</v>
+      </c>
+      <c r="Z4">
+        <v>3.71</v>
+      </c>
+      <c r="AA4">
+        <v>1.83</v>
+      </c>
+      <c r="AB4">
+        <v>1.97</v>
+      </c>
+      <c r="AC4">
         <v>3.09</v>
       </c>
-      <c r="Q4">
-        <v>3.04</v>
-      </c>
-      <c r="R4">
-        <v>2.1</v>
-      </c>
-      <c r="S4">
-        <v>1.47</v>
-      </c>
-      <c r="T4">
-        <v>2.45</v>
-      </c>
-      <c r="U4">
-        <v>3.3</v>
-      </c>
-      <c r="V4">
-        <v>1.32</v>
-      </c>
-      <c r="W4">
-        <v>1.06</v>
-      </c>
-      <c r="X4">
-        <v>1.04</v>
-      </c>
-      <c r="Y4">
-        <v>1.39</v>
-      </c>
-      <c r="Z4">
-        <v>2.99</v>
-      </c>
-      <c r="AA4">
-        <v>2.27</v>
-      </c>
-      <c r="AB4">
-        <v>1.65</v>
-      </c>
-      <c r="AC4">
-        <v>4.14</v>
-      </c>
       <c r="AD4">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AG4">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.81</v>
+        <v>2</v>
       </c>
       <c r="O5">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="P5">
+        <v>3.44</v>
+      </c>
+      <c r="Q5">
+        <v>2.57</v>
+      </c>
+      <c r="R5">
+        <v>2.32</v>
+      </c>
+      <c r="S5">
+        <v>1.33</v>
+      </c>
+      <c r="T5">
+        <v>3.14</v>
+      </c>
+      <c r="U5">
+        <v>2.66</v>
+      </c>
+      <c r="V5">
+        <v>1.44</v>
+      </c>
+      <c r="W5">
+        <v>1.08</v>
+      </c>
+      <c r="X5">
+        <v>1.03</v>
+      </c>
+      <c r="Y5">
+        <v>1.24</v>
+      </c>
+      <c r="Z5">
+        <v>3.99</v>
+      </c>
+      <c r="AA5">
         <v>1.9</v>
       </c>
-      <c r="Q5">
-        <v>4.54</v>
-      </c>
-      <c r="R5">
-        <v>2.31</v>
-      </c>
-      <c r="S5">
-        <v>1.34</v>
-      </c>
-      <c r="T5">
-        <v>3.1</v>
-      </c>
-      <c r="U5">
-        <v>2.74</v>
-      </c>
-      <c r="V5">
-        <v>1.42</v>
-      </c>
-      <c r="W5">
-        <v>1.1</v>
-      </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5">
-        <v>1.23</v>
-      </c>
-      <c r="Z5">
-        <v>3.71</v>
-      </c>
-      <c r="AA5">
-        <v>1.83</v>
-      </c>
       <c r="AB5">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AC5">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="AD5">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.18</v>
+        <v>3.31</v>
       </c>
       <c r="O6">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>3.14</v>
+        <v>2.11</v>
       </c>
       <c r="Q6">
-        <v>2.75</v>
+        <v>4.07</v>
       </c>
       <c r="R6">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
         <v>1.07</v>
@@ -1323,22 +1323,22 @@
         <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>3.73</v>
+        <v>3.48</v>
       </c>
       <c r="AA6">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AB6">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC6">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
         <v>1.67</v>
@@ -1360,7 +1360,7 @@
         <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>3.44</v>
+        <v>4.13</v>
       </c>
       <c r="Q7">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="R7">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="S7">
+        <v>1.4</v>
+      </c>
+      <c r="T7">
+        <v>2.84</v>
+      </c>
+      <c r="U7">
+        <v>3.03</v>
+      </c>
+      <c r="V7">
+        <v>1.36</v>
+      </c>
+      <c r="W7">
+        <v>1.05</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
         <v>1.33</v>
       </c>
-      <c r="T7">
-        <v>3.14</v>
-      </c>
-      <c r="U7">
-        <v>2.66</v>
-      </c>
-      <c r="V7">
-        <v>1.44</v>
-      </c>
-      <c r="W7">
-        <v>1.08</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.24</v>
-      </c>
       <c r="Z7">
-        <v>3.99</v>
+        <v>3.25</v>
       </c>
       <c r="AA7">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AB7">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC7">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="AD7">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG7">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P8">
-        <v>4.13</v>
+        <v>3.14</v>
       </c>
       <c r="Q8">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="R8">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
-        <v>2.84</v>
+        <v>3.09</v>
       </c>
       <c r="U8">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>3.25</v>
+        <v>3.73</v>
       </c>
       <c r="AA8">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AB8">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC8">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.46</v>
+        <v>2.28</v>
       </c>
       <c r="O20">
-        <v>4.51</v>
+        <v>3.82</v>
       </c>
       <c r="P20">
-        <v>7.05</v>
+        <v>2.88</v>
       </c>
       <c r="Q20">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="R20">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="U20">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="V20">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W20">
         <v>1.13</v>
@@ -3605,28 +3605,28 @@
         <v>1.12</v>
       </c>
       <c r="Z20">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AA20">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB20">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="AC20">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AD20">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AE20">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF20">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AG20">
-        <v>1.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>4.46</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="O21">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="P21">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="Q21">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U21">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V21">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W21">
         <v>1.13</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>4.75</v>
+        <v>5.33</v>
       </c>
       <c r="AA21">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AC21">
-        <v>2.39</v>
+        <v>2.16</v>
       </c>
       <c r="AD21">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AE21">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.37</v>
+        <v>2.92</v>
       </c>
       <c r="O22">
-        <v>3.76</v>
+        <v>3.94</v>
       </c>
       <c r="P22">
-        <v>2.79</v>
+        <v>2.22</v>
       </c>
       <c r="Q22">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R22">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T22">
         <v>4</v>
       </c>
       <c r="U22">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="V22">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z22">
-        <v>5.33</v>
+        <v>6.26</v>
       </c>
       <c r="AA22">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AB22">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="AC22">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="AD22">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AE22">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF22">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AG22">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="U23">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="V23">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
+        <v>1.09</v>
+      </c>
+      <c r="Z23">
+        <v>5.4</v>
+      </c>
+      <c r="AA23">
+        <v>1.38</v>
+      </c>
+      <c r="AB23">
+        <v>2.75</v>
+      </c>
+      <c r="AC23">
+        <v>2.07</v>
+      </c>
+      <c r="AD23">
+        <v>1.73</v>
+      </c>
+      <c r="AE23">
+        <v>1.31</v>
+      </c>
+      <c r="AF23">
+        <v>1.39</v>
+      </c>
+      <c r="AG23">
+        <v>2.77</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.22</v>
       </c>
-      <c r="Z23">
-        <v>4</v>
-      </c>
-      <c r="AA23">
-        <v>1.73</v>
-      </c>
-      <c r="AB23">
-        <v>2.05</v>
-      </c>
-      <c r="AC23">
-        <v>2.77</v>
-      </c>
-      <c r="AD23">
-        <v>1.36</v>
-      </c>
-      <c r="AE23">
-        <v>1.15</v>
-      </c>
-      <c r="AF23">
-        <v>1.59</v>
-      </c>
-      <c r="AG23">
-        <v>2.21</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.6</v>
-      </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="R24">
-        <v>2.68</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="V24">
-        <v>1.81</v>
+        <v>1.46</v>
       </c>
       <c r="W24">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>6.35</v>
+        <v>4</v>
       </c>
       <c r="AA24">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="AB24">
-        <v>3.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>1.85</v>
+        <v>2.77</v>
       </c>
       <c r="AD24">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="AG24">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AK24">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G26">
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="S26">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T26">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U26">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="V26">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="W26">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z26">
-        <v>5.4</v>
+        <v>6.35</v>
       </c>
       <c r="AA26">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AB26">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="AC26">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AD26">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AE26">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AF26">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AG26">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.92</v>
+        <v>1.46</v>
       </c>
       <c r="O27">
-        <v>3.94</v>
+        <v>4.51</v>
       </c>
       <c r="P27">
-        <v>2.22</v>
+        <v>7.05</v>
       </c>
       <c r="Q27">
-        <v>3.4</v>
+        <v>1.57</v>
       </c>
       <c r="R27">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="S27">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="U27">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="V27">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="W27">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z27">
-        <v>6.26</v>
+        <v>4.65</v>
       </c>
       <c r="AA27">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="AC27">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AD27">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="AE27">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AF27">
-        <v>1.35</v>
+        <v>2.14</v>
       </c>
       <c r="AG27">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK27">
-        <v>1.32</v>
+        <v>4.46</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
+        <v>2.74</v>
+      </c>
+      <c r="O33">
+        <v>3.16</v>
+      </c>
+      <c r="P33">
+        <v>2.47</v>
+      </c>
+      <c r="Q33">
+        <v>3.22</v>
+      </c>
+      <c r="R33">
         <v>2.05</v>
       </c>
-      <c r="O33">
-        <v>3.25</v>
-      </c>
-      <c r="P33">
-        <v>3.53</v>
-      </c>
-      <c r="Q33">
-        <v>2.48</v>
-      </c>
-      <c r="R33">
-        <v>1.97</v>
-      </c>
       <c r="S33">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="U33">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="V33">
+        <v>1.34</v>
+      </c>
+      <c r="W33">
+        <v>1.08</v>
+      </c>
+      <c r="X33">
+        <v>1.02</v>
+      </c>
+      <c r="Y33">
         <v>1.3</v>
       </c>
-      <c r="W33">
-        <v>1.01</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.32</v>
-      </c>
       <c r="Z33">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA33">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB33">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AC33">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE33">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG33">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK33">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="O34">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>2.47</v>
+        <v>3.53</v>
       </c>
       <c r="Q34">
-        <v>3.22</v>
+        <v>2.48</v>
       </c>
       <c r="R34">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T34">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="U34">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="V34">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.32</v>
+      </c>
+      <c r="Z34">
+        <v>2.88</v>
+      </c>
+      <c r="AA34">
+        <v>2.15</v>
+      </c>
+      <c r="AB34">
+        <v>1.71</v>
+      </c>
+      <c r="AC34">
+        <v>3.74</v>
+      </c>
+      <c r="AD34">
+        <v>1.25</v>
+      </c>
+      <c r="AE34">
         <v>1.02</v>
       </c>
-      <c r="Y34">
-        <v>1.3</v>
-      </c>
-      <c r="Z34">
-        <v>2.97</v>
-      </c>
-      <c r="AA34">
-        <v>1.9</v>
-      </c>
-      <c r="AB34">
-        <v>1.86</v>
-      </c>
-      <c r="AC34">
-        <v>3.34</v>
-      </c>
-      <c r="AD34">
-        <v>1.24</v>
-      </c>
-      <c r="AE34">
-        <v>1.05</v>
-      </c>
       <c r="AF34">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AG34">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="O75">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P75">
-        <v>2.99</v>
+        <v>5.34</v>
       </c>
       <c r="Q75">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="R75">
         <v>2.4</v>
       </c>
       <c r="S75">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T75">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U75">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="V75">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="W75">
+        <v>1.11</v>
+      </c>
+      <c r="X75">
+        <v>1.01</v>
+      </c>
+      <c r="Y75">
         <v>1.15</v>
       </c>
-      <c r="X75">
-        <v>1.02</v>
-      </c>
-      <c r="Y75">
-        <v>1.11</v>
-      </c>
       <c r="Z75">
-        <v>4.95</v>
+        <v>4.3</v>
       </c>
       <c r="AA75">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB75">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AC75">
-        <v>2.17</v>
+        <v>2.49</v>
       </c>
       <c r="AD75">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AE75">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF75">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AG75">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AK75">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="O76">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P76">
-        <v>5.34</v>
+        <v>2.99</v>
       </c>
       <c r="Q76">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="R76">
         <v>2.4</v>
       </c>
       <c r="S76">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U76">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="V76">
+        <v>1.65</v>
+      </c>
+      <c r="W76">
+        <v>1.15</v>
+      </c>
+      <c r="X76">
+        <v>1.02</v>
+      </c>
+      <c r="Y76">
+        <v>1.11</v>
+      </c>
+      <c r="Z76">
+        <v>4.95</v>
+      </c>
+      <c r="AA76">
         <v>1.53</v>
       </c>
-      <c r="W76">
-        <v>1.11</v>
-      </c>
-      <c r="X76">
-        <v>1.01</v>
-      </c>
-      <c r="Y76">
-        <v>1.15</v>
-      </c>
-      <c r="Z76">
-        <v>4.3</v>
-      </c>
-      <c r="AA76">
-        <v>1.57</v>
-      </c>
       <c r="AB76">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC76">
-        <v>2.49</v>
+        <v>2.17</v>
       </c>
       <c r="AD76">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="AE76">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF76">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG76">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G82">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.45</v>
+        <v>3.35</v>
       </c>
       <c r="O139">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="P139">
-        <v>7.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q139">
-        <v>1.94</v>
+        <v>4.05</v>
       </c>
       <c r="R139">
-        <v>2.78</v>
+        <v>1.92</v>
       </c>
       <c r="S139">
+        <v>1.46</v>
+      </c>
+      <c r="T139">
+        <v>2.75</v>
+      </c>
+      <c r="U139">
+        <v>3.29</v>
+      </c>
+      <c r="V139">
+        <v>1.36</v>
+      </c>
+      <c r="W139">
+        <v>1.04</v>
+      </c>
+      <c r="X139">
+        <v>1.05</v>
+      </c>
+      <c r="Y139">
+        <v>1.35</v>
+      </c>
+      <c r="Z139">
+        <v>2.86</v>
+      </c>
+      <c r="AA139">
+        <v>2.29</v>
+      </c>
+      <c r="AB139">
+        <v>1.66</v>
+      </c>
+      <c r="AC139">
+        <v>4.1</v>
+      </c>
+      <c r="AD139">
         <v>1.22</v>
       </c>
-      <c r="T139">
-        <v>3.9</v>
-      </c>
-      <c r="U139">
-        <v>2.18</v>
-      </c>
-      <c r="V139">
-        <v>1.69</v>
-      </c>
-      <c r="W139">
-        <v>1.14</v>
-      </c>
-      <c r="X139">
-        <v>1.02</v>
-      </c>
-      <c r="Y139">
-        <v>1.1</v>
-      </c>
-      <c r="Z139">
-        <v>5</v>
-      </c>
-      <c r="AA139">
-        <v>1.48</v>
-      </c>
-      <c r="AB139">
-        <v>2.75</v>
-      </c>
-      <c r="AC139">
-        <v>2.04</v>
-      </c>
-      <c r="AD139">
-        <v>1.7</v>
-      </c>
       <c r="AE139">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AF139">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG139">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK139">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>3.35</v>
+        <v>1.45</v>
       </c>
       <c r="O140">
-        <v>3.13</v>
+        <v>5.1</v>
       </c>
       <c r="P140">
-        <v>2.52</v>
+        <v>7.6</v>
       </c>
       <c r="Q140">
-        <v>4.05</v>
+        <v>1.94</v>
       </c>
       <c r="R140">
-        <v>1.92</v>
+        <v>2.78</v>
       </c>
       <c r="S140">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="T140">
+        <v>3.9</v>
+      </c>
+      <c r="U140">
+        <v>2.18</v>
+      </c>
+      <c r="V140">
+        <v>1.69</v>
+      </c>
+      <c r="W140">
+        <v>1.14</v>
+      </c>
+      <c r="X140">
+        <v>1.02</v>
+      </c>
+      <c r="Y140">
+        <v>1.1</v>
+      </c>
+      <c r="Z140">
+        <v>5</v>
+      </c>
+      <c r="AA140">
+        <v>1.48</v>
+      </c>
+      <c r="AB140">
         <v>2.75</v>
       </c>
-      <c r="U140">
-        <v>3.29</v>
-      </c>
-      <c r="V140">
-        <v>1.36</v>
-      </c>
-      <c r="W140">
-        <v>1.04</v>
-      </c>
-      <c r="X140">
-        <v>1.05</v>
-      </c>
-      <c r="Y140">
-        <v>1.35</v>
-      </c>
-      <c r="Z140">
-        <v>2.86</v>
-      </c>
-      <c r="AA140">
-        <v>2.29</v>
-      </c>
-      <c r="AB140">
-        <v>1.66</v>
-      </c>
       <c r="AC140">
-        <v>4.1</v>
+        <v>2.04</v>
       </c>
       <c r="AD140">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AE140">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AF140">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG140">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK140">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O145">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="P145">
-        <v>2.55</v>
+        <v>3.12</v>
       </c>
       <c r="Q145">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R145">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="S145">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T145">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U145">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="V145">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="W145">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X145">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y145">
+        <v>1.14</v>
+      </c>
+      <c r="Z145">
+        <v>5.39</v>
+      </c>
+      <c r="AA145">
+        <v>1.42</v>
+      </c>
+      <c r="AB145">
+        <v>2.58</v>
+      </c>
+      <c r="AC145">
+        <v>2.16</v>
+      </c>
+      <c r="AD145">
+        <v>1.68</v>
+      </c>
+      <c r="AE145">
         <v>1.22</v>
       </c>
-      <c r="Z145">
-        <v>3.97</v>
-      </c>
-      <c r="AA145">
-        <v>1.75</v>
-      </c>
-      <c r="AB145">
-        <v>2.09</v>
-      </c>
-      <c r="AC145">
-        <v>2.8</v>
-      </c>
-      <c r="AD145">
-        <v>1.36</v>
-      </c>
-      <c r="AE145">
-        <v>1.1</v>
-      </c>
       <c r="AF145">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG145">
-        <v>2.26</v>
+        <v>2.73</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.24</v>
       </c>
       <c r="AK145">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O146">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="P146">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="Q146">
+        <v>2.79</v>
+      </c>
+      <c r="R146">
+        <v>2.24</v>
+      </c>
+      <c r="S146">
+        <v>1.3</v>
+      </c>
+      <c r="T146">
+        <v>3.25</v>
+      </c>
+      <c r="U146">
+        <v>2.47</v>
+      </c>
+      <c r="V146">
+        <v>1.46</v>
+      </c>
+      <c r="W146">
+        <v>1.11</v>
+      </c>
+      <c r="X146">
+        <v>1.03</v>
+      </c>
+      <c r="Y146">
+        <v>1.22</v>
+      </c>
+      <c r="Z146">
+        <v>3.97</v>
+      </c>
+      <c r="AA146">
+        <v>1.75</v>
+      </c>
+      <c r="AB146">
+        <v>2.09</v>
+      </c>
+      <c r="AC146">
         <v>2.8</v>
       </c>
-      <c r="R146">
-        <v>2.33</v>
-      </c>
-      <c r="S146">
-        <v>1.2</v>
-      </c>
-      <c r="T146">
-        <v>4</v>
-      </c>
-      <c r="U146">
-        <v>2.1</v>
-      </c>
-      <c r="V146">
-        <v>1.67</v>
-      </c>
-      <c r="W146">
-        <v>1.18</v>
-      </c>
-      <c r="X146">
-        <v>1.02</v>
-      </c>
-      <c r="Y146">
-        <v>1.14</v>
-      </c>
-      <c r="Z146">
-        <v>5.39</v>
-      </c>
-      <c r="AA146">
-        <v>1.42</v>
-      </c>
-      <c r="AB146">
-        <v>2.58</v>
-      </c>
-      <c r="AC146">
-        <v>2.16</v>
-      </c>
       <c r="AD146">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AE146">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF146">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG146">
-        <v>2.73</v>
+        <v>2.26</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>1.24</v>
       </c>
       <c r="AK146">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,64 +24596,64 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.37</v>
+        <v>1.33</v>
       </c>
       <c r="O149">
-        <v>4.06</v>
+        <v>6.49</v>
       </c>
       <c r="P149">
-        <v>2.88</v>
+        <v>9.1</v>
       </c>
       <c r="Q149">
-        <v>2.54</v>
+        <v>1.73</v>
       </c>
       <c r="R149">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="S149">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T149">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="U149">
-        <v>2.41</v>
+        <v>1.86</v>
       </c>
       <c r="V149">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="W149">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="X149">
         <v>1.01</v>
       </c>
       <c r="Y149">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z149">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA149">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="AB149">
-        <v>2.35</v>
+        <v>3.75</v>
       </c>
       <c r="AC149">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD149">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AE149">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AF149">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG149">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AK149">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.33</v>
+        <v>2.37</v>
       </c>
       <c r="O152">
-        <v>6.49</v>
+        <v>4.06</v>
       </c>
       <c r="P152">
-        <v>9.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q152">
-        <v>1.73</v>
+        <v>2.54</v>
       </c>
       <c r="R152">
-        <v>2.9</v>
+        <v>2.49</v>
       </c>
       <c r="S152">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T152">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="U152">
-        <v>1.86</v>
+        <v>2.41</v>
       </c>
       <c r="V152">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="W152">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X152">
         <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z152">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA152">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AB152">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC152">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AD152">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AE152">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AF152">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG152">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AK152">
-        <v>2.8</v>
+        <v>1.61</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.31</v>
+        <v>2.35</v>
       </c>
       <c r="O163">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="P163">
-        <v>8.300000000000001</v>
+        <v>2.73</v>
       </c>
       <c r="Q163">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="R163">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S163">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T163">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="U163">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="V163">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W163">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X163">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y163">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z163">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="AA163">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="AB163">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AC163">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD163">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE163">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF163">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG163">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK163">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.44</v>
+        <v>5.06</v>
       </c>
       <c r="O164">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P164">
-        <v>7.27</v>
+        <v>1.65</v>
       </c>
       <c r="Q164">
-        <v>1.91</v>
+        <v>5.75</v>
       </c>
       <c r="R164">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S164">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T164">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="U164">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V164">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W164">
         <v>1.06</v>
       </c>
       <c r="X164">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y164">
+        <v>1.29</v>
+      </c>
+      <c r="Z164">
+        <v>3.3</v>
+      </c>
+      <c r="AA164">
+        <v>1.92</v>
+      </c>
+      <c r="AB164">
+        <v>1.76</v>
+      </c>
+      <c r="AC164">
+        <v>3.6</v>
+      </c>
+      <c r="AD164">
         <v>1.25</v>
       </c>
-      <c r="Z164">
-        <v>3.6</v>
-      </c>
-      <c r="AA164">
-        <v>1.8</v>
-      </c>
-      <c r="AB164">
-        <v>1.87</v>
-      </c>
-      <c r="AC164">
-        <v>3.13</v>
-      </c>
-      <c r="AD164">
-        <v>1.3</v>
-      </c>
       <c r="AE164">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF164">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG164">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK164">
-        <v>2.7</v>
+        <v>1.15</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="O165">
-        <v>3.06</v>
+        <v>4.1</v>
       </c>
       <c r="P165">
-        <v>2.73</v>
+        <v>7.27</v>
       </c>
       <c r="Q165">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="R165">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S165">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T165">
+        <v>3.2</v>
+      </c>
+      <c r="U165">
         <v>2.53</v>
       </c>
-      <c r="U165">
-        <v>2.82</v>
-      </c>
       <c r="V165">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W165">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X165">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y165">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z165">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AA165">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AB165">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AC165">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="AD165">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE165">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF165">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG165">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK165">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>5.06</v>
+        <v>1.31</v>
       </c>
       <c r="O167">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="P167">
-        <v>1.65</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q167">
-        <v>5.75</v>
+        <v>1.75</v>
       </c>
       <c r="R167">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="S167">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T167">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="U167">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="V167">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="W167">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X167">
         <v>1.03</v>
       </c>
       <c r="Y167">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z167">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA167">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AB167">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AC167">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD167">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE167">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF167">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG167">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK167">
-        <v>1.15</v>
+        <v>3.1</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,31 +30790,31 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="O187">
-        <v>3.96</v>
+        <v>3.72</v>
       </c>
       <c r="P187">
-        <v>3.77</v>
+        <v>3.52</v>
       </c>
       <c r="Q187">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="R187">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S187">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T187">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U187">
         <v>2.05</v>
       </c>
       <c r="V187">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W187">
         <v>1.18</v>
@@ -30823,31 +30823,31 @@
         <v>1.02</v>
       </c>
       <c r="Y187">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z187">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AA187">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB187">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC187">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD187">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AE187">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AF187">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AG187">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK187">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,80 +30953,80 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="O188">
-        <v>3.72</v>
+        <v>5.1</v>
       </c>
       <c r="P188">
-        <v>3.52</v>
+        <v>4.95</v>
       </c>
       <c r="Q188">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="R188">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="S188">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T188">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="U188">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="V188">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="W188">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="X188">
+        <v>0</v>
+      </c>
+      <c r="Y188">
         <v>1.02</v>
       </c>
-      <c r="Y188">
-        <v>1.12</v>
-      </c>
       <c r="Z188">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AA188">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AB188">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="AC188">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="AD188">
-        <v>1.84</v>
+        <v>3.15</v>
       </c>
       <c r="AE188">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="AF188">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AG188">
+        <v>4.2</v>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ188">
+        <v>1.13</v>
+      </c>
+      <c r="AK188">
         <v>2.4</v>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ188">
-        <v>1.22</v>
-      </c>
-      <c r="AK188">
-        <v>2.15</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,80 +31116,80 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="O189">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="P189">
-        <v>4.95</v>
+        <v>3.26</v>
       </c>
       <c r="Q189">
+        <v>2.2</v>
+      </c>
+      <c r="R189">
+        <v>2.88</v>
+      </c>
+      <c r="S189">
+        <v>1.09</v>
+      </c>
+      <c r="T189">
+        <v>5.45</v>
+      </c>
+      <c r="U189">
+        <v>1.67</v>
+      </c>
+      <c r="V189">
+        <v>2.14</v>
+      </c>
+      <c r="W189">
+        <v>1.32</v>
+      </c>
+      <c r="X189">
+        <v>0</v>
+      </c>
+      <c r="Y189">
+        <v>1.05</v>
+      </c>
+      <c r="Z189">
+        <v>10</v>
+      </c>
+      <c r="AA189">
+        <v>1.2</v>
+      </c>
+      <c r="AB189">
+        <v>4.33</v>
+      </c>
+      <c r="AC189">
+        <v>1.46</v>
+      </c>
+      <c r="AD189">
+        <v>2.44</v>
+      </c>
+      <c r="AE189">
+        <v>1.66</v>
+      </c>
+      <c r="AF189">
+        <v>1.19</v>
+      </c>
+      <c r="AG189">
+        <v>3.8</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ189">
+        <v>1.17</v>
+      </c>
+      <c r="AK189">
         <v>1.83</v>
-      </c>
-      <c r="R189">
-        <v>3.2</v>
-      </c>
-      <c r="S189">
-        <v>1.1</v>
-      </c>
-      <c r="T189">
-        <v>6.5</v>
-      </c>
-      <c r="U189">
-        <v>1.44</v>
-      </c>
-      <c r="V189">
-        <v>2.63</v>
-      </c>
-      <c r="W189">
-        <v>1.5</v>
-      </c>
-      <c r="X189">
-        <v>0</v>
-      </c>
-      <c r="Y189">
-        <v>1.02</v>
-      </c>
-      <c r="Z189">
-        <v>15</v>
-      </c>
-      <c r="AA189">
-        <v>1.08</v>
-      </c>
-      <c r="AB189">
-        <v>6.5</v>
-      </c>
-      <c r="AC189">
-        <v>1.31</v>
-      </c>
-      <c r="AD189">
-        <v>3.15</v>
-      </c>
-      <c r="AE189">
-        <v>2</v>
-      </c>
-      <c r="AF189">
-        <v>1.2</v>
-      </c>
-      <c r="AG189">
-        <v>4.2</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ189">
-        <v>1.13</v>
-      </c>
-      <c r="AK189">
-        <v>2.4</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,80 +31279,80 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="O190">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="P190">
-        <v>3.26</v>
+        <v>3.77</v>
       </c>
       <c r="Q190">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="R190">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="S190">
+        <v>1.2</v>
+      </c>
+      <c r="T190">
+        <v>3.75</v>
+      </c>
+      <c r="U190">
+        <v>2.05</v>
+      </c>
+      <c r="V190">
+        <v>1.7</v>
+      </c>
+      <c r="W190">
+        <v>1.18</v>
+      </c>
+      <c r="X190">
+        <v>1.02</v>
+      </c>
+      <c r="Y190">
         <v>1.09</v>
       </c>
-      <c r="T190">
-        <v>5.45</v>
-      </c>
-      <c r="U190">
-        <v>1.67</v>
-      </c>
-      <c r="V190">
-        <v>2.14</v>
-      </c>
-      <c r="W190">
-        <v>1.32</v>
-      </c>
-      <c r="X190">
-        <v>0</v>
-      </c>
-      <c r="Y190">
-        <v>1.05</v>
-      </c>
       <c r="Z190">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="AA190">
+        <v>1.44</v>
+      </c>
+      <c r="AB190">
+        <v>2.62</v>
+      </c>
+      <c r="AC190">
+        <v>1.85</v>
+      </c>
+      <c r="AD190">
+        <v>1.91</v>
+      </c>
+      <c r="AE190">
+        <v>1.28</v>
+      </c>
+      <c r="AF190">
+        <v>1.39</v>
+      </c>
+      <c r="AG190">
+        <v>2.6</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ190">
         <v>1.2</v>
       </c>
-      <c r="AB190">
-        <v>4.33</v>
-      </c>
-      <c r="AC190">
-        <v>1.46</v>
-      </c>
-      <c r="AD190">
-        <v>2.44</v>
-      </c>
-      <c r="AE190">
-        <v>1.66</v>
-      </c>
-      <c r="AF190">
-        <v>1.19</v>
-      </c>
-      <c r="AG190">
-        <v>3.8</v>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ190">
-        <v>1.17</v>
-      </c>
       <c r="AK190">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="O191">
-        <v>4.85</v>
+        <v>4.3</v>
       </c>
       <c r="P191">
-        <v>7.39</v>
+        <v>4.35</v>
       </c>
       <c r="Q191">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="R191">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="S191">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T191">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U191">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="V191">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W191">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X191">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y191">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z191">
-        <v>4.75</v>
+        <v>5.45</v>
       </c>
       <c r="AA191">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AB191">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AC191">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD191">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AE191">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF191">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AG191">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK191">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O192">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P192">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="Q192">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="R192">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="S192">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="T192">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U192">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="V192">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W192">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X192">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y192">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="Z192">
-        <v>4.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA192">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB192">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AC192">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="AD192">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AE192">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF192">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG192">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK192">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="O193">
-        <v>4.3</v>
+        <v>3.36</v>
       </c>
       <c r="P193">
-        <v>4.35</v>
+        <v>2.81</v>
       </c>
       <c r="Q193">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="R193">
-        <v>2.47</v>
+        <v>2.06</v>
       </c>
       <c r="S193">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="T193">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="U193">
-        <v>2.14</v>
+        <v>2.61</v>
       </c>
       <c r="V193">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="W193">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X193">
         <v>1.02</v>
       </c>
       <c r="Y193">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z193">
-        <v>5.45</v>
+        <v>3.28</v>
       </c>
       <c r="AA193">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="AB193">
-        <v>2.62</v>
+        <v>1.92</v>
       </c>
       <c r="AC193">
-        <v>2.15</v>
+        <v>3.33</v>
       </c>
       <c r="AD193">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AE193">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AF193">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG193">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AK193">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.56</v>
+        <v>1.37</v>
       </c>
       <c r="O194">
-        <v>3.2</v>
+        <v>4.85</v>
       </c>
       <c r="P194">
-        <v>2.69</v>
+        <v>7.39</v>
       </c>
       <c r="Q194">
-        <v>3.06</v>
+        <v>1.83</v>
       </c>
       <c r="R194">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="S194">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="T194">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="U194">
-        <v>2.87</v>
+        <v>2.21</v>
       </c>
       <c r="V194">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="W194">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X194">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y194">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="Z194">
-        <v>2.92</v>
+        <v>4.75</v>
       </c>
       <c r="AA194">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="AB194">
-        <v>1.73</v>
+        <v>2.37</v>
       </c>
       <c r="AC194">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="AD194">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AE194">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF194">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AG194">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK194">
-        <v>1.44</v>
+        <v>2.88</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>3.05</v>
+        <v>2.37</v>
       </c>
       <c r="O196">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P196">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="Q196">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="R196">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S196">
         <v>1.35</v>
       </c>
       <c r="T196">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U196">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="V196">
         <v>1.42</v>
       </c>
       <c r="W196">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X196">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y196">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z196">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AA196">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB196">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC196">
-        <v>2.97</v>
+        <v>3.16</v>
       </c>
       <c r="AD196">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE196">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF196">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG196">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>1.27</v>
       </c>
       <c r="AK196">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="O197">
         <v>3.3</v>
       </c>
       <c r="P197">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q197">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="R197">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S197">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="T197">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U197">
-        <v>2.77</v>
+        <v>2.27</v>
       </c>
       <c r="V197">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W197">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X197">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="Z197">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA197">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB197">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC197">
-        <v>3.16</v>
+        <v>2.35</v>
       </c>
       <c r="AD197">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AE197">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF197">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AG197">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK197">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="O198">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="P198">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="Q198">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="R198">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="S198">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T198">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="U198">
-        <v>2.61</v>
+        <v>2.87</v>
       </c>
       <c r="V198">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W198">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X198">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y198">
+        <v>1.31</v>
+      </c>
+      <c r="Z198">
+        <v>2.92</v>
+      </c>
+      <c r="AA198">
+        <v>2.11</v>
+      </c>
+      <c r="AB198">
+        <v>1.73</v>
+      </c>
+      <c r="AC198">
+        <v>3.45</v>
+      </c>
+      <c r="AD198">
         <v>1.25</v>
       </c>
-      <c r="Z198">
-        <v>3.28</v>
-      </c>
-      <c r="AA198">
-        <v>1.88</v>
-      </c>
-      <c r="AB198">
-        <v>1.92</v>
-      </c>
-      <c r="AC198">
-        <v>3.33</v>
-      </c>
-      <c r="AD198">
-        <v>1.27</v>
-      </c>
       <c r="AE198">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF198">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG198">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AK198">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,80 +33072,80 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="O201">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="P201">
-        <v>9.6</v>
+        <v>3.98</v>
       </c>
       <c r="Q201">
-        <v>1.54</v>
+        <v>2.29</v>
       </c>
       <c r="R201">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="S201">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T201">
-        <v>3.9</v>
+        <v>3.46</v>
       </c>
       <c r="U201">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="V201">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="W201">
         <v>1.15</v>
       </c>
       <c r="X201">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y201">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z201">
-        <v>4.95</v>
+        <v>4.6</v>
       </c>
       <c r="AA201">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AB201">
-        <v>2.66</v>
+        <v>2.23</v>
       </c>
       <c r="AC201">
-        <v>2.23</v>
+        <v>2.53</v>
       </c>
       <c r="AD201">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE201">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AF201">
+        <v>1.53</v>
+      </c>
+      <c r="AG201">
+        <v>2.3</v>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ201">
+        <v>1.19</v>
+      </c>
+      <c r="AK201">
         <v>1.95</v>
-      </c>
-      <c r="AG201">
-        <v>1.75</v>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ201">
-        <v>1.08</v>
-      </c>
-      <c r="AK201">
-        <v>3.81</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.02</v>
+        <v>1.28</v>
       </c>
       <c r="O202">
-        <v>3.62</v>
+        <v>5.4</v>
       </c>
       <c r="P202">
-        <v>3.35</v>
+        <v>9.6</v>
       </c>
       <c r="Q202">
-        <v>2.44</v>
+        <v>1.54</v>
       </c>
       <c r="R202">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="S202">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T202">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U202">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="V202">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W202">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X202">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y202">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z202">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA202">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AB202">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AC202">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AD202">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE202">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF202">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AG202">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AK202">
-        <v>1.61</v>
+        <v>3.81</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="O204">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="P204">
-        <v>3.98</v>
+        <v>3.35</v>
       </c>
       <c r="Q204">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="R204">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S204">
         <v>1.25</v>
       </c>
       <c r="T204">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="U204">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="V204">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W204">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X204">
         <v>1.02</v>
       </c>
       <c r="Y204">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z204">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA204">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB204">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC204">
-        <v>2.53</v>
+        <v>2.29</v>
       </c>
       <c r="AD204">
         <v>1.53</v>
       </c>
       <c r="AE204">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF204">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG204">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK204">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="O209">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P209">
-        <v>2.02</v>
+        <v>4.14</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34415,10 +34415,10 @@
         <v>0</v>
       </c>
       <c r="AA209">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AB209">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AC209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O210">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P210">
-        <v>2.43</v>
+        <v>2.02</v>
       </c>
       <c r="Q210">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R210">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S210">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T210">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U210">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V210">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W210">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X210">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y210">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z210">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA210">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AB210">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AC210">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD210">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE210">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF210">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG210">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK210">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="O211">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P211">
+        <v>2.89</v>
+      </c>
+      <c r="Q211">
+        <v>2.93</v>
+      </c>
+      <c r="R211">
+        <v>2.23</v>
+      </c>
+      <c r="S211">
+        <v>1.3</v>
+      </c>
+      <c r="T211">
+        <v>3.3</v>
+      </c>
+      <c r="U211">
         <v>2.42</v>
       </c>
-      <c r="Q211">
-        <v>3.4</v>
-      </c>
-      <c r="R211">
-        <v>2.2</v>
-      </c>
-      <c r="S211">
-        <v>1.37</v>
-      </c>
-      <c r="T211">
-        <v>2.76</v>
-      </c>
-      <c r="U211">
-        <v>2.56</v>
-      </c>
       <c r="V211">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W211">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X211">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z211">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="AA211">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB211">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC211">
-        <v>2.92</v>
+        <v>2.59</v>
       </c>
       <c r="AD211">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE211">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF211">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG211">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK211">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.26</v>
+        <v>2.57</v>
       </c>
       <c r="O212">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="P212">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="Q212">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="R212">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S212">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T212">
-        <v>3.3</v>
+        <v>2.68</v>
       </c>
       <c r="U212">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="V212">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W212">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X212">
         <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z212">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="AA212">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AB212">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AC212">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="AD212">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE212">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF212">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG212">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
+        <v>1.25</v>
+      </c>
+      <c r="AK212">
         <v>1.44</v>
-      </c>
-      <c r="AK212">
-        <v>1.5</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="O213">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="P213">
-        <v>4.14</v>
+        <v>2.42</v>
       </c>
       <c r="Q213">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R213">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S213">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T213">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U213">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V213">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W213">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X213">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y213">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z213">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA213">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AB213">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC213">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD213">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG213">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK213">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="O215">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P215">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="Q215">
         <v>3.1</v>
       </c>
       <c r="R215">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S215">
+        <v>1.35</v>
+      </c>
+      <c r="T215">
+        <v>3.08</v>
+      </c>
+      <c r="U215">
+        <v>2.53</v>
+      </c>
+      <c r="V215">
+        <v>1.47</v>
+      </c>
+      <c r="W215">
+        <v>1.06</v>
+      </c>
+      <c r="X215">
+        <v>1.02</v>
+      </c>
+      <c r="Y215">
+        <v>1.18</v>
+      </c>
+      <c r="Z215">
+        <v>3.85</v>
+      </c>
+      <c r="AA215">
+        <v>1.74</v>
+      </c>
+      <c r="AB215">
+        <v>2.02</v>
+      </c>
+      <c r="AC215">
+        <v>2.78</v>
+      </c>
+      <c r="AD215">
         <v>1.39</v>
       </c>
-      <c r="T215">
-        <v>2.68</v>
-      </c>
-      <c r="U215">
-        <v>2.63</v>
-      </c>
-      <c r="V215">
-        <v>1.41</v>
-      </c>
-      <c r="W215">
-        <v>1.07</v>
-      </c>
-      <c r="X215">
-        <v>1.01</v>
-      </c>
-      <c r="Y215">
-        <v>1.24</v>
-      </c>
-      <c r="Z215">
-        <v>3.34</v>
-      </c>
-      <c r="AA215">
-        <v>1.98</v>
-      </c>
-      <c r="AB215">
-        <v>1.88</v>
-      </c>
-      <c r="AC215">
-        <v>3.2</v>
-      </c>
-      <c r="AD215">
-        <v>1.26</v>
-      </c>
       <c r="AE215">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF215">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AG215">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G243">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="G244">

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P7">
-        <v>4.13</v>
+        <v>3.14</v>
       </c>
       <c r="Q7">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="R7">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T7">
-        <v>2.84</v>
+        <v>3.09</v>
       </c>
       <c r="U7">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>3.25</v>
+        <v>3.73</v>
       </c>
       <c r="AA7">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AB7">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="AD7">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE7">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="O8">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>3.14</v>
+        <v>4.13</v>
       </c>
       <c r="Q8">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T8">
-        <v>3.09</v>
+        <v>2.84</v>
       </c>
       <c r="U8">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>3.73</v>
+        <v>3.25</v>
       </c>
       <c r="AA8">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AB8">
+        <v>1.76</v>
+      </c>
+      <c r="AC8">
+        <v>3.48</v>
+      </c>
+      <c r="AD8">
+        <v>1.22</v>
+      </c>
+      <c r="AE8">
+        <v>1.04</v>
+      </c>
+      <c r="AF8">
         <v>1.85</v>
       </c>
-      <c r="AC8">
-        <v>2.92</v>
-      </c>
-      <c r="AD8">
-        <v>1.31</v>
-      </c>
-      <c r="AE8">
-        <v>1.13</v>
-      </c>
-      <c r="AF8">
-        <v>1.67</v>
-      </c>
       <c r="AG8">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
       </c>
       <c r="R22">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S22">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U22">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V22">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="W22">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z22">
-        <v>6.26</v>
+        <v>5.4</v>
       </c>
       <c r="AA22">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AB22">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AC22">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AD22">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE22">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF22">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AG22">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Q23">
-        <v>3.4</v>
+        <v>1.57</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S23">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>4.5</v>
+        <v>3.56</v>
       </c>
       <c r="U23">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="V23">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="W23">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z23">
-        <v>5.4</v>
+        <v>4.65</v>
       </c>
       <c r="AA23">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AB23">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC23">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AD23">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AE23">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AF23">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="AG23">
-        <v>2.77</v>
+        <v>1.63</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>1.33</v>
+        <v>4.46</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="U24">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="V24">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="AA24">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AB24">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AC24">
-        <v>2.77</v>
+        <v>2.51</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE24">
         <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q25">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="R25">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AA25">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AB25">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AC25">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="AD25">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
         <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AK25">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.46</v>
+        <v>2.92</v>
       </c>
       <c r="O27">
-        <v>4.51</v>
+        <v>3.94</v>
       </c>
       <c r="P27">
-        <v>7.05</v>
+        <v>2.22</v>
       </c>
       <c r="Q27">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="R27">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S27">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T27">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="U27">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="V27">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>4.65</v>
+        <v>6.26</v>
       </c>
       <c r="AA27">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="AB27">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="AC27">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AD27">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="AE27">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AF27">
-        <v>2.14</v>
+        <v>1.35</v>
       </c>
       <c r="AG27">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>4.46</v>
+        <v>1.32</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.47</v>
+        <v>3.53</v>
       </c>
       <c r="Q33">
-        <v>3.22</v>
+        <v>2.48</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T33">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="V33">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.32</v>
+      </c>
+      <c r="Z33">
+        <v>2.88</v>
+      </c>
+      <c r="AA33">
+        <v>2.15</v>
+      </c>
+      <c r="AB33">
+        <v>1.71</v>
+      </c>
+      <c r="AC33">
+        <v>3.74</v>
+      </c>
+      <c r="AD33">
+        <v>1.25</v>
+      </c>
+      <c r="AE33">
         <v>1.02</v>
       </c>
-      <c r="Y33">
-        <v>1.3</v>
-      </c>
-      <c r="Z33">
-        <v>2.97</v>
-      </c>
-      <c r="AA33">
-        <v>1.9</v>
-      </c>
-      <c r="AB33">
-        <v>1.86</v>
-      </c>
-      <c r="AC33">
-        <v>3.34</v>
-      </c>
-      <c r="AD33">
-        <v>1.24</v>
-      </c>
-      <c r="AE33">
-        <v>1.05</v>
-      </c>
       <c r="AF33">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AG33">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
+        <v>2.74</v>
+      </c>
+      <c r="O34">
+        <v>3.16</v>
+      </c>
+      <c r="P34">
+        <v>2.47</v>
+      </c>
+      <c r="Q34">
+        <v>3.22</v>
+      </c>
+      <c r="R34">
         <v>2.05</v>
       </c>
-      <c r="O34">
-        <v>3.25</v>
-      </c>
-      <c r="P34">
-        <v>3.53</v>
-      </c>
-      <c r="Q34">
-        <v>2.48</v>
-      </c>
-      <c r="R34">
-        <v>1.97</v>
-      </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="U34">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="V34">
+        <v>1.34</v>
+      </c>
+      <c r="W34">
+        <v>1.08</v>
+      </c>
+      <c r="X34">
+        <v>1.02</v>
+      </c>
+      <c r="Y34">
         <v>1.3</v>
       </c>
-      <c r="W34">
-        <v>1.01</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.32</v>
-      </c>
       <c r="Z34">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA34">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AC34">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE34">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF34">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG34">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="O40">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="P40">
-        <v>4.71</v>
+        <v>2.1</v>
       </c>
       <c r="Q40">
-        <v>2.17</v>
+        <v>3.25</v>
       </c>
       <c r="R40">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T40">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="U40">
         <v>2.5</v>
@@ -6856,37 +6856,37 @@
         <v>1.47</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z40">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA40">
         <v>1.78</v>
       </c>
       <c r="AB40">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC40">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD40">
         <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AG40">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>2.11</v>
+        <v>1.4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,25 +6992,25 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.91</v>
       </c>
       <c r="P41">
-        <v>2.1</v>
+        <v>4.71</v>
       </c>
       <c r="Q41">
-        <v>3.25</v>
+        <v>2.17</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="U41">
         <v>2.5</v>
@@ -7019,37 +7019,37 @@
         <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
         <v>1.78</v>
       </c>
       <c r="AB41">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC41">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD41">
         <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AG41">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK41">
-        <v>1.4</v>
+        <v>2.11</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="P57">
-        <v>3.43</v>
+        <v>4.14</v>
       </c>
       <c r="Q57">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="R57">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="S57">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T57">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="U57">
-        <v>2.11</v>
+        <v>1.82</v>
       </c>
       <c r="V57">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="W57">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Z57">
-        <v>5.15</v>
+        <v>7.4</v>
       </c>
       <c r="AA57">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AB57">
-        <v>2.42</v>
+        <v>3.34</v>
       </c>
       <c r="AC57">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AD57">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AE57">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AF57">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AG57">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK57">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="O58">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="P58">
-        <v>4.14</v>
+        <v>3.43</v>
       </c>
       <c r="Q58">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="R58">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="S58">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T58">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="U58">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
       <c r="V58">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="W58">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z58">
-        <v>7.4</v>
+        <v>5.15</v>
       </c>
       <c r="AA58">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AB58">
-        <v>3.34</v>
+        <v>2.42</v>
       </c>
       <c r="AC58">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AD58">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AE58">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AF58">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AG58">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK58">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.59</v>
+        <v>2.29</v>
       </c>
       <c r="O65">
-        <v>3.98</v>
+        <v>3.32</v>
       </c>
       <c r="P65">
-        <v>5.02</v>
+        <v>2.93</v>
       </c>
       <c r="Q65">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S65">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T65">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U65">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V65">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X65">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z65">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="AA65">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB65">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AC65">
-        <v>2.74</v>
+        <v>3.14</v>
       </c>
       <c r="AD65">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE65">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF65">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG65">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK65">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.29</v>
+        <v>1.59</v>
       </c>
       <c r="O66">
-        <v>3.32</v>
+        <v>3.98</v>
       </c>
       <c r="P66">
-        <v>2.93</v>
+        <v>5.02</v>
       </c>
       <c r="Q66">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="R66">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T66">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U66">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="V66">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="W66">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z66">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="AA66">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB66">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC66">
-        <v>3.14</v>
+        <v>2.74</v>
       </c>
       <c r="AD66">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE66">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF66">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK66">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="O75">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P75">
-        <v>5.34</v>
+        <v>2.99</v>
       </c>
       <c r="Q75">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="R75">
         <v>2.4</v>
       </c>
       <c r="S75">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T75">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U75">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="V75">
+        <v>1.65</v>
+      </c>
+      <c r="W75">
+        <v>1.15</v>
+      </c>
+      <c r="X75">
+        <v>1.02</v>
+      </c>
+      <c r="Y75">
+        <v>1.11</v>
+      </c>
+      <c r="Z75">
+        <v>4.95</v>
+      </c>
+      <c r="AA75">
         <v>1.53</v>
       </c>
-      <c r="W75">
-        <v>1.11</v>
-      </c>
-      <c r="X75">
-        <v>1.01</v>
-      </c>
-      <c r="Y75">
-        <v>1.15</v>
-      </c>
-      <c r="Z75">
-        <v>4.3</v>
-      </c>
-      <c r="AA75">
-        <v>1.57</v>
-      </c>
       <c r="AB75">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC75">
-        <v>2.49</v>
+        <v>2.17</v>
       </c>
       <c r="AD75">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="AE75">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF75">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG75">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AK75">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="O76">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P76">
-        <v>2.99</v>
+        <v>5.34</v>
       </c>
       <c r="Q76">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="R76">
         <v>2.4</v>
       </c>
       <c r="S76">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T76">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U76">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="V76">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="W76">
+        <v>1.11</v>
+      </c>
+      <c r="X76">
+        <v>1.01</v>
+      </c>
+      <c r="Y76">
         <v>1.15</v>
       </c>
-      <c r="X76">
-        <v>1.02</v>
-      </c>
-      <c r="Y76">
-        <v>1.11</v>
-      </c>
       <c r="Z76">
-        <v>4.95</v>
+        <v>4.3</v>
       </c>
       <c r="AA76">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB76">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AC76">
-        <v>2.17</v>
+        <v>2.49</v>
       </c>
       <c r="AD76">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AE76">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF76">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AG76">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AK76">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>3.35</v>
+        <v>1.45</v>
       </c>
       <c r="O139">
-        <v>3.13</v>
+        <v>5.1</v>
       </c>
       <c r="P139">
-        <v>2.52</v>
+        <v>7.6</v>
       </c>
       <c r="Q139">
-        <v>4.05</v>
+        <v>1.94</v>
       </c>
       <c r="R139">
-        <v>1.92</v>
+        <v>2.78</v>
       </c>
       <c r="S139">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="T139">
+        <v>3.9</v>
+      </c>
+      <c r="U139">
+        <v>2.18</v>
+      </c>
+      <c r="V139">
+        <v>1.69</v>
+      </c>
+      <c r="W139">
+        <v>1.14</v>
+      </c>
+      <c r="X139">
+        <v>1.02</v>
+      </c>
+      <c r="Y139">
+        <v>1.1</v>
+      </c>
+      <c r="Z139">
+        <v>5</v>
+      </c>
+      <c r="AA139">
+        <v>1.48</v>
+      </c>
+      <c r="AB139">
         <v>2.75</v>
       </c>
-      <c r="U139">
-        <v>3.29</v>
-      </c>
-      <c r="V139">
-        <v>1.36</v>
-      </c>
-      <c r="W139">
-        <v>1.04</v>
-      </c>
-      <c r="X139">
-        <v>1.05</v>
-      </c>
-      <c r="Y139">
-        <v>1.35</v>
-      </c>
-      <c r="Z139">
-        <v>2.86</v>
-      </c>
-      <c r="AA139">
-        <v>2.29</v>
-      </c>
-      <c r="AB139">
-        <v>1.66</v>
-      </c>
       <c r="AC139">
-        <v>4.1</v>
+        <v>2.04</v>
       </c>
       <c r="AD139">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AE139">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AF139">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG139">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK139">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>1.45</v>
+        <v>3.35</v>
       </c>
       <c r="O140">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="P140">
-        <v>7.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q140">
-        <v>1.94</v>
+        <v>4.05</v>
       </c>
       <c r="R140">
-        <v>2.78</v>
+        <v>1.92</v>
       </c>
       <c r="S140">
+        <v>1.46</v>
+      </c>
+      <c r="T140">
+        <v>2.75</v>
+      </c>
+      <c r="U140">
+        <v>3.29</v>
+      </c>
+      <c r="V140">
+        <v>1.36</v>
+      </c>
+      <c r="W140">
+        <v>1.04</v>
+      </c>
+      <c r="X140">
+        <v>1.05</v>
+      </c>
+      <c r="Y140">
+        <v>1.35</v>
+      </c>
+      <c r="Z140">
+        <v>2.86</v>
+      </c>
+      <c r="AA140">
+        <v>2.29</v>
+      </c>
+      <c r="AB140">
+        <v>1.66</v>
+      </c>
+      <c r="AC140">
+        <v>4.1</v>
+      </c>
+      <c r="AD140">
         <v>1.22</v>
       </c>
-      <c r="T140">
-        <v>3.9</v>
-      </c>
-      <c r="U140">
-        <v>2.18</v>
-      </c>
-      <c r="V140">
-        <v>1.69</v>
-      </c>
-      <c r="W140">
-        <v>1.14</v>
-      </c>
-      <c r="X140">
-        <v>1.02</v>
-      </c>
-      <c r="Y140">
-        <v>1.1</v>
-      </c>
-      <c r="Z140">
-        <v>5</v>
-      </c>
-      <c r="AA140">
-        <v>1.48</v>
-      </c>
-      <c r="AB140">
-        <v>2.75</v>
-      </c>
-      <c r="AC140">
-        <v>2.04</v>
-      </c>
-      <c r="AD140">
-        <v>1.7</v>
-      </c>
       <c r="AE140">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AF140">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG140">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK140">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,58 +24433,58 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.29</v>
+        <v>1.84</v>
       </c>
       <c r="O148">
-        <v>3.84</v>
+        <v>4.27</v>
       </c>
       <c r="P148">
-        <v>3.14</v>
+        <v>4.21</v>
       </c>
       <c r="Q148">
+        <v>2.24</v>
+      </c>
+      <c r="R148">
+        <v>2.44</v>
+      </c>
+      <c r="S148">
+        <v>1.24</v>
+      </c>
+      <c r="T148">
+        <v>3.75</v>
+      </c>
+      <c r="U148">
         <v>2.35</v>
       </c>
-      <c r="R148">
-        <v>2.29</v>
-      </c>
-      <c r="S148">
-        <v>1.25</v>
-      </c>
-      <c r="T148">
-        <v>3.6</v>
-      </c>
-      <c r="U148">
-        <v>2.3</v>
-      </c>
       <c r="V148">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W148">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X148">
         <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z148">
         <v>4.6</v>
       </c>
       <c r="AA148">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AB148">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AC148">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AD148">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AE148">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF148">
         <v>1.5</v>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK148">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,64 +24596,64 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.33</v>
+        <v>2.37</v>
       </c>
       <c r="O149">
-        <v>6.49</v>
+        <v>4.06</v>
       </c>
       <c r="P149">
-        <v>9.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q149">
-        <v>1.73</v>
+        <v>2.54</v>
       </c>
       <c r="R149">
-        <v>2.9</v>
+        <v>2.49</v>
       </c>
       <c r="S149">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T149">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="U149">
-        <v>1.86</v>
+        <v>2.41</v>
       </c>
       <c r="V149">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="W149">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X149">
         <v>1.01</v>
       </c>
       <c r="Y149">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z149">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA149">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AB149">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC149">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AD149">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AE149">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AF149">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG149">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AK149">
-        <v>2.8</v>
+        <v>1.61</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,58 +24922,58 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.84</v>
+        <v>2.29</v>
       </c>
       <c r="O151">
-        <v>4.27</v>
+        <v>3.84</v>
       </c>
       <c r="P151">
-        <v>4.21</v>
+        <v>3.14</v>
       </c>
       <c r="Q151">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="R151">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="S151">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T151">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U151">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="V151">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W151">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X151">
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z151">
         <v>4.6</v>
       </c>
       <c r="AA151">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="AB151">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AC151">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AD151">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AE151">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF151">
         <v>1.5</v>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK151">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.37</v>
+        <v>1.33</v>
       </c>
       <c r="O152">
-        <v>4.06</v>
+        <v>6.49</v>
       </c>
       <c r="P152">
-        <v>2.88</v>
+        <v>9.1</v>
       </c>
       <c r="Q152">
-        <v>2.54</v>
+        <v>1.73</v>
       </c>
       <c r="R152">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="S152">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T152">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="U152">
-        <v>2.41</v>
+        <v>1.86</v>
       </c>
       <c r="V152">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="W152">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="X152">
         <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z152">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA152">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="AB152">
-        <v>2.35</v>
+        <v>3.75</v>
       </c>
       <c r="AC152">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD152">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AE152">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AF152">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG152">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AK152">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O163">
-        <v>3.06</v>
+        <v>3.24</v>
       </c>
       <c r="P163">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="Q163">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="R163">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S163">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T163">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="U163">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="V163">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W163">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X163">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y163">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z163">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA163">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB163">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC163">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD163">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE163">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF163">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG163">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>1.3</v>
       </c>
       <c r="AK163">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>5.06</v>
+        <v>1.31</v>
       </c>
       <c r="O164">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="P164">
-        <v>1.65</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q164">
-        <v>5.75</v>
+        <v>1.75</v>
       </c>
       <c r="R164">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="S164">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T164">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="U164">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="V164">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="W164">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X164">
         <v>1.03</v>
       </c>
       <c r="Y164">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z164">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA164">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AB164">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AC164">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD164">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE164">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF164">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG164">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK164">
-        <v>1.15</v>
+        <v>3.1</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.44</v>
+        <v>5.06</v>
       </c>
       <c r="O165">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P165">
-        <v>7.27</v>
+        <v>1.65</v>
       </c>
       <c r="Q165">
-        <v>1.91</v>
+        <v>5.75</v>
       </c>
       <c r="R165">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S165">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T165">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="U165">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V165">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W165">
         <v>1.06</v>
       </c>
       <c r="X165">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y165">
+        <v>1.29</v>
+      </c>
+      <c r="Z165">
+        <v>3.3</v>
+      </c>
+      <c r="AA165">
+        <v>1.92</v>
+      </c>
+      <c r="AB165">
+        <v>1.76</v>
+      </c>
+      <c r="AC165">
+        <v>3.6</v>
+      </c>
+      <c r="AD165">
         <v>1.25</v>
       </c>
-      <c r="Z165">
-        <v>3.6</v>
-      </c>
-      <c r="AA165">
-        <v>1.8</v>
-      </c>
-      <c r="AB165">
-        <v>1.87</v>
-      </c>
-      <c r="AC165">
-        <v>3.13</v>
-      </c>
-      <c r="AD165">
-        <v>1.3</v>
-      </c>
       <c r="AE165">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF165">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG165">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK165">
-        <v>2.7</v>
+        <v>1.15</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="O166">
-        <v>3.24</v>
+        <v>4.1</v>
       </c>
       <c r="P166">
-        <v>2.05</v>
+        <v>7.27</v>
       </c>
       <c r="Q166">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="R166">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S166">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T166">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U166">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="V166">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W166">
         <v>1.06</v>
       </c>
       <c r="X166">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y166">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z166">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA166">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB166">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AC166">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="AD166">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE166">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF166">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AG166">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK166">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.31</v>
+        <v>2.35</v>
       </c>
       <c r="O167">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="P167">
-        <v>8.300000000000001</v>
+        <v>2.73</v>
       </c>
       <c r="Q167">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="R167">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S167">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T167">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="U167">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="V167">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W167">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X167">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y167">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z167">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="AA167">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="AB167">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AC167">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD167">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE167">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF167">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG167">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK167">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,19 +28997,19 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="O176">
-        <v>3.65</v>
+        <v>3.82</v>
       </c>
       <c r="P176">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="Q176">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="R176">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S176">
         <v>1.3</v>
@@ -29018,10 +29018,10 @@
         <v>3.12</v>
       </c>
       <c r="U176">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V176">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W176">
         <v>1.07</v>
@@ -29033,28 +29033,28 @@
         <v>1.18</v>
       </c>
       <c r="Z176">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="AA176">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB176">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC176">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AD176">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE176">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF176">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG176">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>1.22</v>
       </c>
       <c r="AK176">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,19 +29160,19 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="O177">
-        <v>3.82</v>
+        <v>3.65</v>
       </c>
       <c r="P177">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q177">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="R177">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S177">
         <v>1.3</v>
@@ -29181,10 +29181,10 @@
         <v>3.12</v>
       </c>
       <c r="U177">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V177">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W177">
         <v>1.07</v>
@@ -29196,28 +29196,28 @@
         <v>1.18</v>
       </c>
       <c r="Z177">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="AA177">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB177">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC177">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AD177">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE177">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF177">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG177">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>1.22</v>
       </c>
       <c r="AK177">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G183">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,80 +31116,80 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="O189">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="P189">
-        <v>3.26</v>
+        <v>3.77</v>
       </c>
       <c r="Q189">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="R189">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="S189">
+        <v>1.2</v>
+      </c>
+      <c r="T189">
+        <v>3.75</v>
+      </c>
+      <c r="U189">
+        <v>2.05</v>
+      </c>
+      <c r="V189">
+        <v>1.7</v>
+      </c>
+      <c r="W189">
+        <v>1.18</v>
+      </c>
+      <c r="X189">
+        <v>1.02</v>
+      </c>
+      <c r="Y189">
         <v>1.09</v>
       </c>
-      <c r="T189">
-        <v>5.45</v>
-      </c>
-      <c r="U189">
-        <v>1.67</v>
-      </c>
-      <c r="V189">
-        <v>2.14</v>
-      </c>
-      <c r="W189">
-        <v>1.32</v>
-      </c>
-      <c r="X189">
-        <v>0</v>
-      </c>
-      <c r="Y189">
-        <v>1.05</v>
-      </c>
       <c r="Z189">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="AA189">
+        <v>1.44</v>
+      </c>
+      <c r="AB189">
+        <v>2.62</v>
+      </c>
+      <c r="AC189">
+        <v>1.85</v>
+      </c>
+      <c r="AD189">
+        <v>1.91</v>
+      </c>
+      <c r="AE189">
+        <v>1.28</v>
+      </c>
+      <c r="AF189">
+        <v>1.39</v>
+      </c>
+      <c r="AG189">
+        <v>2.6</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ189">
         <v>1.2</v>
       </c>
-      <c r="AB189">
-        <v>4.33</v>
-      </c>
-      <c r="AC189">
-        <v>1.46</v>
-      </c>
-      <c r="AD189">
-        <v>2.44</v>
-      </c>
-      <c r="AE189">
-        <v>1.66</v>
-      </c>
-      <c r="AF189">
-        <v>1.19</v>
-      </c>
-      <c r="AG189">
-        <v>3.8</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ189">
-        <v>1.17</v>
-      </c>
       <c r="AK189">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="O190">
-        <v>3.96</v>
+        <v>4.5</v>
       </c>
       <c r="P190">
-        <v>3.77</v>
+        <v>3.26</v>
       </c>
       <c r="Q190">
+        <v>2.2</v>
+      </c>
+      <c r="R190">
+        <v>2.88</v>
+      </c>
+      <c r="S190">
+        <v>1.09</v>
+      </c>
+      <c r="T190">
+        <v>5.45</v>
+      </c>
+      <c r="U190">
+        <v>1.67</v>
+      </c>
+      <c r="V190">
+        <v>2.14</v>
+      </c>
+      <c r="W190">
+        <v>1.32</v>
+      </c>
+      <c r="X190">
+        <v>0</v>
+      </c>
+      <c r="Y190">
+        <v>1.05</v>
+      </c>
+      <c r="Z190">
+        <v>10</v>
+      </c>
+      <c r="AA190">
+        <v>1.2</v>
+      </c>
+      <c r="AB190">
+        <v>4.33</v>
+      </c>
+      <c r="AC190">
+        <v>1.46</v>
+      </c>
+      <c r="AD190">
         <v>2.44</v>
       </c>
-      <c r="R190">
-        <v>2.43</v>
-      </c>
-      <c r="S190">
-        <v>1.2</v>
-      </c>
-      <c r="T190">
-        <v>3.75</v>
-      </c>
-      <c r="U190">
-        <v>2.05</v>
-      </c>
-      <c r="V190">
-        <v>1.7</v>
-      </c>
-      <c r="W190">
-        <v>1.18</v>
-      </c>
-      <c r="X190">
-        <v>1.02</v>
-      </c>
-      <c r="Y190">
-        <v>1.09</v>
-      </c>
-      <c r="Z190">
-        <v>5.3</v>
-      </c>
-      <c r="AA190">
-        <v>1.44</v>
-      </c>
-      <c r="AB190">
-        <v>2.62</v>
-      </c>
-      <c r="AC190">
-        <v>1.85</v>
-      </c>
-      <c r="AD190">
-        <v>1.91</v>
-      </c>
       <c r="AE190">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AF190">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AG190">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK190">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,80 +31605,80 @@
         </is>
       </c>
       <c r="N192">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O192">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P192">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="Q192">
-        <v>3.15</v>
+        <v>2.73</v>
       </c>
       <c r="R192">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="S192">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="T192">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U192">
-        <v>2.67</v>
+        <v>2.27</v>
       </c>
       <c r="V192">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W192">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X192">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y192">
+        <v>1.11</v>
+      </c>
+      <c r="Z192">
+        <v>4.8</v>
+      </c>
+      <c r="AA192">
+        <v>1.83</v>
+      </c>
+      <c r="AB192">
+        <v>1.91</v>
+      </c>
+      <c r="AC192">
+        <v>2.35</v>
+      </c>
+      <c r="AD192">
+        <v>1.55</v>
+      </c>
+      <c r="AE192">
+        <v>1.17</v>
+      </c>
+      <c r="AF192">
+        <v>1.44</v>
+      </c>
+      <c r="AG192">
+        <v>2.6</v>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ192">
         <v>1.23</v>
       </c>
-      <c r="Z192">
-        <v>3.42</v>
-      </c>
-      <c r="AA192">
-        <v>1.91</v>
-      </c>
-      <c r="AB192">
-        <v>1.89</v>
-      </c>
-      <c r="AC192">
-        <v>2.97</v>
-      </c>
-      <c r="AD192">
-        <v>1.3</v>
-      </c>
-      <c r="AE192">
-        <v>1.08</v>
-      </c>
-      <c r="AF192">
-        <v>1.67</v>
-      </c>
-      <c r="AG192">
-        <v>2.1</v>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ192">
-        <v>1.27</v>
-      </c>
       <c r="AK192">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.4</v>
+        <v>1.37</v>
       </c>
       <c r="O193">
-        <v>3.36</v>
+        <v>4.85</v>
       </c>
       <c r="P193">
-        <v>2.81</v>
+        <v>7.39</v>
       </c>
       <c r="Q193">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="R193">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="S193">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="T193">
-        <v>2.99</v>
+        <v>3.75</v>
       </c>
       <c r="U193">
-        <v>2.61</v>
+        <v>2.21</v>
       </c>
       <c r="V193">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W193">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X193">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y193">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="Z193">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="AA193">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AB193">
-        <v>1.92</v>
+        <v>2.37</v>
       </c>
       <c r="AC193">
-        <v>3.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD193">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AE193">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF193">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG193">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AK193">
-        <v>1.47</v>
+        <v>2.88</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.37</v>
+        <v>2.4</v>
       </c>
       <c r="O194">
-        <v>4.85</v>
+        <v>3.36</v>
       </c>
       <c r="P194">
-        <v>7.39</v>
+        <v>2.81</v>
       </c>
       <c r="Q194">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="R194">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="S194">
+        <v>1.39</v>
+      </c>
+      <c r="T194">
+        <v>2.99</v>
+      </c>
+      <c r="U194">
+        <v>2.61</v>
+      </c>
+      <c r="V194">
+        <v>1.4</v>
+      </c>
+      <c r="W194">
+        <v>1.06</v>
+      </c>
+      <c r="X194">
+        <v>1.02</v>
+      </c>
+      <c r="Y194">
         <v>1.25</v>
       </c>
-      <c r="T194">
-        <v>3.75</v>
-      </c>
-      <c r="U194">
-        <v>2.21</v>
-      </c>
-      <c r="V194">
-        <v>1.6</v>
-      </c>
-      <c r="W194">
-        <v>1.12</v>
-      </c>
-      <c r="X194">
-        <v>1.03</v>
-      </c>
-      <c r="Y194">
-        <v>1.12</v>
-      </c>
       <c r="Z194">
-        <v>4.75</v>
+        <v>3.28</v>
       </c>
       <c r="AA194">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AB194">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="AC194">
-        <v>2.3</v>
+        <v>3.33</v>
       </c>
       <c r="AD194">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AE194">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF194">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG194">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AK194">
-        <v>2.88</v>
+        <v>1.47</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,28 +32094,28 @@
         </is>
       </c>
       <c r="N195">
-        <v>3.41</v>
+        <v>2.37</v>
       </c>
       <c r="O195">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P195">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="Q195">
-        <v>3.59</v>
+        <v>2.9</v>
       </c>
       <c r="R195">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S195">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T195">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="U195">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="V195">
         <v>1.42</v>
@@ -32124,50 +32124,50 @@
         <v>1.06</v>
       </c>
       <c r="X195">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y195">
+        <v>1.29</v>
+      </c>
+      <c r="Z195">
+        <v>3.2</v>
+      </c>
+      <c r="AA195">
+        <v>1.85</v>
+      </c>
+      <c r="AB195">
+        <v>1.85</v>
+      </c>
+      <c r="AC195">
+        <v>3.16</v>
+      </c>
+      <c r="AD195">
+        <v>1.33</v>
+      </c>
+      <c r="AE195">
+        <v>1.13</v>
+      </c>
+      <c r="AF195">
+        <v>1.73</v>
+      </c>
+      <c r="AG195">
+        <v>2.05</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ195">
         <v>1.27</v>
       </c>
-      <c r="Z195">
-        <v>3.71</v>
-      </c>
-      <c r="AA195">
-        <v>2</v>
-      </c>
-      <c r="AB195">
-        <v>1.81</v>
-      </c>
-      <c r="AC195">
-        <v>2.93</v>
-      </c>
-      <c r="AD195">
-        <v>1.34</v>
-      </c>
-      <c r="AE195">
-        <v>1.07</v>
-      </c>
-      <c r="AF195">
-        <v>1.7</v>
-      </c>
-      <c r="AG195">
-        <v>2</v>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ195">
-        <v>1.23</v>
-      </c>
       <c r="AK195">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,28 +32257,28 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.37</v>
+        <v>3.41</v>
       </c>
       <c r="O196">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="P196">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="Q196">
-        <v>2.9</v>
+        <v>3.59</v>
       </c>
       <c r="R196">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S196">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T196">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="U196">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="V196">
         <v>1.42</v>
@@ -32287,34 +32287,34 @@
         <v>1.06</v>
       </c>
       <c r="X196">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z196">
-        <v>3.2</v>
+        <v>3.71</v>
       </c>
       <c r="AA196">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB196">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC196">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="AD196">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE196">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF196">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG196">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK196">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O197">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P197">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="Q197">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="R197">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="S197">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="T197">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U197">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="V197">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W197">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X197">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="Z197">
-        <v>4.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA197">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB197">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AC197">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="AD197">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AE197">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF197">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG197">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK197">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32918,34 +32918,34 @@
         <v>2.22</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S200">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T200">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U200">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V200">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W200">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X200">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y200">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z200">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA200">
         <v>1.87</v>
@@ -32954,19 +32954,19 @@
         <v>1.88</v>
       </c>
       <c r="AC200">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD200">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE200">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG200">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK200">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="O202">
-        <v>5.4</v>
+        <v>3.62</v>
       </c>
       <c r="P202">
-        <v>9.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q202">
-        <v>1.54</v>
+        <v>2.44</v>
       </c>
       <c r="R202">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="S202">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T202">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U202">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="V202">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="W202">
+        <v>1.13</v>
+      </c>
+      <c r="X202">
+        <v>1.02</v>
+      </c>
+      <c r="Y202">
         <v>1.15</v>
       </c>
-      <c r="X202">
-        <v>1.01</v>
-      </c>
-      <c r="Y202">
-        <v>1.11</v>
-      </c>
       <c r="Z202">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA202">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AB202">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AC202">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AD202">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE202">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF202">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AG202">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AK202">
-        <v>3.81</v>
+        <v>1.61</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.02</v>
+        <v>1.28</v>
       </c>
       <c r="O204">
-        <v>3.62</v>
+        <v>5.4</v>
       </c>
       <c r="P204">
-        <v>3.35</v>
+        <v>9.6</v>
       </c>
       <c r="Q204">
-        <v>2.44</v>
+        <v>1.54</v>
       </c>
       <c r="R204">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="S204">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T204">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U204">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="V204">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W204">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X204">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y204">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z204">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA204">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AB204">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AC204">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AD204">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE204">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF204">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AG204">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AK204">
-        <v>1.61</v>
+        <v>3.81</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="O208">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P208">
+        <v>4.14</v>
+      </c>
+      <c r="Q208">
+        <v>0</v>
+      </c>
+      <c r="R208">
+        <v>0</v>
+      </c>
+      <c r="S208">
+        <v>0</v>
+      </c>
+      <c r="T208">
+        <v>0</v>
+      </c>
+      <c r="U208">
+        <v>0</v>
+      </c>
+      <c r="V208">
+        <v>0</v>
+      </c>
+      <c r="W208">
+        <v>0</v>
+      </c>
+      <c r="X208">
+        <v>0</v>
+      </c>
+      <c r="Y208">
+        <v>0</v>
+      </c>
+      <c r="Z208">
+        <v>0</v>
+      </c>
+      <c r="AA208">
+        <v>1.44</v>
+      </c>
+      <c r="AB208">
         <v>2.7</v>
       </c>
-      <c r="Q208">
-        <v>3</v>
-      </c>
-      <c r="R208">
-        <v>2.3</v>
-      </c>
-      <c r="S208">
-        <v>1.3</v>
-      </c>
-      <c r="T208">
-        <v>3.3</v>
-      </c>
-      <c r="U208">
-        <v>2.39</v>
-      </c>
-      <c r="V208">
-        <v>1.49</v>
-      </c>
-      <c r="W208">
-        <v>1.07</v>
-      </c>
-      <c r="X208">
-        <v>1.01</v>
-      </c>
-      <c r="Y208">
-        <v>1.17</v>
-      </c>
-      <c r="Z208">
-        <v>3.94</v>
-      </c>
-      <c r="AA208">
-        <v>1.7</v>
-      </c>
-      <c r="AB208">
-        <v>2.1</v>
-      </c>
       <c r="AC208">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD208">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE208">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF208">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG208">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK208">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.71</v>
+        <v>3.4</v>
       </c>
       <c r="O209">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P209">
-        <v>4.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34415,10 +34415,10 @@
         <v>0</v>
       </c>
       <c r="AA209">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AB209">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AC209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
+        <v>2.65</v>
+      </c>
+      <c r="O210">
         <v>3.4</v>
       </c>
-      <c r="O210">
-        <v>3.3</v>
-      </c>
       <c r="P210">
-        <v>2.02</v>
+        <v>2.33</v>
       </c>
       <c r="Q210">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R210">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S210">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T210">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U210">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V210">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W210">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X210">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y210">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z210">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA210">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AB210">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AC210">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD210">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE210">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF210">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG210">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK210">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,19 +34702,19 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="O211">
         <v>3.3</v>
       </c>
       <c r="P211">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="Q211">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="R211">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S211">
         <v>1.3</v>
@@ -34723,13 +34723,13 @@
         <v>3.3</v>
       </c>
       <c r="U211">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="V211">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W211">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X211">
         <v>1.01</v>
@@ -34738,22 +34738,22 @@
         <v>1.17</v>
       </c>
       <c r="Z211">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="AA211">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB211">
         <v>2.1</v>
       </c>
       <c r="AC211">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD211">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE211">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF211">
         <v>1.53</v>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
+        <v>1.25</v>
+      </c>
+      <c r="AK211">
         <v>1.44</v>
-      </c>
-      <c r="AK211">
-        <v>1.5</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="O213">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P213">
+        <v>2.89</v>
+      </c>
+      <c r="Q213">
+        <v>2.93</v>
+      </c>
+      <c r="R213">
+        <v>2.23</v>
+      </c>
+      <c r="S213">
+        <v>1.3</v>
+      </c>
+      <c r="T213">
+        <v>3.3</v>
+      </c>
+      <c r="U213">
         <v>2.42</v>
       </c>
-      <c r="Q213">
-        <v>3.4</v>
-      </c>
-      <c r="R213">
-        <v>2.2</v>
-      </c>
-      <c r="S213">
-        <v>1.37</v>
-      </c>
-      <c r="T213">
-        <v>2.76</v>
-      </c>
-      <c r="U213">
-        <v>2.56</v>
-      </c>
       <c r="V213">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W213">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X213">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z213">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="AA213">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB213">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC213">
-        <v>2.92</v>
+        <v>2.59</v>
       </c>
       <c r="AD213">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE213">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF213">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG213">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK213">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,80 +35191,80 @@
         </is>
       </c>
       <c r="N214">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O214">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P214">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="Q214">
         <v>3.1</v>
       </c>
       <c r="R214">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S214">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T214">
-        <v>3.48</v>
+        <v>3.08</v>
       </c>
       <c r="U214">
-        <v>2.19</v>
+        <v>2.53</v>
       </c>
       <c r="V214">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="W214">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X214">
         <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z214">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AA214">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB214">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="AC214">
-        <v>2.27</v>
+        <v>2.78</v>
       </c>
       <c r="AD214">
+        <v>1.39</v>
+      </c>
+      <c r="AE214">
+        <v>1.11</v>
+      </c>
+      <c r="AF214">
         <v>1.57</v>
       </c>
-      <c r="AE214">
-        <v>1.21</v>
-      </c>
-      <c r="AF214">
+      <c r="AG214">
+        <v>2.25</v>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ214">
+        <v>1.25</v>
+      </c>
+      <c r="AK214">
         <v>1.44</v>
-      </c>
-      <c r="AG214">
-        <v>2.6</v>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ214">
-        <v>1.24</v>
-      </c>
-      <c r="AK214">
-        <v>1.43</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O215">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P215">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="Q215">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R215">
         <v>2.2</v>
       </c>
       <c r="S215">
+        <v>1.37</v>
+      </c>
+      <c r="T215">
+        <v>2.76</v>
+      </c>
+      <c r="U215">
+        <v>2.56</v>
+      </c>
+      <c r="V215">
+        <v>1.43</v>
+      </c>
+      <c r="W215">
+        <v>1.07</v>
+      </c>
+      <c r="X215">
+        <v>1.03</v>
+      </c>
+      <c r="Y215">
+        <v>1.23</v>
+      </c>
+      <c r="Z215">
+        <v>3.42</v>
+      </c>
+      <c r="AA215">
+        <v>1.75</v>
+      </c>
+      <c r="AB215">
+        <v>1.95</v>
+      </c>
+      <c r="AC215">
+        <v>2.92</v>
+      </c>
+      <c r="AD215">
         <v>1.35</v>
       </c>
-      <c r="T215">
-        <v>3.08</v>
-      </c>
-      <c r="U215">
-        <v>2.53</v>
-      </c>
-      <c r="V215">
-        <v>1.47</v>
-      </c>
-      <c r="W215">
-        <v>1.06</v>
-      </c>
-      <c r="X215">
-        <v>1.02</v>
-      </c>
-      <c r="Y215">
-        <v>1.18</v>
-      </c>
-      <c r="Z215">
-        <v>3.85</v>
-      </c>
-      <c r="AA215">
-        <v>1.74</v>
-      </c>
-      <c r="AB215">
-        <v>2.02</v>
-      </c>
-      <c r="AC215">
-        <v>2.78</v>
-      </c>
-      <c r="AD215">
-        <v>1.39</v>
-      </c>
       <c r="AE215">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF215">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG215">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK215">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,64 +39592,64 @@
         </is>
       </c>
       <c r="N241">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="O241">
+        <v>3.5</v>
+      </c>
+      <c r="P241">
+        <v>2.68</v>
+      </c>
+      <c r="Q241">
+        <v>2.79</v>
+      </c>
+      <c r="R241">
+        <v>2.3</v>
+      </c>
+      <c r="S241">
+        <v>1.29</v>
+      </c>
+      <c r="T241">
         <v>3.4</v>
       </c>
-      <c r="P241">
-        <v>2.56</v>
-      </c>
-      <c r="Q241">
-        <v>2.88</v>
-      </c>
-      <c r="R241">
-        <v>2.2</v>
-      </c>
-      <c r="S241">
-        <v>1.36</v>
-      </c>
-      <c r="T241">
-        <v>3.08</v>
-      </c>
       <c r="U241">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="V241">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W241">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X241">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y241">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z241">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA241">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AB241">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC241">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AD241">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE241">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF241">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG241">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>1.28</v>
       </c>
       <c r="AK241">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G242">
@@ -39755,64 +39755,64 @@
         </is>
       </c>
       <c r="N242">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="O242">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P242">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q242">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="R242">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S242">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T242">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U242">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="V242">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W242">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X242">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y242">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z242">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA242">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AB242">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC242">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AD242">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE242">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AF242">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG242">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>1.28</v>
       </c>
       <c r="AK242">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O270">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P270">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="O277">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P277">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O294">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P294">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O307">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="P307">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q307">
         <v>0</v>
@@ -53121,13 +53121,13 @@
         </is>
       </c>
       <c r="N324">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O324">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P324">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q324">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>3.14</v>
+        <v>4.13</v>
       </c>
       <c r="Q7">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="R7">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="S7">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
-        <v>3.09</v>
+        <v>2.84</v>
       </c>
       <c r="U7">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z7">
-        <v>3.73</v>
+        <v>3.25</v>
       </c>
       <c r="AA7">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AB7">
+        <v>1.76</v>
+      </c>
+      <c r="AC7">
+        <v>3.48</v>
+      </c>
+      <c r="AD7">
+        <v>1.22</v>
+      </c>
+      <c r="AE7">
+        <v>1.04</v>
+      </c>
+      <c r="AF7">
         <v>1.85</v>
       </c>
-      <c r="AC7">
-        <v>2.92</v>
-      </c>
-      <c r="AD7">
-        <v>1.31</v>
-      </c>
-      <c r="AE7">
-        <v>1.13</v>
-      </c>
-      <c r="AF7">
-        <v>1.67</v>
-      </c>
       <c r="AG7">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P8">
-        <v>4.13</v>
+        <v>3.14</v>
       </c>
       <c r="Q8">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="R8">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
-        <v>2.84</v>
+        <v>3.09</v>
       </c>
       <c r="U8">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>3.25</v>
+        <v>3.73</v>
       </c>
       <c r="AA8">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AB8">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC8">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>7.05</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="R23">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="S23">
         <v>1.22</v>
@@ -4079,10 +4079,10 @@
         <v>3.56</v>
       </c>
       <c r="U23">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="V23">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W23">
         <v>1.13</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z23">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="AA23">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AB23">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AC23">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AD23">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE23">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF23">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>4.46</v>
+        <v>1.82</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="R24">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="V24">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AA24">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AB24">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="AD24">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
         <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AK24">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.32</v>
+        <v>1.46</v>
       </c>
       <c r="O25">
-        <v>3.65</v>
+        <v>4.51</v>
       </c>
       <c r="P25">
-        <v>2.12</v>
+        <v>7.05</v>
       </c>
       <c r="Q25">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="U25">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="V25">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="AA25">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AC25">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AE25">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF25">
-        <v>1.59</v>
+        <v>2.14</v>
       </c>
       <c r="AG25">
-        <v>2.21</v>
+        <v>1.63</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="AK25">
-        <v>1.36</v>
+        <v>4.46</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
+        <v>2.74</v>
+      </c>
+      <c r="O33">
+        <v>3.16</v>
+      </c>
+      <c r="P33">
+        <v>2.47</v>
+      </c>
+      <c r="Q33">
+        <v>3.22</v>
+      </c>
+      <c r="R33">
         <v>2.05</v>
       </c>
-      <c r="O33">
-        <v>3.25</v>
-      </c>
-      <c r="P33">
-        <v>3.53</v>
-      </c>
-      <c r="Q33">
-        <v>2.48</v>
-      </c>
-      <c r="R33">
-        <v>1.97</v>
-      </c>
       <c r="S33">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="U33">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="V33">
+        <v>1.34</v>
+      </c>
+      <c r="W33">
+        <v>1.08</v>
+      </c>
+      <c r="X33">
+        <v>1.02</v>
+      </c>
+      <c r="Y33">
         <v>1.3</v>
       </c>
-      <c r="W33">
-        <v>1.01</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.32</v>
-      </c>
       <c r="Z33">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA33">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB33">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AC33">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE33">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG33">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK33">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="O34">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>2.47</v>
+        <v>3.53</v>
       </c>
       <c r="Q34">
-        <v>3.22</v>
+        <v>2.48</v>
       </c>
       <c r="R34">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T34">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="U34">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="V34">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.32</v>
+      </c>
+      <c r="Z34">
+        <v>2.88</v>
+      </c>
+      <c r="AA34">
+        <v>2.15</v>
+      </c>
+      <c r="AB34">
+        <v>1.71</v>
+      </c>
+      <c r="AC34">
+        <v>3.74</v>
+      </c>
+      <c r="AD34">
+        <v>1.25</v>
+      </c>
+      <c r="AE34">
         <v>1.02</v>
       </c>
-      <c r="Y34">
-        <v>1.3</v>
-      </c>
-      <c r="Z34">
-        <v>2.97</v>
-      </c>
-      <c r="AA34">
-        <v>1.9</v>
-      </c>
-      <c r="AB34">
-        <v>1.86</v>
-      </c>
-      <c r="AC34">
-        <v>3.34</v>
-      </c>
-      <c r="AD34">
-        <v>1.24</v>
-      </c>
-      <c r="AE34">
-        <v>1.05</v>
-      </c>
       <c r="AF34">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AG34">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="O40">
-        <v>3.5</v>
+        <v>3.91</v>
       </c>
       <c r="P40">
-        <v>2.1</v>
+        <v>4.71</v>
       </c>
       <c r="Q40">
-        <v>3.25</v>
+        <v>2.17</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="U40">
         <v>2.5</v>
@@ -6856,37 +6856,37 @@
         <v>1.47</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA40">
         <v>1.78</v>
       </c>
       <c r="AB40">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC40">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD40">
         <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AG40">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK40">
-        <v>1.4</v>
+        <v>2.11</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,25 +6992,25 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="O41">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>4.71</v>
+        <v>2.1</v>
       </c>
       <c r="Q41">
-        <v>2.17</v>
+        <v>3.25</v>
       </c>
       <c r="R41">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="U41">
         <v>2.5</v>
@@ -7019,37 +7019,37 @@
         <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA41">
         <v>1.78</v>
       </c>
       <c r="AB41">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC41">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD41">
         <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AG41">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>2.11</v>
+        <v>1.4</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O56">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="P56">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="Q56">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="R56">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="S56">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="U56">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="V56">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="W56">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z56">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA56">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AB56">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="AC56">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AD56">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AE56">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AF56">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AG56">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.15</v>
       </c>
       <c r="AK56">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="O57">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
-        <v>4.14</v>
+        <v>3.43</v>
       </c>
       <c r="Q57">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="R57">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="S57">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="U57">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
       <c r="V57">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="W57">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>7.4</v>
+        <v>5.15</v>
       </c>
       <c r="AA57">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AB57">
-        <v>3.34</v>
+        <v>2.42</v>
       </c>
       <c r="AC57">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AD57">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AE57">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AF57">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AG57">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK57">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="O58">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="P58">
-        <v>3.43</v>
+        <v>4.08</v>
       </c>
       <c r="Q58">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="R58">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="S58">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T58">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U58">
+        <v>2.02</v>
+      </c>
+      <c r="V58">
+        <v>1.73</v>
+      </c>
+      <c r="W58">
+        <v>1.18</v>
+      </c>
+      <c r="X58">
+        <v>1.01</v>
+      </c>
+      <c r="Y58">
+        <v>1.09</v>
+      </c>
+      <c r="Z58">
+        <v>5.3</v>
+      </c>
+      <c r="AA58">
+        <v>1.39</v>
+      </c>
+      <c r="AB58">
+        <v>2.59</v>
+      </c>
+      <c r="AC58">
+        <v>2.08</v>
+      </c>
+      <c r="AD58">
+        <v>1.7</v>
+      </c>
+      <c r="AE58">
+        <v>1.26</v>
+      </c>
+      <c r="AF58">
+        <v>1.43</v>
+      </c>
+      <c r="AG58">
+        <v>2.63</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>1.15</v>
+      </c>
+      <c r="AK58">
         <v>2.11</v>
-      </c>
-      <c r="V58">
-        <v>1.61</v>
-      </c>
-      <c r="W58">
-        <v>1.12</v>
-      </c>
-      <c r="X58">
-        <v>1.02</v>
-      </c>
-      <c r="Y58">
-        <v>1.1</v>
-      </c>
-      <c r="Z58">
-        <v>5.15</v>
-      </c>
-      <c r="AA58">
-        <v>1.53</v>
-      </c>
-      <c r="AB58">
-        <v>2.42</v>
-      </c>
-      <c r="AC58">
-        <v>2.15</v>
-      </c>
-      <c r="AD58">
-        <v>1.62</v>
-      </c>
-      <c r="AE58">
-        <v>1.19</v>
-      </c>
-      <c r="AF58">
-        <v>1.44</v>
-      </c>
-      <c r="AG58">
-        <v>2.49</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.17</v>
-      </c>
-      <c r="AK58">
-        <v>1.99</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U62">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF62">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK62">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="O66">
-        <v>3.98</v>
+        <v>3.28</v>
       </c>
       <c r="P66">
-        <v>5.02</v>
+        <v>3.35</v>
       </c>
       <c r="Q66">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="R66">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S66">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="T66">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="U66">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="V66">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
         <v>1.04</v>
       </c>
       <c r="Y66">
+        <v>1.32</v>
+      </c>
+      <c r="Z66">
+        <v>2.88</v>
+      </c>
+      <c r="AA66">
+        <v>2.15</v>
+      </c>
+      <c r="AB66">
+        <v>1.65</v>
+      </c>
+      <c r="AC66">
+        <v>3.74</v>
+      </c>
+      <c r="AD66">
         <v>1.2</v>
       </c>
-      <c r="Z66">
-        <v>3.86</v>
-      </c>
-      <c r="AA66">
-        <v>1.72</v>
-      </c>
-      <c r="AB66">
-        <v>2.02</v>
-      </c>
-      <c r="AC66">
-        <v>2.74</v>
-      </c>
-      <c r="AD66">
-        <v>1.35</v>
-      </c>
       <c r="AE66">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF66">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG66">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="O67">
-        <v>3.28</v>
+        <v>3.98</v>
       </c>
       <c r="P67">
-        <v>3.35</v>
+        <v>5.02</v>
       </c>
       <c r="Q67">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="R67">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S67">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="T67">
-        <v>2.53</v>
+        <v>3.3</v>
       </c>
       <c r="U67">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="V67">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
         <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z67">
-        <v>2.88</v>
+        <v>3.86</v>
       </c>
       <c r="AA67">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AB67">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AC67">
-        <v>3.74</v>
+        <v>2.74</v>
       </c>
       <c r="AD67">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AE67">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF67">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK67">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,64 +24596,64 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.37</v>
+        <v>1.33</v>
       </c>
       <c r="O149">
-        <v>4.06</v>
+        <v>6.49</v>
       </c>
       <c r="P149">
-        <v>2.88</v>
+        <v>9.1</v>
       </c>
       <c r="Q149">
-        <v>2.54</v>
+        <v>1.73</v>
       </c>
       <c r="R149">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="S149">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T149">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="U149">
-        <v>2.41</v>
+        <v>1.86</v>
       </c>
       <c r="V149">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="W149">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="X149">
         <v>1.01</v>
       </c>
       <c r="Y149">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z149">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA149">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="AB149">
-        <v>2.35</v>
+        <v>3.75</v>
       </c>
       <c r="AC149">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD149">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AE149">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AF149">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG149">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AK149">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.33</v>
+        <v>2.37</v>
       </c>
       <c r="O152">
-        <v>6.49</v>
+        <v>4.06</v>
       </c>
       <c r="P152">
-        <v>9.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q152">
-        <v>1.73</v>
+        <v>2.54</v>
       </c>
       <c r="R152">
-        <v>2.9</v>
+        <v>2.49</v>
       </c>
       <c r="S152">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T152">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="U152">
-        <v>1.86</v>
+        <v>2.41</v>
       </c>
       <c r="V152">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="W152">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X152">
         <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z152">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA152">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AB152">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC152">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AD152">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AE152">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AF152">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG152">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AK152">
-        <v>2.8</v>
+        <v>1.61</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>3.1</v>
+        <v>1.31</v>
       </c>
       <c r="O163">
-        <v>3.24</v>
+        <v>4.5</v>
       </c>
       <c r="P163">
-        <v>2.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q163">
-        <v>3.75</v>
+        <v>1.75</v>
       </c>
       <c r="R163">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S163">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="T163">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="U163">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="V163">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W163">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X163">
         <v>1.03</v>
       </c>
       <c r="Y163">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z163">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA163">
+        <v>1.79</v>
+      </c>
+      <c r="AB163">
+        <v>1.97</v>
+      </c>
+      <c r="AC163">
+        <v>2.75</v>
+      </c>
+      <c r="AD163">
+        <v>1.4</v>
+      </c>
+      <c r="AE163">
+        <v>1.13</v>
+      </c>
+      <c r="AF163">
         <v>1.95</v>
       </c>
-      <c r="AB163">
-        <v>1.78</v>
-      </c>
-      <c r="AC163">
-        <v>3.3</v>
-      </c>
-      <c r="AD163">
-        <v>1.29</v>
-      </c>
-      <c r="AE163">
-        <v>1.06</v>
-      </c>
-      <c r="AF163">
-        <v>1.73</v>
-      </c>
       <c r="AG163">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK163">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.31</v>
+        <v>2.35</v>
       </c>
       <c r="O164">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="P164">
-        <v>8.300000000000001</v>
+        <v>2.73</v>
       </c>
       <c r="Q164">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="R164">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S164">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T164">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="U164">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="V164">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W164">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X164">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y164">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z164">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="AA164">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="AB164">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AC164">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD164">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE164">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF164">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG164">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK164">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,31 +27204,31 @@
         </is>
       </c>
       <c r="N165">
-        <v>5.06</v>
+        <v>3.1</v>
       </c>
       <c r="O165">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="P165">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Q165">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="R165">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S165">
+        <v>1.39</v>
+      </c>
+      <c r="T165">
+        <v>2.69</v>
+      </c>
+      <c r="U165">
+        <v>2.62</v>
+      </c>
+      <c r="V165">
         <v>1.41</v>
-      </c>
-      <c r="T165">
-        <v>2.62</v>
-      </c>
-      <c r="U165">
-        <v>2.7</v>
-      </c>
-      <c r="V165">
-        <v>1.39</v>
       </c>
       <c r="W165">
         <v>1.06</v>
@@ -27243,25 +27243,25 @@
         <v>3.3</v>
       </c>
       <c r="AA165">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB165">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC165">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD165">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE165">
         <v>1.06</v>
       </c>
       <c r="AF165">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AG165">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK165">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.35</v>
+        <v>5.06</v>
       </c>
       <c r="O167">
-        <v>3.06</v>
+        <v>3.7</v>
       </c>
       <c r="P167">
-        <v>2.73</v>
+        <v>1.65</v>
       </c>
       <c r="Q167">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="R167">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S167">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T167">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U167">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="V167">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W167">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X167">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y167">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z167">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA167">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AB167">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AC167">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD167">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE167">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF167">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG167">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK167">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,19 +28997,19 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="O176">
-        <v>3.82</v>
+        <v>3.65</v>
       </c>
       <c r="P176">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q176">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="R176">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S176">
         <v>1.3</v>
@@ -29018,10 +29018,10 @@
         <v>3.12</v>
       </c>
       <c r="U176">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V176">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W176">
         <v>1.07</v>
@@ -29033,28 +29033,28 @@
         <v>1.18</v>
       </c>
       <c r="Z176">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="AA176">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB176">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC176">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AD176">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE176">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF176">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG176">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>1.22</v>
       </c>
       <c r="AK176">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,19 +29160,19 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="O177">
-        <v>3.65</v>
+        <v>3.82</v>
       </c>
       <c r="P177">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="Q177">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="R177">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S177">
         <v>1.3</v>
@@ -29181,10 +29181,10 @@
         <v>3.12</v>
       </c>
       <c r="U177">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V177">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W177">
         <v>1.07</v>
@@ -29196,28 +29196,28 @@
         <v>1.18</v>
       </c>
       <c r="Z177">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="AA177">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB177">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC177">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AD177">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE177">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF177">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG177">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>1.22</v>
       </c>
       <c r="AK177">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O192">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P192">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="Q192">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="R192">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="S192">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="T192">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U192">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="V192">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W192">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X192">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y192">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="Z192">
-        <v>4.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA192">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB192">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AC192">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="AD192">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AE192">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF192">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG192">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK192">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.37</v>
+        <v>3.41</v>
       </c>
       <c r="O193">
-        <v>4.85</v>
+        <v>3.42</v>
       </c>
       <c r="P193">
-        <v>7.39</v>
+        <v>2.07</v>
       </c>
       <c r="Q193">
-        <v>1.83</v>
+        <v>3.59</v>
       </c>
       <c r="R193">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="S193">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T193">
-        <v>3.75</v>
+        <v>2.97</v>
       </c>
       <c r="U193">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="V193">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="W193">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X193">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="Z193">
-        <v>4.75</v>
+        <v>3.71</v>
       </c>
       <c r="AA193">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AB193">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="AC193">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="AD193">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AE193">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF193">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG193">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK193">
-        <v>2.88</v>
+        <v>1.2</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,61 +31931,61 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O194">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P194">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="Q194">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R194">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="S194">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T194">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U194">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="V194">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W194">
         <v>1.06</v>
       </c>
       <c r="X194">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y194">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z194">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA194">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB194">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC194">
-        <v>3.33</v>
+        <v>3.16</v>
       </c>
       <c r="AD194">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE194">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF194">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG194">
         <v>2.05</v>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AK194">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="O195">
         <v>3.3</v>
       </c>
       <c r="P195">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q195">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="R195">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S195">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="T195">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U195">
-        <v>2.77</v>
+        <v>2.27</v>
       </c>
       <c r="V195">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W195">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X195">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y195">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="Z195">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA195">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB195">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC195">
-        <v>3.16</v>
+        <v>2.35</v>
       </c>
       <c r="AD195">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AE195">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF195">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AG195">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK195">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>3.41</v>
+        <v>1.37</v>
       </c>
       <c r="O196">
-        <v>3.42</v>
+        <v>4.85</v>
       </c>
       <c r="P196">
-        <v>2.07</v>
+        <v>7.39</v>
       </c>
       <c r="Q196">
-        <v>3.59</v>
+        <v>1.83</v>
       </c>
       <c r="R196">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="S196">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T196">
-        <v>2.97</v>
+        <v>3.75</v>
       </c>
       <c r="U196">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="V196">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="W196">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X196">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="Z196">
-        <v>3.71</v>
+        <v>4.75</v>
       </c>
       <c r="AA196">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AB196">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="AC196">
-        <v>2.93</v>
+        <v>2.3</v>
       </c>
       <c r="AD196">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AE196">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AF196">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG196">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK196">
-        <v>1.2</v>
+        <v>2.88</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="O197">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="P197">
-        <v>2.22</v>
+        <v>2.81</v>
       </c>
       <c r="Q197">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="R197">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S197">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T197">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U197">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="V197">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W197">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X197">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z197">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA197">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AB197">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC197">
-        <v>2.97</v>
+        <v>3.33</v>
       </c>
       <c r="AD197">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE197">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF197">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG197">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AK197">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,80 +34539,80 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="O210">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P210">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q210">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R210">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S210">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T210">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="U210">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="V210">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="W210">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X210">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z210">
-        <v>4.75</v>
+        <v>3.94</v>
       </c>
       <c r="AA210">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB210">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC210">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="AD210">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AE210">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF210">
+        <v>1.53</v>
+      </c>
+      <c r="AG210">
+        <v>2.3</v>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ210">
+        <v>1.25</v>
+      </c>
+      <c r="AK210">
         <v>1.44</v>
-      </c>
-      <c r="AG210">
-        <v>2.6</v>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ210">
-        <v>1.24</v>
-      </c>
-      <c r="AK210">
-        <v>1.43</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="O211">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P211">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="Q211">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R211">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S211">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T211">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="U211">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="V211">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W211">
         <v>1.07</v>
       </c>
       <c r="X211">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y211">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z211">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="AA211">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB211">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC211">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AD211">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE211">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF211">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG211">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK211">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="O212">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P212">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
       </c>
       <c r="R212">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S212">
+        <v>1.35</v>
+      </c>
+      <c r="T212">
+        <v>3.08</v>
+      </c>
+      <c r="U212">
+        <v>2.53</v>
+      </c>
+      <c r="V212">
+        <v>1.47</v>
+      </c>
+      <c r="W212">
+        <v>1.06</v>
+      </c>
+      <c r="X212">
+        <v>1.02</v>
+      </c>
+      <c r="Y212">
+        <v>1.18</v>
+      </c>
+      <c r="Z212">
+        <v>3.85</v>
+      </c>
+      <c r="AA212">
+        <v>1.74</v>
+      </c>
+      <c r="AB212">
+        <v>2.02</v>
+      </c>
+      <c r="AC212">
+        <v>2.78</v>
+      </c>
+      <c r="AD212">
         <v>1.39</v>
       </c>
-      <c r="T212">
-        <v>2.68</v>
-      </c>
-      <c r="U212">
-        <v>2.63</v>
-      </c>
-      <c r="V212">
-        <v>1.41</v>
-      </c>
-      <c r="W212">
-        <v>1.07</v>
-      </c>
-      <c r="X212">
-        <v>1.01</v>
-      </c>
-      <c r="Y212">
-        <v>1.24</v>
-      </c>
-      <c r="Z212">
-        <v>3.34</v>
-      </c>
-      <c r="AA212">
-        <v>1.98</v>
-      </c>
-      <c r="AB212">
-        <v>1.88</v>
-      </c>
-      <c r="AC212">
-        <v>3.2</v>
-      </c>
-      <c r="AD212">
-        <v>1.26</v>
-      </c>
       <c r="AE212">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF212">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AG212">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.26</v>
+        <v>2.57</v>
       </c>
       <c r="O213">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="P213">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="Q213">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="R213">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S213">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T213">
-        <v>3.3</v>
+        <v>2.68</v>
       </c>
       <c r="U213">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="V213">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W213">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X213">
         <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z213">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="AA213">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AB213">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AC213">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="AD213">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE213">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF213">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG213">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
+        <v>1.25</v>
+      </c>
+      <c r="AK213">
         <v>1.44</v>
-      </c>
-      <c r="AK213">
-        <v>1.5</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O214">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P214">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="Q214">
         <v>3.1</v>
       </c>
       <c r="R214">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S214">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T214">
-        <v>3.08</v>
+        <v>3.48</v>
       </c>
       <c r="U214">
-        <v>2.53</v>
+        <v>2.19</v>
       </c>
       <c r="V214">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="W214">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X214">
         <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z214">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AA214">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AB214">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AC214">
-        <v>2.78</v>
+        <v>2.27</v>
       </c>
       <c r="AD214">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AE214">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF214">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG214">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK214">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="O215">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P215">
+        <v>2.89</v>
+      </c>
+      <c r="Q215">
+        <v>2.93</v>
+      </c>
+      <c r="R215">
+        <v>2.23</v>
+      </c>
+      <c r="S215">
+        <v>1.3</v>
+      </c>
+      <c r="T215">
+        <v>3.3</v>
+      </c>
+      <c r="U215">
         <v>2.42</v>
       </c>
-      <c r="Q215">
-        <v>3.4</v>
-      </c>
-      <c r="R215">
-        <v>2.2</v>
-      </c>
-      <c r="S215">
-        <v>1.37</v>
-      </c>
-      <c r="T215">
-        <v>2.76</v>
-      </c>
-      <c r="U215">
-        <v>2.56</v>
-      </c>
       <c r="V215">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W215">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X215">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y215">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z215">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="AA215">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB215">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC215">
-        <v>2.92</v>
+        <v>2.59</v>
       </c>
       <c r="AD215">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE215">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF215">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG215">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK215">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="O275">
         <v>4</v>
       </c>
       <c r="P275">
-        <v>2.4</v>
+        <v>3.79</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45179,10 +45179,10 @@
         <v>0</v>
       </c>
       <c r="AC275">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD275">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="O276">
         <v>4</v>
       </c>
       <c r="P276">
-        <v>3.79</v>
+        <v>2.4</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45342,10 +45342,10 @@
         <v>0</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE276">
         <v>0</v>
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G372">
@@ -60945,13 +60945,13 @@
         </is>
       </c>
       <c r="N372">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O372">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P372">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q372">
         <v>0</v>
@@ -60984,10 +60984,10 @@
         <v>0</v>
       </c>
       <c r="AA372">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB372">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC372">
         <v>0</v>
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G373">
@@ -61108,13 +61108,13 @@
         </is>
       </c>
       <c r="N373">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="O373">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P373">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q373">
         <v>0</v>
@@ -61147,10 +61147,10 @@
         <v>0</v>
       </c>
       <c r="AA373">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB373">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC373">
         <v>0</v>
@@ -62054,12 +62054,12 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G379">
@@ -62086,13 +62086,13 @@
         </is>
       </c>
       <c r="N379">
-        <v>1.75</v>
+        <v>2.83</v>
       </c>
       <c r="O379">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P379">
-        <v>3.9</v>
+        <v>2.36</v>
       </c>
       <c r="Q379">
         <v>0</v>
@@ -62125,10 +62125,10 @@
         <v>0</v>
       </c>
       <c r="AA379">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AB379">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AC379">
         <v>0</v>
@@ -62217,12 +62217,12 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G380">
@@ -62249,13 +62249,13 @@
         </is>
       </c>
       <c r="N380">
-        <v>2.83</v>
+        <v>1.75</v>
       </c>
       <c r="O380">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="P380">
-        <v>2.36</v>
+        <v>3.9</v>
       </c>
       <c r="Q380">
         <v>0</v>
@@ -62288,10 +62288,10 @@
         <v>0</v>
       </c>
       <c r="AA380">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AB380">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AC380">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.31</v>
+        <v>1.85</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>2.11</v>
+        <v>4.13</v>
       </c>
       <c r="Q6">
-        <v>4.07</v>
+        <v>2.42</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="U6">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
+        <v>3.25</v>
+      </c>
+      <c r="AA6">
+        <v>2.06</v>
+      </c>
+      <c r="AB6">
+        <v>1.76</v>
+      </c>
+      <c r="AC6">
         <v>3.48</v>
       </c>
-      <c r="AA6">
-        <v>1.84</v>
-      </c>
-      <c r="AB6">
-        <v>1.98</v>
-      </c>
-      <c r="AC6">
-        <v>3.03</v>
-      </c>
       <c r="AD6">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.21</v>
+        <v>1.91</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P7">
-        <v>4.13</v>
+        <v>3.14</v>
       </c>
       <c r="Q7">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="R7">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="S7">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T7">
-        <v>2.84</v>
+        <v>3.09</v>
       </c>
       <c r="U7">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z7">
-        <v>3.25</v>
+        <v>3.73</v>
       </c>
       <c r="AA7">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AB7">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="AD7">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE7">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.18</v>
+        <v>3.31</v>
       </c>
       <c r="O8">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>3.14</v>
+        <v>2.11</v>
       </c>
       <c r="Q8">
-        <v>2.75</v>
+        <v>4.07</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W8">
         <v>1.07</v>
@@ -1649,22 +1649,22 @@
         <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>3.73</v>
+        <v>3.48</v>
       </c>
       <c r="AA8">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AB8">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC8">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="AD8">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
         <v>1.67</v>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q23">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="R23">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="V23">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AA23">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AB23">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AC23">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="AD23">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
         <v>1.15</v>
       </c>
       <c r="AF23">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AK23">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.32</v>
+        <v>2.92</v>
       </c>
       <c r="O24">
-        <v>3.65</v>
+        <v>3.94</v>
       </c>
       <c r="P24">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q24">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U24">
-        <v>2.55</v>
+        <v>1.94</v>
       </c>
       <c r="V24">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
+        <v>1.1</v>
+      </c>
+      <c r="Z24">
+        <v>6.26</v>
+      </c>
+      <c r="AA24">
+        <v>1.32</v>
+      </c>
+      <c r="AB24">
+        <v>3</v>
+      </c>
+      <c r="AC24">
+        <v>1.96</v>
+      </c>
+      <c r="AD24">
+        <v>1.8</v>
+      </c>
+      <c r="AE24">
+        <v>1.33</v>
+      </c>
+      <c r="AF24">
+        <v>1.35</v>
+      </c>
+      <c r="AG24">
+        <v>3</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.22</v>
       </c>
-      <c r="Z24">
-        <v>4</v>
-      </c>
-      <c r="AA24">
-        <v>1.73</v>
-      </c>
-      <c r="AB24">
-        <v>2.05</v>
-      </c>
-      <c r="AC24">
-        <v>2.77</v>
-      </c>
-      <c r="AD24">
-        <v>1.36</v>
-      </c>
-      <c r="AE24">
-        <v>1.15</v>
-      </c>
-      <c r="AF24">
-        <v>1.59</v>
-      </c>
-      <c r="AG24">
-        <v>2.21</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.6</v>
-      </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>7.05</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="R25">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="S25">
         <v>1.22</v>
@@ -4405,10 +4405,10 @@
         <v>3.56</v>
       </c>
       <c r="U25">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="V25">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
         <v>1.13</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="AA25">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AB25">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AC25">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AD25">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE25">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>4.46</v>
+        <v>1.82</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.92</v>
+        <v>1.46</v>
       </c>
       <c r="O27">
-        <v>3.94</v>
+        <v>4.51</v>
       </c>
       <c r="P27">
-        <v>2.22</v>
+        <v>7.05</v>
       </c>
       <c r="Q27">
-        <v>3.4</v>
+        <v>1.57</v>
       </c>
       <c r="R27">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="S27">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="U27">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="V27">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="W27">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z27">
-        <v>6.26</v>
+        <v>4.65</v>
       </c>
       <c r="AA27">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="AC27">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AD27">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="AE27">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AF27">
-        <v>1.35</v>
+        <v>2.14</v>
       </c>
       <c r="AG27">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK27">
-        <v>1.32</v>
+        <v>4.46</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.47</v>
+        <v>3.53</v>
       </c>
       <c r="Q33">
-        <v>3.22</v>
+        <v>2.48</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T33">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="V33">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.32</v>
+      </c>
+      <c r="Z33">
+        <v>2.88</v>
+      </c>
+      <c r="AA33">
+        <v>2.15</v>
+      </c>
+      <c r="AB33">
+        <v>1.71</v>
+      </c>
+      <c r="AC33">
+        <v>3.74</v>
+      </c>
+      <c r="AD33">
+        <v>1.25</v>
+      </c>
+      <c r="AE33">
         <v>1.02</v>
       </c>
-      <c r="Y33">
-        <v>1.3</v>
-      </c>
-      <c r="Z33">
-        <v>2.97</v>
-      </c>
-      <c r="AA33">
-        <v>1.9</v>
-      </c>
-      <c r="AB33">
-        <v>1.86</v>
-      </c>
-      <c r="AC33">
-        <v>3.34</v>
-      </c>
-      <c r="AD33">
-        <v>1.24</v>
-      </c>
-      <c r="AE33">
-        <v>1.05</v>
-      </c>
       <c r="AF33">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AG33">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
+        <v>2.74</v>
+      </c>
+      <c r="O34">
+        <v>3.16</v>
+      </c>
+      <c r="P34">
+        <v>2.47</v>
+      </c>
+      <c r="Q34">
+        <v>3.22</v>
+      </c>
+      <c r="R34">
         <v>2.05</v>
       </c>
-      <c r="O34">
-        <v>3.25</v>
-      </c>
-      <c r="P34">
-        <v>3.53</v>
-      </c>
-      <c r="Q34">
-        <v>2.48</v>
-      </c>
-      <c r="R34">
-        <v>1.97</v>
-      </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="U34">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="V34">
+        <v>1.34</v>
+      </c>
+      <c r="W34">
+        <v>1.08</v>
+      </c>
+      <c r="X34">
+        <v>1.02</v>
+      </c>
+      <c r="Y34">
         <v>1.3</v>
       </c>
-      <c r="W34">
-        <v>1.01</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.32</v>
-      </c>
       <c r="Z34">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA34">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AC34">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE34">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF34">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG34">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="O66">
-        <v>3.28</v>
+        <v>3.98</v>
       </c>
       <c r="P66">
-        <v>3.35</v>
+        <v>5.02</v>
       </c>
       <c r="Q66">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="R66">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="T66">
-        <v>2.53</v>
+        <v>3.3</v>
       </c>
       <c r="U66">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="V66">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W66">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
         <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z66">
-        <v>2.88</v>
+        <v>3.86</v>
       </c>
       <c r="AA66">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AB66">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AC66">
-        <v>3.74</v>
+        <v>2.74</v>
       </c>
       <c r="AD66">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AE66">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF66">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK66">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="O67">
-        <v>3.98</v>
+        <v>3.28</v>
       </c>
       <c r="P67">
-        <v>5.02</v>
+        <v>3.35</v>
       </c>
       <c r="Q67">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="R67">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S67">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="T67">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="U67">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="V67">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
         <v>1.04</v>
       </c>
       <c r="Y67">
+        <v>1.32</v>
+      </c>
+      <c r="Z67">
+        <v>2.88</v>
+      </c>
+      <c r="AA67">
+        <v>2.15</v>
+      </c>
+      <c r="AB67">
+        <v>1.65</v>
+      </c>
+      <c r="AC67">
+        <v>3.74</v>
+      </c>
+      <c r="AD67">
         <v>1.2</v>
       </c>
-      <c r="Z67">
-        <v>3.86</v>
-      </c>
-      <c r="AA67">
-        <v>1.72</v>
-      </c>
-      <c r="AB67">
-        <v>2.02</v>
-      </c>
-      <c r="AC67">
-        <v>2.74</v>
-      </c>
-      <c r="AD67">
-        <v>1.35</v>
-      </c>
       <c r="AE67">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF67">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG67">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G74">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,61 +24759,61 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="O150">
-        <v>4.36</v>
+        <v>4.06</v>
       </c>
       <c r="P150">
-        <v>4.36</v>
+        <v>2.88</v>
       </c>
       <c r="Q150">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="R150">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="S150">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T150">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U150">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="V150">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="W150">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X150">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y150">
         <v>1.13</v>
       </c>
       <c r="Z150">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA150">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AB150">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AC150">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD150">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE150">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF150">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG150">
         <v>2.5</v>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK150">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,61 +25085,61 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="O152">
-        <v>4.06</v>
+        <v>4.36</v>
       </c>
       <c r="P152">
-        <v>2.88</v>
+        <v>4.36</v>
       </c>
       <c r="Q152">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="R152">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="S152">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T152">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U152">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="V152">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W152">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X152">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y152">
         <v>1.13</v>
       </c>
       <c r="Z152">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA152">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AB152">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AC152">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD152">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE152">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF152">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AG152">
         <v>2.5</v>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK152">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.31</v>
+        <v>2.35</v>
       </c>
       <c r="O163">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="P163">
-        <v>8.300000000000001</v>
+        <v>2.73</v>
       </c>
       <c r="Q163">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="R163">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S163">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T163">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="U163">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="V163">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W163">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X163">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y163">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z163">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="AA163">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="AB163">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AC163">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD163">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE163">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF163">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG163">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK163">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O164">
-        <v>3.06</v>
+        <v>3.24</v>
       </c>
       <c r="P164">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="Q164">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="R164">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S164">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T164">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="U164">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="V164">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W164">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X164">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y164">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z164">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA164">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB164">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC164">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD164">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE164">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF164">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG164">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>1.3</v>
       </c>
       <c r="AK164">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,31 +27204,31 @@
         </is>
       </c>
       <c r="N165">
-        <v>3.1</v>
+        <v>5.06</v>
       </c>
       <c r="O165">
-        <v>3.24</v>
+        <v>3.7</v>
       </c>
       <c r="P165">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Q165">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="R165">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S165">
+        <v>1.41</v>
+      </c>
+      <c r="T165">
+        <v>2.62</v>
+      </c>
+      <c r="U165">
+        <v>2.7</v>
+      </c>
+      <c r="V165">
         <v>1.39</v>
-      </c>
-      <c r="T165">
-        <v>2.69</v>
-      </c>
-      <c r="U165">
-        <v>2.62</v>
-      </c>
-      <c r="V165">
-        <v>1.41</v>
       </c>
       <c r="W165">
         <v>1.06</v>
@@ -27243,25 +27243,25 @@
         <v>3.3</v>
       </c>
       <c r="AA165">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB165">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC165">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD165">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE165">
         <v>1.06</v>
       </c>
       <c r="AF165">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AG165">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK165">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="O166">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P166">
-        <v>7.27</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q166">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="R166">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S166">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T166">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U166">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="V166">
+        <v>1.51</v>
+      </c>
+      <c r="W166">
+        <v>1.11</v>
+      </c>
+      <c r="X166">
+        <v>1.03</v>
+      </c>
+      <c r="Y166">
+        <v>1.18</v>
+      </c>
+      <c r="Z166">
+        <v>4.33</v>
+      </c>
+      <c r="AA166">
+        <v>1.79</v>
+      </c>
+      <c r="AB166">
+        <v>1.97</v>
+      </c>
+      <c r="AC166">
+        <v>2.75</v>
+      </c>
+      <c r="AD166">
         <v>1.4</v>
       </c>
-      <c r="W166">
-        <v>1.06</v>
-      </c>
-      <c r="X166">
-        <v>1.02</v>
-      </c>
-      <c r="Y166">
-        <v>1.25</v>
-      </c>
-      <c r="Z166">
-        <v>3.6</v>
-      </c>
-      <c r="AA166">
-        <v>1.8</v>
-      </c>
-      <c r="AB166">
-        <v>1.87</v>
-      </c>
-      <c r="AC166">
-        <v>3.13</v>
-      </c>
-      <c r="AD166">
-        <v>1.3</v>
-      </c>
       <c r="AE166">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF166">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG166">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK166">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>5.06</v>
+        <v>1.44</v>
       </c>
       <c r="O167">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P167">
-        <v>1.65</v>
+        <v>7.27</v>
       </c>
       <c r="Q167">
-        <v>5.75</v>
+        <v>1.91</v>
       </c>
       <c r="R167">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S167">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T167">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="U167">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="V167">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W167">
         <v>1.06</v>
       </c>
       <c r="X167">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y167">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z167">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA167">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB167">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AC167">
-        <v>3.6</v>
+        <v>3.13</v>
       </c>
       <c r="AD167">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE167">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF167">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG167">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK167">
-        <v>1.15</v>
+        <v>2.7</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
+        <v>1.37</v>
+      </c>
+      <c r="O194">
+        <v>4.85</v>
+      </c>
+      <c r="P194">
+        <v>7.39</v>
+      </c>
+      <c r="Q194">
+        <v>1.83</v>
+      </c>
+      <c r="R194">
+        <v>2.55</v>
+      </c>
+      <c r="S194">
+        <v>1.25</v>
+      </c>
+      <c r="T194">
+        <v>3.75</v>
+      </c>
+      <c r="U194">
+        <v>2.21</v>
+      </c>
+      <c r="V194">
+        <v>1.6</v>
+      </c>
+      <c r="W194">
+        <v>1.12</v>
+      </c>
+      <c r="X194">
+        <v>1.03</v>
+      </c>
+      <c r="Y194">
+        <v>1.12</v>
+      </c>
+      <c r="Z194">
+        <v>4.75</v>
+      </c>
+      <c r="AA194">
+        <v>1.55</v>
+      </c>
+      <c r="AB194">
         <v>2.37</v>
       </c>
-      <c r="O194">
-        <v>3.3</v>
-      </c>
-      <c r="P194">
-        <v>2.9</v>
-      </c>
-      <c r="Q194">
-        <v>2.9</v>
-      </c>
-      <c r="R194">
-        <v>2.28</v>
-      </c>
-      <c r="S194">
-        <v>1.35</v>
-      </c>
-      <c r="T194">
-        <v>3.1</v>
-      </c>
-      <c r="U194">
-        <v>2.77</v>
-      </c>
-      <c r="V194">
-        <v>1.42</v>
-      </c>
-      <c r="W194">
-        <v>1.06</v>
-      </c>
-      <c r="X194">
-        <v>1</v>
-      </c>
-      <c r="Y194">
-        <v>1.29</v>
-      </c>
-      <c r="Z194">
-        <v>3.2</v>
-      </c>
-      <c r="AA194">
-        <v>1.85</v>
-      </c>
-      <c r="AB194">
-        <v>1.85</v>
-      </c>
       <c r="AC194">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="AD194">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AE194">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF194">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG194">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK194">
-        <v>1.53</v>
+        <v>2.88</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="O195">
         <v>3.3</v>
       </c>
       <c r="P195">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="Q195">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="R195">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S195">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="T195">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U195">
-        <v>2.27</v>
+        <v>2.77</v>
       </c>
       <c r="V195">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W195">
+        <v>1.06</v>
+      </c>
+      <c r="X195">
+        <v>1</v>
+      </c>
+      <c r="Y195">
+        <v>1.29</v>
+      </c>
+      <c r="Z195">
+        <v>3.2</v>
+      </c>
+      <c r="AA195">
+        <v>1.85</v>
+      </c>
+      <c r="AB195">
+        <v>1.85</v>
+      </c>
+      <c r="AC195">
+        <v>3.16</v>
+      </c>
+      <c r="AD195">
+        <v>1.33</v>
+      </c>
+      <c r="AE195">
         <v>1.13</v>
       </c>
-      <c r="X195">
-        <v>1.02</v>
-      </c>
-      <c r="Y195">
-        <v>1.11</v>
-      </c>
-      <c r="Z195">
-        <v>4.8</v>
-      </c>
-      <c r="AA195">
-        <v>1.83</v>
-      </c>
-      <c r="AB195">
-        <v>1.91</v>
-      </c>
-      <c r="AC195">
-        <v>2.35</v>
-      </c>
-      <c r="AD195">
-        <v>1.55</v>
-      </c>
-      <c r="AE195">
-        <v>1.17</v>
-      </c>
       <c r="AF195">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AG195">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK195">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.37</v>
+        <v>2.4</v>
       </c>
       <c r="O196">
-        <v>4.85</v>
+        <v>3.36</v>
       </c>
       <c r="P196">
-        <v>7.39</v>
+        <v>2.81</v>
       </c>
       <c r="Q196">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="R196">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="S196">
+        <v>1.39</v>
+      </c>
+      <c r="T196">
+        <v>2.99</v>
+      </c>
+      <c r="U196">
+        <v>2.61</v>
+      </c>
+      <c r="V196">
+        <v>1.4</v>
+      </c>
+      <c r="W196">
+        <v>1.06</v>
+      </c>
+      <c r="X196">
+        <v>1.02</v>
+      </c>
+      <c r="Y196">
         <v>1.25</v>
       </c>
-      <c r="T196">
-        <v>3.75</v>
-      </c>
-      <c r="U196">
-        <v>2.21</v>
-      </c>
-      <c r="V196">
-        <v>1.6</v>
-      </c>
-      <c r="W196">
-        <v>1.12</v>
-      </c>
-      <c r="X196">
-        <v>1.03</v>
-      </c>
-      <c r="Y196">
-        <v>1.12</v>
-      </c>
       <c r="Z196">
-        <v>4.75</v>
+        <v>3.28</v>
       </c>
       <c r="AA196">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AB196">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="AC196">
-        <v>2.3</v>
+        <v>3.33</v>
       </c>
       <c r="AD196">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AE196">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF196">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG196">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AK196">
-        <v>2.88</v>
+        <v>1.47</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="O197">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="P197">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="Q197">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="R197">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="S197">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T197">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="U197">
-        <v>2.61</v>
+        <v>2.87</v>
       </c>
       <c r="V197">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W197">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X197">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y197">
+        <v>1.31</v>
+      </c>
+      <c r="Z197">
+        <v>2.92</v>
+      </c>
+      <c r="AA197">
+        <v>2.11</v>
+      </c>
+      <c r="AB197">
+        <v>1.73</v>
+      </c>
+      <c r="AC197">
+        <v>3.45</v>
+      </c>
+      <c r="AD197">
         <v>1.25</v>
       </c>
-      <c r="Z197">
-        <v>3.28</v>
-      </c>
-      <c r="AA197">
-        <v>1.88</v>
-      </c>
-      <c r="AB197">
-        <v>1.92</v>
-      </c>
-      <c r="AC197">
-        <v>3.33</v>
-      </c>
-      <c r="AD197">
-        <v>1.27</v>
-      </c>
       <c r="AE197">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF197">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG197">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AK197">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,80 +32583,80 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="O198">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P198">
-        <v>2.69</v>
+        <v>2.37</v>
       </c>
       <c r="Q198">
-        <v>3.06</v>
+        <v>2.73</v>
       </c>
       <c r="R198">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="S198">
+        <v>1.24</v>
+      </c>
+      <c r="T198">
+        <v>3.4</v>
+      </c>
+      <c r="U198">
+        <v>2.27</v>
+      </c>
+      <c r="V198">
+        <v>1.57</v>
+      </c>
+      <c r="W198">
+        <v>1.13</v>
+      </c>
+      <c r="X198">
+        <v>1.02</v>
+      </c>
+      <c r="Y198">
+        <v>1.11</v>
+      </c>
+      <c r="Z198">
+        <v>4.8</v>
+      </c>
+      <c r="AA198">
+        <v>1.83</v>
+      </c>
+      <c r="AB198">
+        <v>1.91</v>
+      </c>
+      <c r="AC198">
+        <v>2.35</v>
+      </c>
+      <c r="AD198">
+        <v>1.55</v>
+      </c>
+      <c r="AE198">
+        <v>1.17</v>
+      </c>
+      <c r="AF198">
+        <v>1.44</v>
+      </c>
+      <c r="AG198">
+        <v>2.6</v>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ198">
+        <v>1.23</v>
+      </c>
+      <c r="AK198">
         <v>1.45</v>
-      </c>
-      <c r="T198">
-        <v>2.5</v>
-      </c>
-      <c r="U198">
-        <v>2.87</v>
-      </c>
-      <c r="V198">
-        <v>1.35</v>
-      </c>
-      <c r="W198">
-        <v>1.04</v>
-      </c>
-      <c r="X198">
-        <v>1.01</v>
-      </c>
-      <c r="Y198">
-        <v>1.31</v>
-      </c>
-      <c r="Z198">
-        <v>2.92</v>
-      </c>
-      <c r="AA198">
-        <v>2.11</v>
-      </c>
-      <c r="AB198">
-        <v>1.73</v>
-      </c>
-      <c r="AC198">
-        <v>3.45</v>
-      </c>
-      <c r="AD198">
-        <v>1.25</v>
-      </c>
-      <c r="AE198">
-        <v>1.05</v>
-      </c>
-      <c r="AF198">
-        <v>1.81</v>
-      </c>
-      <c r="AG198">
-        <v>1.87</v>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ198">
-        <v>1.3</v>
-      </c>
-      <c r="AK198">
-        <v>1.44</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="O212">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="P212">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
       </c>
       <c r="R212">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S212">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T212">
-        <v>3.08</v>
+        <v>2.68</v>
       </c>
       <c r="U212">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="V212">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W212">
+        <v>1.07</v>
+      </c>
+      <c r="X212">
+        <v>1.01</v>
+      </c>
+      <c r="Y212">
+        <v>1.24</v>
+      </c>
+      <c r="Z212">
+        <v>3.34</v>
+      </c>
+      <c r="AA212">
+        <v>1.98</v>
+      </c>
+      <c r="AB212">
+        <v>1.88</v>
+      </c>
+      <c r="AC212">
+        <v>3.2</v>
+      </c>
+      <c r="AD212">
+        <v>1.26</v>
+      </c>
+      <c r="AE212">
         <v>1.06</v>
       </c>
-      <c r="X212">
-        <v>1.02</v>
-      </c>
-      <c r="Y212">
-        <v>1.18</v>
-      </c>
-      <c r="Z212">
-        <v>3.85</v>
-      </c>
-      <c r="AA212">
-        <v>1.74</v>
-      </c>
-      <c r="AB212">
-        <v>2.02</v>
-      </c>
-      <c r="AC212">
-        <v>2.78</v>
-      </c>
-      <c r="AD212">
-        <v>1.39</v>
-      </c>
-      <c r="AE212">
-        <v>1.11</v>
-      </c>
       <c r="AF212">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AG212">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
       <c r="O213">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P213">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="Q213">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="R213">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S213">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T213">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="U213">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="V213">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W213">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X213">
         <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z213">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="AA213">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AB213">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AC213">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AD213">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE213">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF213">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AG213">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK213">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="O215">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P215">
-        <v>2.89</v>
+        <v>2.43</v>
       </c>
       <c r="Q215">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="R215">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S215">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T215">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U215">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="V215">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W215">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X215">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y215">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z215">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="AA215">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AB215">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC215">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="AD215">
         <v>1.39</v>
       </c>
       <c r="AE215">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF215">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG215">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
+        <v>1.25</v>
+      </c>
+      <c r="AK215">
         <v>1.44</v>
-      </c>
-      <c r="AK215">
-        <v>1.5</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -48240,55 +48240,55 @@
         <v>3.31</v>
       </c>
       <c r="Q294">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R294">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S294">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T294">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U294">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V294">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W294">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X294">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y294">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z294">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA294">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB294">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC294">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD294">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE294">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF294">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG294">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK294">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48566,55 +48566,55 @@
         <v>0</v>
       </c>
       <c r="Q296">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R296">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S296">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T296">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U296">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V296">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W296">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X296">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y296">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z296">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA296">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB296">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC296">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD296">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE296">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF296">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG296">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK296">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G353">
@@ -57848,13 +57848,13 @@
         </is>
       </c>
       <c r="N353">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="O353">
-        <v>3.33</v>
+        <v>3.39</v>
       </c>
       <c r="P353">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="Q353">
         <v>0</v>
@@ -57887,10 +57887,10 @@
         <v>0</v>
       </c>
       <c r="AA353">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB353">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC353">
         <v>0</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,13 +58011,13 @@
         </is>
       </c>
       <c r="N354">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="O354">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="P354">
-        <v>2.72</v>
+        <v>3.53</v>
       </c>
       <c r="Q354">
         <v>0</v>
@@ -58050,10 +58050,10 @@
         <v>0</v>
       </c>
       <c r="AA354">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB354">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC354">
         <v>0</v>
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G355">
@@ -58174,13 +58174,13 @@
         </is>
       </c>
       <c r="N355">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="O355">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="P355">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q355">
         <v>0</v>
@@ -58213,10 +58213,10 @@
         <v>0</v>
       </c>
       <c r="AA355">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB355">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC355">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="O3">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P3">
-        <v>3.09</v>
+        <v>2.77</v>
       </c>
       <c r="Q3">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
         <v>2.45</v>
@@ -828,7 +828,7 @@
         <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
         <v>1.39</v>
@@ -837,19 +837,19 @@
         <v>2.99</v>
       </c>
       <c r="AA3">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB3">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC3">
-        <v>4.14</v>
+        <v>4.2</v>
       </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
         <v>1.87</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.81</v>
+        <v>3.43</v>
       </c>
       <c r="O4">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="Q4">
-        <v>4.54</v>
+        <v>4</v>
       </c>
       <c r="R4">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
         <v>1.34</v>
@@ -991,19 +991,19 @@
         <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.23</v>
       </c>
       <c r="Z4">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="AA4">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AB4">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AC4">
         <v>3.09</v>
@@ -1139,7 +1139,7 @@
         <v>2.32</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
         <v>3.14</v>
@@ -1163,16 +1163,16 @@
         <v>3.99</v>
       </c>
       <c r="AA5">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB5">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AC5">
         <v>2.9</v>
       </c>
       <c r="AD5">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE5">
         <v>1.11</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>4.13</v>
+        <v>3.77</v>
       </c>
       <c r="Q6">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
         <v>2.02</v>
@@ -1308,13 +1308,13 @@
         <v>2.84</v>
       </c>
       <c r="U6">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="V6">
         <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1338,10 +1338,10 @@
         <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG6">
         <v>1.85</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
         <v>3.4</v>
       </c>
       <c r="P7">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="Q7">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="R7">
         <v>2.08</v>
@@ -1468,22 +1468,22 @@
         <v>1.3</v>
       </c>
       <c r="T7">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
         <v>3.48</v>
@@ -1495,16 +1495,16 @@
         <v>1.98</v>
       </c>
       <c r="AC7">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="AD7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
         <v>2.1</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="O8">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="P8">
-        <v>3.14</v>
+        <v>2.82</v>
       </c>
       <c r="Q8">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R8">
         <v>2.28</v>
@@ -1631,7 +1631,7 @@
         <v>1.34</v>
       </c>
       <c r="T8">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
         <v>2.75</v>
@@ -1640,7 +1640,7 @@
         <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
         <v>1.01</v>
@@ -1652,10 +1652,10 @@
         <v>3.73</v>
       </c>
       <c r="AA8">
+        <v>1.84</v>
+      </c>
+      <c r="AB8">
         <v>1.95</v>
-      </c>
-      <c r="AB8">
-        <v>1.85</v>
       </c>
       <c r="AC8">
         <v>2.92</v>
@@ -1664,7 +1664,7 @@
         <v>1.31</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
         <v>1.67</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.28</v>
+        <v>4.15</v>
       </c>
       <c r="O11">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="P11">
         <v>1.6</v>
@@ -2114,7 +2114,7 @@
         <v>4.76</v>
       </c>
       <c r="R11">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="S11">
         <v>1.21</v>
@@ -2123,28 +2123,28 @@
         <v>3.6</v>
       </c>
       <c r="U11">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V11">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W11">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z11">
-        <v>4.86</v>
+        <v>4.65</v>
       </c>
       <c r="AA11">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB11">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="AC11">
         <v>2.34</v>
@@ -2159,7 +2159,7 @@
         <v>1.53</v>
       </c>
       <c r="AG11">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3614,7 +3614,7 @@
         <v>2.28</v>
       </c>
       <c r="AC20">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AD20">
         <v>1.59</v>
@@ -3626,7 +3626,7 @@
         <v>1.44</v>
       </c>
       <c r="AG20">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>2.79</v>
       </c>
       <c r="Q21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
         <v>2.4</v>
@@ -3753,13 +3753,13 @@
         <v>4</v>
       </c>
       <c r="U21">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V21">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.02</v>
@@ -3768,28 +3768,28 @@
         <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB21">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="AC21">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AD21">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE21">
         <v>1.23</v>
       </c>
       <c r="AF21">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG21">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3904,10 +3904,10 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="R22">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S22">
         <v>1.17</v>
@@ -3916,31 +3916,31 @@
         <v>4.5</v>
       </c>
       <c r="U22">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V22">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W22">
         <v>1.17</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.09</v>
       </c>
       <c r="Z22">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA22">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AB22">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC22">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AD22">
         <v>1.73</v>
@@ -3952,7 +3952,7 @@
         <v>1.39</v>
       </c>
       <c r="AG22">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4082,7 +4082,7 @@
         <v>2.55</v>
       </c>
       <c r="V23">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
         <v>1.08</v>
@@ -4094,7 +4094,7 @@
         <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AA23">
         <v>1.73</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="R24">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="S24">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="U24">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="V24">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>6.26</v>
+        <v>4.4</v>
       </c>
       <c r="AA24">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AB24">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AC24">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="AD24">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Q25">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="R25">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="S25">
         <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="U25">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z25">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA25">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB25">
         <v>2.33</v>
       </c>
       <c r="AC25">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AD25">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE25">
         <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK25">
-        <v>1.82</v>
+        <v>3.9</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>7.05</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="R26">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="S26">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="T26">
-        <v>3.56</v>
+        <v>5.5</v>
       </c>
       <c r="U26">
-        <v>2.19</v>
+        <v>1.79</v>
       </c>
       <c r="V26">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="Z26">
-        <v>4.65</v>
+        <v>7.4</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="AB26">
-        <v>1.93</v>
+        <v>3.49</v>
       </c>
       <c r="AC26">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AD26">
-        <v>1.49</v>
+        <v>2.15</v>
       </c>
       <c r="AE26">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AF26">
-        <v>2.14</v>
+        <v>1.26</v>
       </c>
       <c r="AG26">
-        <v>1.63</v>
+        <v>3.4</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK26">
-        <v>4.46</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q27">
+        <v>3.4</v>
+      </c>
+      <c r="R27">
         <v>2.6</v>
-      </c>
-      <c r="R27">
-        <v>2.68</v>
       </c>
       <c r="S27">
         <v>1.14</v>
@@ -4731,10 +4731,10 @@
         <v>4.8</v>
       </c>
       <c r="U27">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V27">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W27">
         <v>1.2</v>
@@ -4743,25 +4743,25 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>6.35</v>
+        <v>6.26</v>
       </c>
       <c r="AA27">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AB27">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="AC27">
+        <v>1.88</v>
+      </c>
+      <c r="AD27">
         <v>1.85</v>
       </c>
-      <c r="AD27">
-        <v>1.93</v>
-      </c>
       <c r="AE27">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AF27">
         <v>1.35</v>
@@ -4783,7 +4783,7 @@
         <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,25 +4882,25 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R28">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
         <v>2.95</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4927,10 +4927,10 @@
         <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG28">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -8948,25 +8948,25 @@
         </is>
       </c>
       <c r="N53">
-        <v>5.28</v>
+        <v>3.95</v>
       </c>
       <c r="O53">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P53">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="Q53">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R53">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="S53">
         <v>1.4</v>
       </c>
       <c r="T53">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="U53">
         <v>3.03</v>
@@ -8975,16 +8975,16 @@
         <v>1.36</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z53">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="AA53">
         <v>2.03</v>
@@ -9002,10 +9002,10 @@
         <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG53">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="O56">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="P56">
-        <v>3.43</v>
+        <v>4.14</v>
       </c>
       <c r="Q56">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="R56">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T56">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="U56">
-        <v>2.11</v>
+        <v>1.82</v>
       </c>
       <c r="V56">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="W56">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Z56">
-        <v>5.15</v>
+        <v>7.4</v>
       </c>
       <c r="AA56">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AB56">
-        <v>2.42</v>
+        <v>3.34</v>
       </c>
       <c r="AC56">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AD56">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AE56">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AF56">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AG56">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK56">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="O57">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
-        <v>4.14</v>
+        <v>3.43</v>
       </c>
       <c r="Q57">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="R57">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="S57">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="U57">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
       <c r="V57">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="W57">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>7.4</v>
+        <v>5.15</v>
       </c>
       <c r="AA57">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AB57">
-        <v>3.34</v>
+        <v>2.42</v>
       </c>
       <c r="AC57">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AD57">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AE57">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AF57">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AG57">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK57">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -12543,25 +12543,25 @@
         <v>2.99</v>
       </c>
       <c r="Q75">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R75">
         <v>2.4</v>
       </c>
       <c r="S75">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T75">
         <v>4</v>
       </c>
       <c r="U75">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V75">
         <v>1.65</v>
       </c>
       <c r="W75">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X75">
         <v>1.02</v>
@@ -12573,7 +12573,7 @@
         <v>4.95</v>
       </c>
       <c r="AA75">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB75">
         <v>2.6</v>
@@ -12712,16 +12712,16 @@
         <v>2.4</v>
       </c>
       <c r="S76">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T76">
         <v>3.4</v>
       </c>
       <c r="U76">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V76">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W76">
         <v>1.11</v>
@@ -12754,7 +12754,7 @@
         <v>1.75</v>
       </c>
       <c r="AG76">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK76">
         <v>2.63</v>
@@ -13032,10 +13032,10 @@
         <v>1.64</v>
       </c>
       <c r="Q78">
-        <v>4.87</v>
+        <v>4.8</v>
       </c>
       <c r="R78">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S78">
         <v>1.2</v>
@@ -13044,13 +13044,13 @@
         <v>4</v>
       </c>
       <c r="U78">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V78">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W78">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X78">
         <v>1.02</v>
@@ -13062,19 +13062,19 @@
         <v>5.6</v>
       </c>
       <c r="AA78">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB78">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AC78">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AD78">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AE78">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF78">
         <v>1.49</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.2</v>
+        <v>2.29</v>
       </c>
       <c r="AK78">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,49 +24433,49 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O148">
-        <v>4.27</v>
+        <v>4.36</v>
       </c>
       <c r="P148">
-        <v>4.21</v>
+        <v>4.36</v>
       </c>
       <c r="Q148">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R148">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="S148">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T148">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U148">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="V148">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W148">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X148">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y148">
         <v>1.13</v>
       </c>
       <c r="Z148">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA148">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB148">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AC148">
         <v>2.2</v>
@@ -24484,10 +24484,10 @@
         <v>1.6</v>
       </c>
       <c r="AE148">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF148">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG148">
         <v>2.5</v>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK148">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,64 +24596,64 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="O149">
-        <v>3.84</v>
+        <v>6.49</v>
       </c>
       <c r="P149">
-        <v>3.14</v>
+        <v>9.1</v>
       </c>
       <c r="Q149">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="R149">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="S149">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="T149">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="U149">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="V149">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="W149">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="X149">
         <v>1.01</v>
       </c>
       <c r="Y149">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="Z149">
-        <v>4.6</v>
+        <v>7.1</v>
       </c>
       <c r="AA149">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="AB149">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="AC149">
-        <v>2.33</v>
+        <v>1.71</v>
       </c>
       <c r="AD149">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AE149">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="AF149">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG149">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK149">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,31 +24759,31 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.37</v>
+        <v>1.84</v>
       </c>
       <c r="O150">
-        <v>4.06</v>
+        <v>4.27</v>
       </c>
       <c r="P150">
-        <v>2.88</v>
+        <v>4.21</v>
       </c>
       <c r="Q150">
-        <v>2.54</v>
+        <v>2.24</v>
       </c>
       <c r="R150">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="S150">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T150">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U150">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="V150">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W150">
         <v>1.17</v>
@@ -24795,25 +24795,25 @@
         <v>1.13</v>
       </c>
       <c r="Z150">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA150">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AB150">
         <v>2.35</v>
       </c>
       <c r="AC150">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD150">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE150">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AF150">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG150">
         <v>2.5</v>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK150">
-        <v>1.61</v>
+        <v>2.13</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,61 +24922,61 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="O151">
-        <v>4.36</v>
+        <v>3.84</v>
       </c>
       <c r="P151">
-        <v>4.36</v>
+        <v>3.14</v>
       </c>
       <c r="Q151">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="R151">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="S151">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T151">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U151">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V151">
         <v>1.64</v>
       </c>
       <c r="W151">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X151">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z151">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA151">
+        <v>1.63</v>
+      </c>
+      <c r="AB151">
+        <v>2.15</v>
+      </c>
+      <c r="AC151">
+        <v>2.33</v>
+      </c>
+      <c r="AD151">
+        <v>1.52</v>
+      </c>
+      <c r="AE151">
+        <v>1.18</v>
+      </c>
+      <c r="AF151">
         <v>1.5</v>
-      </c>
-      <c r="AB151">
-        <v>2.62</v>
-      </c>
-      <c r="AC151">
-        <v>2.2</v>
-      </c>
-      <c r="AD151">
-        <v>1.6</v>
-      </c>
-      <c r="AE151">
-        <v>1.22</v>
-      </c>
-      <c r="AF151">
-        <v>1.53</v>
       </c>
       <c r="AG151">
         <v>2.5</v>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK151">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.33</v>
+        <v>2.37</v>
       </c>
       <c r="O152">
-        <v>6.49</v>
+        <v>4.06</v>
       </c>
       <c r="P152">
-        <v>9.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q152">
-        <v>1.73</v>
+        <v>2.54</v>
       </c>
       <c r="R152">
-        <v>2.9</v>
+        <v>2.49</v>
       </c>
       <c r="S152">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T152">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="U152">
-        <v>1.86</v>
+        <v>2.41</v>
       </c>
       <c r="V152">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="W152">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X152">
         <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z152">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA152">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AB152">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC152">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AD152">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AE152">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AF152">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG152">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AK152">
-        <v>2.8</v>
+        <v>1.61</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>9.25</v>
+        <v>1.49</v>
       </c>
       <c r="O160">
-        <v>5.45</v>
+        <v>4.3</v>
       </c>
       <c r="P160">
-        <v>1.23</v>
+        <v>4.94</v>
       </c>
       <c r="Q160">
-        <v>7.75</v>
+        <v>1.98</v>
       </c>
       <c r="R160">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="S160">
         <v>1.22</v>
       </c>
       <c r="T160">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U160">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V160">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="W160">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X160">
         <v>1.02</v>
       </c>
       <c r="Y160">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z160">
-        <v>4.8</v>
+        <v>5.52</v>
       </c>
       <c r="AA160">
+        <v>1.57</v>
+      </c>
+      <c r="AB160">
+        <v>2.35</v>
+      </c>
+      <c r="AC160">
+        <v>2.2</v>
+      </c>
+      <c r="AD160">
+        <v>1.65</v>
+      </c>
+      <c r="AE160">
+        <v>1.25</v>
+      </c>
+      <c r="AF160">
         <v>1.52</v>
       </c>
-      <c r="AB160">
-        <v>2.48</v>
-      </c>
-      <c r="AC160">
-        <v>2.32</v>
-      </c>
-      <c r="AD160">
-        <v>1.58</v>
-      </c>
-      <c r="AE160">
-        <v>1.22</v>
-      </c>
-      <c r="AF160">
-        <v>1.83</v>
-      </c>
       <c r="AG160">
-        <v>1.86</v>
+        <v>2.34</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK160">
-        <v>1.04</v>
+        <v>2.27</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,80 +26552,80 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.49</v>
+        <v>9.25</v>
       </c>
       <c r="O161">
-        <v>4.3</v>
+        <v>5.45</v>
       </c>
       <c r="P161">
-        <v>4.94</v>
+        <v>1.23</v>
       </c>
       <c r="Q161">
-        <v>1.98</v>
+        <v>7.75</v>
       </c>
       <c r="R161">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="S161">
         <v>1.22</v>
       </c>
       <c r="T161">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U161">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="V161">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="W161">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X161">
         <v>1.02</v>
       </c>
       <c r="Y161">
+        <v>1.16</v>
+      </c>
+      <c r="Z161">
+        <v>4.8</v>
+      </c>
+      <c r="AA161">
+        <v>1.52</v>
+      </c>
+      <c r="AB161">
+        <v>2.48</v>
+      </c>
+      <c r="AC161">
+        <v>2.32</v>
+      </c>
+      <c r="AD161">
+        <v>1.58</v>
+      </c>
+      <c r="AE161">
+        <v>1.22</v>
+      </c>
+      <c r="AF161">
+        <v>1.83</v>
+      </c>
+      <c r="AG161">
+        <v>1.86</v>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ161">
         <v>1.1</v>
       </c>
-      <c r="Z161">
-        <v>5.52</v>
-      </c>
-      <c r="AA161">
-        <v>1.57</v>
-      </c>
-      <c r="AB161">
-        <v>2.35</v>
-      </c>
-      <c r="AC161">
-        <v>2.2</v>
-      </c>
-      <c r="AD161">
-        <v>1.65</v>
-      </c>
-      <c r="AE161">
-        <v>1.25</v>
-      </c>
-      <c r="AF161">
-        <v>1.52</v>
-      </c>
-      <c r="AG161">
-        <v>2.34</v>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ161">
-        <v>1.13</v>
-      </c>
       <c r="AK161">
-        <v>2.27</v>
+        <v>1.04</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O164">
-        <v>3.06</v>
+        <v>3.24</v>
       </c>
       <c r="P164">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="Q164">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="R164">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S164">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T164">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="U164">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="V164">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W164">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X164">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y164">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z164">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA164">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB164">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AC164">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD164">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE164">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF164">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG164">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>1.3</v>
       </c>
       <c r="AK164">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,31 +27204,31 @@
         </is>
       </c>
       <c r="N165">
-        <v>3.1</v>
+        <v>5.06</v>
       </c>
       <c r="O165">
-        <v>3.24</v>
+        <v>3.7</v>
       </c>
       <c r="P165">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Q165">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="R165">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S165">
+        <v>1.41</v>
+      </c>
+      <c r="T165">
+        <v>2.62</v>
+      </c>
+      <c r="U165">
+        <v>2.7</v>
+      </c>
+      <c r="V165">
         <v>1.39</v>
-      </c>
-      <c r="T165">
-        <v>2.69</v>
-      </c>
-      <c r="U165">
-        <v>2.62</v>
-      </c>
-      <c r="V165">
-        <v>1.41</v>
       </c>
       <c r="W165">
         <v>1.06</v>
@@ -27243,25 +27243,25 @@
         <v>3.3</v>
       </c>
       <c r="AA165">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB165">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC165">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD165">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE165">
         <v>1.06</v>
       </c>
       <c r="AF165">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AG165">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK165">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>5.06</v>
+        <v>1.31</v>
       </c>
       <c r="O166">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="P166">
-        <v>1.65</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q166">
-        <v>5.75</v>
+        <v>1.75</v>
       </c>
       <c r="R166">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="S166">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T166">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="U166">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="V166">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="W166">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X166">
         <v>1.03</v>
       </c>
       <c r="Y166">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z166">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA166">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AB166">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AC166">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD166">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE166">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF166">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG166">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK166">
-        <v>1.15</v>
+        <v>3.1</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.31</v>
+        <v>2.35</v>
       </c>
       <c r="O167">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="P167">
-        <v>8.300000000000001</v>
+        <v>2.73</v>
       </c>
       <c r="Q167">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="R167">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S167">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T167">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="U167">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="V167">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W167">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X167">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y167">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z167">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="AA167">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="AB167">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AC167">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD167">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE167">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF167">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG167">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK167">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="Q169">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R169">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S169">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T169">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U169">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V169">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W169">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X169">
         <v>0</v>
       </c>
       <c r="Y169">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z169">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="AA169">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AB169">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AC169">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AD169">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE169">
         <v>0</v>
       </c>
       <c r="AF169">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG169">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK169">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.99</v>
+        <v>2.32</v>
       </c>
       <c r="O172">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P172">
-        <v>2.18</v>
+        <v>2.96</v>
       </c>
       <c r="Q172">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R172">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S172">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T172">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U172">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V172">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W172">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X172">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y172">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z172">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA172">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB172">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC172">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD172">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE172">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF172">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG172">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK172">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
       <c r="O173">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="P173">
-        <v>2.96</v>
+        <v>3.96</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB173">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.86</v>
+        <v>2.37</v>
       </c>
       <c r="O174">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P174">
-        <v>3.96</v>
+        <v>2.83</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB174">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.37</v>
+        <v>1.87</v>
       </c>
       <c r="O175">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="P175">
-        <v>2.83</v>
+        <v>3.7</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA175">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AB175">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>3.11</v>
+        <v>1.71</v>
       </c>
       <c r="O176">
-        <v>3.35</v>
+        <v>3.82</v>
       </c>
       <c r="P176">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="Q176">
-        <v>3.7</v>
+        <v>2.27</v>
       </c>
       <c r="R176">
+        <v>2.24</v>
+      </c>
+      <c r="S176">
+        <v>1.3</v>
+      </c>
+      <c r="T176">
+        <v>3.12</v>
+      </c>
+      <c r="U176">
+        <v>2.47</v>
+      </c>
+      <c r="V176">
+        <v>1.46</v>
+      </c>
+      <c r="W176">
+        <v>1.07</v>
+      </c>
+      <c r="X176">
+        <v>1.04</v>
+      </c>
+      <c r="Y176">
+        <v>1.18</v>
+      </c>
+      <c r="Z176">
+        <v>3.84</v>
+      </c>
+      <c r="AA176">
+        <v>1.65</v>
+      </c>
+      <c r="AB176">
         <v>2.1</v>
       </c>
-      <c r="S176">
-        <v>1.39</v>
-      </c>
-      <c r="T176">
-        <v>2.7</v>
-      </c>
-      <c r="U176">
-        <v>2.78</v>
-      </c>
-      <c r="V176">
-        <v>1.37</v>
-      </c>
-      <c r="W176">
-        <v>1.06</v>
-      </c>
-      <c r="X176">
-        <v>1.03</v>
-      </c>
-      <c r="Y176">
-        <v>1.25</v>
-      </c>
-      <c r="Z176">
-        <v>3.28</v>
-      </c>
-      <c r="AA176">
-        <v>1.98</v>
-      </c>
-      <c r="AB176">
-        <v>1.88</v>
-      </c>
       <c r="AC176">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="AD176">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE176">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF176">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG176">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK176">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.87</v>
+        <v>2.99</v>
       </c>
       <c r="O177">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P177">
-        <v>3.7</v>
+        <v>2.18</v>
       </c>
       <c r="Q177">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="R177">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S177">
         <v>1.3</v>
       </c>
       <c r="T177">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U177">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V177">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W177">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X177">
         <v>1.04</v>
       </c>
       <c r="Y177">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z177">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AA177">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB177">
         <v>2</v>
       </c>
       <c r="AC177">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD177">
         <v>1.35</v>
       </c>
       <c r="AE177">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF177">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG177">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK177">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.71</v>
+        <v>3.11</v>
       </c>
       <c r="O178">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="P178">
-        <v>4.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q178">
-        <v>2.27</v>
+        <v>3.7</v>
       </c>
       <c r="R178">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S178">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T178">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="U178">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="V178">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W178">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X178">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y178">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z178">
-        <v>3.84</v>
+        <v>3.28</v>
       </c>
       <c r="AA178">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AB178">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AC178">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="AD178">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE178">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF178">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG178">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK178">
-        <v>1.96</v>
+        <v>1.32</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="O186">
-        <v>4.6</v>
+        <v>3.72</v>
       </c>
       <c r="P186">
-        <v>4.7</v>
+        <v>3.52</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y186">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z186">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG186">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK186">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="O187">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="P187">
-        <v>3.35</v>
+        <v>4.95</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X187">
         <v>0</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,31 +30953,31 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="O188">
-        <v>3.72</v>
+        <v>3.96</v>
       </c>
       <c r="P188">
-        <v>3.52</v>
+        <v>3.77</v>
       </c>
       <c r="Q188">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="R188">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S188">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T188">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U188">
         <v>2.05</v>
       </c>
       <c r="V188">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W188">
         <v>1.18</v>
@@ -30986,31 +30986,31 @@
         <v>1.02</v>
       </c>
       <c r="Y188">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z188">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AA188">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB188">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC188">
+        <v>1.85</v>
+      </c>
+      <c r="AD188">
         <v>1.91</v>
       </c>
-      <c r="AD188">
-        <v>1.84</v>
-      </c>
       <c r="AE188">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF188">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AG188">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK188">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,80 +31116,80 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="O189">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="P189">
-        <v>4.95</v>
+        <v>3.26</v>
       </c>
       <c r="Q189">
+        <v>2.2</v>
+      </c>
+      <c r="R189">
+        <v>2.88</v>
+      </c>
+      <c r="S189">
+        <v>1.09</v>
+      </c>
+      <c r="T189">
+        <v>5.45</v>
+      </c>
+      <c r="U189">
+        <v>1.67</v>
+      </c>
+      <c r="V189">
+        <v>2.14</v>
+      </c>
+      <c r="W189">
+        <v>1.32</v>
+      </c>
+      <c r="X189">
+        <v>0</v>
+      </c>
+      <c r="Y189">
+        <v>1.05</v>
+      </c>
+      <c r="Z189">
+        <v>10</v>
+      </c>
+      <c r="AA189">
+        <v>1.2</v>
+      </c>
+      <c r="AB189">
+        <v>4.33</v>
+      </c>
+      <c r="AC189">
+        <v>1.46</v>
+      </c>
+      <c r="AD189">
+        <v>2.44</v>
+      </c>
+      <c r="AE189">
+        <v>1.66</v>
+      </c>
+      <c r="AF189">
+        <v>1.19</v>
+      </c>
+      <c r="AG189">
+        <v>3.8</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ189">
+        <v>1.17</v>
+      </c>
+      <c r="AK189">
         <v>1.83</v>
-      </c>
-      <c r="R189">
-        <v>3.2</v>
-      </c>
-      <c r="S189">
-        <v>1.1</v>
-      </c>
-      <c r="T189">
-        <v>6.5</v>
-      </c>
-      <c r="U189">
-        <v>1.44</v>
-      </c>
-      <c r="V189">
-        <v>2.63</v>
-      </c>
-      <c r="W189">
-        <v>1.5</v>
-      </c>
-      <c r="X189">
-        <v>0</v>
-      </c>
-      <c r="Y189">
-        <v>1.02</v>
-      </c>
-      <c r="Z189">
-        <v>15</v>
-      </c>
-      <c r="AA189">
-        <v>1.08</v>
-      </c>
-      <c r="AB189">
-        <v>6.5</v>
-      </c>
-      <c r="AC189">
-        <v>1.31</v>
-      </c>
-      <c r="AD189">
-        <v>3.15</v>
-      </c>
-      <c r="AE189">
-        <v>2</v>
-      </c>
-      <c r="AF189">
-        <v>1.2</v>
-      </c>
-      <c r="AG189">
-        <v>4.2</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ189">
-        <v>1.13</v>
-      </c>
-      <c r="AK189">
-        <v>2.4</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="O190">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="P190">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="Q190">
-        <v>2.44</v>
+        <v>1.92</v>
       </c>
       <c r="R190">
-        <v>2.43</v>
+        <v>2.77</v>
       </c>
       <c r="S190">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T190">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="U190">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="V190">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="W190">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X190">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y190">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z190">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA190">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AB190">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="AC190">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AD190">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AE190">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AF190">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AG190">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK190">
-        <v>1.73</v>
+        <v>2.42</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="O191">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P191">
-        <v>3.26</v>
+        <v>4.7</v>
       </c>
       <c r="Q191">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="R191">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="S191">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="T191">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="U191">
         <v>1.67</v>
       </c>
       <c r="V191">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="W191">
+        <v>1.3</v>
+      </c>
+      <c r="X191">
+        <v>0</v>
+      </c>
+      <c r="Y191">
+        <v>1.01</v>
+      </c>
+      <c r="Z191">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA191">
+        <v>1.23</v>
+      </c>
+      <c r="AB191">
+        <v>3.9</v>
+      </c>
+      <c r="AC191">
+        <v>1.61</v>
+      </c>
+      <c r="AD191">
+        <v>2.26</v>
+      </c>
+      <c r="AE191">
+        <v>1.53</v>
+      </c>
+      <c r="AF191">
         <v>1.32</v>
       </c>
-      <c r="X191">
-        <v>0</v>
-      </c>
-      <c r="Y191">
-        <v>1.05</v>
-      </c>
-      <c r="Z191">
-        <v>10</v>
-      </c>
-      <c r="AA191">
-        <v>1.2</v>
-      </c>
-      <c r="AB191">
-        <v>4.33</v>
-      </c>
-      <c r="AC191">
-        <v>1.46</v>
-      </c>
-      <c r="AD191">
-        <v>2.44</v>
-      </c>
-      <c r="AE191">
-        <v>1.66</v>
-      </c>
-      <c r="AF191">
-        <v>1.19</v>
-      </c>
       <c r="AG191">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK191">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="O193">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P193">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="Q193">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="R193">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="S193">
+        <v>1.45</v>
+      </c>
+      <c r="T193">
+        <v>2.5</v>
+      </c>
+      <c r="U193">
+        <v>2.87</v>
+      </c>
+      <c r="V193">
         <v>1.35</v>
       </c>
-      <c r="T193">
-        <v>3.1</v>
-      </c>
-      <c r="U193">
-        <v>2.77</v>
-      </c>
-      <c r="V193">
-        <v>1.42</v>
-      </c>
       <c r="W193">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X193">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z193">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA193">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AB193">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC193">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="AD193">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE193">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF193">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG193">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK193">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,80 +31931,80 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="O194">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P194">
-        <v>2.69</v>
+        <v>2.37</v>
       </c>
       <c r="Q194">
-        <v>3.06</v>
+        <v>2.73</v>
       </c>
       <c r="R194">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="S194">
+        <v>1.24</v>
+      </c>
+      <c r="T194">
+        <v>3.4</v>
+      </c>
+      <c r="U194">
+        <v>2.27</v>
+      </c>
+      <c r="V194">
+        <v>1.57</v>
+      </c>
+      <c r="W194">
+        <v>1.13</v>
+      </c>
+      <c r="X194">
+        <v>1.02</v>
+      </c>
+      <c r="Y194">
+        <v>1.11</v>
+      </c>
+      <c r="Z194">
+        <v>4.8</v>
+      </c>
+      <c r="AA194">
+        <v>1.83</v>
+      </c>
+      <c r="AB194">
+        <v>1.91</v>
+      </c>
+      <c r="AC194">
+        <v>2.35</v>
+      </c>
+      <c r="AD194">
+        <v>1.55</v>
+      </c>
+      <c r="AE194">
+        <v>1.17</v>
+      </c>
+      <c r="AF194">
+        <v>1.44</v>
+      </c>
+      <c r="AG194">
+        <v>2.6</v>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ194">
+        <v>1.23</v>
+      </c>
+      <c r="AK194">
         <v>1.45</v>
-      </c>
-      <c r="T194">
-        <v>2.5</v>
-      </c>
-      <c r="U194">
-        <v>2.87</v>
-      </c>
-      <c r="V194">
-        <v>1.35</v>
-      </c>
-      <c r="W194">
-        <v>1.04</v>
-      </c>
-      <c r="X194">
-        <v>1.01</v>
-      </c>
-      <c r="Y194">
-        <v>1.31</v>
-      </c>
-      <c r="Z194">
-        <v>2.92</v>
-      </c>
-      <c r="AA194">
-        <v>2.11</v>
-      </c>
-      <c r="AB194">
-        <v>1.73</v>
-      </c>
-      <c r="AC194">
-        <v>3.45</v>
-      </c>
-      <c r="AD194">
-        <v>1.25</v>
-      </c>
-      <c r="AE194">
-        <v>1.05</v>
-      </c>
-      <c r="AF194">
-        <v>1.81</v>
-      </c>
-      <c r="AG194">
-        <v>1.87</v>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ194">
-        <v>1.3</v>
-      </c>
-      <c r="AK194">
-        <v>1.44</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.37</v>
+        <v>3.05</v>
       </c>
       <c r="O195">
-        <v>4.85</v>
+        <v>3.44</v>
       </c>
       <c r="P195">
-        <v>7.39</v>
+        <v>2.22</v>
       </c>
       <c r="Q195">
-        <v>1.83</v>
+        <v>3.15</v>
       </c>
       <c r="R195">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="S195">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T195">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="U195">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="V195">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="W195">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X195">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="Z195">
-        <v>4.75</v>
+        <v>3.42</v>
       </c>
       <c r="AA195">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AB195">
-        <v>2.37</v>
+        <v>1.89</v>
       </c>
       <c r="AC195">
-        <v>2.3</v>
+        <v>2.97</v>
       </c>
       <c r="AD195">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AE195">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF195">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG195">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK195">
-        <v>2.88</v>
+        <v>1.33</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>3.41</v>
+        <v>1.37</v>
       </c>
       <c r="O196">
-        <v>3.42</v>
+        <v>4.85</v>
       </c>
       <c r="P196">
-        <v>2.07</v>
+        <v>7.39</v>
       </c>
       <c r="Q196">
-        <v>3.59</v>
+        <v>1.83</v>
       </c>
       <c r="R196">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="S196">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T196">
-        <v>2.97</v>
+        <v>3.75</v>
       </c>
       <c r="U196">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="V196">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="W196">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X196">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="Z196">
-        <v>3.71</v>
+        <v>4.75</v>
       </c>
       <c r="AA196">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AB196">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="AC196">
-        <v>2.93</v>
+        <v>2.3</v>
       </c>
       <c r="AD196">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AE196">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AF196">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG196">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK196">
-        <v>1.2</v>
+        <v>2.88</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,80 +32420,80 @@
         </is>
       </c>
       <c r="N197">
-        <v>3.05</v>
+        <v>3.41</v>
       </c>
       <c r="O197">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="P197">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="Q197">
-        <v>3.15</v>
+        <v>3.59</v>
       </c>
       <c r="R197">
         <v>2.08</v>
       </c>
       <c r="S197">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T197">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="U197">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="V197">
         <v>1.42</v>
       </c>
       <c r="W197">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X197">
         <v>1.01</v>
       </c>
       <c r="Y197">
+        <v>1.27</v>
+      </c>
+      <c r="Z197">
+        <v>3.71</v>
+      </c>
+      <c r="AA197">
+        <v>2</v>
+      </c>
+      <c r="AB197">
+        <v>1.81</v>
+      </c>
+      <c r="AC197">
+        <v>2.93</v>
+      </c>
+      <c r="AD197">
+        <v>1.34</v>
+      </c>
+      <c r="AE197">
+        <v>1.07</v>
+      </c>
+      <c r="AF197">
+        <v>1.7</v>
+      </c>
+      <c r="AG197">
+        <v>2</v>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ197">
         <v>1.23</v>
       </c>
-      <c r="Z197">
-        <v>3.42</v>
-      </c>
-      <c r="AA197">
-        <v>1.91</v>
-      </c>
-      <c r="AB197">
-        <v>1.89</v>
-      </c>
-      <c r="AC197">
-        <v>2.97</v>
-      </c>
-      <c r="AD197">
-        <v>1.3</v>
-      </c>
-      <c r="AE197">
-        <v>1.08</v>
-      </c>
-      <c r="AF197">
-        <v>1.67</v>
-      </c>
-      <c r="AG197">
-        <v>2.1</v>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ197">
-        <v>1.27</v>
-      </c>
       <c r="AK197">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="O198">
         <v>3.3</v>
       </c>
       <c r="P198">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="Q198">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="R198">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S198">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="T198">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U198">
-        <v>2.27</v>
+        <v>2.77</v>
       </c>
       <c r="V198">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W198">
+        <v>1.06</v>
+      </c>
+      <c r="X198">
+        <v>1</v>
+      </c>
+      <c r="Y198">
+        <v>1.29</v>
+      </c>
+      <c r="Z198">
+        <v>3.2</v>
+      </c>
+      <c r="AA198">
+        <v>1.85</v>
+      </c>
+      <c r="AB198">
+        <v>1.85</v>
+      </c>
+      <c r="AC198">
+        <v>3.16</v>
+      </c>
+      <c r="AD198">
+        <v>1.33</v>
+      </c>
+      <c r="AE198">
         <v>1.13</v>
       </c>
-      <c r="X198">
-        <v>1.02</v>
-      </c>
-      <c r="Y198">
-        <v>1.11</v>
-      </c>
-      <c r="Z198">
-        <v>4.8</v>
-      </c>
-      <c r="AA198">
-        <v>1.83</v>
-      </c>
-      <c r="AB198">
-        <v>1.91</v>
-      </c>
-      <c r="AC198">
-        <v>2.35</v>
-      </c>
-      <c r="AD198">
-        <v>1.55</v>
-      </c>
-      <c r="AE198">
-        <v>1.17</v>
-      </c>
       <c r="AF198">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AG198">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK198">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="O214">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P214">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="Q214">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R214">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S214">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T214">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U214">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="V214">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W214">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X214">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z214">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="AA214">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB214">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC214">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AD214">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE214">
         <v>1.11</v>
       </c>
       <c r="AF214">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG214">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="O216">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P216">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="Q216">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R216">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S216">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T216">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U216">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="V216">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W216">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X216">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z216">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="AA216">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB216">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC216">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="AD216">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE216">
         <v>1.11</v>
       </c>
       <c r="AF216">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG216">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O255">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P255">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42076,10 +42076,10 @@
         <v>0</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC256">
         <v>0</v>
@@ -43993,64 +43993,64 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q268">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R268">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S268">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T268">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U268">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V268">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W268">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y268">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z268">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA268">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB268">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC268">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD268">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE268">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF268">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG268">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK268">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44165,55 +44165,55 @@
         <v>0</v>
       </c>
       <c r="Q269">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R269">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S269">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T269">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U269">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V269">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W269">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X269">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y269">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z269">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA269">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB269">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC269">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD269">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE269">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF269">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG269">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK269">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44319,64 +44319,64 @@
         </is>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O270">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P270">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q270">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R270">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S270">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T270">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U270">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V270">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W270">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X270">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y270">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z270">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA270">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB270">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC270">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD270">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE270">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF270">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG270">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK270">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.07</v>
+        <v>6.05</v>
       </c>
       <c r="O272">
+        <v>4.5</v>
+      </c>
+      <c r="P272">
+        <v>1.45</v>
+      </c>
+      <c r="Q272">
+        <v>6.35</v>
+      </c>
+      <c r="R272">
+        <v>2.49</v>
+      </c>
+      <c r="S272">
+        <v>1.3</v>
+      </c>
+      <c r="T272">
         <v>3.2</v>
       </c>
-      <c r="P272">
-        <v>3.61</v>
-      </c>
-      <c r="Q272">
+      <c r="U272">
         <v>2.63</v>
       </c>
-      <c r="R272">
-        <v>2.13</v>
-      </c>
-      <c r="S272">
-        <v>1.4</v>
-      </c>
-      <c r="T272">
-        <v>2.75</v>
-      </c>
-      <c r="U272">
-        <v>3</v>
-      </c>
       <c r="V272">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W272">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X272">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y272">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="Z272">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA272">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AB272">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="AC272">
-        <v>3.76</v>
+        <v>2.62</v>
       </c>
       <c r="AD272">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE272">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF272">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG272">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK272">
-        <v>1.73</v>
+        <v>1.07</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>6.05</v>
+        <v>2.07</v>
       </c>
       <c r="O273">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="P273">
-        <v>1.45</v>
+        <v>3.61</v>
       </c>
       <c r="Q273">
-        <v>6.35</v>
+        <v>2.63</v>
       </c>
       <c r="R273">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
       <c r="S273">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T273">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U273">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V273">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W273">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X273">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y273">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="Z273">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA273">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB273">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="AC273">
-        <v>2.62</v>
+        <v>3.76</v>
       </c>
       <c r="AD273">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE273">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF273">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG273">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK273">
-        <v>1.07</v>
+        <v>1.73</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="O276">
         <v>4</v>
       </c>
       <c r="P276">
-        <v>3.79</v>
+        <v>2.4</v>
       </c>
       <c r="Q276">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="R276">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="S276">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T276">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U276">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V276">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="W276">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X276">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y276">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z276">
-        <v>5.96</v>
+        <v>6.65</v>
       </c>
       <c r="AA276">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AB276">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
       <c r="AC276">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AD276">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AE276">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF276">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG276">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK276">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="O277">
         <v>4</v>
       </c>
       <c r="P277">
-        <v>2.4</v>
+        <v>3.79</v>
       </c>
       <c r="Q277">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="R277">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="S277">
+        <v>1.22</v>
+      </c>
+      <c r="T277">
+        <v>4</v>
+      </c>
+      <c r="U277">
+        <v>2</v>
+      </c>
+      <c r="V277">
+        <v>1.71</v>
+      </c>
+      <c r="W277">
         <v>1.16</v>
       </c>
-      <c r="T277">
-        <v>4.8</v>
-      </c>
-      <c r="U277">
-        <v>1.97</v>
-      </c>
-      <c r="V277">
-        <v>1.89</v>
-      </c>
-      <c r="W277">
-        <v>1.18</v>
-      </c>
       <c r="X277">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y277">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z277">
-        <v>6.65</v>
+        <v>5.96</v>
       </c>
       <c r="AA277">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB277">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="AC277">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AD277">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AE277">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF277">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AG277">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK277">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -49870,55 +49870,55 @@
         <v>2.78</v>
       </c>
       <c r="Q304">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R304">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S304">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T304">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U304">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V304">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W304">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X304">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y304">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z304">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA304">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB304">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC304">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AD304">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE304">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF304">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG304">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK304">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G313">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G314">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G315">
@@ -57694,55 +57694,55 @@
         <v>0</v>
       </c>
       <c r="Q352">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R352">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S352">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T352">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U352">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="V352">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W352">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X352">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y352">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z352">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA352">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB352">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC352">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD352">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE352">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF352">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG352">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH352" t="inlineStr">
         <is>
@@ -57755,10 +57755,10 @@
         </is>
       </c>
       <c r="AJ352">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK352">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL352">
         <v>0</v>
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G356">
@@ -58337,64 +58337,64 @@
         </is>
       </c>
       <c r="N356">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="O356">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="P356">
-        <v>2.72</v>
+        <v>3.53</v>
       </c>
       <c r="Q356">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R356">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S356">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T356">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U356">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V356">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W356">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X356">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y356">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z356">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AA356">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB356">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC356">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD356">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE356">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF356">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG356">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH356" t="inlineStr">
         <is>
@@ -58407,10 +58407,10 @@
         </is>
       </c>
       <c r="AJ356">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK356">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL356">
         <v>0</v>
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G357">
@@ -58500,64 +58500,64 @@
         </is>
       </c>
       <c r="N357">
+        <v>2.64</v>
+      </c>
+      <c r="O357">
+        <v>3.39</v>
+      </c>
+      <c r="P357">
+        <v>2.72</v>
+      </c>
+      <c r="Q357">
+        <v>3</v>
+      </c>
+      <c r="R357">
         <v>2.1</v>
       </c>
-      <c r="O357">
-        <v>3.55</v>
-      </c>
-      <c r="P357">
-        <v>3.53</v>
-      </c>
-      <c r="Q357">
-        <v>0</v>
-      </c>
-      <c r="R357">
-        <v>0</v>
-      </c>
       <c r="S357">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T357">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U357">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V357">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W357">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X357">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y357">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z357">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA357">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB357">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AC357">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD357">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE357">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF357">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG357">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH357" t="inlineStr">
         <is>
@@ -58570,10 +58570,10 @@
         </is>
       </c>
       <c r="AJ357">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK357">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL357">
         <v>0</v>
@@ -58672,55 +58672,55 @@
         <v>3.3</v>
       </c>
       <c r="Q358">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R358">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S358">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T358">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U358">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V358">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W358">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X358">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y358">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z358">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA358">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB358">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC358">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD358">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE358">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF358">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG358">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH358" t="inlineStr">
         <is>
@@ -58733,10 +58733,10 @@
         </is>
       </c>
       <c r="AJ358">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK358">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL358">
         <v>0</v>
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G361">
@@ -59152,64 +59152,64 @@
         </is>
       </c>
       <c r="N361">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="O361">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="P361">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
       <c r="Q361">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="R361">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S361">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="T361">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="U361">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="V361">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="W361">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X361">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y361">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="Z361">
-        <v>3.67</v>
+        <v>2.92</v>
       </c>
       <c r="AA361">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB361">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AC361">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="AD361">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AE361">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AF361">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG361">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AH361" t="inlineStr">
         <is>
@@ -59222,10 +59222,10 @@
         </is>
       </c>
       <c r="AJ361">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK361">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AL361">
         <v>0</v>
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G362">
@@ -59315,64 +59315,64 @@
         </is>
       </c>
       <c r="N362">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="O362">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="P362">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="Q362">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="R362">
+        <v>2.05</v>
+      </c>
+      <c r="S362">
+        <v>1.35</v>
+      </c>
+      <c r="T362">
+        <v>3</v>
+      </c>
+      <c r="U362">
+        <v>2.6</v>
+      </c>
+      <c r="V362">
+        <v>1.42</v>
+      </c>
+      <c r="W362">
+        <v>1.07</v>
+      </c>
+      <c r="X362">
+        <v>1</v>
+      </c>
+      <c r="Y362">
+        <v>1.27</v>
+      </c>
+      <c r="Z362">
+        <v>3.67</v>
+      </c>
+      <c r="AA362">
         <v>1.95</v>
       </c>
-      <c r="S362">
-        <v>1.48</v>
-      </c>
-      <c r="T362">
-        <v>2.41</v>
-      </c>
-      <c r="U362">
-        <v>3.3</v>
-      </c>
-      <c r="V362">
-        <v>1.3</v>
-      </c>
-      <c r="W362">
-        <v>1.04</v>
-      </c>
-      <c r="X362">
-        <v>1.03</v>
-      </c>
-      <c r="Y362">
-        <v>1.4</v>
-      </c>
-      <c r="Z362">
-        <v>2.92</v>
-      </c>
-      <c r="AA362">
-        <v>2.2</v>
-      </c>
       <c r="AB362">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AC362">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="AD362">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AE362">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF362">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG362">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AH362" t="inlineStr">
         <is>
@@ -59385,10 +59385,10 @@
         </is>
       </c>
       <c r="AJ362">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK362">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL362">
         <v>0</v>
@@ -60465,55 +60465,55 @@
         <v>4.2</v>
       </c>
       <c r="Q369">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R369">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S369">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T369">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U369">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V369">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W369">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X369">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y369">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z369">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA369">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB369">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC369">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD369">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE369">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF369">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG369">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH369" t="inlineStr">
         <is>
@@ -60526,10 +60526,10 @@
         </is>
       </c>
       <c r="AJ369">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK369">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL369">
         <v>0</v>
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G371">
@@ -60782,64 +60782,64 @@
         </is>
       </c>
       <c r="N371">
-        <v>1.59</v>
+        <v>1.91</v>
       </c>
       <c r="O371">
-        <v>4.08</v>
+        <v>3.61</v>
       </c>
       <c r="P371">
-        <v>5.98</v>
+        <v>4.17</v>
       </c>
       <c r="Q371">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R371">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S371">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T371">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U371">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V371">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W371">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X371">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y371">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z371">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA371">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AB371">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AC371">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD371">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE371">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF371">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG371">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH371" t="inlineStr">
         <is>
@@ -60852,10 +60852,10 @@
         </is>
       </c>
       <c r="AJ371">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK371">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL371">
         <v>0</v>
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G372">
@@ -60945,64 +60945,64 @@
         </is>
       </c>
       <c r="N372">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="O372">
-        <v>3.61</v>
+        <v>4.08</v>
       </c>
       <c r="P372">
-        <v>4.17</v>
+        <v>5.98</v>
       </c>
       <c r="Q372">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R372">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S372">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T372">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U372">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V372">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W372">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X372">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y372">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z372">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA372">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AB372">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AC372">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD372">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE372">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF372">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG372">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH372" t="inlineStr">
         <is>
@@ -61015,10 +61015,10 @@
         </is>
       </c>
       <c r="AJ372">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK372">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL372">
         <v>0</v>
@@ -61117,34 +61117,34 @@
         <v>4.81</v>
       </c>
       <c r="Q373">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R373">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S373">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T373">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U373">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V373">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W373">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X373">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y373">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z373">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA373">
         <v>1.95</v>
@@ -61153,19 +61153,19 @@
         <v>1.81</v>
       </c>
       <c r="AC373">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD373">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE373">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF373">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG373">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH373" t="inlineStr">
         <is>
@@ -61178,10 +61178,10 @@
         </is>
       </c>
       <c r="AJ373">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK373">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL373">
         <v>0</v>
@@ -61769,55 +61769,55 @@
         <v>5</v>
       </c>
       <c r="Q377">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R377">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S377">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T377">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U377">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V377">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W377">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X377">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y377">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z377">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AA377">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB377">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC377">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD377">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE377">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF377">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG377">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH377" t="inlineStr">
         <is>
@@ -61830,10 +61830,10 @@
         </is>
       </c>
       <c r="AJ377">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK377">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL377">
         <v>0</v>
@@ -62095,34 +62095,34 @@
         <v>1.9</v>
       </c>
       <c r="Q379">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R379">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S379">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T379">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U379">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V379">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W379">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X379">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y379">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z379">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA379">
         <v>2.05</v>
@@ -62131,19 +62131,19 @@
         <v>1.8</v>
       </c>
       <c r="AC379">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD379">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE379">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF379">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG379">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH379" t="inlineStr">
         <is>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="AJ379">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK379">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL379">
         <v>0</v>
@@ -62258,55 +62258,55 @@
         <v>5.36</v>
       </c>
       <c r="Q380">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R380">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S380">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T380">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U380">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V380">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W380">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X380">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y380">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z380">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA380">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB380">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AC380">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD380">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE380">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF380">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG380">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH380" t="inlineStr">
         <is>
@@ -62319,10 +62319,10 @@
         </is>
       </c>
       <c r="AJ380">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK380">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL380">
         <v>0</v>
@@ -62421,55 +62421,55 @@
         <v>0</v>
       </c>
       <c r="Q381">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R381">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S381">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T381">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U381">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V381">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W381">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X381">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y381">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z381">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA381">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB381">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC381">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD381">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE381">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF381">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG381">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH381" t="inlineStr">
         <is>
@@ -62482,10 +62482,10 @@
         </is>
       </c>
       <c r="AJ381">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK381">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL381">
         <v>0</v>
@@ -62584,34 +62584,34 @@
         <v>2.36</v>
       </c>
       <c r="Q382">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R382">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S382">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T382">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U382">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V382">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W382">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X382">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y382">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z382">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA382">
         <v>1.85</v>
@@ -62620,19 +62620,19 @@
         <v>1.91</v>
       </c>
       <c r="AC382">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD382">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE382">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF382">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG382">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH382" t="inlineStr">
         <is>
@@ -62645,10 +62645,10 @@
         </is>
       </c>
       <c r="AJ382">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK382">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL382">
         <v>0</v>
@@ -62747,34 +62747,34 @@
         <v>3.9</v>
       </c>
       <c r="Q383">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R383">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S383">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T383">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U383">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V383">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W383">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X383">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y383">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z383">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA383">
         <v>2.03</v>
@@ -62783,19 +62783,19 @@
         <v>1.78</v>
       </c>
       <c r="AC383">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD383">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE383">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF383">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG383">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH383" t="inlineStr">
         <is>
@@ -62808,10 +62808,10 @@
         </is>
       </c>
       <c r="AJ383">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK383">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL383">
         <v>0</v>
@@ -62901,64 +62901,64 @@
         </is>
       </c>
       <c r="N384">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O384">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P384">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q384">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R384">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S384">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T384">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U384">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V384">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W384">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X384">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y384">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z384">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="AA384">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB384">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC384">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD384">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE384">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF384">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG384">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH384" t="inlineStr">
         <is>
@@ -62971,10 +62971,10 @@
         </is>
       </c>
       <c r="AJ384">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK384">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL384">
         <v>0</v>
@@ -63236,55 +63236,55 @@
         <v>0</v>
       </c>
       <c r="Q386">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R386">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S386">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T386">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U386">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V386">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W386">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X386">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y386">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z386">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA386">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB386">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC386">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD386">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE386">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF386">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG386">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH386" t="inlineStr">
         <is>
@@ -63297,10 +63297,10 @@
         </is>
       </c>
       <c r="AJ386">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK386">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL386">
         <v>0</v>
@@ -64214,55 +64214,55 @@
         <v>3</v>
       </c>
       <c r="Q392">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R392">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S392">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T392">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U392">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V392">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W392">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X392">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y392">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z392">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA392">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB392">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC392">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD392">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE392">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF392">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG392">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH392" t="inlineStr">
         <is>
@@ -64275,10 +64275,10 @@
         </is>
       </c>
       <c r="AJ392">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK392">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL392">
         <v>0</v>
@@ -64540,34 +64540,34 @@
         <v>4.9</v>
       </c>
       <c r="Q394">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R394">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S394">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T394">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U394">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V394">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W394">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X394">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y394">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z394">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA394">
         <v>1.83</v>
@@ -64576,19 +64576,19 @@
         <v>1.93</v>
       </c>
       <c r="AC394">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD394">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE394">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF394">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG394">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH394" t="inlineStr">
         <is>
@@ -64601,10 +64601,10 @@
         </is>
       </c>
       <c r="AJ394">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK394">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL394">
         <v>0</v>
@@ -65355,55 +65355,55 @@
         <v>3.58</v>
       </c>
       <c r="Q399">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R399">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S399">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T399">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U399">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V399">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W399">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X399">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y399">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z399">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA399">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB399">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC399">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD399">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE399">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF399">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG399">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH399" t="inlineStr">
         <is>
@@ -65416,10 +65416,10 @@
         </is>
       </c>
       <c r="AJ399">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK399">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL399">
         <v>0</v>
@@ -65509,64 +65509,64 @@
         </is>
       </c>
       <c r="N400">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O400">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P400">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q400">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R400">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S400">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T400">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U400">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V400">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W400">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X400">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y400">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z400">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA400">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB400">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC400">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD400">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE400">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF400">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG400">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH400" t="inlineStr">
         <is>
@@ -65579,10 +65579,10 @@
         </is>
       </c>
       <c r="AJ400">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK400">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL400">
         <v>0</v>
@@ -65681,55 +65681,55 @@
         <v>3.58</v>
       </c>
       <c r="Q401">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R401">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S401">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T401">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U401">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V401">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W401">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X401">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y401">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z401">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA401">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB401">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC401">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD401">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE401">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF401">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG401">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH401" t="inlineStr">
         <is>
@@ -65742,10 +65742,10 @@
         </is>
       </c>
       <c r="AJ401">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK401">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL401">
         <v>0</v>
@@ -66170,55 +66170,55 @@
         <v>2.32</v>
       </c>
       <c r="Q404">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R404">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S404">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T404">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U404">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V404">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W404">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X404">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y404">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z404">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA404">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB404">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC404">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD404">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE404">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF404">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG404">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH404" t="inlineStr">
         <is>
@@ -66231,10 +66231,10 @@
         </is>
       </c>
       <c r="AJ404">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK404">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL404">
         <v>0</v>
@@ -66333,55 +66333,55 @@
         <v>2.39</v>
       </c>
       <c r="Q405">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R405">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S405">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T405">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U405">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V405">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W405">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X405">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y405">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z405">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA405">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB405">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC405">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD405">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE405">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF405">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG405">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH405" t="inlineStr">
         <is>
@@ -66394,10 +66394,10 @@
         </is>
       </c>
       <c r="AJ405">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK405">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL405">
         <v>0</v>
@@ -66496,34 +66496,34 @@
         <v>5.91</v>
       </c>
       <c r="Q406">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R406">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S406">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T406">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U406">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V406">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W406">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X406">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y406">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z406">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA406">
         <v>1.83</v>
@@ -66532,19 +66532,19 @@
         <v>1.93</v>
       </c>
       <c r="AC406">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD406">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE406">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF406">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG406">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH406" t="inlineStr">
         <is>
@@ -66557,10 +66557,10 @@
         </is>
       </c>
       <c r="AJ406">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK406">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL406">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P2">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="Q2">
         <v>2.46</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="O3">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="Q3">
         <v>2.8</v>
@@ -852,10 +852,10 @@
         <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK3">
         <v>1.57</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="O4">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK4">
         <v>1.22</v>
@@ -1293,7 +1293,7 @@
         <v>3.25</v>
       </c>
       <c r="P6">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -1329,7 +1329,7 @@
         <v>2.06</v>
       </c>
       <c r="AB6">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
         <v>3.48</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
         <v>1.91</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P7">
         <v>2.02</v>
       </c>
       <c r="Q7">
-        <v>4.03</v>
+        <v>3.44</v>
       </c>
       <c r="R7">
         <v>2.08</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK7">
         <v>1.21</v>
@@ -1631,7 +1631,7 @@
         <v>1.34</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="U8">
         <v>2.75</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
         <v>1.65</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="O11">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="P11">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q11">
         <v>4.76</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="O14">
-        <v>3.61</v>
+        <v>3.48</v>
       </c>
       <c r="P14">
-        <v>2.24</v>
+        <v>2.59</v>
       </c>
       <c r="Q14">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="R14">
         <v>2.11</v>
@@ -2612,31 +2612,31 @@
         <v>3.21</v>
       </c>
       <c r="U14">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA14">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB14">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AD14">
         <v>1.33</v>
@@ -2645,10 +2645,10 @@
         <v>1.09</v>
       </c>
       <c r="AF14">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG14">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.27</v>
       </c>
       <c r="AK14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="O20">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>2.88</v>
+        <v>2.27</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -3590,10 +3590,10 @@
         <v>3.8</v>
       </c>
       <c r="U20">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="V20">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W20">
         <v>1.13</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.32</v>
+        <v>2.91</v>
       </c>
       <c r="O23">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="Q23">
         <v>3.3</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Q24">
-        <v>2.43</v>
+        <v>1.61</v>
       </c>
       <c r="R24">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="U24">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z24">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA24">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB24">
         <v>2.33</v>
       </c>
       <c r="AC24">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD24">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE24">
         <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AG24">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK24">
-        <v>1.79</v>
+        <v>3.9</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.46</v>
+        <v>3.25</v>
       </c>
       <c r="O25">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="P25">
-        <v>7.05</v>
+        <v>1.87</v>
       </c>
       <c r="Q25">
-        <v>1.61</v>
+        <v>3.4</v>
       </c>
       <c r="R25">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T25">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="U25">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="V25">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z25">
-        <v>4.5</v>
+        <v>6.26</v>
       </c>
       <c r="AA25">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="AB25">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AC25">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="AD25">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AE25">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF25">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AG25">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>3.9</v>
+        <v>1.33</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>2.5</v>
       </c>
       <c r="R26">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="S26">
         <v>1.11</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="R27">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="S27">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>4.8</v>
+        <v>3.56</v>
       </c>
       <c r="U27">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="V27">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="W27">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>6.26</v>
+        <v>4.4</v>
       </c>
       <c r="AA27">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AC27">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD27">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AE27">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="O31">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="Q31">
         <v>2.87</v>
@@ -5377,43 +5377,43 @@
         <v>2.14</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z31">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA31">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB31">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AD31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF31">
         <v>1.62</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
         <v>1.5</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>5.99</v>
+        <v>4.98</v>
       </c>
       <c r="O32">
-        <v>4.26</v>
+        <v>3.92</v>
       </c>
       <c r="P32">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Q32">
         <v>5.5</v>
       </c>
       <c r="R32">
-        <v>2.26</v>
+        <v>2.41</v>
       </c>
       <c r="S32">
         <v>1.36</v>
@@ -5555,25 +5555,25 @@
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA32">
         <v>1.79</v>
       </c>
       <c r="AB32">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC32">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AD32">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE32">
         <v>1.15</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK32">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,22 +5688,22 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q33">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="R33">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="S33">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T33">
         <v>2.75</v>
@@ -5727,13 +5727,13 @@
         <v>2.88</v>
       </c>
       <c r="AA33">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB33">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="AD33">
         <v>1.25</v>
@@ -5745,7 +5745,7 @@
         <v>1.87</v>
       </c>
       <c r="AG33">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="O34">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="Q34">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="R34">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
         <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="U34">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
         <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>2.97</v>
+        <v>3.69</v>
       </c>
       <c r="AA34">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB34">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC34">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="AD34">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AG34">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
+        <v>1.25</v>
+      </c>
+      <c r="AK34">
         <v>1.36</v>
-      </c>
-      <c r="AK34">
-        <v>1.4</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="O36">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P36">
-        <v>4.54</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="O40">
-        <v>3.91</v>
+        <v>4.02</v>
       </c>
       <c r="P40">
-        <v>4.71</v>
+        <v>4.32</v>
       </c>
       <c r="Q40">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="R40">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="U40">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z40">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA40">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AB40">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AC40">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG40">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="P41">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -7007,31 +7007,31 @@
         <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
         <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB41">
         <v>1.95</v>
@@ -7158,28 +7158,28 @@
         <v>2.45</v>
       </c>
       <c r="O42">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q42">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="R42">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
         <v>3.3</v>
       </c>
       <c r="U42">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="V42">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W42">
         <v>1.08</v>
@@ -7188,31 +7188,31 @@
         <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>4</v>
+        <v>4.42</v>
       </c>
       <c r="AA42">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AC42">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="AD42">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AE42">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
         <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,31 +7318,31 @@
         </is>
       </c>
       <c r="N43">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="O43">
-        <v>4.2</v>
+        <v>4.04</v>
       </c>
       <c r="P43">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q43">
-        <v>6.38</v>
+        <v>5.03</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U43">
         <v>2.88</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W43">
         <v>1.06</v>
@@ -7351,7 +7351,7 @@
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z43">
         <v>3.14</v>
@@ -7372,10 +7372,10 @@
         <v>1.07</v>
       </c>
       <c r="AF43">
+        <v>1.95</v>
+      </c>
+      <c r="AG43">
         <v>1.75</v>
-      </c>
-      <c r="AG43">
-        <v>1.95</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q44">
         <v>2.78</v>
@@ -7532,13 +7532,13 @@
         <v>1.27</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
         <v>1.7</v>
       </c>
       <c r="AG44">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q45">
         <v>2.86</v>
@@ -7662,19 +7662,19 @@
         <v>1.4</v>
       </c>
       <c r="T45">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="U45">
         <v>3.04</v>
       </c>
       <c r="V45">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
         <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
         <v>1.32</v>
@@ -7692,13 +7692,13 @@
         <v>3.42</v>
       </c>
       <c r="AD45">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE45">
         <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG45">
         <v>1.91</v>
@@ -9120,22 +9120,22 @@
         <v>3.3</v>
       </c>
       <c r="Q54">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S54">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U54">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="V54">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W54">
         <v>1.11</v>
@@ -9144,31 +9144,31 @@
         <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z54">
-        <v>4.7</v>
+        <v>4.35</v>
       </c>
       <c r="AA54">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB54">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AC54">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AD54">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AE54">
         <v>1.21</v>
       </c>
       <c r="AF54">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG54">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
         <v>1.83</v>
@@ -9286,7 +9286,7 @@
         <v>2.04</v>
       </c>
       <c r="R55">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
         <v>1.29</v>
@@ -9310,28 +9310,28 @@
         <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>4.07</v>
+        <v>3.86</v>
       </c>
       <c r="AA55">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB55">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC55">
         <v>2.59</v>
       </c>
       <c r="AD55">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE55">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF55">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG55">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK55">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
+        <v>1.8</v>
+      </c>
+      <c r="O56">
+        <v>3.92</v>
+      </c>
+      <c r="P56">
+        <v>3.28</v>
+      </c>
+      <c r="Q56">
+        <v>2.22</v>
+      </c>
+      <c r="R56">
+        <v>2.34</v>
+      </c>
+      <c r="S56">
+        <v>1.22</v>
+      </c>
+      <c r="T56">
+        <v>3.55</v>
+      </c>
+      <c r="U56">
+        <v>2.19</v>
+      </c>
+      <c r="V56">
+        <v>1.62</v>
+      </c>
+      <c r="W56">
+        <v>1.12</v>
+      </c>
+      <c r="X56">
+        <v>1.02</v>
+      </c>
+      <c r="Y56">
+        <v>1.1</v>
+      </c>
+      <c r="Z56">
+        <v>5.15</v>
+      </c>
+      <c r="AA56">
+        <v>1.53</v>
+      </c>
+      <c r="AB56">
+        <v>2.42</v>
+      </c>
+      <c r="AC56">
+        <v>2.28</v>
+      </c>
+      <c r="AD56">
         <v>1.65</v>
       </c>
-      <c r="O56">
-        <v>4.7</v>
-      </c>
-      <c r="P56">
-        <v>4.14</v>
-      </c>
-      <c r="Q56">
-        <v>1.94</v>
-      </c>
-      <c r="R56">
-        <v>2.64</v>
-      </c>
-      <c r="S56">
-        <v>1.13</v>
-      </c>
-      <c r="T56">
-        <v>4.6</v>
-      </c>
-      <c r="U56">
-        <v>1.82</v>
-      </c>
-      <c r="V56">
-        <v>1.89</v>
-      </c>
-      <c r="W56">
-        <v>1.23</v>
-      </c>
-      <c r="X56">
-        <v>1.01</v>
-      </c>
-      <c r="Y56">
-        <v>1.03</v>
-      </c>
-      <c r="Z56">
-        <v>7.4</v>
-      </c>
-      <c r="AA56">
-        <v>1.24</v>
-      </c>
-      <c r="AB56">
-        <v>3.34</v>
-      </c>
-      <c r="AC56">
-        <v>1.68</v>
-      </c>
-      <c r="AD56">
-        <v>2.05</v>
-      </c>
       <c r="AE56">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AF56">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AG56">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="O57">
+        <v>4.2</v>
+      </c>
+      <c r="P57">
+        <v>3.9</v>
+      </c>
+      <c r="Q57">
+        <v>2</v>
+      </c>
+      <c r="R57">
+        <v>2.64</v>
+      </c>
+      <c r="S57">
+        <v>1.13</v>
+      </c>
+      <c r="T57">
+        <v>4.6</v>
+      </c>
+      <c r="U57">
+        <v>1.83</v>
+      </c>
+      <c r="V57">
+        <v>1.89</v>
+      </c>
+      <c r="W57">
+        <v>1.23</v>
+      </c>
+      <c r="X57">
+        <v>1.01</v>
+      </c>
+      <c r="Y57">
+        <v>1.03</v>
+      </c>
+      <c r="Z57">
+        <v>7.4</v>
+      </c>
+      <c r="AA57">
+        <v>1.22</v>
+      </c>
+      <c r="AB57">
         <v>3.8</v>
       </c>
-      <c r="P57">
-        <v>3.43</v>
-      </c>
-      <c r="Q57">
-        <v>2.22</v>
-      </c>
-      <c r="R57">
-        <v>2.34</v>
-      </c>
-      <c r="S57">
-        <v>1.22</v>
-      </c>
-      <c r="T57">
-        <v>3.8</v>
-      </c>
-      <c r="U57">
-        <v>2.11</v>
-      </c>
-      <c r="V57">
-        <v>1.61</v>
-      </c>
-      <c r="W57">
-        <v>1.12</v>
-      </c>
-      <c r="X57">
-        <v>1.02</v>
-      </c>
-      <c r="Y57">
-        <v>1.1</v>
-      </c>
-      <c r="Z57">
-        <v>5.15</v>
-      </c>
-      <c r="AA57">
-        <v>1.53</v>
-      </c>
-      <c r="AB57">
-        <v>2.42</v>
-      </c>
       <c r="AC57">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AD57">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="AE57">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AF57">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AG57">
-        <v>2.49</v>
+        <v>3.04</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9775,7 +9775,7 @@
         <v>2.12</v>
       </c>
       <c r="R58">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S58">
         <v>1.2</v>
@@ -9784,28 +9784,28 @@
         <v>4</v>
       </c>
       <c r="U58">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="V58">
         <v>1.73</v>
       </c>
       <c r="W58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
         <v>1.09</v>
       </c>
       <c r="Z58">
-        <v>5.3</v>
+        <v>5.98</v>
       </c>
       <c r="AA58">
         <v>1.39</v>
       </c>
       <c r="AB58">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="AC58">
         <v>2.08</v>
@@ -9814,7 +9814,7 @@
         <v>1.7</v>
       </c>
       <c r="AE58">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AF58">
         <v>1.43</v>
@@ -9926,34 +9926,34 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O59">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P59">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="Q59">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="R59">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="S59">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T59">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U59">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="V59">
         <v>1.36</v>
       </c>
       <c r="W59">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X59">
         <v>1.02</v>
@@ -9962,19 +9962,19 @@
         <v>1.32</v>
       </c>
       <c r="Z59">
-        <v>3.24</v>
+        <v>2.88</v>
       </c>
       <c r="AA59">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB59">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC59">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AD59">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE59">
         <v>1.03</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK59">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q62">
         <v>3</v>
@@ -10578,34 +10578,34 @@
         </is>
       </c>
       <c r="N63">
-        <v>4.45</v>
+        <v>4.05</v>
       </c>
       <c r="O63">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="P63">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="Q63">
-        <v>3.71</v>
+        <v>4.65</v>
       </c>
       <c r="R63">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S63">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T63">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U63">
         <v>2.28</v>
       </c>
       <c r="V63">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X63">
         <v>1.01</v>
@@ -10617,16 +10617,16 @@
         <v>4.55</v>
       </c>
       <c r="AA63">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AB63">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AC63">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AD63">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE63">
         <v>1.2</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10907,22 +10907,22 @@
         <v>1.59</v>
       </c>
       <c r="O65">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="P65">
-        <v>5.02</v>
+        <v>5.07</v>
       </c>
       <c r="Q65">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S65">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U65">
         <v>2.4</v>
@@ -11070,10 +11070,10 @@
         <v>2.29</v>
       </c>
       <c r="O66">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="Q66">
         <v>2.88</v>
@@ -11106,10 +11106,10 @@
         <v>3.2</v>
       </c>
       <c r="AA66">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB66">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC66">
         <v>3.14</v>
@@ -11236,7 +11236,7 @@
         <v>3.28</v>
       </c>
       <c r="P67">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="Q67">
         <v>2.7</v>
@@ -11257,7 +11257,7 @@
         <v>1.36</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X67">
         <v>1.04</v>
@@ -11272,7 +11272,7 @@
         <v>2.15</v>
       </c>
       <c r="AB67">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC67">
         <v>3.74</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK67">
         <v>1.66</v>
@@ -11402,55 +11402,55 @@
         <v>1.72</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="O69">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P69">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q69">
         <v>3.73</v>
@@ -11595,10 +11595,10 @@
         <v>3.5</v>
       </c>
       <c r="AA69">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB69">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AC69">
         <v>2.97</v>
@@ -11607,13 +11607,13 @@
         <v>1.3</v>
       </c>
       <c r="AE69">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF69">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG69">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="AK69">
         <v>1.25</v>
@@ -11719,31 +11719,31 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O70">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q70">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R70">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
         <v>2.66</v>
       </c>
       <c r="U70">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="V70">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W70">
         <v>1.06</v>
@@ -11758,10 +11758,10 @@
         <v>3.05</v>
       </c>
       <c r="AA70">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AB70">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC70">
         <v>3.1</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,19 +11882,19 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O71">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P71">
         <v>3.9</v>
       </c>
       <c r="Q71">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="R71">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="S71">
         <v>1.3</v>
@@ -11903,10 +11903,10 @@
         <v>2.84</v>
       </c>
       <c r="U71">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="V71">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
         <v>1.07</v>
@@ -11921,10 +11921,10 @@
         <v>3.58</v>
       </c>
       <c r="AA71">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AB71">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AC71">
         <v>2.83</v>
@@ -11936,10 +11936,10 @@
         <v>1.14</v>
       </c>
       <c r="AF71">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG71">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK71">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O85">
         <v>3.4</v>
       </c>
       <c r="P85">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q85">
         <v>2.74</v>
@@ -14185,13 +14185,13 @@
         <v>3.12</v>
       </c>
       <c r="U85">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="V85">
         <v>1.55</v>
       </c>
       <c r="W85">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X85">
         <v>1.03</v>
@@ -14200,28 +14200,28 @@
         <v>1.18</v>
       </c>
       <c r="Z85">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="AA85">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AB85">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AC85">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="AD85">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AE85">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF85">
         <v>1.47</v>
       </c>
       <c r="AG85">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK85">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="O86">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="Q86">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="R86">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="S86">
         <v>1.25</v>
       </c>
       <c r="T86">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="U86">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V86">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W86">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z86">
-        <v>4.65</v>
+        <v>4.85</v>
       </c>
       <c r="AA86">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB86">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AC86">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AD86">
+        <v>1.54</v>
+      </c>
+      <c r="AE86">
+        <v>1.21</v>
+      </c>
+      <c r="AF86">
         <v>1.47</v>
       </c>
-      <c r="AE86">
-        <v>1.15</v>
-      </c>
-      <c r="AF86">
-        <v>1.55</v>
-      </c>
       <c r="AG86">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK86">
         <v>1.68</v>
@@ -14490,80 +14490,80 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="O87">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P87">
-        <v>3.06</v>
+        <v>2.55</v>
       </c>
       <c r="Q87">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="R87">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S87">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T87">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="U87">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="V87">
+        <v>1.44</v>
+      </c>
+      <c r="W87">
+        <v>1.1</v>
+      </c>
+      <c r="X87">
+        <v>1.02</v>
+      </c>
+      <c r="Y87">
+        <v>1.22</v>
+      </c>
+      <c r="Z87">
+        <v>3.8</v>
+      </c>
+      <c r="AA87">
+        <v>1.82</v>
+      </c>
+      <c r="AB87">
+        <v>2</v>
+      </c>
+      <c r="AC87">
+        <v>3.02</v>
+      </c>
+      <c r="AD87">
         <v>1.37</v>
       </c>
-      <c r="W87">
-        <v>1.08</v>
-      </c>
-      <c r="X87">
-        <v>1.01</v>
-      </c>
-      <c r="Y87">
-        <v>1.24</v>
-      </c>
-      <c r="Z87">
-        <v>3.34</v>
-      </c>
-      <c r="AA87">
-        <v>1.93</v>
-      </c>
-      <c r="AB87">
-        <v>1.77</v>
-      </c>
-      <c r="AC87">
-        <v>3.14</v>
-      </c>
-      <c r="AD87">
+      <c r="AE87">
+        <v>1.14</v>
+      </c>
+      <c r="AF87">
+        <v>1.6</v>
+      </c>
+      <c r="AG87">
+        <v>2.15</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
         <v>1.27</v>
       </c>
-      <c r="AE87">
-        <v>1.06</v>
-      </c>
-      <c r="AF87">
-        <v>1.75</v>
-      </c>
-      <c r="AG87">
-        <v>1.95</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>1.28</v>
-      </c>
       <c r="AK87">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,10 +14662,10 @@
         <v>2</v>
       </c>
       <c r="Q88">
-        <v>3.63</v>
+        <v>3.15</v>
       </c>
       <c r="R88">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="S88">
         <v>1.25</v>
@@ -14674,13 +14674,13 @@
         <v>3.7</v>
       </c>
       <c r="U88">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V88">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W88">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -14689,22 +14689,22 @@
         <v>1.17</v>
       </c>
       <c r="Z88">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="AA88">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB88">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="AC88">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AD88">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE88">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF88">
         <v>1.5</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK88">
         <v>1.28</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O89">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P89">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q89">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="R89">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S89">
         <v>1.22</v>
       </c>
       <c r="T89">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="U89">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V89">
+        <v>1.47</v>
+      </c>
+      <c r="W89">
+        <v>1.15</v>
+      </c>
+      <c r="X89">
+        <v>1.02</v>
+      </c>
+      <c r="Y89">
+        <v>1.16</v>
+      </c>
+      <c r="Z89">
+        <v>4.92</v>
+      </c>
+      <c r="AA89">
+        <v>1.57</v>
+      </c>
+      <c r="AB89">
+        <v>2.35</v>
+      </c>
+      <c r="AC89">
+        <v>1.97</v>
+      </c>
+      <c r="AD89">
         <v>1.44</v>
       </c>
-      <c r="W89">
-        <v>1.08</v>
-      </c>
-      <c r="X89">
-        <v>1.01</v>
-      </c>
-      <c r="Y89">
-        <v>1.13</v>
-      </c>
-      <c r="Z89">
-        <v>3.2</v>
-      </c>
-      <c r="AA89">
-        <v>1.47</v>
-      </c>
-      <c r="AB89">
-        <v>1.92</v>
-      </c>
-      <c r="AC89">
-        <v>2.07</v>
-      </c>
-      <c r="AD89">
-        <v>1.39</v>
-      </c>
       <c r="AE89">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF89">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AG89">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AK89">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,80 +14979,80 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="O90">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P90">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q90">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="R90">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="S90">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="T90">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="U90">
-        <v>2.26</v>
+        <v>1.69</v>
       </c>
       <c r="V90">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="W90">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
+        <v>1.06</v>
+      </c>
+      <c r="Z90">
+        <v>4.1</v>
+      </c>
+      <c r="AA90">
+        <v>1.36</v>
+      </c>
+      <c r="AB90">
+        <v>3.1</v>
+      </c>
+      <c r="AC90">
+        <v>1.85</v>
+      </c>
+      <c r="AD90">
+        <v>1.9</v>
+      </c>
+      <c r="AE90">
+        <v>1.29</v>
+      </c>
+      <c r="AF90">
+        <v>1.38</v>
+      </c>
+      <c r="AG90">
+        <v>2.77</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
         <v>1.16</v>
       </c>
-      <c r="Z90">
-        <v>4.92</v>
-      </c>
-      <c r="AA90">
-        <v>1.53</v>
-      </c>
-      <c r="AB90">
-        <v>2.01</v>
-      </c>
-      <c r="AC90">
-        <v>1.97</v>
-      </c>
-      <c r="AD90">
-        <v>1.44</v>
-      </c>
-      <c r="AE90">
-        <v>1.18</v>
-      </c>
-      <c r="AF90">
-        <v>1.36</v>
-      </c>
-      <c r="AG90">
-        <v>2.47</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.08</v>
-      </c>
       <c r="AK90">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
+        <v>1.95</v>
+      </c>
+      <c r="O91">
+        <v>3.5</v>
+      </c>
+      <c r="P91">
+        <v>3.1</v>
+      </c>
+      <c r="Q91">
+        <v>2.45</v>
+      </c>
+      <c r="R91">
+        <v>2.24</v>
+      </c>
+      <c r="S91">
+        <v>1.25</v>
+      </c>
+      <c r="T91">
+        <v>3.5</v>
+      </c>
+      <c r="U91">
+        <v>2.32</v>
+      </c>
+      <c r="V91">
         <v>1.57</v>
       </c>
-      <c r="O91">
-        <v>4.5</v>
-      </c>
-      <c r="P91">
-        <v>4.2</v>
-      </c>
-      <c r="Q91">
-        <v>2.02</v>
-      </c>
-      <c r="R91">
-        <v>2.61</v>
-      </c>
-      <c r="S91">
-        <v>1.18</v>
-      </c>
-      <c r="T91">
-        <v>4.5</v>
-      </c>
-      <c r="U91">
-        <v>1.69</v>
-      </c>
-      <c r="V91">
-        <v>1.64</v>
-      </c>
       <c r="W91">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z91">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA91">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AB91">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC91">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="AD91">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AE91">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF91">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG91">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK91">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O92">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P92">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q92">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="R92">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S92">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T92">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U92">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="V92">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X92">
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z92">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA92">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AB92">
-        <v>2.33</v>
+        <v>1.92</v>
       </c>
       <c r="AC92">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="AD92">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AE92">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AF92">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK92">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15507,7 +15507,7 @@
         <v>3.95</v>
       </c>
       <c r="AA93">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AB93">
         <v>1.91</v>
@@ -15541,7 +15541,7 @@
         <v>1.22</v>
       </c>
       <c r="AK93">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,80 +15631,80 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="O94">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="P94">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="Q94">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="R94">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="S94">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="T94">
-        <v>2.48</v>
+        <v>2.79</v>
       </c>
       <c r="U94">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="V94">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W94">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z94">
-        <v>2.69</v>
+        <v>3.19</v>
       </c>
       <c r="AA94">
-        <v>2.39</v>
+        <v>2.11</v>
       </c>
       <c r="AB94">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AC94">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AD94">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE94">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF94">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG94">
+        <v>1.92</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ94">
+        <v>1.35</v>
+      </c>
+      <c r="AK94">
         <v>1.78</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ94">
-        <v>1.38</v>
-      </c>
-      <c r="AK94">
-        <v>1.73</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16784,19 +16784,19 @@
         <v>4.2</v>
       </c>
       <c r="R101">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S101">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T101">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="U101">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V101">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="W101">
         <v>1.25</v>
@@ -16811,10 +16811,10 @@
         <v>7.6</v>
       </c>
       <c r="AA101">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB101">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AC101">
         <v>1.74</v>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK101">
         <v>1.2</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,31 +20847,31 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q126">
-        <v>4.33</v>
+        <v>2.15</v>
       </c>
       <c r="R126">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S126">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T126">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="U126">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V126">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W126">
         <v>1.1</v>
@@ -20880,31 +20880,31 @@
         <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z126">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA126">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AB126">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AC126">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AD126">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE126">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF126">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG126">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK126">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,31 +21010,31 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O127">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P127">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q127">
-        <v>2.15</v>
+        <v>4.33</v>
       </c>
       <c r="R127">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S127">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T127">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="U127">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V127">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W127">
         <v>1.1</v>
@@ -21043,31 +21043,31 @@
         <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z127">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA127">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB127">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AC127">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AD127">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE127">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF127">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG127">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK127">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,61 +24433,61 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="O148">
-        <v>4.36</v>
+        <v>3.84</v>
       </c>
       <c r="P148">
-        <v>4.36</v>
+        <v>3.14</v>
       </c>
       <c r="Q148">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="R148">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="S148">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T148">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U148">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V148">
         <v>1.64</v>
       </c>
       <c r="W148">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X148">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z148">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA148">
+        <v>1.63</v>
+      </c>
+      <c r="AB148">
+        <v>2.15</v>
+      </c>
+      <c r="AC148">
+        <v>2.33</v>
+      </c>
+      <c r="AD148">
+        <v>1.52</v>
+      </c>
+      <c r="AE148">
+        <v>1.18</v>
+      </c>
+      <c r="AF148">
         <v>1.5</v>
-      </c>
-      <c r="AB148">
-        <v>2.62</v>
-      </c>
-      <c r="AC148">
-        <v>2.2</v>
-      </c>
-      <c r="AD148">
-        <v>1.6</v>
-      </c>
-      <c r="AE148">
-        <v>1.22</v>
-      </c>
-      <c r="AF148">
-        <v>1.53</v>
       </c>
       <c r="AG148">
         <v>2.5</v>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK148">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,64 +24596,64 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="O149">
-        <v>6.49</v>
+        <v>4.36</v>
       </c>
       <c r="P149">
-        <v>9.1</v>
+        <v>4.36</v>
       </c>
       <c r="Q149">
-        <v>1.73</v>
+        <v>2.32</v>
       </c>
       <c r="R149">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="S149">
+        <v>1.23</v>
+      </c>
+      <c r="T149">
+        <v>3.7</v>
+      </c>
+      <c r="U149">
+        <v>2.28</v>
+      </c>
+      <c r="V149">
+        <v>1.64</v>
+      </c>
+      <c r="W149">
         <v>1.13</v>
       </c>
-      <c r="T149">
-        <v>5.2</v>
-      </c>
-      <c r="U149">
-        <v>1.86</v>
-      </c>
-      <c r="V149">
-        <v>1.91</v>
-      </c>
-      <c r="W149">
-        <v>1.3</v>
-      </c>
       <c r="X149">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y149">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z149">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA149">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AB149">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC149">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AD149">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AE149">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AF149">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG149">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AK149">
-        <v>2.8</v>
+        <v>1.94</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,31 +24759,31 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.84</v>
+        <v>2.37</v>
       </c>
       <c r="O150">
-        <v>4.27</v>
+        <v>4.06</v>
       </c>
       <c r="P150">
-        <v>4.21</v>
+        <v>2.88</v>
       </c>
       <c r="Q150">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="R150">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="S150">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T150">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U150">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="V150">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W150">
         <v>1.17</v>
@@ -24795,25 +24795,25 @@
         <v>1.13</v>
       </c>
       <c r="Z150">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA150">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="AB150">
         <v>2.35</v>
       </c>
       <c r="AC150">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD150">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE150">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF150">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG150">
         <v>2.5</v>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK150">
-        <v>2.13</v>
+        <v>1.61</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,58 +24922,58 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.29</v>
+        <v>1.84</v>
       </c>
       <c r="O151">
-        <v>3.84</v>
+        <v>4.27</v>
       </c>
       <c r="P151">
-        <v>3.14</v>
+        <v>4.21</v>
       </c>
       <c r="Q151">
+        <v>2.24</v>
+      </c>
+      <c r="R151">
+        <v>2.44</v>
+      </c>
+      <c r="S151">
+        <v>1.24</v>
+      </c>
+      <c r="T151">
+        <v>3.75</v>
+      </c>
+      <c r="U151">
         <v>2.35</v>
       </c>
-      <c r="R151">
-        <v>2.29</v>
-      </c>
-      <c r="S151">
-        <v>1.25</v>
-      </c>
-      <c r="T151">
-        <v>3.6</v>
-      </c>
-      <c r="U151">
-        <v>2.3</v>
-      </c>
       <c r="V151">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W151">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X151">
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z151">
         <v>4.6</v>
       </c>
       <c r="AA151">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AB151">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AC151">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AD151">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AE151">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF151">
         <v>1.5</v>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK151">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.37</v>
+        <v>1.33</v>
       </c>
       <c r="O152">
-        <v>4.06</v>
+        <v>6.49</v>
       </c>
       <c r="P152">
-        <v>2.88</v>
+        <v>9.1</v>
       </c>
       <c r="Q152">
-        <v>2.54</v>
+        <v>1.73</v>
       </c>
       <c r="R152">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="S152">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T152">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="U152">
-        <v>2.41</v>
+        <v>1.86</v>
       </c>
       <c r="V152">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="W152">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="X152">
         <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z152">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA152">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="AB152">
-        <v>2.35</v>
+        <v>3.75</v>
       </c>
       <c r="AC152">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD152">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AE152">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AF152">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG152">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AK152">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,19 +25248,19 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.47</v>
+        <v>3.21</v>
       </c>
       <c r="O153">
-        <v>4.93</v>
+        <v>3.64</v>
       </c>
       <c r="P153">
-        <v>7.6</v>
+        <v>2.33</v>
       </c>
       <c r="Q153">
-        <v>1.87</v>
+        <v>3.14</v>
       </c>
       <c r="R153">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="S153">
         <v>1.35</v>
@@ -25269,43 +25269,43 @@
         <v>3.12</v>
       </c>
       <c r="U153">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V153">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W153">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X153">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z153">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AA153">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB153">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AC153">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="AD153">
         <v>1.38</v>
       </c>
       <c r="AE153">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF153">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AG153">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AK153">
-        <v>3</v>
+        <v>1.37</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,19 +25411,19 @@
         </is>
       </c>
       <c r="N154">
-        <v>3.21</v>
+        <v>1.47</v>
       </c>
       <c r="O154">
-        <v>3.64</v>
+        <v>4.93</v>
       </c>
       <c r="P154">
-        <v>2.33</v>
+        <v>7.6</v>
       </c>
       <c r="Q154">
-        <v>3.14</v>
+        <v>1.87</v>
       </c>
       <c r="R154">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="S154">
         <v>1.35</v>
@@ -25432,59 +25432,59 @@
         <v>3.12</v>
       </c>
       <c r="U154">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V154">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W154">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X154">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y154">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z154">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AA154">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB154">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AC154">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="AD154">
         <v>1.38</v>
       </c>
       <c r="AE154">
+        <v>1.11</v>
+      </c>
+      <c r="AF154">
+        <v>2.1</v>
+      </c>
+      <c r="AG154">
+        <v>1.73</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ154">
         <v>1.1</v>
       </c>
-      <c r="AF154">
-        <v>1.58</v>
-      </c>
-      <c r="AG154">
-        <v>2.26</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ154">
-        <v>1.26</v>
-      </c>
       <c r="AK154">
-        <v>1.37</v>
+        <v>3</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -26724,55 +26724,55 @@
         <v>0</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S162">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T162">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U162">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V162">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W162">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X162">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z162">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA162">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB162">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC162">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD162">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE162">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF162">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG162">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK162">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="O167">
-        <v>3.06</v>
+        <v>4.1</v>
       </c>
       <c r="P167">
-        <v>2.73</v>
+        <v>7.27</v>
       </c>
       <c r="Q167">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="R167">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S167">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T167">
+        <v>3.2</v>
+      </c>
+      <c r="U167">
         <v>2.53</v>
       </c>
-      <c r="U167">
-        <v>2.82</v>
-      </c>
       <c r="V167">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W167">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X167">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y167">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z167">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AA167">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AB167">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AC167">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="AD167">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE167">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF167">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG167">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK167">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,80 +27693,80 @@
         </is>
       </c>
       <c r="N168">
+        <v>2.35</v>
+      </c>
+      <c r="O168">
+        <v>3.06</v>
+      </c>
+      <c r="P168">
+        <v>2.73</v>
+      </c>
+      <c r="Q168">
+        <v>3</v>
+      </c>
+      <c r="R168">
+        <v>2.05</v>
+      </c>
+      <c r="S168">
         <v>1.44</v>
       </c>
-      <c r="O168">
-        <v>4.1</v>
-      </c>
-      <c r="P168">
-        <v>7.27</v>
-      </c>
-      <c r="Q168">
-        <v>1.91</v>
-      </c>
-      <c r="R168">
-        <v>2.3</v>
-      </c>
-      <c r="S168">
+      <c r="T168">
+        <v>2.53</v>
+      </c>
+      <c r="U168">
+        <v>2.82</v>
+      </c>
+      <c r="V168">
+        <v>1.36</v>
+      </c>
+      <c r="W168">
+        <v>1.05</v>
+      </c>
+      <c r="X168">
+        <v>1.04</v>
+      </c>
+      <c r="Y168">
+        <v>1.33</v>
+      </c>
+      <c r="Z168">
+        <v>3</v>
+      </c>
+      <c r="AA168">
+        <v>2.04</v>
+      </c>
+      <c r="AB168">
+        <v>1.67</v>
+      </c>
+      <c r="AC168">
+        <v>3.8</v>
+      </c>
+      <c r="AD168">
+        <v>1.22</v>
+      </c>
+      <c r="AE168">
+        <v>1.05</v>
+      </c>
+      <c r="AF168">
+        <v>1.8</v>
+      </c>
+      <c r="AG168">
+        <v>1.9</v>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ168">
         <v>1.3</v>
       </c>
-      <c r="T168">
-        <v>3.2</v>
-      </c>
-      <c r="U168">
-        <v>2.53</v>
-      </c>
-      <c r="V168">
-        <v>1.4</v>
-      </c>
-      <c r="W168">
-        <v>1.06</v>
-      </c>
-      <c r="X168">
-        <v>1.02</v>
-      </c>
-      <c r="Y168">
-        <v>1.25</v>
-      </c>
-      <c r="Z168">
-        <v>3.6</v>
-      </c>
-      <c r="AA168">
-        <v>1.8</v>
-      </c>
-      <c r="AB168">
-        <v>1.87</v>
-      </c>
-      <c r="AC168">
-        <v>3.13</v>
-      </c>
-      <c r="AD168">
-        <v>1.3</v>
-      </c>
-      <c r="AE168">
-        <v>1.08</v>
-      </c>
-      <c r="AF168">
-        <v>2</v>
-      </c>
-      <c r="AG168">
-        <v>1.7</v>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ168">
-        <v>1.13</v>
-      </c>
       <c r="AK168">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27865,55 +27865,55 @@
         <v>4.18</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S169">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T169">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U169">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V169">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W169">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X169">
         <v>0</v>
       </c>
       <c r="Y169">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z169">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC169">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE169">
         <v>0</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG169">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK169">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.71</v>
+        <v>2.99</v>
       </c>
       <c r="O176">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="P176">
-        <v>4.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q176">
-        <v>2.27</v>
+        <v>3.5</v>
       </c>
       <c r="R176">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S176">
         <v>1.3</v>
       </c>
       <c r="T176">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U176">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V176">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W176">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X176">
         <v>1.04</v>
       </c>
       <c r="Y176">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z176">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AA176">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB176">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC176">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AD176">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE176">
         <v>1.11</v>
       </c>
       <c r="AF176">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG176">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK176">
-        <v>1.96</v>
+        <v>1.34</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,65 +29160,65 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="O177">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P177">
         <v>2.18</v>
       </c>
       <c r="Q177">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R177">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S177">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T177">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U177">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="V177">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="W177">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X177">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y177">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z177">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AA177">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AB177">
+        <v>1.88</v>
+      </c>
+      <c r="AC177">
+        <v>3.3</v>
+      </c>
+      <c r="AD177">
+        <v>1.29</v>
+      </c>
+      <c r="AE177">
+        <v>1.06</v>
+      </c>
+      <c r="AF177">
+        <v>1.7</v>
+      </c>
+      <c r="AG177">
         <v>2</v>
       </c>
-      <c r="AC177">
-        <v>2.66</v>
-      </c>
-      <c r="AD177">
-        <v>1.35</v>
-      </c>
-      <c r="AE177">
-        <v>1.11</v>
-      </c>
-      <c r="AF177">
-        <v>1.6</v>
-      </c>
-      <c r="AG177">
-        <v>2.25</v>
-      </c>
       <c r="AH177" t="inlineStr">
         <is>
           <t>[]</t>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK177">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>3.11</v>
+        <v>1.71</v>
       </c>
       <c r="O178">
-        <v>3.35</v>
+        <v>3.82</v>
       </c>
       <c r="P178">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="Q178">
-        <v>3.7</v>
+        <v>2.27</v>
       </c>
       <c r="R178">
+        <v>2.24</v>
+      </c>
+      <c r="S178">
+        <v>1.3</v>
+      </c>
+      <c r="T178">
+        <v>3.12</v>
+      </c>
+      <c r="U178">
+        <v>2.47</v>
+      </c>
+      <c r="V178">
+        <v>1.46</v>
+      </c>
+      <c r="W178">
+        <v>1.07</v>
+      </c>
+      <c r="X178">
+        <v>1.04</v>
+      </c>
+      <c r="Y178">
+        <v>1.18</v>
+      </c>
+      <c r="Z178">
+        <v>3.84</v>
+      </c>
+      <c r="AA178">
+        <v>1.65</v>
+      </c>
+      <c r="AB178">
         <v>2.1</v>
       </c>
-      <c r="S178">
-        <v>1.39</v>
-      </c>
-      <c r="T178">
-        <v>2.7</v>
-      </c>
-      <c r="U178">
-        <v>2.78</v>
-      </c>
-      <c r="V178">
-        <v>1.37</v>
-      </c>
-      <c r="W178">
-        <v>1.06</v>
-      </c>
-      <c r="X178">
-        <v>1.03</v>
-      </c>
-      <c r="Y178">
-        <v>1.25</v>
-      </c>
-      <c r="Z178">
-        <v>3.28</v>
-      </c>
-      <c r="AA178">
-        <v>1.98</v>
-      </c>
-      <c r="AB178">
-        <v>1.88</v>
-      </c>
       <c r="AC178">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="AD178">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE178">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF178">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG178">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK178">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -30473,55 +30473,55 @@
         <v>11.2</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S185">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T185">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="U185">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V185">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W185">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X185">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y185">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z185">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC185">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD185">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG185">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK185">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.56</v>
+        <v>1.37</v>
       </c>
       <c r="O193">
-        <v>3.2</v>
+        <v>4.85</v>
       </c>
       <c r="P193">
-        <v>2.69</v>
+        <v>7.39</v>
       </c>
       <c r="Q193">
-        <v>3.06</v>
+        <v>1.83</v>
       </c>
       <c r="R193">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="S193">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="T193">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="U193">
-        <v>2.87</v>
+        <v>2.21</v>
       </c>
       <c r="V193">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="W193">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X193">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y193">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="Z193">
-        <v>2.92</v>
+        <v>4.75</v>
       </c>
       <c r="AA193">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="AB193">
-        <v>1.73</v>
+        <v>2.37</v>
       </c>
       <c r="AC193">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="AD193">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AE193">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF193">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AG193">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK193">
-        <v>1.44</v>
+        <v>2.88</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>3.05</v>
+        <v>2.37</v>
       </c>
       <c r="O195">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P195">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="Q195">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="R195">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S195">
         <v>1.35</v>
       </c>
       <c r="T195">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U195">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="V195">
         <v>1.42</v>
       </c>
       <c r="W195">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X195">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y195">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z195">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AA195">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB195">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC195">
-        <v>2.97</v>
+        <v>3.16</v>
       </c>
       <c r="AD195">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE195">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF195">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG195">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>1.27</v>
       </c>
       <c r="AK195">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.37</v>
+        <v>2.56</v>
       </c>
       <c r="O196">
-        <v>4.85</v>
+        <v>3.2</v>
       </c>
       <c r="P196">
-        <v>7.39</v>
+        <v>2.69</v>
       </c>
       <c r="Q196">
-        <v>1.83</v>
+        <v>3.06</v>
       </c>
       <c r="R196">
-        <v>2.55</v>
+        <v>1.97</v>
       </c>
       <c r="S196">
+        <v>1.45</v>
+      </c>
+      <c r="T196">
+        <v>2.5</v>
+      </c>
+      <c r="U196">
+        <v>2.87</v>
+      </c>
+      <c r="V196">
+        <v>1.35</v>
+      </c>
+      <c r="W196">
+        <v>1.04</v>
+      </c>
+      <c r="X196">
+        <v>1.01</v>
+      </c>
+      <c r="Y196">
+        <v>1.31</v>
+      </c>
+      <c r="Z196">
+        <v>2.92</v>
+      </c>
+      <c r="AA196">
+        <v>2.11</v>
+      </c>
+      <c r="AB196">
+        <v>1.73</v>
+      </c>
+      <c r="AC196">
+        <v>3.45</v>
+      </c>
+      <c r="AD196">
         <v>1.25</v>
       </c>
-      <c r="T196">
-        <v>3.75</v>
-      </c>
-      <c r="U196">
-        <v>2.21</v>
-      </c>
-      <c r="V196">
-        <v>1.6</v>
-      </c>
-      <c r="W196">
-        <v>1.12</v>
-      </c>
-      <c r="X196">
-        <v>1.03</v>
-      </c>
-      <c r="Y196">
-        <v>1.12</v>
-      </c>
-      <c r="Z196">
-        <v>4.75</v>
-      </c>
-      <c r="AA196">
-        <v>1.55</v>
-      </c>
-      <c r="AB196">
-        <v>2.37</v>
-      </c>
-      <c r="AC196">
-        <v>2.3</v>
-      </c>
-      <c r="AD196">
-        <v>1.49</v>
-      </c>
       <c r="AE196">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AF196">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG196">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK196">
-        <v>2.88</v>
+        <v>1.44</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.37</v>
+        <v>3.05</v>
       </c>
       <c r="O198">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P198">
-        <v>2.9</v>
+        <v>2.22</v>
       </c>
       <c r="Q198">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="R198">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S198">
         <v>1.35</v>
       </c>
       <c r="T198">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U198">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="V198">
         <v>1.42</v>
       </c>
       <c r="W198">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X198">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y198">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z198">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA198">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB198">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC198">
-        <v>3.16</v>
+        <v>2.97</v>
       </c>
       <c r="AD198">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE198">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF198">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG198">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>1.27</v>
       </c>
       <c r="AK198">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,80 +33561,80 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.18</v>
+        <v>1.28</v>
       </c>
       <c r="O204">
-        <v>3.54</v>
+        <v>5.4</v>
       </c>
       <c r="P204">
-        <v>3.05</v>
+        <v>9.6</v>
       </c>
       <c r="Q204">
-        <v>2.48</v>
+        <v>1.54</v>
       </c>
       <c r="R204">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="S204">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T204">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="U204">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="V204">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="W204">
+        <v>1.15</v>
+      </c>
+      <c r="X204">
+        <v>1.01</v>
+      </c>
+      <c r="Y204">
+        <v>1.11</v>
+      </c>
+      <c r="Z204">
+        <v>4.95</v>
+      </c>
+      <c r="AA204">
+        <v>1.44</v>
+      </c>
+      <c r="AB204">
+        <v>2.66</v>
+      </c>
+      <c r="AC204">
+        <v>2.23</v>
+      </c>
+      <c r="AD204">
+        <v>1.62</v>
+      </c>
+      <c r="AE204">
+        <v>1.21</v>
+      </c>
+      <c r="AF204">
+        <v>1.95</v>
+      </c>
+      <c r="AG204">
+        <v>1.75</v>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ204">
         <v>1.08</v>
       </c>
-      <c r="X204">
-        <v>1.04</v>
-      </c>
-      <c r="Y204">
-        <v>1.17</v>
-      </c>
-      <c r="Z204">
-        <v>3.98</v>
-      </c>
-      <c r="AA204">
-        <v>1.72</v>
-      </c>
-      <c r="AB204">
-        <v>2.11</v>
-      </c>
-      <c r="AC204">
-        <v>2.79</v>
-      </c>
-      <c r="AD204">
-        <v>1.44</v>
-      </c>
-      <c r="AE204">
-        <v>1.1</v>
-      </c>
-      <c r="AF204">
-        <v>1.57</v>
-      </c>
-      <c r="AG204">
-        <v>2.26</v>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ204">
-        <v>1.3</v>
-      </c>
       <c r="AK204">
-        <v>1.62</v>
+        <v>3.81</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,80 +33724,80 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.28</v>
+        <v>2.18</v>
       </c>
       <c r="O205">
-        <v>5.4</v>
+        <v>3.54</v>
       </c>
       <c r="P205">
-        <v>9.6</v>
+        <v>3.05</v>
       </c>
       <c r="Q205">
-        <v>1.54</v>
+        <v>2.48</v>
       </c>
       <c r="R205">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="S205">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T205">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="U205">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="V205">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="W205">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X205">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y205">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z205">
-        <v>4.95</v>
+        <v>3.98</v>
       </c>
       <c r="AA205">
+        <v>1.72</v>
+      </c>
+      <c r="AB205">
+        <v>2.11</v>
+      </c>
+      <c r="AC205">
+        <v>2.79</v>
+      </c>
+      <c r="AD205">
         <v>1.44</v>
       </c>
-      <c r="AB205">
-        <v>2.66</v>
-      </c>
-      <c r="AC205">
-        <v>2.23</v>
-      </c>
-      <c r="AD205">
+      <c r="AE205">
+        <v>1.1</v>
+      </c>
+      <c r="AF205">
+        <v>1.57</v>
+      </c>
+      <c r="AG205">
+        <v>2.26</v>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ205">
+        <v>1.3</v>
+      </c>
+      <c r="AK205">
         <v>1.62</v>
-      </c>
-      <c r="AE205">
-        <v>1.21</v>
-      </c>
-      <c r="AF205">
-        <v>1.95</v>
-      </c>
-      <c r="AG205">
-        <v>1.75</v>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ205">
-        <v>1.08</v>
-      </c>
-      <c r="AK205">
-        <v>3.81</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="O214">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P214">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="Q214">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R214">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S214">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T214">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U214">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="V214">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W214">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X214">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z214">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="AA214">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB214">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC214">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="AD214">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE214">
         <v>1.11</v>
       </c>
       <c r="AF214">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG214">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="O216">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P216">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="Q216">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R216">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S216">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T216">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U216">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="V216">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W216">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X216">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y216">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z216">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="AA216">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB216">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC216">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AD216">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE216">
         <v>1.11</v>
       </c>
       <c r="AF216">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG216">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -36830,55 +36830,55 @@
         <v>4.73</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T224">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V224">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X224">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC224">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD224">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK224">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -41424,10 +41424,10 @@
         <v>0</v>
       </c>
       <c r="AA252">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB252">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC252">
         <v>0</v>
@@ -41587,10 +41587,10 @@
         <v>0</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC253">
         <v>0</v>
@@ -41913,10 +41913,10 @@
         <v>0</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC255">
         <v>0</v>
@@ -42372,55 +42372,55 @@
         <v>0</v>
       </c>
       <c r="Q258">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R258">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S258">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T258">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U258">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V258">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W258">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X258">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y258">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z258">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA258">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB258">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC258">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD258">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE258">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF258">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG258">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK258">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>6.05</v>
+        <v>2.07</v>
       </c>
       <c r="O272">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="P272">
-        <v>1.45</v>
+        <v>3.61</v>
       </c>
       <c r="Q272">
-        <v>6.35</v>
+        <v>2.63</v>
       </c>
       <c r="R272">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
       <c r="S272">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T272">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U272">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V272">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W272">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X272">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y272">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="Z272">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA272">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB272">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="AC272">
-        <v>2.62</v>
+        <v>3.76</v>
       </c>
       <c r="AD272">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE272">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF272">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG272">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK272">
-        <v>1.07</v>
+        <v>1.73</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>2.07</v>
+        <v>6.05</v>
       </c>
       <c r="O273">
+        <v>4.5</v>
+      </c>
+      <c r="P273">
+        <v>1.45</v>
+      </c>
+      <c r="Q273">
+        <v>6.35</v>
+      </c>
+      <c r="R273">
+        <v>2.49</v>
+      </c>
+      <c r="S273">
+        <v>1.3</v>
+      </c>
+      <c r="T273">
         <v>3.2</v>
       </c>
-      <c r="P273">
-        <v>3.61</v>
-      </c>
-      <c r="Q273">
+      <c r="U273">
         <v>2.63</v>
       </c>
-      <c r="R273">
-        <v>2.13</v>
-      </c>
-      <c r="S273">
-        <v>1.4</v>
-      </c>
-      <c r="T273">
-        <v>2.75</v>
-      </c>
-      <c r="U273">
-        <v>3</v>
-      </c>
       <c r="V273">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W273">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X273">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y273">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="Z273">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA273">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AB273">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="AC273">
-        <v>3.76</v>
+        <v>2.62</v>
       </c>
       <c r="AD273">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE273">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF273">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG273">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK273">
-        <v>1.73</v>
+        <v>1.07</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>3.02</v>
+        <v>4.38</v>
       </c>
       <c r="O291">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P291">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="Q291">
-        <v>3.22</v>
+        <v>5.08</v>
       </c>
       <c r="R291">
-        <v>2.17</v>
+        <v>2.59</v>
       </c>
       <c r="S291">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T291">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U291">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="V291">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W291">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X291">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y291">
         <v>1.15</v>
       </c>
       <c r="Z291">
-        <v>4.3</v>
+        <v>5.05</v>
       </c>
       <c r="AA291">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AB291">
-        <v>2.17</v>
+        <v>2.53</v>
       </c>
       <c r="AC291">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="AD291">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AE291">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF291">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG291">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK291">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>4.38</v>
+        <v>3.02</v>
       </c>
       <c r="O292">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P292">
-        <v>1.68</v>
+        <v>2.18</v>
       </c>
       <c r="Q292">
-        <v>5.08</v>
+        <v>3.22</v>
       </c>
       <c r="R292">
-        <v>2.59</v>
+        <v>2.17</v>
       </c>
       <c r="S292">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T292">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U292">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="V292">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="W292">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X292">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y292">
         <v>1.15</v>
       </c>
       <c r="Z292">
-        <v>5.05</v>
+        <v>4.3</v>
       </c>
       <c r="AA292">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AB292">
-        <v>2.53</v>
+        <v>2.17</v>
       </c>
       <c r="AC292">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="AD292">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AE292">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF292">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG292">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK292">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -54099,64 +54099,64 @@
         </is>
       </c>
       <c r="N330">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O330">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P330">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q330">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R330">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S330">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T330">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U330">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V330">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W330">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X330">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y330">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z330">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA330">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB330">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC330">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD330">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE330">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF330">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG330">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK330">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G357">
@@ -58500,49 +58500,49 @@
         </is>
       </c>
       <c r="N357">
-        <v>2.64</v>
+        <v>2.28</v>
       </c>
       <c r="O357">
-        <v>3.39</v>
+        <v>3.33</v>
       </c>
       <c r="P357">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="Q357">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="R357">
         <v>2.1</v>
       </c>
       <c r="S357">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T357">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="U357">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V357">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W357">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X357">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y357">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z357">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA357">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB357">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC357">
         <v>3.28</v>
@@ -58551,13 +58551,13 @@
         <v>1.25</v>
       </c>
       <c r="AE357">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF357">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AG357">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH357" t="inlineStr">
         <is>
@@ -58570,10 +58570,10 @@
         </is>
       </c>
       <c r="AJ357">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK357">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AL357">
         <v>0</v>
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G358">
@@ -58663,49 +58663,49 @@
         </is>
       </c>
       <c r="N358">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="O358">
-        <v>3.33</v>
+        <v>3.39</v>
       </c>
       <c r="P358">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="Q358">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="R358">
         <v>2.1</v>
       </c>
       <c r="S358">
+        <v>1.33</v>
+      </c>
+      <c r="T358">
+        <v>3</v>
+      </c>
+      <c r="U358">
+        <v>2.88</v>
+      </c>
+      <c r="V358">
         <v>1.36</v>
       </c>
-      <c r="T358">
-        <v>2.67</v>
-      </c>
-      <c r="U358">
-        <v>2.75</v>
-      </c>
-      <c r="V358">
-        <v>1.4</v>
-      </c>
       <c r="W358">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X358">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y358">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z358">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA358">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AB358">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC358">
         <v>3.28</v>
@@ -58714,13 +58714,13 @@
         <v>1.25</v>
       </c>
       <c r="AE358">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF358">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AG358">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH358" t="inlineStr">
         <is>
@@ -58733,10 +58733,10 @@
         </is>
       </c>
       <c r="AJ358">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK358">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AL358">
         <v>0</v>
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G364">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G365">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G366">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G368">
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G371">
@@ -60782,64 +60782,64 @@
         </is>
       </c>
       <c r="N371">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="O371">
-        <v>3.61</v>
+        <v>4.08</v>
       </c>
       <c r="P371">
-        <v>4.17</v>
+        <v>5.98</v>
       </c>
       <c r="Q371">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="R371">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="S371">
+        <v>1.29</v>
+      </c>
+      <c r="T371">
+        <v>3.3</v>
+      </c>
+      <c r="U371">
+        <v>2.55</v>
+      </c>
+      <c r="V371">
+        <v>1.45</v>
+      </c>
+      <c r="W371">
+        <v>1.08</v>
+      </c>
+      <c r="X371">
+        <v>1.02</v>
+      </c>
+      <c r="Y371">
+        <v>1.18</v>
+      </c>
+      <c r="Z371">
+        <v>3.88</v>
+      </c>
+      <c r="AA371">
+        <v>1.88</v>
+      </c>
+      <c r="AB371">
+        <v>1.98</v>
+      </c>
+      <c r="AC371">
+        <v>2.7</v>
+      </c>
+      <c r="AD371">
         <v>1.36</v>
-      </c>
-      <c r="T371">
-        <v>2.88</v>
-      </c>
-      <c r="U371">
-        <v>2.88</v>
-      </c>
-      <c r="V371">
-        <v>1.36</v>
-      </c>
-      <c r="W371">
-        <v>1.05</v>
-      </c>
-      <c r="X371">
-        <v>1</v>
-      </c>
-      <c r="Y371">
-        <v>1.3</v>
-      </c>
-      <c r="Z371">
-        <v>3.3</v>
-      </c>
-      <c r="AA371">
-        <v>2.03</v>
-      </c>
-      <c r="AB371">
-        <v>1.83</v>
-      </c>
-      <c r="AC371">
-        <v>3.2</v>
-      </c>
-      <c r="AD371">
-        <v>1.26</v>
       </c>
       <c r="AE371">
         <v>1.1</v>
       </c>
       <c r="AF371">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG371">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AH371" t="inlineStr">
         <is>
@@ -60852,10 +60852,10 @@
         </is>
       </c>
       <c r="AJ371">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK371">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AL371">
         <v>0</v>
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G372">
@@ -60945,64 +60945,64 @@
         </is>
       </c>
       <c r="N372">
-        <v>1.59</v>
+        <v>1.91</v>
       </c>
       <c r="O372">
-        <v>4.08</v>
+        <v>3.61</v>
       </c>
       <c r="P372">
-        <v>5.98</v>
+        <v>4.17</v>
       </c>
       <c r="Q372">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="R372">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="S372">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T372">
+        <v>2.88</v>
+      </c>
+      <c r="U372">
+        <v>2.88</v>
+      </c>
+      <c r="V372">
+        <v>1.36</v>
+      </c>
+      <c r="W372">
+        <v>1.05</v>
+      </c>
+      <c r="X372">
+        <v>1</v>
+      </c>
+      <c r="Y372">
+        <v>1.3</v>
+      </c>
+      <c r="Z372">
         <v>3.3</v>
       </c>
-      <c r="U372">
-        <v>2.55</v>
-      </c>
-      <c r="V372">
-        <v>1.45</v>
-      </c>
-      <c r="W372">
-        <v>1.08</v>
-      </c>
-      <c r="X372">
-        <v>1.02</v>
-      </c>
-      <c r="Y372">
-        <v>1.18</v>
-      </c>
-      <c r="Z372">
-        <v>3.88</v>
-      </c>
       <c r="AA372">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AB372">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AC372">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD372">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE372">
         <v>1.1</v>
       </c>
       <c r="AF372">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG372">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AH372" t="inlineStr">
         <is>
@@ -61015,10 +61015,10 @@
         </is>
       </c>
       <c r="AJ372">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK372">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="AL372">
         <v>0</v>
@@ -62380,12 +62380,12 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G381">
@@ -62412,64 +62412,64 @@
         </is>
       </c>
       <c r="N381">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O381">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P381">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q381">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="R381">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S381">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T381">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="U381">
         <v>2.88</v>
       </c>
       <c r="V381">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W381">
+        <v>1.07</v>
+      </c>
+      <c r="X381">
+        <v>1.02</v>
+      </c>
+      <c r="Y381">
+        <v>1.3</v>
+      </c>
+      <c r="Z381">
+        <v>3.05</v>
+      </c>
+      <c r="AA381">
+        <v>1.85</v>
+      </c>
+      <c r="AB381">
+        <v>1.91</v>
+      </c>
+      <c r="AC381">
+        <v>3.28</v>
+      </c>
+      <c r="AD381">
+        <v>1.28</v>
+      </c>
+      <c r="AE381">
         <v>1.06</v>
       </c>
-      <c r="X381">
-        <v>1.01</v>
-      </c>
-      <c r="Y381">
-        <v>1.29</v>
-      </c>
-      <c r="Z381">
-        <v>3.04</v>
-      </c>
-      <c r="AA381">
-        <v>1.98</v>
-      </c>
-      <c r="AB381">
-        <v>1.71</v>
-      </c>
-      <c r="AC381">
-        <v>3.5</v>
-      </c>
-      <c r="AD381">
-        <v>1.22</v>
-      </c>
-      <c r="AE381">
-        <v>1.04</v>
-      </c>
       <c r="AF381">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AG381">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AH381" t="inlineStr">
         <is>
@@ -62482,10 +62482,10 @@
         </is>
       </c>
       <c r="AJ381">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK381">
-        <v>1.92</v>
+        <v>1.4</v>
       </c>
       <c r="AL381">
         <v>0</v>
@@ -62543,12 +62543,12 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G382">
@@ -62575,25 +62575,25 @@
         </is>
       </c>
       <c r="N382">
-        <v>2.83</v>
+        <v>1.75</v>
       </c>
       <c r="O382">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="P382">
-        <v>2.36</v>
+        <v>3.9</v>
       </c>
       <c r="Q382">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="R382">
         <v>2.15</v>
       </c>
       <c r="S382">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T382">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U382">
         <v>2.88</v>
@@ -62608,31 +62608,31 @@
         <v>1.02</v>
       </c>
       <c r="Y382">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z382">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA382">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AB382">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AC382">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD382">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE382">
         <v>1.06</v>
       </c>
       <c r="AF382">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG382">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AH382" t="inlineStr">
         <is>
@@ -62645,10 +62645,10 @@
         </is>
       </c>
       <c r="AJ382">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK382">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AL382">
         <v>0</v>
@@ -62706,12 +62706,12 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G383">
@@ -62738,65 +62738,65 @@
         </is>
       </c>
       <c r="N383">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O383">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P383">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q383">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R383">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S383">
         <v>1.36</v>
       </c>
       <c r="T383">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="U383">
         <v>2.88</v>
       </c>
       <c r="V383">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W383">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X383">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y383">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z383">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA383">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB383">
+        <v>1.71</v>
+      </c>
+      <c r="AC383">
+        <v>3.5</v>
+      </c>
+      <c r="AD383">
+        <v>1.22</v>
+      </c>
+      <c r="AE383">
+        <v>1.04</v>
+      </c>
+      <c r="AF383">
+        <v>1.88</v>
+      </c>
+      <c r="AG383">
         <v>1.78</v>
       </c>
-      <c r="AC383">
-        <v>3.2</v>
-      </c>
-      <c r="AD383">
-        <v>1.26</v>
-      </c>
-      <c r="AE383">
-        <v>1.06</v>
-      </c>
-      <c r="AF383">
-        <v>1.8</v>
-      </c>
-      <c r="AG383">
-        <v>1.89</v>
-      </c>
       <c r="AH383" t="inlineStr">
         <is>
           <t>[]</t>
@@ -62808,10 +62808,10 @@
         </is>
       </c>
       <c r="AJ383">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK383">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AL383">
         <v>0</v>
@@ -63245,16 +63245,16 @@
         <v>1.13</v>
       </c>
       <c r="T386">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="U386">
         <v>1.91</v>
       </c>
       <c r="V386">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W386">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X386">
         <v>1</v>
@@ -63266,10 +63266,10 @@
         <v>6.15</v>
       </c>
       <c r="AA386">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AB386">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AC386">
         <v>1.83</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,28 +1287,28 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="O6">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q6">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
         <v>1.34</v>
       </c>
       <c r="T6">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="V6">
         <v>1.42</v>
@@ -1317,34 +1317,34 @@
         <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z6">
-        <v>3.73</v>
+        <v>3.6</v>
       </c>
       <c r="AA6">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC6">
-        <v>2.92</v>
+        <v>3.09</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
+        <v>3.38</v>
+      </c>
+      <c r="P7">
+        <v>2.02</v>
+      </c>
+      <c r="Q7">
+        <v>3.44</v>
+      </c>
+      <c r="R7">
+        <v>2.08</v>
+      </c>
+      <c r="S7">
+        <v>1.3</v>
+      </c>
+      <c r="T7">
         <v>3.3</v>
       </c>
-      <c r="P7">
-        <v>1.87</v>
-      </c>
-      <c r="Q7">
-        <v>4</v>
-      </c>
-      <c r="R7">
-        <v>2.2</v>
-      </c>
-      <c r="S7">
-        <v>1.34</v>
-      </c>
-      <c r="T7">
-        <v>3.1</v>
-      </c>
       <c r="U7">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.1</v>
@@ -1483,47 +1483,47 @@
         <v>1.02</v>
       </c>
       <c r="Y7">
+        <v>1.25</v>
+      </c>
+      <c r="Z7">
+        <v>3.48</v>
+      </c>
+      <c r="AA7">
+        <v>1.84</v>
+      </c>
+      <c r="AB7">
+        <v>1.98</v>
+      </c>
+      <c r="AC7">
+        <v>3.1</v>
+      </c>
+      <c r="AD7">
+        <v>1.38</v>
+      </c>
+      <c r="AE7">
+        <v>1.08</v>
+      </c>
+      <c r="AF7">
+        <v>1.65</v>
+      </c>
+      <c r="AG7">
+        <v>2.1</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.23</v>
       </c>
-      <c r="Z7">
-        <v>3.6</v>
-      </c>
-      <c r="AA7">
-        <v>1.89</v>
-      </c>
-      <c r="AB7">
-        <v>1.93</v>
-      </c>
-      <c r="AC7">
-        <v>3.09</v>
-      </c>
-      <c r="AD7">
-        <v>1.36</v>
-      </c>
-      <c r="AE7">
-        <v>1.13</v>
-      </c>
-      <c r="AF7">
-        <v>1.71</v>
-      </c>
-      <c r="AG7">
-        <v>2.05</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
+      <c r="AK7">
         <v>1.21</v>
-      </c>
-      <c r="AK7">
-        <v>1.22</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,61 +1613,61 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="O8">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="P8">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="Q8">
-        <v>3.44</v>
+        <v>2.62</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="U8">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
         <v>1.1</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>3.48</v>
+        <v>3.73</v>
       </c>
       <c r="AA8">
         <v>1.84</v>
       </c>
       <c r="AB8">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD8">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
         <v>2.1</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q24">
-        <v>2.43</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T24">
-        <v>3.56</v>
+        <v>4.8</v>
       </c>
       <c r="U24">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>4.4</v>
+        <v>6.26</v>
       </c>
       <c r="AA24">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="AB24">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AC24">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AD24">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AG24">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,65 +4384,65 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Q25">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="R25">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="S25">
+        <v>1.25</v>
+      </c>
+      <c r="T25">
+        <v>3.6</v>
+      </c>
+      <c r="U25">
+        <v>2.25</v>
+      </c>
+      <c r="V25">
+        <v>1.57</v>
+      </c>
+      <c r="W25">
         <v>1.11</v>
-      </c>
-      <c r="T25">
-        <v>5.5</v>
-      </c>
-      <c r="U25">
-        <v>1.79</v>
-      </c>
-      <c r="V25">
-        <v>1.91</v>
-      </c>
-      <c r="W25">
-        <v>1.29</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Z25">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA25">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="AB25">
-        <v>3.49</v>
+        <v>2.33</v>
       </c>
       <c r="AC25">
+        <v>2.38</v>
+      </c>
+      <c r="AD25">
+        <v>1.46</v>
+      </c>
+      <c r="AE25">
+        <v>1.15</v>
+      </c>
+      <c r="AF25">
+        <v>2.1</v>
+      </c>
+      <c r="AG25">
         <v>1.67</v>
       </c>
-      <c r="AD25">
-        <v>2.15</v>
-      </c>
-      <c r="AE25">
-        <v>1.5</v>
-      </c>
-      <c r="AF25">
-        <v>1.26</v>
-      </c>
-      <c r="AG25">
-        <v>3.4</v>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AK25">
-        <v>1.67</v>
+        <v>3.9</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>7.05</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="R26">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="S26">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T26">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="U26">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="V26">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z26">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA26">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="AB26">
-        <v>2.33</v>
+        <v>3.49</v>
       </c>
       <c r="AC26">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AD26">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="AE26">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AF26">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="AG26">
+        <v>3.4</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.21</v>
+      </c>
+      <c r="AK26">
         <v>1.67</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.12</v>
-      </c>
-      <c r="AK26">
-        <v>3.9</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="R27">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="S27">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>4.8</v>
+        <v>3.56</v>
       </c>
       <c r="U27">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="V27">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="W27">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>6.26</v>
+        <v>4.4</v>
       </c>
       <c r="AA27">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AC27">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD27">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AE27">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.98</v>
+        <v>2.67</v>
       </c>
       <c r="O33">
         <v>3.2</v>
       </c>
       <c r="P33">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q33">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="R33">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z33">
-        <v>2.88</v>
+        <v>3.69</v>
       </c>
       <c r="AA33">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AB33">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AC33">
-        <v>3.82</v>
+        <v>3.37</v>
       </c>
       <c r="AD33">
+        <v>1.27</v>
+      </c>
+      <c r="AE33">
+        <v>1.1</v>
+      </c>
+      <c r="AF33">
+        <v>1.71</v>
+      </c>
+      <c r="AG33">
+        <v>1.99</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
         <v>1.25</v>
       </c>
-      <c r="AE33">
-        <v>1.02</v>
-      </c>
-      <c r="AF33">
-        <v>1.87</v>
-      </c>
-      <c r="AG33">
-        <v>1.85</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.29</v>
-      </c>
       <c r="AK33">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.67</v>
+        <v>1.98</v>
       </c>
       <c r="O34">
         <v>3.2</v>
       </c>
       <c r="P34">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q34">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T34">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U34">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z34">
-        <v>3.69</v>
+        <v>2.88</v>
       </c>
       <c r="AA34">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AB34">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AC34">
-        <v>3.37</v>
+        <v>3.82</v>
       </c>
       <c r="AD34">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF34">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AG34">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         <v>3.45</v>
       </c>
       <c r="U40">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="V40">
         <v>1.53</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q50">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB50">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC50">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9153,7 +9153,7 @@
         <v>1.57</v>
       </c>
       <c r="AB54">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC54">
         <v>2.35</v>
@@ -9313,10 +9313,10 @@
         <v>3.86</v>
       </c>
       <c r="AA55">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB55">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC55">
         <v>2.59</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G56">
@@ -9440,77 +9440,77 @@
         <v>1.67</v>
       </c>
       <c r="O56">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P56">
-        <v>4.08</v>
+        <v>3.9</v>
       </c>
       <c r="Q56">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R56">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="S56">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="U56">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="V56">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="W56">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Z56">
-        <v>5.98</v>
+        <v>7.4</v>
       </c>
       <c r="AA56">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AB56">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="AC56">
+        <v>1.73</v>
+      </c>
+      <c r="AD56">
+        <v>2.04</v>
+      </c>
+      <c r="AE56">
+        <v>1.41</v>
+      </c>
+      <c r="AF56">
+        <v>1.32</v>
+      </c>
+      <c r="AG56">
+        <v>3.04</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>1.2</v>
+      </c>
+      <c r="AK56">
         <v>2.08</v>
-      </c>
-      <c r="AD56">
-        <v>1.7</v>
-      </c>
-      <c r="AE56">
-        <v>1.31</v>
-      </c>
-      <c r="AF56">
-        <v>1.43</v>
-      </c>
-      <c r="AG56">
-        <v>2.63</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.15</v>
-      </c>
-      <c r="AK56">
-        <v>2.11</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G58">
@@ -9766,61 +9766,61 @@
         <v>1.67</v>
       </c>
       <c r="O58">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P58">
-        <v>3.9</v>
+        <v>4.08</v>
       </c>
       <c r="Q58">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R58">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="S58">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="T58">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U58">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="V58">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="W58">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Z58">
-        <v>7.4</v>
+        <v>5.98</v>
       </c>
       <c r="AA58">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AB58">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="AC58">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AD58">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AE58">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AF58">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AG58">
-        <v>3.04</v>
+        <v>2.63</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O59">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P59">
         <v>2.7</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10261,34 +10261,34 @@
         <v>2.47</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA61">
         <v>1.95</v>
@@ -10297,19 +10297,19 @@
         <v>1.85</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.6</v>
+        <v>2.37</v>
       </c>
       <c r="O65">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="P65">
-        <v>4.82</v>
+        <v>3</v>
       </c>
       <c r="Q65">
-        <v>2.05</v>
+        <v>3.03</v>
       </c>
       <c r="R65">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T65">
-        <v>3.6</v>
+        <v>3.01</v>
       </c>
       <c r="U65">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="V65">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W65">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="Z65">
-        <v>4.45</v>
+        <v>3.51</v>
       </c>
       <c r="AA65">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB65">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AC65">
-        <v>2.42</v>
+        <v>3.14</v>
       </c>
       <c r="AD65">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AE65">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF65">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AG65">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK65">
-        <v>2.21</v>
+        <v>1.52</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.37</v>
+        <v>1.6</v>
       </c>
       <c r="O67">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="P67">
-        <v>3</v>
+        <v>4.82</v>
       </c>
       <c r="Q67">
-        <v>3.03</v>
+        <v>2.05</v>
       </c>
       <c r="R67">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S67">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>3.01</v>
+        <v>3.6</v>
       </c>
       <c r="U67">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
       <c r="V67">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>3.51</v>
+        <v>4.45</v>
       </c>
       <c r="AA67">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB67">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC67">
-        <v>3.14</v>
+        <v>2.42</v>
       </c>
       <c r="AD67">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE67">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>1.52</v>
+        <v>2.21</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>2.99</v>
       </c>
       <c r="Q75">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R75">
         <v>2.4</v>
       </c>
       <c r="S75">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="T75">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="U75">
-        <v>2.37</v>
+        <v>2.14</v>
       </c>
       <c r="V75">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W75">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X75">
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z75">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AA75">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AB75">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AC75">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD75">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AE75">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AF75">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG75">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK75">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12709,68 +12709,68 @@
         <v>1.81</v>
       </c>
       <c r="R76">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="S76">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T76">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="U76">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="V76">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W76">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z76">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA76">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB76">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AC76">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AD76">
         <v>1.54</v>
       </c>
       <c r="AE76">
+        <v>1.16</v>
+      </c>
+      <c r="AF76">
+        <v>1.79</v>
+      </c>
+      <c r="AG76">
+        <v>1.92</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.15</v>
       </c>
-      <c r="AF76">
-        <v>1.75</v>
-      </c>
-      <c r="AG76">
-        <v>1.94</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.16</v>
-      </c>
       <c r="AK76">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13041,13 +13041,13 @@
         <v>1.2</v>
       </c>
       <c r="T78">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U78">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V78">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W78">
         <v>1.18</v>
@@ -13062,10 +13062,10 @@
         <v>5.6</v>
       </c>
       <c r="AA78">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB78">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AC78">
         <v>2.06</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,19 +14979,19 @@
         </is>
       </c>
       <c r="N90">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O90">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P90">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q90">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="R90">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S90">
         <v>1.25</v>
@@ -15000,40 +15000,40 @@
         <v>3.5</v>
       </c>
       <c r="U90">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V90">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W90">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z90">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA90">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AB90">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AC90">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="AD90">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AE90">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF90">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG90">
         <v>2.38</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK90">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,19 +15305,19 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O92">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P92">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q92">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="R92">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S92">
         <v>1.25</v>
@@ -15326,40 +15326,40 @@
         <v>3.5</v>
       </c>
       <c r="U92">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V92">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W92">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X92">
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z92">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA92">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AB92">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AC92">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="AD92">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AE92">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF92">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG92">
         <v>2.38</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK92">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O102">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P102">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="Q102">
+        <v>2.5</v>
+      </c>
+      <c r="R102">
+        <v>2.2</v>
+      </c>
+      <c r="S102">
+        <v>1.3</v>
+      </c>
+      <c r="T102">
         <v>3.2</v>
       </c>
-      <c r="R102">
-        <v>2.1</v>
-      </c>
-      <c r="S102">
-        <v>1.36</v>
-      </c>
-      <c r="T102">
-        <v>2.88</v>
-      </c>
       <c r="U102">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="V102">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W102">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z102">
-        <v>3.08</v>
+        <v>3.74</v>
       </c>
       <c r="AA102">
+        <v>1.72</v>
+      </c>
+      <c r="AB102">
         <v>2</v>
       </c>
-      <c r="AB102">
-        <v>1.8</v>
-      </c>
       <c r="AC102">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="AD102">
+        <v>1.34</v>
+      </c>
+      <c r="AE102">
+        <v>1.1</v>
+      </c>
+      <c r="AF102">
+        <v>1.61</v>
+      </c>
+      <c r="AG102">
+        <v>2.13</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
         <v>1.22</v>
       </c>
-      <c r="AE102">
-        <v>1.03</v>
-      </c>
-      <c r="AF102">
-        <v>1.75</v>
-      </c>
-      <c r="AG102">
-        <v>1.93</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.25</v>
-      </c>
       <c r="AK102">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
+        <v>2.55</v>
+      </c>
+      <c r="O104">
+        <v>3.1</v>
+      </c>
+      <c r="P104">
+        <v>2.45</v>
+      </c>
+      <c r="Q104">
+        <v>3.2</v>
+      </c>
+      <c r="R104">
+        <v>2.1</v>
+      </c>
+      <c r="S104">
+        <v>1.36</v>
+      </c>
+      <c r="T104">
+        <v>2.88</v>
+      </c>
+      <c r="U104">
+        <v>2.88</v>
+      </c>
+      <c r="V104">
+        <v>1.36</v>
+      </c>
+      <c r="W104">
+        <v>1.07</v>
+      </c>
+      <c r="X104">
+        <v>1</v>
+      </c>
+      <c r="Y104">
+        <v>1.28</v>
+      </c>
+      <c r="Z104">
+        <v>3.08</v>
+      </c>
+      <c r="AA104">
         <v>2</v>
       </c>
-      <c r="O104">
+      <c r="AB104">
+        <v>1.8</v>
+      </c>
+      <c r="AC104">
         <v>3.5</v>
       </c>
-      <c r="P104">
-        <v>3</v>
-      </c>
-      <c r="Q104">
-        <v>2.5</v>
-      </c>
-      <c r="R104">
-        <v>2.2</v>
-      </c>
-      <c r="S104">
-        <v>1.3</v>
-      </c>
-      <c r="T104">
-        <v>3.2</v>
-      </c>
-      <c r="U104">
-        <v>2.63</v>
-      </c>
-      <c r="V104">
+      <c r="AD104">
+        <v>1.22</v>
+      </c>
+      <c r="AE104">
+        <v>1.03</v>
+      </c>
+      <c r="AF104">
+        <v>1.75</v>
+      </c>
+      <c r="AG104">
+        <v>1.93</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
+        <v>1.25</v>
+      </c>
+      <c r="AK104">
         <v>1.44</v>
-      </c>
-      <c r="W104">
-        <v>1.11</v>
-      </c>
-      <c r="X104">
-        <v>1.01</v>
-      </c>
-      <c r="Y104">
-        <v>1.19</v>
-      </c>
-      <c r="Z104">
-        <v>3.74</v>
-      </c>
-      <c r="AA104">
-        <v>1.72</v>
-      </c>
-      <c r="AB104">
-        <v>1.96</v>
-      </c>
-      <c r="AC104">
-        <v>2.78</v>
-      </c>
-      <c r="AD104">
-        <v>1.34</v>
-      </c>
-      <c r="AE104">
-        <v>1.1</v>
-      </c>
-      <c r="AF104">
-        <v>1.61</v>
-      </c>
-      <c r="AG104">
-        <v>2.13</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.22</v>
-      </c>
-      <c r="AK104">
-        <v>1.73</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O108">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="P108">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="Q108">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="R108">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="S108">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T108">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="U108">
-        <v>2.51</v>
+        <v>2.72</v>
       </c>
       <c r="V108">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W108">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
+        <v>1.29</v>
+      </c>
+      <c r="Z108">
+        <v>3.04</v>
+      </c>
+      <c r="AA108">
+        <v>2.07</v>
+      </c>
+      <c r="AB108">
+        <v>1.72</v>
+      </c>
+      <c r="AC108">
+        <v>3.34</v>
+      </c>
+      <c r="AD108">
         <v>1.24</v>
       </c>
-      <c r="Z108">
-        <v>3.34</v>
-      </c>
-      <c r="AA108">
-        <v>1.8</v>
-      </c>
-      <c r="AB108">
-        <v>1.87</v>
-      </c>
-      <c r="AC108">
-        <v>2.97</v>
-      </c>
-      <c r="AD108">
-        <v>1.3</v>
-      </c>
       <c r="AE108">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF108">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG108">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O109">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P109">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA109">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AB109">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18417,19 +18417,19 @@
         <v>2.2</v>
       </c>
       <c r="S111">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T111">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U111">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V111">
         <v>1.5</v>
       </c>
       <c r="W111">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X111">
         <v>1.02</v>
@@ -18444,7 +18444,7 @@
         <v>1.66</v>
       </c>
       <c r="AB111">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC111">
         <v>2.56</v>
@@ -18456,10 +18456,10 @@
         <v>1.12</v>
       </c>
       <c r="AF111">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG111">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
+        <v>1.57</v>
+      </c>
+      <c r="O124">
+        <v>3.7</v>
+      </c>
+      <c r="P124">
+        <v>4.6</v>
+      </c>
+      <c r="Q124">
         <v>2.1</v>
       </c>
-      <c r="O124">
-        <v>3.1</v>
-      </c>
-      <c r="P124">
-        <v>3.25</v>
-      </c>
-      <c r="Q124">
-        <v>2.7</v>
-      </c>
       <c r="R124">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S124">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T124">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="U124">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V124">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W124">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X124">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y124">
         <v>1.25</v>
       </c>
       <c r="Z124">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA124">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB124">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC124">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD124">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE124">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF124">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG124">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK124">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,80 +20847,80 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O126">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P126">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q126">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="R126">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S126">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T126">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="U126">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V126">
         <v>1.42</v>
       </c>
       <c r="W126">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X126">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
+        <v>1.26</v>
+      </c>
+      <c r="Z126">
+        <v>3.69</v>
+      </c>
+      <c r="AA126">
+        <v>1.76</v>
+      </c>
+      <c r="AB126">
+        <v>1.98</v>
+      </c>
+      <c r="AC126">
+        <v>3.12</v>
+      </c>
+      <c r="AD126">
+        <v>1.35</v>
+      </c>
+      <c r="AE126">
+        <v>1.12</v>
+      </c>
+      <c r="AF126">
+        <v>1.67</v>
+      </c>
+      <c r="AG126">
+        <v>2.05</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126">
         <v>1.25</v>
       </c>
-      <c r="Z126">
-        <v>3.8</v>
-      </c>
-      <c r="AA126">
-        <v>1.81</v>
-      </c>
-      <c r="AB126">
-        <v>1.95</v>
-      </c>
-      <c r="AC126">
-        <v>2.9</v>
-      </c>
-      <c r="AD126">
-        <v>1.36</v>
-      </c>
-      <c r="AE126">
-        <v>1.11</v>
-      </c>
-      <c r="AF126">
-        <v>1.75</v>
-      </c>
-      <c r="AG126">
-        <v>2</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>1.17</v>
-      </c>
       <c r="AK126">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,61 +21010,61 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q127">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="R127">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S127">
         <v>1.33</v>
       </c>
       <c r="T127">
-        <v>3.07</v>
+        <v>2.73</v>
       </c>
       <c r="U127">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V127">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W127">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X127">
         <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z127">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="AA127">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB127">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC127">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AD127">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE127">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF127">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG127">
         <v>2.05</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK127">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -22477,43 +22477,43 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="O136">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="P136">
-        <v>6.35</v>
+        <v>6.75</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X136">
         <v>0</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA136">
         <v>1.65</v>
@@ -22522,19 +22522,19 @@
         <v>2.2</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,43 +22640,43 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O137">
         <v>3.4</v>
       </c>
       <c r="P137">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA137">
         <v>1.9</v>
@@ -22685,19 +22685,19 @@
         <v>1.9</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22815,7 +22815,7 @@
         <v>1.62</v>
       </c>
       <c r="R138">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="S138">
         <v>1.23</v>
@@ -22824,10 +22824,10 @@
         <v>3.7</v>
       </c>
       <c r="U138">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V138">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W138">
         <v>1.17</v>
@@ -22839,19 +22839,19 @@
         <v>1.13</v>
       </c>
       <c r="Z138">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AA138">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB138">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC138">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AD138">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE138">
         <v>1.25</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.38</v>
+        <v>2.68</v>
       </c>
       <c r="O139">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="P139">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="Q139">
-        <v>1.95</v>
+        <v>4.05</v>
       </c>
       <c r="R139">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="S139">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T139">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="U139">
-        <v>2.18</v>
+        <v>3.29</v>
       </c>
       <c r="V139">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="W139">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X139">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y139">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="Z139">
-        <v>5.05</v>
+        <v>2.86</v>
       </c>
       <c r="AA139">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="AB139">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC139">
-        <v>2.19</v>
+        <v>3.6</v>
       </c>
       <c r="AD139">
-        <v>1.77</v>
+        <v>1.23</v>
       </c>
       <c r="AE139">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="AF139">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AG139">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK139">
-        <v>2.59</v>
+        <v>1.33</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.68</v>
+        <v>1.42</v>
       </c>
       <c r="O140">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="P140">
-        <v>2.31</v>
+        <v>6</v>
       </c>
       <c r="Q140">
-        <v>4.05</v>
+        <v>1.95</v>
       </c>
       <c r="R140">
-        <v>1.92</v>
+        <v>2.48</v>
       </c>
       <c r="S140">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T140">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="U140">
-        <v>3.29</v>
+        <v>2.18</v>
       </c>
       <c r="V140">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="W140">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X140">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="Z140">
-        <v>2.86</v>
+        <v>5.05</v>
       </c>
       <c r="AA140">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="AB140">
-        <v>1.65</v>
+        <v>2.56</v>
       </c>
       <c r="AC140">
-        <v>3.6</v>
+        <v>2.19</v>
       </c>
       <c r="AD140">
-        <v>1.23</v>
+        <v>1.77</v>
       </c>
       <c r="AE140">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="AF140">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AG140">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK140">
-        <v>1.33</v>
+        <v>2.59</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23660,7 +23660,7 @@
         <v>1.65</v>
       </c>
       <c r="AB143">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AC143">
         <v>2.46</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O147">
         <v>3.3</v>
       </c>
       <c r="P147">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q147">
         <v>2.41</v>
@@ -24312,7 +24312,7 @@
         <v>1.89</v>
       </c>
       <c r="AB147">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC147">
         <v>3.08</v>
@@ -24605,7 +24605,7 @@
         <v>3.18</v>
       </c>
       <c r="Q149">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R149">
         <v>2.45</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="O151">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="P151">
-        <v>4.05</v>
+        <v>6.5</v>
       </c>
       <c r="Q151">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="R151">
-        <v>2.44</v>
+        <v>2.93</v>
       </c>
       <c r="S151">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="T151">
+        <v>5.2</v>
+      </c>
+      <c r="U151">
+        <v>1.75</v>
+      </c>
+      <c r="V151">
+        <v>1.95</v>
+      </c>
+      <c r="W151">
+        <v>1.3</v>
+      </c>
+      <c r="X151">
+        <v>1.01</v>
+      </c>
+      <c r="Y151">
+        <v>1.04</v>
+      </c>
+      <c r="Z151">
+        <v>7.1</v>
+      </c>
+      <c r="AA151">
+        <v>1.28</v>
+      </c>
+      <c r="AB151">
         <v>3.75</v>
       </c>
-      <c r="U151">
-        <v>2.35</v>
-      </c>
-      <c r="V151">
-        <v>1.66</v>
-      </c>
-      <c r="W151">
-        <v>1.17</v>
-      </c>
-      <c r="X151">
-        <v>1.02</v>
-      </c>
-      <c r="Y151">
-        <v>1.13</v>
-      </c>
-      <c r="Z151">
-        <v>4.6</v>
-      </c>
-      <c r="AA151">
-        <v>1.5</v>
-      </c>
-      <c r="AB151">
-        <v>2.4</v>
-      </c>
       <c r="AC151">
-        <v>2.38</v>
+        <v>1.74</v>
       </c>
       <c r="AD151">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AE151">
-        <v>1.21</v>
+        <v>1.51</v>
       </c>
       <c r="AF151">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG151">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK151">
-        <v>2.13</v>
+        <v>3.1</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="O152">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="P152">
-        <v>6.5</v>
+        <v>4.25</v>
       </c>
       <c r="Q152">
-        <v>1.76</v>
+        <v>2.24</v>
       </c>
       <c r="R152">
-        <v>2.93</v>
+        <v>2.44</v>
       </c>
       <c r="S152">
+        <v>1.24</v>
+      </c>
+      <c r="T152">
+        <v>3.75</v>
+      </c>
+      <c r="U152">
+        <v>2.35</v>
+      </c>
+      <c r="V152">
+        <v>1.66</v>
+      </c>
+      <c r="W152">
+        <v>1.17</v>
+      </c>
+      <c r="X152">
+        <v>1.02</v>
+      </c>
+      <c r="Y152">
         <v>1.13</v>
       </c>
-      <c r="T152">
-        <v>5.2</v>
-      </c>
-      <c r="U152">
-        <v>1.75</v>
-      </c>
-      <c r="V152">
-        <v>1.95</v>
-      </c>
-      <c r="W152">
-        <v>1.3</v>
-      </c>
-      <c r="X152">
-        <v>1.01</v>
-      </c>
-      <c r="Y152">
-        <v>1.04</v>
-      </c>
       <c r="Z152">
-        <v>7.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA152">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AB152">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC152">
-        <v>1.74</v>
+        <v>2.38</v>
       </c>
       <c r="AD152">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AE152">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="AF152">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG152">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK152">
-        <v>3.1</v>
+        <v>2.13</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,49 +25248,49 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.31</v>
+        <v>2.9</v>
       </c>
       <c r="O153">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P153">
-        <v>7.75</v>
+        <v>2.35</v>
       </c>
       <c r="Q153">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="R153">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S153">
         <v>1.29</v>
       </c>
       <c r="T153">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U153">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="V153">
         <v>1.45</v>
       </c>
       <c r="W153">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X153">
         <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z153">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AA153">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB153">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AC153">
         <v>2.76</v>
@@ -25299,13 +25299,13 @@
         <v>1.38</v>
       </c>
       <c r="AE153">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF153">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AG153">
-        <v>1.71</v>
+        <v>2.45</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.14</v>
+        <v>1.55</v>
       </c>
       <c r="AK153">
-        <v>3.1</v>
+        <v>1.37</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,49 +25411,49 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.9</v>
+        <v>1.31</v>
       </c>
       <c r="O154">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P154">
-        <v>2.35</v>
+        <v>7.75</v>
       </c>
       <c r="Q154">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="R154">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S154">
         <v>1.29</v>
       </c>
       <c r="T154">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="U154">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="V154">
         <v>1.45</v>
       </c>
       <c r="W154">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X154">
         <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z154">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AA154">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB154">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AC154">
         <v>2.76</v>
@@ -25462,13 +25462,13 @@
         <v>1.38</v>
       </c>
       <c r="AE154">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF154">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AG154">
-        <v>2.45</v>
+        <v>1.71</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="AK154">
-        <v>1.37</v>
+        <v>3.1</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q156">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R156">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S156">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T156">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U156">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V156">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W156">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y156">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z156">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA156">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB156">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC156">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD156">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE156">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF156">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG156">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK156">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -26727,13 +26727,13 @@
         <v>2</v>
       </c>
       <c r="R162">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S162">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T162">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="U162">
         <v>2.27</v>
@@ -26745,19 +26745,19 @@
         <v>1.11</v>
       </c>
       <c r="X162">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y162">
         <v>1.18</v>
       </c>
       <c r="Z162">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="AA162">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB162">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC162">
         <v>2.56</v>
@@ -26769,10 +26769,10 @@
         <v>1.13</v>
       </c>
       <c r="AF162">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG162">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK162">
         <v>2.38</v>
@@ -27044,7 +27044,7 @@
         <v>3.1</v>
       </c>
       <c r="O164">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="P164">
         <v>2.05</v>
@@ -27083,7 +27083,7 @@
         <v>1.97</v>
       </c>
       <c r="AB164">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC164">
         <v>3.34</v>
@@ -27207,16 +27207,16 @@
         <v>5.64</v>
       </c>
       <c r="O165">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P165">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q165">
         <v>5.55</v>
       </c>
       <c r="R165">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S165">
         <v>1.33</v>
@@ -27237,25 +27237,25 @@
         <v>1</v>
       </c>
       <c r="Y165">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z165">
         <v>3.42</v>
       </c>
       <c r="AA165">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB165">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC165">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="AD165">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE165">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF165">
         <v>1.87</v>
@@ -27409,7 +27409,7 @@
         <v>1.66</v>
       </c>
       <c r="AB166">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AC166">
         <v>2.75</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,65 +27530,65 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="O167">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P167">
-        <v>6.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q167">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="R167">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S167">
+        <v>1.37</v>
+      </c>
+      <c r="T167">
+        <v>2.53</v>
+      </c>
+      <c r="U167">
+        <v>2.82</v>
+      </c>
+      <c r="V167">
+        <v>1.33</v>
+      </c>
+      <c r="W167">
+        <v>1.04</v>
+      </c>
+      <c r="X167">
+        <v>1.01</v>
+      </c>
+      <c r="Y167">
         <v>1.31</v>
       </c>
-      <c r="T167">
-        <v>3.11</v>
-      </c>
-      <c r="U167">
-        <v>2.75</v>
-      </c>
-      <c r="V167">
-        <v>1.4</v>
-      </c>
-      <c r="W167">
-        <v>1.08</v>
-      </c>
-      <c r="X167">
+      <c r="Z167">
+        <v>2.92</v>
+      </c>
+      <c r="AA167">
+        <v>2.13</v>
+      </c>
+      <c r="AB167">
+        <v>1.69</v>
+      </c>
+      <c r="AC167">
+        <v>3.78</v>
+      </c>
+      <c r="AD167">
+        <v>1.19</v>
+      </c>
+      <c r="AE167">
         <v>1.02</v>
       </c>
-      <c r="Y167">
-        <v>1.27</v>
-      </c>
-      <c r="Z167">
-        <v>3.58</v>
-      </c>
-      <c r="AA167">
-        <v>1.79</v>
-      </c>
-      <c r="AB167">
+      <c r="AF167">
+        <v>1.8</v>
+      </c>
+      <c r="AG167">
         <v>1.85</v>
       </c>
-      <c r="AC167">
-        <v>3.05</v>
-      </c>
-      <c r="AD167">
-        <v>1.35</v>
-      </c>
-      <c r="AE167">
-        <v>1.12</v>
-      </c>
-      <c r="AF167">
-        <v>1.98</v>
-      </c>
-      <c r="AG167">
-        <v>1.72</v>
-      </c>
       <c r="AH167" t="inlineStr">
         <is>
           <t>[]</t>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AK167">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,80 +27693,80 @@
         </is>
       </c>
       <c r="N168">
+        <v>1.44</v>
+      </c>
+      <c r="O168">
+        <v>4</v>
+      </c>
+      <c r="P168">
+        <v>6.5</v>
+      </c>
+      <c r="Q168">
+        <v>1.91</v>
+      </c>
+      <c r="R168">
         <v>2.3</v>
       </c>
-      <c r="O168">
-        <v>3.1</v>
-      </c>
-      <c r="P168">
+      <c r="S168">
+        <v>1.31</v>
+      </c>
+      <c r="T168">
+        <v>3.11</v>
+      </c>
+      <c r="U168">
+        <v>2.75</v>
+      </c>
+      <c r="V168">
+        <v>1.4</v>
+      </c>
+      <c r="W168">
+        <v>1.08</v>
+      </c>
+      <c r="X168">
+        <v>1.02</v>
+      </c>
+      <c r="Y168">
+        <v>1.27</v>
+      </c>
+      <c r="Z168">
+        <v>3.58</v>
+      </c>
+      <c r="AA168">
+        <v>1.79</v>
+      </c>
+      <c r="AB168">
+        <v>1.85</v>
+      </c>
+      <c r="AC168">
+        <v>3.05</v>
+      </c>
+      <c r="AD168">
+        <v>1.35</v>
+      </c>
+      <c r="AE168">
+        <v>1.12</v>
+      </c>
+      <c r="AF168">
+        <v>1.98</v>
+      </c>
+      <c r="AG168">
+        <v>1.72</v>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ168">
+        <v>1.03</v>
+      </c>
+      <c r="AK168">
         <v>2.7</v>
-      </c>
-      <c r="Q168">
-        <v>2.88</v>
-      </c>
-      <c r="R168">
-        <v>2.1</v>
-      </c>
-      <c r="S168">
-        <v>1.37</v>
-      </c>
-      <c r="T168">
-        <v>2.53</v>
-      </c>
-      <c r="U168">
-        <v>2.82</v>
-      </c>
-      <c r="V168">
-        <v>1.33</v>
-      </c>
-      <c r="W168">
-        <v>1.04</v>
-      </c>
-      <c r="X168">
-        <v>1.01</v>
-      </c>
-      <c r="Y168">
-        <v>1.31</v>
-      </c>
-      <c r="Z168">
-        <v>2.92</v>
-      </c>
-      <c r="AA168">
-        <v>2.13</v>
-      </c>
-      <c r="AB168">
-        <v>1.69</v>
-      </c>
-      <c r="AC168">
-        <v>3.78</v>
-      </c>
-      <c r="AD168">
-        <v>1.19</v>
-      </c>
-      <c r="AE168">
-        <v>1.02</v>
-      </c>
-      <c r="AF168">
-        <v>1.8</v>
-      </c>
-      <c r="AG168">
-        <v>1.85</v>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ168">
-        <v>1.3</v>
-      </c>
-      <c r="AK168">
-        <v>1.57</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>3.4</v>
+        <v>1.66</v>
       </c>
       <c r="O176">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="P176">
-        <v>2.05</v>
+        <v>4.2</v>
       </c>
       <c r="Q176">
-        <v>3.8</v>
+        <v>2.13</v>
       </c>
       <c r="R176">
-        <v>2.09</v>
+        <v>2.49</v>
       </c>
       <c r="S176">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T176">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U176">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
       <c r="V176">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W176">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X176">
         <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z176">
-        <v>3.34</v>
+        <v>4.67</v>
       </c>
       <c r="AA176">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="AB176">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AC176">
-        <v>3.14</v>
+        <v>2.49</v>
       </c>
       <c r="AD176">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AE176">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF176">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG176">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK176">
-        <v>1.27</v>
+        <v>2.11</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.66</v>
+        <v>3.4</v>
       </c>
       <c r="O177">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="P177">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q177">
-        <v>2.13</v>
+        <v>3.8</v>
       </c>
       <c r="R177">
-        <v>2.49</v>
+        <v>2.09</v>
       </c>
       <c r="S177">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T177">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U177">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="V177">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W177">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X177">
         <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z177">
-        <v>4.67</v>
+        <v>3.34</v>
       </c>
       <c r="AA177">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="AB177">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AC177">
-        <v>2.49</v>
+        <v>3.14</v>
       </c>
       <c r="AD177">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AE177">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF177">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG177">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK177">
-        <v>2.11</v>
+        <v>1.27</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29649,10 +29649,10 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="O180">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P180">
         <v>11</v>
@@ -29661,22 +29661,22 @@
         <v>1.36</v>
       </c>
       <c r="R180">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="S180">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="T180">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="U180">
         <v>1.6</v>
       </c>
       <c r="V180">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="W180">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X180">
         <v>1</v>
@@ -29688,25 +29688,25 @@
         <v>12</v>
       </c>
       <c r="AA180">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AB180">
-        <v>4.7</v>
+        <v>5.17</v>
       </c>
       <c r="AC180">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AD180">
-        <v>2.52</v>
+        <v>2.71</v>
       </c>
       <c r="AE180">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AF180">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG180">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK180">
         <v>6</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="O193">
-        <v>3.12</v>
+        <v>3.65</v>
       </c>
       <c r="P193">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q193">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R193">
-        <v>1.96</v>
+        <v>2.47</v>
       </c>
       <c r="S193">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T193">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U193">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="V193">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="W193">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X193">
         <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="Z193">
-        <v>3.12</v>
+        <v>4.8</v>
       </c>
       <c r="AA193">
-        <v>2.17</v>
+        <v>1.49</v>
       </c>
       <c r="AB193">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="AC193">
-        <v>3.89</v>
+        <v>2.35</v>
       </c>
       <c r="AD193">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AE193">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AF193">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AG193">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK193">
         <v>1.44</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,80 +31931,80 @@
         </is>
       </c>
       <c r="N194">
+        <v>3.5</v>
+      </c>
+      <c r="O194">
+        <v>3.5</v>
+      </c>
+      <c r="P194">
+        <v>2</v>
+      </c>
+      <c r="Q194">
+        <v>4</v>
+      </c>
+      <c r="R194">
+        <v>2.1</v>
+      </c>
+      <c r="S194">
+        <v>1.33</v>
+      </c>
+      <c r="T194">
+        <v>3</v>
+      </c>
+      <c r="U194">
+        <v>2.75</v>
+      </c>
+      <c r="V194">
         <v>1.4</v>
       </c>
-      <c r="O194">
-        <v>5</v>
-      </c>
-      <c r="P194">
-        <v>7.5</v>
-      </c>
-      <c r="Q194">
+      <c r="W194">
+        <v>1.06</v>
+      </c>
+      <c r="X194">
+        <v>1.01</v>
+      </c>
+      <c r="Y194">
+        <v>1.27</v>
+      </c>
+      <c r="Z194">
+        <v>3.48</v>
+      </c>
+      <c r="AA194">
+        <v>1.88</v>
+      </c>
+      <c r="AB194">
+        <v>1.96</v>
+      </c>
+      <c r="AC194">
+        <v>3.19</v>
+      </c>
+      <c r="AD194">
+        <v>1.35</v>
+      </c>
+      <c r="AE194">
+        <v>1.13</v>
+      </c>
+      <c r="AF194">
+        <v>1.7</v>
+      </c>
+      <c r="AG194">
+        <v>2</v>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ194">
         <v>1.8</v>
       </c>
-      <c r="R194">
-        <v>2.5</v>
-      </c>
-      <c r="S194">
-        <v>1.25</v>
-      </c>
-      <c r="T194">
-        <v>3.75</v>
-      </c>
-      <c r="U194">
-        <v>2.25</v>
-      </c>
-      <c r="V194">
-        <v>1.57</v>
-      </c>
-      <c r="W194">
-        <v>1.11</v>
-      </c>
-      <c r="X194">
-        <v>1.03</v>
-      </c>
-      <c r="Y194">
-        <v>1.18</v>
-      </c>
-      <c r="Z194">
-        <v>4.66</v>
-      </c>
-      <c r="AA194">
-        <v>1.55</v>
-      </c>
-      <c r="AB194">
-        <v>2.35</v>
-      </c>
-      <c r="AC194">
-        <v>2.3</v>
-      </c>
-      <c r="AD194">
-        <v>1.53</v>
-      </c>
-      <c r="AE194">
-        <v>1.16</v>
-      </c>
-      <c r="AF194">
-        <v>1.77</v>
-      </c>
-      <c r="AG194">
-        <v>1.92</v>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ194">
-        <v>1.14</v>
-      </c>
       <c r="AK194">
-        <v>2.88</v>
+        <v>1.22</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="O195">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P195">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="Q195">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R195">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="S195">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="T195">
-        <v>3.8</v>
+        <v>3.02</v>
       </c>
       <c r="U195">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="V195">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="W195">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X195">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y195">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="Z195">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA195">
-        <v>1.49</v>
+        <v>1.94</v>
       </c>
       <c r="AB195">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AC195">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="AD195">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AE195">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF195">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AG195">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK195">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.85</v>
+        <v>1.4</v>
       </c>
       <c r="O196">
-        <v>3.43</v>
+        <v>5</v>
       </c>
       <c r="P196">
-        <v>2.31</v>
+        <v>7.5</v>
       </c>
       <c r="Q196">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="R196">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S196">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T196">
-        <v>3.09</v>
+        <v>3.75</v>
       </c>
       <c r="U196">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="V196">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W196">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X196">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z196">
-        <v>3.42</v>
+        <v>4.66</v>
       </c>
       <c r="AA196">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AB196">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AC196">
-        <v>2.97</v>
+        <v>2.3</v>
       </c>
       <c r="AD196">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AE196">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF196">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AG196">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK196">
-        <v>1.36</v>
+        <v>2.88</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,52 +32420,52 @@
         </is>
       </c>
       <c r="N197">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="O197">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="P197">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="Q197">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R197">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="S197">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T197">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="U197">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="V197">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W197">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X197">
         <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z197">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AA197">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB197">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC197">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="AD197">
         <v>1.35</v>
@@ -32474,10 +32474,10 @@
         <v>1.13</v>
       </c>
       <c r="AF197">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG197">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AK197">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,31 +32583,31 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O198">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P198">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="Q198">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="R198">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S198">
         <v>1.37</v>
       </c>
       <c r="T198">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U198">
         <v>2.88</v>
       </c>
       <c r="V198">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W198">
         <v>1.06</v>
@@ -32616,31 +32616,31 @@
         <v>1</v>
       </c>
       <c r="Y198">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z198">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA198">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AB198">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC198">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AD198">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE198">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF198">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG198">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK198">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="O199">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="P199">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="Q199">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="R199">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S199">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T199">
+        <v>2.88</v>
+      </c>
+      <c r="U199">
         <v>3</v>
       </c>
-      <c r="U199">
-        <v>2.88</v>
-      </c>
       <c r="V199">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W199">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X199">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z199">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="AA199">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AB199">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC199">
-        <v>3.34</v>
+        <v>3.89</v>
       </c>
       <c r="AD199">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE199">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF199">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG199">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK199">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -34711,55 +34711,55 @@
         <v>2.89</v>
       </c>
       <c r="Q211">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R211">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S211">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T211">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="U211">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="V211">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W211">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X211">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z211">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AA211">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB211">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AC211">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="AD211">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE211">
         <v>1.18</v>
       </c>
       <c r="AF211">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG211">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK211">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34883,7 +34883,7 @@
         <v>1.23</v>
       </c>
       <c r="T212">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="U212">
         <v>2.2</v>
@@ -34898,22 +34898,22 @@
         <v>1.02</v>
       </c>
       <c r="Y212">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z212">
-        <v>5.51</v>
+        <v>4.9</v>
       </c>
       <c r="AA212">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB212">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AC212">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD212">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE212">
         <v>1.22</v>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK212">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="O213">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="P213">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="Q213">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R213">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S213">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T213">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U213">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="V213">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="W213">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X213">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z213">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="AA213">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB213">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AC213">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="AD213">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE213">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF213">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG213">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK213">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,80 +35191,80 @@
         </is>
       </c>
       <c r="N214">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="O214">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P214">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="Q214">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="R214">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S214">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T214">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U214">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="V214">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="W214">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X214">
         <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z214">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="AA214">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB214">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AC214">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="AD214">
+        <v>1.45</v>
+      </c>
+      <c r="AE214">
+        <v>1.17</v>
+      </c>
+      <c r="AF214">
+        <v>1.53</v>
+      </c>
+      <c r="AG214">
+        <v>2.3</v>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ214">
         <v>1.26</v>
       </c>
-      <c r="AE214">
-        <v>1.06</v>
-      </c>
-      <c r="AF214">
-        <v>1.69</v>
-      </c>
-      <c r="AG214">
-        <v>2.02</v>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ214">
-        <v>1.25</v>
-      </c>
       <c r="AK214">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35363,10 +35363,10 @@
         <v>2.43</v>
       </c>
       <c r="Q215">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="R215">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S215">
         <v>1.29</v>
@@ -35375,10 +35375,10 @@
         <v>3.3</v>
       </c>
       <c r="U215">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="V215">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W215">
         <v>1.08</v>
@@ -35387,31 +35387,31 @@
         <v>1.03</v>
       </c>
       <c r="Y215">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z215">
-        <v>4.2</v>
+        <v>4.58</v>
       </c>
       <c r="AA215">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB215">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AC215">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AD215">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE215">
         <v>1.12</v>
       </c>
       <c r="AF215">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG215">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK215">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35526,22 +35526,22 @@
         <v>2.42</v>
       </c>
       <c r="Q216">
-        <v>4.21</v>
+        <v>4.38</v>
       </c>
       <c r="R216">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S216">
         <v>1.33</v>
       </c>
       <c r="T216">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="U216">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V216">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W216">
         <v>1.07</v>
@@ -35550,31 +35550,31 @@
         <v>1</v>
       </c>
       <c r="Y216">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z216">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA216">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB216">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC216">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD216">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE216">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF216">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG216">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="AK216">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O219">
         <v>3.8</v>
       </c>
       <c r="P219">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -36048,7 +36048,7 @@
         <v>1.68</v>
       </c>
       <c r="AB219">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC219">
         <v>2.76</v>
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O223">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q223">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R223">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S223">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T223">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U223">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V223">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W223">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X223">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y223">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z223">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA223">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB223">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC223">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD223">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE223">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF223">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG223">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK223">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37488,19 +37488,19 @@
         <v>2.22</v>
       </c>
       <c r="S228">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T228">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="U228">
         <v>2.34</v>
       </c>
       <c r="V228">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W228">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X228">
         <v>1.02</v>
@@ -37530,7 +37530,7 @@
         <v>1.5</v>
       </c>
       <c r="AG228">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37636,10 +37636,10 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O229">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="P229">
         <v>2.15</v>
@@ -39142,10 +39142,10 @@
         <v>5</v>
       </c>
       <c r="AA238">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB238">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AC238">
         <v>2.19</v>
@@ -40407,7 +40407,7 @@
         </is>
       </c>
       <c r="N246">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="O246">
         <v>3.1</v>
@@ -40446,10 +40446,10 @@
         <v>2.8</v>
       </c>
       <c r="AA246">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AB246">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC246">
         <v>4.13</v>
@@ -40905,34 +40905,34 @@
         <v>2.96</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S249">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T249">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U249">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V249">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W249">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X249">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z249">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA249">
         <v>1.8</v>
@@ -40941,19 +40941,19 @@
         <v>2</v>
       </c>
       <c r="AC249">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD249">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE249">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF249">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG249">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK249">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41068,34 +41068,34 @@
         <v>2.4</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R250">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S250">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T250">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U250">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V250">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W250">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X250">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y250">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z250">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA250">
         <v>1.9</v>
@@ -41104,19 +41104,19 @@
         <v>1.9</v>
       </c>
       <c r="AC250">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD250">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE250">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF250">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG250">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK250">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41222,43 +41222,43 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="O251">
+        <v>3.52</v>
+      </c>
+      <c r="P251">
+        <v>4.05</v>
+      </c>
+      <c r="Q251">
+        <v>2.24</v>
+      </c>
+      <c r="R251">
+        <v>2.13</v>
+      </c>
+      <c r="S251">
+        <v>1.33</v>
+      </c>
+      <c r="T251">
+        <v>3</v>
+      </c>
+      <c r="U251">
+        <v>2.61</v>
+      </c>
+      <c r="V251">
+        <v>1.39</v>
+      </c>
+      <c r="W251">
+        <v>1.06</v>
+      </c>
+      <c r="X251">
+        <v>1.02</v>
+      </c>
+      <c r="Y251">
+        <v>1.25</v>
+      </c>
+      <c r="Z251">
         <v>3.6</v>
-      </c>
-      <c r="P251">
-        <v>4.4</v>
-      </c>
-      <c r="Q251">
-        <v>0</v>
-      </c>
-      <c r="R251">
-        <v>0</v>
-      </c>
-      <c r="S251">
-        <v>0</v>
-      </c>
-      <c r="T251">
-        <v>0</v>
-      </c>
-      <c r="U251">
-        <v>0</v>
-      </c>
-      <c r="V251">
-        <v>0</v>
-      </c>
-      <c r="W251">
-        <v>0</v>
-      </c>
-      <c r="X251">
-        <v>0</v>
-      </c>
-      <c r="Y251">
-        <v>0</v>
-      </c>
-      <c r="Z251">
-        <v>0</v>
       </c>
       <c r="AA251">
         <v>1.95</v>
@@ -41267,19 +41267,19 @@
         <v>1.85</v>
       </c>
       <c r="AC251">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD251">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE251">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF251">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG251">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK251">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="O253">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P253">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q257">
         <v>3.1</v>
@@ -42215,10 +42215,10 @@
         <v>2.24</v>
       </c>
       <c r="S257">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T257">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U257">
         <v>2.25</v>
@@ -42227,7 +42227,7 @@
         <v>1.52</v>
       </c>
       <c r="W257">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X257">
         <v>1.02</v>
@@ -42242,7 +42242,7 @@
         <v>1.66</v>
       </c>
       <c r="AB257">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC257">
         <v>2.52</v>
@@ -43830,64 +43830,64 @@
         </is>
       </c>
       <c r="N267">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="O267">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P267">
         <v>2.95</v>
       </c>
       <c r="Q267">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="R267">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S267">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T267">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U267">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="V267">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W267">
         <v>1.08</v>
       </c>
       <c r="X267">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y267">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z267">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA267">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB267">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AC267">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD267">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE267">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF267">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG267">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK267">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -44162,7 +44162,7 @@
         <v>3.1</v>
       </c>
       <c r="P269">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q269">
         <v>2.88</v>
@@ -44195,10 +44195,10 @@
         <v>2.88</v>
       </c>
       <c r="AA269">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB269">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC269">
         <v>3.5</v>
@@ -44337,7 +44337,7 @@
         <v>1.29</v>
       </c>
       <c r="T270">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U270">
         <v>2.27</v>
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.15</v>
+        <v>5.75</v>
       </c>
       <c r="O271">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="P271">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="Q271">
-        <v>2.86</v>
+        <v>6.35</v>
       </c>
       <c r="R271">
-        <v>1.94</v>
+        <v>2.49</v>
       </c>
       <c r="S271">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T271">
-        <v>2.75</v>
+        <v>3.26</v>
       </c>
       <c r="U271">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="V271">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="W271">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X271">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y271">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z271">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA271">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AB271">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="AC271">
-        <v>3.84</v>
+        <v>2.62</v>
       </c>
       <c r="AD271">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE271">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF271">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG271">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK271">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>5.75</v>
+        <v>2.15</v>
       </c>
       <c r="O272">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="P272">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="Q272">
-        <v>6.35</v>
+        <v>2.86</v>
       </c>
       <c r="R272">
-        <v>2.49</v>
+        <v>1.94</v>
       </c>
       <c r="S272">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T272">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="U272">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="V272">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="W272">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X272">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y272">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="Z272">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA272">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB272">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="AC272">
-        <v>2.62</v>
+        <v>3.84</v>
       </c>
       <c r="AD272">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AE272">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF272">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG272">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK272">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O281">
         <v>4</v>
       </c>
       <c r="P281">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q281">
         <v>5.34</v>
@@ -46151,10 +46151,10 @@
         <v>4.6</v>
       </c>
       <c r="AA281">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB281">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC281">
         <v>2.36</v>
@@ -48273,7 +48273,7 @@
         <v>2.02</v>
       </c>
       <c r="AB294">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC294">
         <v>3.42</v>
@@ -48394,16 +48394,16 @@
         </is>
       </c>
       <c r="N295">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="O295">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P295">
         <v>2.28</v>
       </c>
       <c r="Q295">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R295">
         <v>2.12</v>
@@ -48578,13 +48578,13 @@
         <v>4</v>
       </c>
       <c r="U296">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V296">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W296">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X296">
         <v>1.02</v>
@@ -48596,7 +48596,7 @@
         <v>5.3</v>
       </c>
       <c r="AA296">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AB296">
         <v>2.59</v>
@@ -48630,7 +48630,7 @@
         <v>1.14</v>
       </c>
       <c r="AK296">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48922,7 +48922,7 @@
         <v>4.4</v>
       </c>
       <c r="AA298">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB298">
         <v>2.25</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50063,10 +50063,10 @@
         <v>0</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC305">
         <v>0</v>
@@ -51011,55 +51011,55 @@
         <v>0</v>
       </c>
       <c r="Q311">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R311">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S311">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T311">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U311">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V311">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W311">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X311">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y311">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z311">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA311">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB311">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC311">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD311">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE311">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF311">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG311">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK311">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,64 +51328,64 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q313">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R313">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S313">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T313">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U313">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="V313">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W313">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X313">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y313">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z313">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA313">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB313">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC313">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD313">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE313">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF313">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG313">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK313">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G314">
@@ -51491,64 +51491,64 @@
         </is>
       </c>
       <c r="N314">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O314">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P314">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q314">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R314">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S314">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T314">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U314">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V314">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W314">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X314">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y314">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z314">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AA314">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="AB314">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AC314">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD314">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE314">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF314">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG314">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK314">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -52022,7 +52022,7 @@
         <v>1.44</v>
       </c>
       <c r="AB317">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AC317">
         <v>2.12</v>
@@ -53936,13 +53936,13 @@
         </is>
       </c>
       <c r="N329">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="O329">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P329">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="Q329">
         <v>3.6</v>
@@ -53951,13 +53951,13 @@
         <v>2.25</v>
       </c>
       <c r="S329">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T329">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U329">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="V329">
         <v>1.43</v>
@@ -53990,10 +53990,10 @@
         <v>1.13</v>
       </c>
       <c r="AF329">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG329">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         </is>
       </c>
       <c r="N333">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="O333">
         <v>3.17</v>
@@ -56257,10 +56257,10 @@
         <v>3.44</v>
       </c>
       <c r="AA343">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB343">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC343">
         <v>3.2</v>
@@ -56417,7 +56417,7 @@
         <v>1.14</v>
       </c>
       <c r="Z344">
-        <v>5.69</v>
+        <v>5.75</v>
       </c>
       <c r="AA344">
         <v>1.43</v>
@@ -56454,7 +56454,7 @@
         <v>1.18</v>
       </c>
       <c r="AK344">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AL344">
         <v>0</v>
@@ -56716,55 +56716,55 @@
         <v>0</v>
       </c>
       <c r="Q346">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="R346">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S346">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T346">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U346">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="V346">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W346">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X346">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y346">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z346">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA346">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB346">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC346">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD346">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE346">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF346">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG346">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH346" t="inlineStr">
         <is>
@@ -56777,10 +56777,10 @@
         </is>
       </c>
       <c r="AJ346">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK346">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL346">
         <v>0</v>
@@ -57854,7 +57854,7 @@
         <v>3.8</v>
       </c>
       <c r="P353">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="Q353">
         <v>3.68</v>
@@ -57890,7 +57890,7 @@
         <v>1.47</v>
       </c>
       <c r="AB353">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AC353">
         <v>2.17</v>
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G356">
@@ -58337,49 +58337,49 @@
         </is>
       </c>
       <c r="N356">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="O356">
         <v>3.3</v>
       </c>
       <c r="P356">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q356">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="R356">
         <v>2.1</v>
       </c>
       <c r="S356">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T356">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="U356">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V356">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W356">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X356">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y356">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z356">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA356">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB356">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC356">
         <v>3.28</v>
@@ -58388,13 +58388,13 @@
         <v>1.25</v>
       </c>
       <c r="AE356">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF356">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AG356">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH356" t="inlineStr">
         <is>
@@ -58407,10 +58407,10 @@
         </is>
       </c>
       <c r="AJ356">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK356">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AL356">
         <v>0</v>
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G357">
@@ -58500,49 +58500,49 @@
         </is>
       </c>
       <c r="N357">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="O357">
         <v>3.3</v>
       </c>
       <c r="P357">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q357">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="R357">
         <v>2.1</v>
       </c>
       <c r="S357">
+        <v>1.35</v>
+      </c>
+      <c r="T357">
+        <v>3</v>
+      </c>
+      <c r="U357">
+        <v>2.88</v>
+      </c>
+      <c r="V357">
         <v>1.36</v>
       </c>
-      <c r="T357">
-        <v>2.67</v>
-      </c>
-      <c r="U357">
-        <v>2.75</v>
-      </c>
-      <c r="V357">
-        <v>1.4</v>
-      </c>
       <c r="W357">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X357">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y357">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z357">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA357">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB357">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC357">
         <v>3.28</v>
@@ -58551,13 +58551,13 @@
         <v>1.25</v>
       </c>
       <c r="AE357">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF357">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AG357">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH357" t="inlineStr">
         <is>
@@ -58570,10 +58570,10 @@
         </is>
       </c>
       <c r="AJ357">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK357">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AL357">
         <v>0</v>
@@ -59478,13 +59478,13 @@
         </is>
       </c>
       <c r="N363">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O363">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P363">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q363">
         <v>0</v>
@@ -59641,13 +59641,13 @@
         </is>
       </c>
       <c r="N364">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O364">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P364">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q364">
         <v>0</v>
@@ -59804,13 +59804,13 @@
         </is>
       </c>
       <c r="N365">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O365">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P365">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q365">
         <v>0</v>
@@ -59967,13 +59967,13 @@
         </is>
       </c>
       <c r="N366">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O366">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P366">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q366">
         <v>0</v>
@@ -60130,13 +60130,13 @@
         </is>
       </c>
       <c r="N367">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O367">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P367">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q367">
         <v>0</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -819,10 +819,10 @@
         <v>2.45</v>
       </c>
       <c r="U3">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
         <v>1.06</v>
@@ -834,16 +834,16 @@
         <v>1.39</v>
       </c>
       <c r="Z3">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AA3">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD3">
         <v>1.2</v>
@@ -976,7 +976,7 @@
         <v>2.32</v>
       </c>
       <c r="S4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
         <v>3.3</v>
@@ -991,7 +991,7 @@
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.24</v>
@@ -1009,7 +1009,7 @@
         <v>2.9</v>
       </c>
       <c r="AD4">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
         <v>1.11</v>
@@ -1145,13 +1145,13 @@
         <v>2.84</v>
       </c>
       <c r="U5">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V5">
         <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1163,7 +1163,7 @@
         <v>3.25</v>
       </c>
       <c r="AA5">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB5">
         <v>1.76</v>
@@ -1175,7 +1175,7 @@
         <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
         <v>1.87</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
         <v>1.91</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,61 +1287,61 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>2.62</v>
+        <v>3.44</v>
       </c>
       <c r="R6">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
         <v>2.6</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>3.73</v>
+        <v>3.48</v>
       </c>
       <c r="AA6">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC6">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
         <v>2.1</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="U7">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
+        <v>1.23</v>
+      </c>
+      <c r="Z7">
+        <v>3.6</v>
+      </c>
+      <c r="AA7">
+        <v>1.83</v>
+      </c>
+      <c r="AB7">
+        <v>1.91</v>
+      </c>
+      <c r="AC7">
+        <v>3.08</v>
+      </c>
+      <c r="AD7">
+        <v>1.36</v>
+      </c>
+      <c r="AE7">
+        <v>1.13</v>
+      </c>
+      <c r="AF7">
+        <v>1.71</v>
+      </c>
+      <c r="AG7">
+        <v>2.05</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.21</v>
+      </c>
+      <c r="AK7">
         <v>1.25</v>
-      </c>
-      <c r="Z7">
-        <v>3.48</v>
-      </c>
-      <c r="AA7">
-        <v>1.84</v>
-      </c>
-      <c r="AB7">
-        <v>1.98</v>
-      </c>
-      <c r="AC7">
-        <v>3.1</v>
-      </c>
-      <c r="AD7">
-        <v>1.38</v>
-      </c>
-      <c r="AE7">
-        <v>1.08</v>
-      </c>
-      <c r="AF7">
-        <v>1.65</v>
-      </c>
-      <c r="AG7">
-        <v>2.1</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.23</v>
-      </c>
-      <c r="AK7">
-        <v>1.29</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.75</v>
+        <v>2.09</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>1.83</v>
+        <v>2.82</v>
       </c>
       <c r="Q8">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
         <v>1.34</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="U8">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="V8">
         <v>1.44</v>
@@ -1643,34 +1643,34 @@
         <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="AA8">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB8">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AC8">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2117,7 +2117,7 @@
         <v>2.56</v>
       </c>
       <c r="S11">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
         <v>3.6</v>
@@ -2129,7 +2129,7 @@
         <v>1.62</v>
       </c>
       <c r="W11">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2147,10 +2147,10 @@
         <v>2.33</v>
       </c>
       <c r="AC11">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AD11">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AE11">
         <v>1.23</v>
@@ -2159,7 +2159,7 @@
         <v>1.53</v>
       </c>
       <c r="AG11">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
         <v>1.14</v>
@@ -2437,55 +2437,55 @@
         <v>7</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>2.26</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="O16">
-        <v>3.64</v>
+        <v>3.28</v>
       </c>
       <c r="P16">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="O17">
-        <v>3.28</v>
+        <v>3.64</v>
       </c>
       <c r="P17">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>3.6</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>3.6</v>
       </c>
       <c r="P20">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
         <v>1.25</v>
@@ -3614,19 +3614,19 @@
         <v>2.28</v>
       </c>
       <c r="AC20">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AD20">
         <v>1.59</v>
       </c>
       <c r="AE20">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF20">
         <v>1.44</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>2.5</v>
       </c>
       <c r="S21">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
         <v>3.56</v>
@@ -3768,13 +3768,13 @@
         <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>5.3</v>
+        <v>4.95</v>
       </c>
       <c r="AA21">
         <v>1.44</v>
       </c>
       <c r="AB21">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="AC21">
         <v>2.17</v>
@@ -3789,7 +3789,7 @@
         <v>1.42</v>
       </c>
       <c r="AG21">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK21">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3910,10 +3910,10 @@
         <v>2.44</v>
       </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U22">
         <v>2.05</v>
@@ -3922,7 +3922,7 @@
         <v>1.71</v>
       </c>
       <c r="W22">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -3931,7 +3931,7 @@
         <v>1.09</v>
       </c>
       <c r="Z22">
-        <v>5.76</v>
+        <v>5.4</v>
       </c>
       <c r="AA22">
         <v>1.41</v>
@@ -3946,13 +3946,13 @@
         <v>1.73</v>
       </c>
       <c r="AE22">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AF22">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
         <v>1.28</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="O23">
         <v>3.5</v>
@@ -4067,7 +4067,7 @@
         <v>2.23</v>
       </c>
       <c r="Q23">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="R23">
         <v>2.14</v>
@@ -4076,7 +4076,7 @@
         <v>1.29</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U23">
         <v>2.55</v>
@@ -4100,7 +4100,7 @@
         <v>1.73</v>
       </c>
       <c r="AB23">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC23">
         <v>2.77</v>
@@ -4112,7 +4112,7 @@
         <v>1.15</v>
       </c>
       <c r="AF23">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
         <v>2.21</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="S24">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="T24">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="U24">
+        <v>1.95</v>
+      </c>
+      <c r="V24">
         <v>1.79</v>
       </c>
-      <c r="V24">
-        <v>1.96</v>
-      </c>
       <c r="W24">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>7.8</v>
+        <v>6.26</v>
       </c>
       <c r="AA24">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AB24">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AC24">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AD24">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AE24">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF24">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AG24">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AK24">
-        <v>1.81</v>
+        <v>1.32</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G25">
@@ -4393,55 +4393,55 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="R25">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T25">
-        <v>3.56</v>
+        <v>5.5</v>
       </c>
       <c r="U25">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="V25">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="Z25">
-        <v>4.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA25">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AB25">
-        <v>2.35</v>
+        <v>3.74</v>
       </c>
       <c r="AC25">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD25">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AE25">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="AF25">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AG25">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,7 +4556,7 @@
         <v>7.05</v>
       </c>
       <c r="Q26">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R26">
         <v>2.57</v>
@@ -4589,10 +4589,10 @@
         <v>1.57</v>
       </c>
       <c r="AB26">
+        <v>2.33</v>
+      </c>
+      <c r="AC26">
         <v>2.35</v>
-      </c>
-      <c r="AC26">
-        <v>2.38</v>
       </c>
       <c r="AD26">
         <v>1.46</v>
@@ -4601,10 +4601,10 @@
         <v>1.15</v>
       </c>
       <c r="AF26">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AG26">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.1</v>
       </c>
       <c r="AK26">
-        <v>3.86</v>
+        <v>4.16</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="R27">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>4.8</v>
+        <v>3.56</v>
       </c>
       <c r="U27">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="V27">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="W27">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>6.26</v>
+        <v>4.4</v>
       </c>
       <c r="AA27">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="AC27">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD27">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AE27">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
+        <v>1.53</v>
+      </c>
+      <c r="AG27">
+        <v>2.4</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.3</v>
       </c>
-      <c r="AG27">
-        <v>3.1</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.22</v>
-      </c>
       <c r="AK27">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,25 +4882,25 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
         <v>2.88</v>
       </c>
       <c r="U28">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4912,25 +4912,25 @@
         <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AB28">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC28">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD28">
         <v>1.29</v>
       </c>
       <c r="AE28">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
         <v>1.84</v>
       </c>
       <c r="AG28">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK28">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z33">
-        <v>3.69</v>
+        <v>2.88</v>
       </c>
       <c r="AA33">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AB33">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.37</v>
+        <v>3.82</v>
       </c>
       <c r="AD33">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF33">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AG33">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q34">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="R34">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U34">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="V34">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA34">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AB34">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AC34">
-        <v>3.82</v>
+        <v>3.37</v>
       </c>
       <c r="AD34">
+        <v>1.27</v>
+      </c>
+      <c r="AE34">
+        <v>1.1</v>
+      </c>
+      <c r="AF34">
+        <v>1.71</v>
+      </c>
+      <c r="AG34">
+        <v>1.99</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
         <v>1.25</v>
       </c>
-      <c r="AE34">
-        <v>1.02</v>
-      </c>
-      <c r="AF34">
-        <v>1.87</v>
-      </c>
-      <c r="AG34">
-        <v>1.85</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.18</v>
-      </c>
       <c r="AK34">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>3.08</v>
       </c>
       <c r="AA39">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB39">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC39">
         <v>3.28</v>
@@ -6720,10 +6720,10 @@
         <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG39">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6847,16 +6847,16 @@
         <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U40">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
         <v>1.02</v>
@@ -6880,7 +6880,7 @@
         <v>1.48</v>
       </c>
       <c r="AE40">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF40">
         <v>1.68</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="O43">
         <v>4.04</v>
@@ -7336,7 +7336,7 @@
         <v>1.36</v>
       </c>
       <c r="T43">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U43">
         <v>2.88</v>
@@ -7357,10 +7357,10 @@
         <v>3.14</v>
       </c>
       <c r="AA43">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB43">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC43">
         <v>3.14</v>
@@ -7834,37 +7834,37 @@
         <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z46">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="AA46">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB46">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC46">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD46">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE46">
         <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG46">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK46">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>2.88</v>
       </c>
       <c r="AA47">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AB47">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC47">
         <v>3.5</v>
@@ -8021,7 +8021,7 @@
         <v>1.22</v>
       </c>
       <c r="AE47">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF47">
         <v>1.8</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="O55">
         <v>4.3</v>
@@ -9313,10 +9313,10 @@
         <v>3.86</v>
       </c>
       <c r="AA55">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB55">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC55">
         <v>2.59</v>
@@ -9347,7 +9347,7 @@
         <v>1.08</v>
       </c>
       <c r="AK55">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="O56">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="P56">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q56">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="R56">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="S56">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="U56">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="V56">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z56">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA56">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AB56">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC56">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="AD56">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="AE56">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AF56">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AG56">
-        <v>3.04</v>
+        <v>2.49</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="O57">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="P57">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q57">
+        <v>2</v>
+      </c>
+      <c r="R57">
+        <v>2.64</v>
+      </c>
+      <c r="S57">
+        <v>1.13</v>
+      </c>
+      <c r="T57">
+        <v>4.6</v>
+      </c>
+      <c r="U57">
+        <v>1.75</v>
+      </c>
+      <c r="V57">
+        <v>1.95</v>
+      </c>
+      <c r="W57">
+        <v>1.23</v>
+      </c>
+      <c r="X57">
+        <v>1.01</v>
+      </c>
+      <c r="Y57">
+        <v>1.03</v>
+      </c>
+      <c r="Z57">
+        <v>7.4</v>
+      </c>
+      <c r="AA57">
+        <v>1.25</v>
+      </c>
+      <c r="AB57">
+        <v>3.8</v>
+      </c>
+      <c r="AC57">
+        <v>1.73</v>
+      </c>
+      <c r="AD57">
+        <v>2.04</v>
+      </c>
+      <c r="AE57">
+        <v>1.41</v>
+      </c>
+      <c r="AF57">
+        <v>1.32</v>
+      </c>
+      <c r="AG57">
+        <v>3.04</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>1.2</v>
+      </c>
+      <c r="AK57">
         <v>2.15</v>
-      </c>
-      <c r="R57">
-        <v>2.35</v>
-      </c>
-      <c r="S57">
-        <v>1.22</v>
-      </c>
-      <c r="T57">
-        <v>3.55</v>
-      </c>
-      <c r="U57">
-        <v>2.2</v>
-      </c>
-      <c r="V57">
-        <v>1.6</v>
-      </c>
-      <c r="W57">
-        <v>1.12</v>
-      </c>
-      <c r="X57">
-        <v>1.02</v>
-      </c>
-      <c r="Y57">
-        <v>1.1</v>
-      </c>
-      <c r="Z57">
-        <v>5.2</v>
-      </c>
-      <c r="AA57">
-        <v>1.52</v>
-      </c>
-      <c r="AB57">
-        <v>2.5</v>
-      </c>
-      <c r="AC57">
-        <v>2.27</v>
-      </c>
-      <c r="AD57">
-        <v>1.65</v>
-      </c>
-      <c r="AE57">
-        <v>1.22</v>
-      </c>
-      <c r="AF57">
-        <v>1.44</v>
-      </c>
-      <c r="AG57">
-        <v>2.49</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.22</v>
-      </c>
-      <c r="AK57">
-        <v>1.99</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10424,7 +10424,7 @@
         <v>2.91</v>
       </c>
       <c r="Q62">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R62">
         <v>2.1</v>
@@ -10436,7 +10436,7 @@
         <v>2.88</v>
       </c>
       <c r="U62">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V62">
         <v>1.4</v>
@@ -10454,25 +10454,25 @@
         <v>3.2</v>
       </c>
       <c r="AA62">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB62">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC62">
         <v>3.3</v>
       </c>
       <c r="AD62">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE62">
         <v>1.06</v>
       </c>
       <c r="AF62">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG62">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK62">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10581,7 +10581,7 @@
         <v>4.1</v>
       </c>
       <c r="O63">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="P63">
         <v>1.58</v>
@@ -10614,13 +10614,13 @@
         <v>1.13</v>
       </c>
       <c r="Z63">
-        <v>4.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA63">
         <v>1.52</v>
       </c>
       <c r="AB63">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC63">
         <v>2.45</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O91">
         <v>3.5</v>
@@ -15151,55 +15151,55 @@
         <v>3.3</v>
       </c>
       <c r="Q91">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R91">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U91">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V91">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W91">
+        <v>1.13</v>
+      </c>
+      <c r="X91">
+        <v>1.01</v>
+      </c>
+      <c r="Y91">
         <v>1.14</v>
       </c>
-      <c r="X91">
-        <v>1.02</v>
-      </c>
-      <c r="Y91">
-        <v>1.16</v>
-      </c>
       <c r="Z91">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA91">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AB91">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AC91">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="AD91">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE91">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF91">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG91">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK91">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="N92">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O92">
         <v>3.5</v>
@@ -15314,55 +15314,55 @@
         <v>3.3</v>
       </c>
       <c r="Q92">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="R92">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S92">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T92">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U92">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V92">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W92">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z92">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA92">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AB92">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="AC92">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="AD92">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE92">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF92">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG92">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK92">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -16956,10 +16956,10 @@
         <v>4.55</v>
       </c>
       <c r="U102">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V102">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="W102">
         <v>1.25</v>
@@ -16968,13 +16968,13 @@
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z102">
         <v>7.6</v>
       </c>
       <c r="AA102">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB102">
         <v>3.5</v>
@@ -17596,55 +17596,55 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O111">
         <v>3.3</v>
       </c>
       <c r="P111">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="Q111">
         <v>3.02</v>
@@ -18767,10 +18767,10 @@
         <v>2.88</v>
       </c>
       <c r="AA113">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB113">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC113">
         <v>3.68</v>
@@ -19057,16 +19057,16 @@
         <v>2.91</v>
       </c>
       <c r="O115">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P115">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q115">
         <v>3.68</v>
       </c>
       <c r="R115">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S115">
         <v>1.45</v>
@@ -19093,7 +19093,7 @@
         <v>2.92</v>
       </c>
       <c r="AA115">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB115">
         <v>1.66</v>
@@ -19419,10 +19419,10 @@
         <v>3.28</v>
       </c>
       <c r="AA117">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AB117">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC117">
         <v>3.14</v>
@@ -19437,7 +19437,7 @@
         <v>1.78</v>
       </c>
       <c r="AG117">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="O118">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P118">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q118">
         <v>2</v>
@@ -19582,7 +19582,7 @@
         <v>4</v>
       </c>
       <c r="AA118">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB118">
         <v>2.12</v>
@@ -20056,7 +20056,7 @@
         <v>3.02</v>
       </c>
       <c r="V121">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W121">
         <v>1.03</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,25 +20847,25 @@
         </is>
       </c>
       <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
         <v>2.1</v>
       </c>
-      <c r="O126">
-        <v>3.1</v>
-      </c>
-      <c r="P126">
-        <v>3.1</v>
-      </c>
-      <c r="Q126">
-        <v>2.7</v>
-      </c>
       <c r="R126">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="S126">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T126">
-        <v>2.79</v>
+        <v>3.14</v>
       </c>
       <c r="U126">
         <v>2.75</v>
@@ -20874,37 +20874,37 @@
         <v>1.4</v>
       </c>
       <c r="W126">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X126">
         <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z126">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="AA126">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB126">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC126">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD126">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE126">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF126">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG126">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AK126">
-        <v>1.54</v>
+        <v>2.09</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G127">
@@ -21019,25 +21019,25 @@
         <v>0</v>
       </c>
       <c r="Q127">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="R127">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S127">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T127">
-        <v>3.14</v>
+        <v>2.96</v>
       </c>
       <c r="U127">
         <v>2.75</v>
       </c>
       <c r="V127">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W127">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X127">
         <v>1.02</v>
@@ -21046,28 +21046,28 @@
         <v>1.2</v>
       </c>
       <c r="Z127">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="AA127">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB127">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AC127">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AD127">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE127">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF127">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG127">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK127">
-        <v>2.09</v>
+        <v>1.25</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,80 +21173,80 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q128">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="R128">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S128">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T128">
-        <v>2.96</v>
+        <v>2.79</v>
       </c>
       <c r="U128">
         <v>2.75</v>
       </c>
       <c r="V128">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W128">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X128">
         <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z128">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="AA128">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB128">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC128">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="AD128">
+        <v>1.35</v>
+      </c>
+      <c r="AE128">
+        <v>1.08</v>
+      </c>
+      <c r="AF128">
+        <v>1.65</v>
+      </c>
+      <c r="AG128">
+        <v>2.1</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ128">
         <v>1.33</v>
       </c>
-      <c r="AE128">
-        <v>1.09</v>
-      </c>
-      <c r="AF128">
-        <v>1.67</v>
-      </c>
-      <c r="AG128">
-        <v>2.05</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>1.25</v>
-      </c>
       <c r="AK128">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="O135">
         <v>3.35</v>
       </c>
       <c r="P135">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q135">
+        <v>2.7</v>
+      </c>
+      <c r="R135">
+        <v>2</v>
+      </c>
+      <c r="S135">
+        <v>1.4</v>
+      </c>
+      <c r="T135">
         <v>2.75</v>
       </c>
-      <c r="R135">
-        <v>2.03</v>
-      </c>
-      <c r="S135">
-        <v>1.38</v>
-      </c>
-      <c r="T135">
-        <v>2.64</v>
-      </c>
       <c r="U135">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="V135">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W135">
         <v>1.05</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y135">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z135">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA135">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB135">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AC135">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="AD135">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE135">
         <v>1.05</v>
       </c>
       <c r="AF135">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AG135">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK135">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,31 +22477,31 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="O136">
         <v>3.35</v>
       </c>
       <c r="P136">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q136">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R136">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S136">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T136">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="U136">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="V136">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W136">
         <v>1.05</v>
@@ -22510,31 +22510,31 @@
         <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z136">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA136">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB136">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC136">
-        <v>3.74</v>
+        <v>3.48</v>
       </c>
       <c r="AD136">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE136">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF136">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AG136">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK136">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22978,13 +22978,13 @@
         <v>1.62</v>
       </c>
       <c r="R139">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="S139">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T139">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="U139">
         <v>2.1</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.68</v>
+        <v>1.42</v>
       </c>
       <c r="O140">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="P140">
-        <v>2.31</v>
+        <v>5.2</v>
       </c>
       <c r="Q140">
-        <v>4.05</v>
+        <v>1.93</v>
       </c>
       <c r="R140">
-        <v>1.92</v>
+        <v>2.48</v>
       </c>
       <c r="S140">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T140">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="U140">
-        <v>3.29</v>
+        <v>2.18</v>
       </c>
       <c r="V140">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="W140">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X140">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="Z140">
-        <v>2.86</v>
+        <v>5.05</v>
       </c>
       <c r="AA140">
-        <v>2.24</v>
+        <v>1.43</v>
       </c>
       <c r="AB140">
-        <v>1.76</v>
+        <v>2.56</v>
       </c>
       <c r="AC140">
-        <v>3.6</v>
+        <v>2.22</v>
       </c>
       <c r="AD140">
-        <v>1.23</v>
+        <v>1.77</v>
       </c>
       <c r="AE140">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AF140">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AG140">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="AK140">
-        <v>1.33</v>
+        <v>2.59</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.42</v>
+        <v>2.68</v>
       </c>
       <c r="O141">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="P141">
-        <v>5.2</v>
+        <v>2.31</v>
       </c>
       <c r="Q141">
-        <v>1.93</v>
+        <v>4.05</v>
       </c>
       <c r="R141">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="S141">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T141">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="U141">
-        <v>2.18</v>
+        <v>3.29</v>
       </c>
       <c r="V141">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="W141">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X141">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y141">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="Z141">
-        <v>5.05</v>
+        <v>2.86</v>
       </c>
       <c r="AA141">
-        <v>1.43</v>
+        <v>2.24</v>
       </c>
       <c r="AB141">
-        <v>2.56</v>
+        <v>1.76</v>
       </c>
       <c r="AC141">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="AD141">
-        <v>1.77</v>
+        <v>1.23</v>
       </c>
       <c r="AE141">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AF141">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AG141">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK141">
-        <v>2.59</v>
+        <v>1.33</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23630,7 +23630,7 @@
         <v>2.8</v>
       </c>
       <c r="R143">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S143">
         <v>1.26</v>
@@ -23854,7 +23854,7 @@
         <v>1.36</v>
       </c>
       <c r="AK144">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24146,7 +24146,7 @@
         <v>3.97</v>
       </c>
       <c r="AA146">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB146">
         <v>2.1</v>
@@ -24436,10 +24436,10 @@
         <v>1.81</v>
       </c>
       <c r="O148">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P148">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q148">
         <v>2.41</v>
@@ -24460,7 +24460,7 @@
         <v>1.36</v>
       </c>
       <c r="W148">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X148">
         <v>1.01</v>
@@ -24469,7 +24469,7 @@
         <v>1.26</v>
       </c>
       <c r="Z148">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="AA148">
         <v>1.89</v>
@@ -24481,7 +24481,7 @@
         <v>3.08</v>
       </c>
       <c r="AD148">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE148">
         <v>1.07</v>
@@ -24605,7 +24605,7 @@
         <v>3.3</v>
       </c>
       <c r="Q149">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="R149">
         <v>2.38</v>
@@ -24666,7 +24666,7 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK149">
         <v>1.75</v>
@@ -24762,10 +24762,10 @@
         <v>1.85</v>
       </c>
       <c r="O150">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="P150">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="Q150">
         <v>2.32</v>
@@ -24798,7 +24798,7 @@
         <v>5.25</v>
       </c>
       <c r="AA150">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB150">
         <v>2.55</v>
@@ -24810,7 +24810,7 @@
         <v>1.73</v>
       </c>
       <c r="AE150">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF150">
         <v>1.45</v>
@@ -24955,10 +24955,10 @@
         <v>1.02</v>
       </c>
       <c r="Y151">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z151">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA151">
         <v>1.53</v>
@@ -25091,7 +25091,7 @@
         <v>5.5</v>
       </c>
       <c r="P152">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q152">
         <v>1.76</v>
@@ -25248,7 +25248,7 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O153">
         <v>4.2</v>
@@ -25281,16 +25281,16 @@
         <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z153">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA153">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB153">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC153">
         <v>2.38</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,49 +25411,49 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.31</v>
+        <v>2.9</v>
       </c>
       <c r="O154">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P154">
-        <v>7.75</v>
+        <v>2.31</v>
       </c>
       <c r="Q154">
-        <v>1.87</v>
+        <v>3.58</v>
       </c>
       <c r="R154">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="S154">
         <v>1.35</v>
       </c>
       <c r="T154">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="U154">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="V154">
         <v>1.45</v>
       </c>
       <c r="W154">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X154">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z154">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AA154">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB154">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AC154">
         <v>2.76</v>
@@ -25462,13 +25462,13 @@
         <v>1.38</v>
       </c>
       <c r="AE154">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF154">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AG154">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="AK154">
-        <v>3.08</v>
+        <v>1.42</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.9</v>
+        <v>1.31</v>
       </c>
       <c r="O155">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P155">
-        <v>2.22</v>
+        <v>7.75</v>
       </c>
       <c r="Q155">
-        <v>3.58</v>
+        <v>1.92</v>
       </c>
       <c r="R155">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="S155">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T155">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U155">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="V155">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W155">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X155">
         <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z155">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="AA155">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB155">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AC155">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AD155">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE155">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF155">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AG155">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.55</v>
+        <v>1.09</v>
       </c>
       <c r="AK155">
-        <v>1.42</v>
+        <v>2.94</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25746,55 +25746,55 @@
         <v>0</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S156">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U156">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V156">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W156">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X156">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z156">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC156">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD156">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE156">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF156">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG156">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK156">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -26715,16 +26715,16 @@
         </is>
       </c>
       <c r="N162">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="O162">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="P162">
         <v>1.28</v>
       </c>
       <c r="Q162">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="R162">
         <v>2.67</v>
@@ -26751,28 +26751,28 @@
         <v>1.1</v>
       </c>
       <c r="Z162">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA162">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB162">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AC162">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AD162">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE162">
         <v>1.18</v>
       </c>
       <c r="AF162">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG162">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>1.07</v>
       </c>
       <c r="AK162">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -27222,13 +27222,13 @@
         <v>1.39</v>
       </c>
       <c r="T165">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U165">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V165">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W165">
         <v>1.08</v>
@@ -27252,7 +27252,7 @@
         <v>3.4</v>
       </c>
       <c r="AD165">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE165">
         <v>1.06</v>
@@ -27274,7 +27274,7 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AK165">
         <v>1.3</v>
@@ -27406,7 +27406,7 @@
         <v>3.9</v>
       </c>
       <c r="AA166">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB166">
         <v>2.18</v>
@@ -27545,10 +27545,10 @@
         <v>2.35</v>
       </c>
       <c r="S167">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T167">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U167">
         <v>2.75</v>
@@ -27563,13 +27563,13 @@
         <v>1</v>
       </c>
       <c r="Y167">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z167">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AA167">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AB167">
         <v>1.85</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,80 +27693,80 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.34</v>
+        <v>1.44</v>
       </c>
       <c r="O168">
+        <v>4</v>
+      </c>
+      <c r="P168">
+        <v>6.25</v>
+      </c>
+      <c r="Q168">
+        <v>1.91</v>
+      </c>
+      <c r="R168">
+        <v>2.3</v>
+      </c>
+      <c r="S168">
+        <v>1.31</v>
+      </c>
+      <c r="T168">
         <v>3.1</v>
       </c>
-      <c r="P168">
+      <c r="U168">
+        <v>2.75</v>
+      </c>
+      <c r="V168">
+        <v>1.4</v>
+      </c>
+      <c r="W168">
+        <v>1.1</v>
+      </c>
+      <c r="X168">
+        <v>1.02</v>
+      </c>
+      <c r="Y168">
+        <v>1.27</v>
+      </c>
+      <c r="Z168">
+        <v>3.58</v>
+      </c>
+      <c r="AA168">
+        <v>1.79</v>
+      </c>
+      <c r="AB168">
+        <v>1.91</v>
+      </c>
+      <c r="AC168">
+        <v>3.1</v>
+      </c>
+      <c r="AD168">
+        <v>1.33</v>
+      </c>
+      <c r="AE168">
+        <v>1.08</v>
+      </c>
+      <c r="AF168">
+        <v>1.98</v>
+      </c>
+      <c r="AG168">
+        <v>1.7</v>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ168">
+        <v>1.13</v>
+      </c>
+      <c r="AK168">
         <v>2.7</v>
-      </c>
-      <c r="Q168">
-        <v>2.88</v>
-      </c>
-      <c r="R168">
-        <v>2.1</v>
-      </c>
-      <c r="S168">
-        <v>1.37</v>
-      </c>
-      <c r="T168">
-        <v>2.53</v>
-      </c>
-      <c r="U168">
-        <v>2.82</v>
-      </c>
-      <c r="V168">
-        <v>1.33</v>
-      </c>
-      <c r="W168">
-        <v>1.04</v>
-      </c>
-      <c r="X168">
-        <v>1.01</v>
-      </c>
-      <c r="Y168">
-        <v>1.31</v>
-      </c>
-      <c r="Z168">
-        <v>2.92</v>
-      </c>
-      <c r="AA168">
-        <v>2.13</v>
-      </c>
-      <c r="AB168">
-        <v>1.69</v>
-      </c>
-      <c r="AC168">
-        <v>3.78</v>
-      </c>
-      <c r="AD168">
-        <v>1.19</v>
-      </c>
-      <c r="AE168">
-        <v>1.02</v>
-      </c>
-      <c r="AF168">
-        <v>1.8</v>
-      </c>
-      <c r="AG168">
-        <v>1.85</v>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ168">
-        <v>1.3</v>
-      </c>
-      <c r="AK168">
-        <v>1.57</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
+        <v>2.34</v>
+      </c>
+      <c r="O169">
+        <v>3.1</v>
+      </c>
+      <c r="P169">
+        <v>2.7</v>
+      </c>
+      <c r="Q169">
+        <v>3</v>
+      </c>
+      <c r="R169">
+        <v>2.05</v>
+      </c>
+      <c r="S169">
         <v>1.44</v>
       </c>
-      <c r="O169">
-        <v>4</v>
-      </c>
-      <c r="P169">
-        <v>6.5</v>
-      </c>
-      <c r="Q169">
-        <v>1.91</v>
-      </c>
-      <c r="R169">
-        <v>2.3</v>
-      </c>
-      <c r="S169">
-        <v>1.31</v>
-      </c>
       <c r="T169">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="U169">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="V169">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W169">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X169">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y169">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z169">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="AA169">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="AB169">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC169">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD169">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE169">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF169">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AG169">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK169">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.37</v>
+        <v>1.62</v>
       </c>
       <c r="O175">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P175">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q175">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="R175">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="S175">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T175">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="U175">
-        <v>3.07</v>
+        <v>2.47</v>
       </c>
       <c r="V175">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="W175">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X175">
         <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="Z175">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA175">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="AB175">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AC175">
-        <v>3.68</v>
+        <v>2.64</v>
       </c>
       <c r="AD175">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AE175">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF175">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AG175">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK175">
-        <v>1.53</v>
+        <v>2.19</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,80 +28997,80 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O176">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P176">
         <v>2.75</v>
       </c>
       <c r="Q176">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R176">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S176">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T176">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="U176">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="V176">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W176">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X176">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y176">
+        <v>1.34</v>
+      </c>
+      <c r="Z176">
+        <v>3.15</v>
+      </c>
+      <c r="AA176">
+        <v>2.07</v>
+      </c>
+      <c r="AB176">
+        <v>1.73</v>
+      </c>
+      <c r="AC176">
+        <v>3.68</v>
+      </c>
+      <c r="AD176">
+        <v>1.26</v>
+      </c>
+      <c r="AE176">
+        <v>1.05</v>
+      </c>
+      <c r="AF176">
+        <v>1.8</v>
+      </c>
+      <c r="AG176">
+        <v>1.9</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ176">
         <v>1.29</v>
       </c>
-      <c r="Z176">
-        <v>3.43</v>
-      </c>
-      <c r="AA176">
-        <v>1.96</v>
-      </c>
-      <c r="AB176">
-        <v>1.83</v>
-      </c>
-      <c r="AC176">
-        <v>3.3</v>
-      </c>
-      <c r="AD176">
-        <v>1.29</v>
-      </c>
-      <c r="AE176">
-        <v>1.1</v>
-      </c>
-      <c r="AF176">
-        <v>1.73</v>
-      </c>
-      <c r="AG176">
-        <v>2</v>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ176">
-        <v>1.28</v>
-      </c>
       <c r="AK176">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,65 +29160,65 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.62</v>
+        <v>2.95</v>
       </c>
       <c r="O177">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P177">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q177">
-        <v>2.13</v>
+        <v>3.5</v>
       </c>
       <c r="R177">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="S177">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T177">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="U177">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="V177">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W177">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z177">
-        <v>4.4</v>
+        <v>3.91</v>
       </c>
       <c r="AA177">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AB177">
+        <v>1.9</v>
+      </c>
+      <c r="AC177">
+        <v>2.93</v>
+      </c>
+      <c r="AD177">
+        <v>1.32</v>
+      </c>
+      <c r="AE177">
+        <v>1.08</v>
+      </c>
+      <c r="AF177">
+        <v>1.65</v>
+      </c>
+      <c r="AG177">
         <v>2.1</v>
       </c>
-      <c r="AC177">
-        <v>2.64</v>
-      </c>
-      <c r="AD177">
-        <v>1.48</v>
-      </c>
-      <c r="AE177">
-        <v>1.16</v>
-      </c>
-      <c r="AF177">
-        <v>1.61</v>
-      </c>
-      <c r="AG177">
-        <v>2.15</v>
-      </c>
       <c r="AH177" t="inlineStr">
         <is>
           <t>[]</t>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK177">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="O178">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P178">
+        <v>2.75</v>
+      </c>
+      <c r="Q178">
+        <v>2.88</v>
+      </c>
+      <c r="R178">
         <v>2.1</v>
       </c>
-      <c r="Q178">
-        <v>3.5</v>
-      </c>
-      <c r="R178">
-        <v>2.11</v>
-      </c>
       <c r="S178">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T178">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="U178">
-        <v>2.63</v>
+        <v>2.97</v>
       </c>
       <c r="V178">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W178">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X178">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y178">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z178">
-        <v>3.91</v>
+        <v>3.43</v>
       </c>
       <c r="AA178">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB178">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC178">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="AD178">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE178">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF178">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG178">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK178">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29815,7 +29815,7 @@
         <v>1.15</v>
       </c>
       <c r="O181">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P181">
         <v>10</v>
@@ -29885,7 +29885,7 @@
         <v>1.04</v>
       </c>
       <c r="AK181">
-        <v>4.69</v>
+        <v>4.6</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="O194">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="P194">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="Q194">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="R194">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="S194">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T194">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U194">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V194">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W194">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X194">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y194">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z194">
-        <v>3.12</v>
+        <v>3.48</v>
       </c>
       <c r="AA194">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AB194">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="AC194">
-        <v>3.89</v>
+        <v>3.05</v>
       </c>
       <c r="AD194">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE194">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF194">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AG194">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AK194">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
+        <v>2.3</v>
+      </c>
+      <c r="O195">
+        <v>3.35</v>
+      </c>
+      <c r="P195">
+        <v>2.63</v>
+      </c>
+      <c r="Q195">
+        <v>2.8</v>
+      </c>
+      <c r="R195">
+        <v>2.2</v>
+      </c>
+      <c r="S195">
+        <v>1.36</v>
+      </c>
+      <c r="T195">
+        <v>3.03</v>
+      </c>
+      <c r="U195">
         <v>2.88</v>
       </c>
-      <c r="O195">
-        <v>3.43</v>
-      </c>
-      <c r="P195">
-        <v>2.21</v>
-      </c>
-      <c r="Q195">
-        <v>3.4</v>
-      </c>
-      <c r="R195">
-        <v>2.08</v>
-      </c>
-      <c r="S195">
-        <v>1.34</v>
-      </c>
-      <c r="T195">
-        <v>3.09</v>
-      </c>
-      <c r="U195">
-        <v>2.67</v>
-      </c>
       <c r="V195">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W195">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X195">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y195">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z195">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="AA195">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AB195">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC195">
-        <v>2.97</v>
+        <v>3.27</v>
       </c>
       <c r="AD195">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE195">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF195">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG195">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK195">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="O196">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="P196">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="Q196">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R196">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="S196">
+        <v>1.36</v>
+      </c>
+      <c r="T196">
+        <v>2.88</v>
+      </c>
+      <c r="U196">
+        <v>3</v>
+      </c>
+      <c r="V196">
         <v>1.33</v>
       </c>
-      <c r="T196">
-        <v>2.97</v>
-      </c>
-      <c r="U196">
-        <v>2.75</v>
-      </c>
-      <c r="V196">
-        <v>1.43</v>
-      </c>
       <c r="W196">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X196">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z196">
-        <v>3.48</v>
+        <v>3.12</v>
       </c>
       <c r="AA196">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AB196">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AC196">
-        <v>3.05</v>
+        <v>3.89</v>
       </c>
       <c r="AD196">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE196">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF196">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG196">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AK196">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
+        <v>2.37</v>
+      </c>
+      <c r="O197">
+        <v>3.62</v>
+      </c>
+      <c r="P197">
+        <v>2.45</v>
+      </c>
+      <c r="Q197">
+        <v>3</v>
+      </c>
+      <c r="R197">
+        <v>2.47</v>
+      </c>
+      <c r="S197">
+        <v>1.24</v>
+      </c>
+      <c r="T197">
+        <v>3.4</v>
+      </c>
+      <c r="U197">
+        <v>2.25</v>
+      </c>
+      <c r="V197">
+        <v>1.57</v>
+      </c>
+      <c r="W197">
+        <v>1.1</v>
+      </c>
+      <c r="X197">
+        <v>1.01</v>
+      </c>
+      <c r="Y197">
+        <v>1.11</v>
+      </c>
+      <c r="Z197">
+        <v>4.8</v>
+      </c>
+      <c r="AA197">
+        <v>1.49</v>
+      </c>
+      <c r="AB197">
         <v>2.3</v>
       </c>
-      <c r="O197">
-        <v>3.35</v>
-      </c>
-      <c r="P197">
-        <v>2.63</v>
-      </c>
-      <c r="Q197">
-        <v>2.8</v>
-      </c>
-      <c r="R197">
-        <v>2.2</v>
-      </c>
-      <c r="S197">
-        <v>1.36</v>
-      </c>
-      <c r="T197">
-        <v>3.03</v>
-      </c>
-      <c r="U197">
-        <v>2.88</v>
-      </c>
-      <c r="V197">
-        <v>1.36</v>
-      </c>
-      <c r="W197">
-        <v>1.06</v>
-      </c>
-      <c r="X197">
-        <v>1</v>
-      </c>
-      <c r="Y197">
-        <v>1.3</v>
-      </c>
-      <c r="Z197">
-        <v>3.1</v>
-      </c>
-      <c r="AA197">
-        <v>1.94</v>
-      </c>
-      <c r="AB197">
-        <v>1.82</v>
-      </c>
       <c r="AC197">
-        <v>3.27</v>
+        <v>2.35</v>
       </c>
       <c r="AD197">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AE197">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF197">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG197">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK197">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="O199">
-        <v>3.62</v>
+        <v>3.43</v>
       </c>
       <c r="P199">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="Q199">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R199">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="S199">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="T199">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="U199">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="V199">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W199">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X199">
         <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="Z199">
-        <v>4.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA199">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="AB199">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC199">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="AD199">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AE199">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF199">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG199">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK199">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="O212">
         <v>3.3</v>
       </c>
       <c r="P212">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="Q212">
-        <v>2.91</v>
+        <v>5.3</v>
       </c>
       <c r="R212">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S212">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T212">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U212">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="V212">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W212">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X212">
         <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z212">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA212">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AB212">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC212">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="AD212">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AE212">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF212">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AG212">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK212">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,19 +35028,19 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="O213">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P213">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="Q213">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R213">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S213">
         <v>1.28</v>
@@ -35049,10 +35049,10 @@
         <v>3.3</v>
       </c>
       <c r="U213">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="V213">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W213">
         <v>1.08</v>
@@ -35061,31 +35061,31 @@
         <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z213">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA213">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB213">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC213">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AD213">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE213">
         <v>1.12</v>
       </c>
       <c r="AF213">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG213">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>1.26</v>
       </c>
       <c r="AK213">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O214">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P214">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="Q214">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="R214">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="S214">
+        <v>1.41</v>
+      </c>
+      <c r="T214">
+        <v>2.63</v>
+      </c>
+      <c r="U214">
+        <v>2.96</v>
+      </c>
+      <c r="V214">
         <v>1.33</v>
       </c>
-      <c r="T214">
-        <v>2.95</v>
-      </c>
-      <c r="U214">
-        <v>2.57</v>
-      </c>
-      <c r="V214">
-        <v>1.43</v>
-      </c>
       <c r="W214">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X214">
         <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z214">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AA214">
-        <v>1.78</v>
+        <v>2.03</v>
       </c>
       <c r="AB214">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AC214">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="AD214">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AE214">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF214">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG214">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AK214">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,19 +35354,19 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="O215">
         <v>3.1</v>
       </c>
       <c r="P215">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="Q215">
-        <v>3.45</v>
+        <v>2.37</v>
       </c>
       <c r="R215">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="S215">
         <v>1.41</v>
@@ -35375,43 +35375,43 @@
         <v>2.63</v>
       </c>
       <c r="U215">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="V215">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W215">
+        <v>1.04</v>
+      </c>
+      <c r="X215">
         <v>1.02</v>
       </c>
-      <c r="X215">
-        <v>1.01</v>
-      </c>
       <c r="Y215">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z215">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA215">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB215">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC215">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD215">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE215">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF215">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AG215">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AK215">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,80 +35517,80 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.71</v>
+        <v>2.55</v>
       </c>
       <c r="O216">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P216">
-        <v>4.14</v>
+        <v>2.43</v>
       </c>
       <c r="Q216">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R216">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S216">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="T216">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U216">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="V216">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="W216">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X216">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z216">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA216">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AB216">
-        <v>2.56</v>
+        <v>2.09</v>
       </c>
       <c r="AC216">
-        <v>2.09</v>
+        <v>2.52</v>
       </c>
       <c r="AD216">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="AE216">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AF216">
+        <v>1.52</v>
+      </c>
+      <c r="AG216">
+        <v>2.4</v>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ216">
+        <v>1.26</v>
+      </c>
+      <c r="AK216">
         <v>1.5</v>
-      </c>
-      <c r="AG216">
-        <v>2.42</v>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ216">
-        <v>1.19</v>
-      </c>
-      <c r="AK216">
-        <v>2.31</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="O217">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P217">
-        <v>2.94</v>
+        <v>4.14</v>
       </c>
       <c r="Q217">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="R217">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="S217">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="T217">
-        <v>2.63</v>
+        <v>3.8</v>
       </c>
       <c r="U217">
-        <v>2.92</v>
+        <v>2.03</v>
       </c>
       <c r="V217">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="W217">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="X217">
         <v>1.02</v>
       </c>
       <c r="Y217">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="Z217">
-        <v>2.97</v>
+        <v>5.2</v>
       </c>
       <c r="AA217">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AB217">
-        <v>1.74</v>
+        <v>2.56</v>
       </c>
       <c r="AC217">
-        <v>3.42</v>
+        <v>2.09</v>
       </c>
       <c r="AD217">
-        <v>1.23</v>
+        <v>1.69</v>
       </c>
       <c r="AE217">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF217">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AG217">
-        <v>1.84</v>
+        <v>2.42</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK217">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -37147,16 +37147,16 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="O226">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P226">
         <v>7.5</v>
       </c>
       <c r="Q226">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R226">
         <v>2.7</v>
@@ -37165,13 +37165,13 @@
         <v>1.25</v>
       </c>
       <c r="T226">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U226">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V226">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W226">
         <v>1.14</v>
@@ -37180,31 +37180,31 @@
         <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z226">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AA226">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB226">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AC226">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD226">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE226">
         <v>1.16</v>
       </c>
       <c r="AF226">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG226">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK226">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -38137,7 +38137,7 @@
         <v>2.1</v>
       </c>
       <c r="R232">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="S232">
         <v>1.18</v>
@@ -38288,16 +38288,16 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="O233">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P233">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q233">
-        <v>3.45</v>
+        <v>3.09</v>
       </c>
       <c r="R233">
         <v>2.5</v>
@@ -38315,7 +38315,7 @@
         <v>1.69</v>
       </c>
       <c r="W233">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X233">
         <v>1.02</v>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK233">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38949,55 +38949,55 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39136,31 +39136,31 @@
         <v>1.03</v>
       </c>
       <c r="Y238">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z238">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AA238">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB238">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC238">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="AD238">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE238">
         <v>1.04</v>
       </c>
       <c r="AF238">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG238">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -40416,10 +40416,10 @@
         <v>4.25</v>
       </c>
       <c r="Q246">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="R246">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="S246">
         <v>1.36</v>
@@ -40428,10 +40428,10 @@
         <v>2.88</v>
       </c>
       <c r="U246">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="V246">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W246">
         <v>1.06</v>
@@ -40440,31 +40440,31 @@
         <v>1.02</v>
       </c>
       <c r="Y246">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z246">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AA246">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AB246">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC246">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD246">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE246">
         <v>1.06</v>
       </c>
       <c r="AF246">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG246">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK246">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40742,7 +40742,7 @@
         <v>2.7</v>
       </c>
       <c r="Q248">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R248">
         <v>2.05</v>
@@ -41439,10 +41439,10 @@
         <v>1.06</v>
       </c>
       <c r="AF252">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG252">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="O254">
         <v>3.5</v>
       </c>
       <c r="P254">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="Q254">
         <v>3.1</v>
@@ -42040,7 +42040,7 @@
         <v>2.37</v>
       </c>
       <c r="O256">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P256">
         <v>2.7</v>
@@ -42206,7 +42206,7 @@
         <v>4.25</v>
       </c>
       <c r="P257">
-        <v>4.94</v>
+        <v>4.5</v>
       </c>
       <c r="Q257">
         <v>2.17</v>
@@ -42242,7 +42242,7 @@
         <v>1.62</v>
       </c>
       <c r="AB257">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC257">
         <v>2.61</v>
@@ -42526,10 +42526,10 @@
         </is>
       </c>
       <c r="N259">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O259">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P259">
         <v>2.8</v>
@@ -42568,7 +42568,7 @@
         <v>1.8</v>
       </c>
       <c r="AB259">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC259">
         <v>3.1</v>
@@ -43543,10 +43543,10 @@
         <v>3.28</v>
       </c>
       <c r="AA265">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB265">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC265">
         <v>3.14</v>
@@ -43706,10 +43706,10 @@
         <v>2.88</v>
       </c>
       <c r="AA266">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB266">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC266">
         <v>3.5</v>
@@ -43887,7 +43887,7 @@
         <v>1.48</v>
       </c>
       <c r="AG267">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -44325,13 +44325,13 @@
         <v>3.5</v>
       </c>
       <c r="P270">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q270">
         <v>3.21</v>
       </c>
       <c r="R270">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="S270">
         <v>1.34</v>
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK270">
         <v>1.42</v>
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="O273">
         <v>4.1</v>
       </c>
       <c r="P273">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q273">
         <v>2.08</v>
@@ -45010,10 +45010,10 @@
         <v>3.95</v>
       </c>
       <c r="AA274">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB274">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC274">
         <v>2.7</v>
@@ -45306,55 +45306,55 @@
         <v>0</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X276">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA276">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB276">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45629,13 +45629,13 @@
         <v>4</v>
       </c>
       <c r="P278">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q278">
         <v>5.33</v>
       </c>
       <c r="R278">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="S278">
         <v>1.25</v>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
+        <v>1.22</v>
+      </c>
+      <c r="AK278">
         <v>1.17</v>
-      </c>
-      <c r="AK278">
-        <v>1.12</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -47618,10 +47618,10 @@
         <v>2.92</v>
       </c>
       <c r="AA290">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB290">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AC290">
         <v>3.48</v>
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O293">
         <v>3.4</v>
       </c>
       <c r="P293">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="Q293">
         <v>3.3</v>
@@ -48089,7 +48089,7 @@
         <v>2.76</v>
       </c>
       <c r="U293">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V293">
         <v>1.45</v>
@@ -48557,7 +48557,7 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="O296">
         <v>3.63</v>
@@ -48723,7 +48723,7 @@
         <v>1.71</v>
       </c>
       <c r="O297">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P297">
         <v>4.3</v>
@@ -48759,16 +48759,16 @@
         <v>4.8</v>
       </c>
       <c r="AA297">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB297">
         <v>2.38</v>
       </c>
       <c r="AC297">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AD297">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE297">
         <v>1.21</v>
@@ -50187,64 +50187,64 @@
         </is>
       </c>
       <c r="N306">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O306">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P306">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q306">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R306">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S306">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T306">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U306">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V306">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W306">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X306">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y306">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z306">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA306">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB306">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC306">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD306">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE306">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF306">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG306">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK306">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50586,7 +50586,7 @@
         <v>1.13</v>
       </c>
       <c r="AK308">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50715,10 +50715,10 @@
         <v>3.2</v>
       </c>
       <c r="AA309">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB309">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC309">
         <v>3.2</v>
@@ -50848,55 +50848,55 @@
         <v>0</v>
       </c>
       <c r="Q310">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R310">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S310">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T310">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U310">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V310">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W310">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X310">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y310">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z310">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC310">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD310">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE310">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF310">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG310">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK310">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51663,10 +51663,10 @@
         <v>2.51</v>
       </c>
       <c r="Q315">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="R315">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="S315">
         <v>1.21</v>
@@ -51724,7 +51724,7 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AK315">
         <v>1.46</v>
@@ -51856,10 +51856,10 @@
         <v>4.15</v>
       </c>
       <c r="AA316">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB316">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AC316">
         <v>2.43</v>
@@ -52143,13 +52143,13 @@
         </is>
       </c>
       <c r="N318">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="O318">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P318">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q318">
         <v>2.61</v>
@@ -52958,10 +52958,10 @@
         </is>
       </c>
       <c r="N323">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="O323">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P323">
         <v>2.4</v>
@@ -53619,55 +53619,55 @@
         <v>0</v>
       </c>
       <c r="Q327">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R327">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S327">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T327">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U327">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V327">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W327">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X327">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y327">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z327">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA327">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB327">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC327">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD327">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE327">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF327">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG327">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK327">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53779,7 +53779,7 @@
         <v>3.53</v>
       </c>
       <c r="P328">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q328">
         <v>3.4</v>
@@ -54600,7 +54600,7 @@
         <v>2.46</v>
       </c>
       <c r="R333">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S333">
         <v>1.33</v>
@@ -54914,13 +54914,13 @@
         </is>
       </c>
       <c r="N335">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="O335">
         <v>4</v>
       </c>
       <c r="P335">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q335">
         <v>2.06</v>
@@ -55738,10 +55738,10 @@
         <v>0</v>
       </c>
       <c r="Q340">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="R340">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="S340">
         <v>1.22</v>
@@ -55753,40 +55753,40 @@
         <v>2.25</v>
       </c>
       <c r="V340">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W340">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X340">
         <v>1.01</v>
       </c>
       <c r="Y340">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z340">
-        <v>4.9</v>
+        <v>5.01</v>
       </c>
       <c r="AA340">
         <v>1.48</v>
       </c>
       <c r="AB340">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AC340">
         <v>2.29</v>
       </c>
       <c r="AD340">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE340">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AF340">
         <v>1.43</v>
       </c>
       <c r="AG340">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK340">
         <v>1.44</v>
@@ -55892,10 +55892,10 @@
         </is>
       </c>
       <c r="N341">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O341">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="P341">
         <v>2.81</v>
@@ -55931,10 +55931,10 @@
         <v>4.3</v>
       </c>
       <c r="AA341">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AB341">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AC341">
         <v>2.49</v>
@@ -56064,10 +56064,10 @@
         <v>0</v>
       </c>
       <c r="Q342">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R342">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="S342">
         <v>1.25</v>
@@ -56079,10 +56079,10 @@
         <v>2.25</v>
       </c>
       <c r="V342">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W342">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X342">
         <v>1.02</v>
@@ -56094,16 +56094,16 @@
         <v>4.45</v>
       </c>
       <c r="AA342">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB342">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC342">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="AD342">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE342">
         <v>1.14</v>
@@ -56125,10 +56125,10 @@
         </is>
       </c>
       <c r="AJ342">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AK342">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL342">
         <v>0</v>
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="O343">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P343">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="Q343">
         <v>1.93</v>
@@ -56614,10 +56614,10 @@
         </is>
       </c>
       <c r="AJ345">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK345">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL345">
         <v>0</v>
@@ -56716,55 +56716,55 @@
         <v>0</v>
       </c>
       <c r="Q346">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R346">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S346">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T346">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U346">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V346">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W346">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X346">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y346">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z346">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA346">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB346">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC346">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD346">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE346">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF346">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG346">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH346" t="inlineStr">
         <is>
@@ -56777,10 +56777,10 @@
         </is>
       </c>
       <c r="AJ346">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK346">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL346">
         <v>0</v>
@@ -57522,64 +57522,64 @@
         </is>
       </c>
       <c r="N351">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O351">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P351">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q351">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R351">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S351">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T351">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U351">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V351">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W351">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X351">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y351">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z351">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA351">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB351">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC351">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD351">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE351">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF351">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG351">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH351" t="inlineStr">
         <is>
@@ -57592,10 +57592,10 @@
         </is>
       </c>
       <c r="AJ351">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK351">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL351">
         <v>0</v>
@@ -58026,10 +58026,10 @@
         <v>1.87</v>
       </c>
       <c r="S354">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T354">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U354">
         <v>3.38</v>
@@ -58041,7 +58041,7 @@
         <v>1.03</v>
       </c>
       <c r="X354">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y354">
         <v>1.41</v>
@@ -58050,16 +58050,16 @@
         <v>2.52</v>
       </c>
       <c r="AA354">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AB354">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC354">
-        <v>4.73</v>
+        <v>4.6</v>
       </c>
       <c r="AD354">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE354">
         <v>1.01</v>
@@ -58084,7 +58084,7 @@
         <v>1.36</v>
       </c>
       <c r="AK354">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL354">
         <v>0</v>
@@ -58213,7 +58213,7 @@
         <v>3.5</v>
       </c>
       <c r="AA355">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB355">
         <v>2.06</v>
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G356">
@@ -58337,64 +58337,64 @@
         </is>
       </c>
       <c r="N356">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O356">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P356">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q356">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="R356">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S356">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T356">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="U356">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V356">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W356">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X356">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y356">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z356">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AA356">
         <v>1.95</v>
       </c>
       <c r="AB356">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AC356">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD356">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE356">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF356">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AG356">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AH356" t="inlineStr">
         <is>
@@ -58410,7 +58410,7 @@
         <v>1.28</v>
       </c>
       <c r="AK356">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AL356">
         <v>0</v>
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G357">
@@ -58500,64 +58500,64 @@
         </is>
       </c>
       <c r="N357">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O357">
         <v>3.3</v>
       </c>
       <c r="P357">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q357">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="R357">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S357">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T357">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="U357">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V357">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W357">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X357">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y357">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z357">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AA357">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB357">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AC357">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD357">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE357">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF357">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG357">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AH357" t="inlineStr">
         <is>
@@ -58570,10 +58570,10 @@
         </is>
       </c>
       <c r="AJ357">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK357">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AL357">
         <v>0</v>
@@ -58989,19 +58989,19 @@
         </is>
       </c>
       <c r="N360">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O360">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P360">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q360">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R360">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S360">
         <v>1.48</v>
@@ -59016,28 +59016,28 @@
         <v>1.3</v>
       </c>
       <c r="W360">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X360">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y360">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z360">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AA360">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AB360">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC360">
         <v>3.98</v>
       </c>
       <c r="AD360">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE360">
         <v>1.01</v>
@@ -59059,7 +59059,7 @@
         </is>
       </c>
       <c r="AJ360">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AK360">
         <v>1.4</v>
@@ -59152,13 +59152,13 @@
         </is>
       </c>
       <c r="N361">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O361">
         <v>3.25</v>
       </c>
       <c r="P361">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q361">
         <v>2.92</v>
@@ -59170,10 +59170,10 @@
         <v>1.35</v>
       </c>
       <c r="T361">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U361">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V361">
         <v>1.42</v>
@@ -59191,22 +59191,22 @@
         <v>3.4</v>
       </c>
       <c r="AA361">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB361">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AC361">
         <v>3.3</v>
       </c>
       <c r="AD361">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE361">
         <v>1.07</v>
       </c>
       <c r="AF361">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG361">
         <v>2.06</v>
@@ -59222,10 +59222,10 @@
         </is>
       </c>
       <c r="AJ361">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK361">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL361">
         <v>0</v>
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G371">
@@ -60782,64 +60782,64 @@
         </is>
       </c>
       <c r="N371">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="O371">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P371">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q371">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="R371">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S371">
+        <v>1.29</v>
+      </c>
+      <c r="T371">
+        <v>3.3</v>
+      </c>
+      <c r="U371">
+        <v>2.38</v>
+      </c>
+      <c r="V371">
+        <v>1.5</v>
+      </c>
+      <c r="W371">
+        <v>1.11</v>
+      </c>
+      <c r="X371">
+        <v>1.02</v>
+      </c>
+      <c r="Y371">
+        <v>1.18</v>
+      </c>
+      <c r="Z371">
+        <v>3.88</v>
+      </c>
+      <c r="AA371">
+        <v>1.65</v>
+      </c>
+      <c r="AB371">
+        <v>2.1</v>
+      </c>
+      <c r="AC371">
+        <v>2.7</v>
+      </c>
+      <c r="AD371">
         <v>1.36</v>
       </c>
-      <c r="T371">
-        <v>3.05</v>
-      </c>
-      <c r="U371">
-        <v>2.88</v>
-      </c>
-      <c r="V371">
-        <v>1.41</v>
-      </c>
-      <c r="W371">
-        <v>1.04</v>
-      </c>
-      <c r="X371">
-        <v>1</v>
-      </c>
-      <c r="Y371">
-        <v>1.29</v>
-      </c>
-      <c r="Z371">
-        <v>3.41</v>
-      </c>
-      <c r="AA371">
-        <v>2</v>
-      </c>
-      <c r="AB371">
-        <v>1.8</v>
-      </c>
-      <c r="AC371">
-        <v>3.2</v>
-      </c>
-      <c r="AD371">
-        <v>1.31</v>
-      </c>
       <c r="AE371">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF371">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG371">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AH371" t="inlineStr">
         <is>
@@ -60852,10 +60852,10 @@
         </is>
       </c>
       <c r="AJ371">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK371">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL371">
         <v>0</v>
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G372">
@@ -60945,64 +60945,64 @@
         </is>
       </c>
       <c r="N372">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="O372">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P372">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q372">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="R372">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S372">
+        <v>1.36</v>
+      </c>
+      <c r="T372">
+        <v>3.05</v>
+      </c>
+      <c r="U372">
+        <v>2.88</v>
+      </c>
+      <c r="V372">
+        <v>1.41</v>
+      </c>
+      <c r="W372">
+        <v>1.04</v>
+      </c>
+      <c r="X372">
+        <v>1</v>
+      </c>
+      <c r="Y372">
         <v>1.29</v>
       </c>
-      <c r="T372">
-        <v>3.1</v>
-      </c>
-      <c r="U372">
-        <v>2.38</v>
-      </c>
-      <c r="V372">
-        <v>1.49</v>
-      </c>
-      <c r="W372">
-        <v>1.08</v>
-      </c>
-      <c r="X372">
-        <v>1.02</v>
-      </c>
-      <c r="Y372">
-        <v>1.18</v>
-      </c>
       <c r="Z372">
-        <v>3.88</v>
+        <v>3.41</v>
       </c>
       <c r="AA372">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AB372">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AC372">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD372">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE372">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF372">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG372">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AH372" t="inlineStr">
         <is>
@@ -61015,10 +61015,10 @@
         </is>
       </c>
       <c r="AJ372">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK372">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL372">
         <v>0</v>
@@ -61434,64 +61434,64 @@
         </is>
       </c>
       <c r="N375">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="O375">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P375">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q375">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R375">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S375">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T375">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U375">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V375">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W375">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X375">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y375">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z375">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA375">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB375">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC375">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD375">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE375">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF375">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG375">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH375" t="inlineStr">
         <is>
@@ -61504,10 +61504,10 @@
         </is>
       </c>
       <c r="AJ375">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK375">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL375">
         <v>0</v>
@@ -61624,7 +61624,7 @@
         <v>1.5</v>
       </c>
       <c r="W376">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X376">
         <v>1.02</v>
@@ -61639,10 +61639,10 @@
         <v>1.72</v>
       </c>
       <c r="AB376">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AC376">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD376">
         <v>1.4</v>
@@ -61654,7 +61654,7 @@
         <v>2.15</v>
       </c>
       <c r="AG376">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AH376" t="inlineStr">
         <is>
@@ -62092,7 +62092,7 @@
         <v>3.7</v>
       </c>
       <c r="P379">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="Q379">
         <v>3.8</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="AJ379">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK379">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AL379">
         <v>0</v>
@@ -62322,7 +62322,7 @@
         <v>1.03</v>
       </c>
       <c r="AK380">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AL380">
         <v>0</v>
@@ -62614,7 +62614,7 @@
         <v>3.2</v>
       </c>
       <c r="AA382">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB382">
         <v>1.79</v>
@@ -62753,49 +62753,49 @@
         <v>2.1</v>
       </c>
       <c r="S383">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T383">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="U383">
         <v>2.88</v>
       </c>
       <c r="V383">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W383">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X383">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y383">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z383">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AA383">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB383">
         <v>1.75</v>
       </c>
       <c r="AC383">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD383">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE383">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF383">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG383">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AH383" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>1.17</v>
       </c>
       <c r="AK383">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL383">
         <v>0</v>
@@ -64205,13 +64205,13 @@
         </is>
       </c>
       <c r="N392">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O392">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P392">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q392">
         <v>2.44</v>
@@ -65364,10 +65364,10 @@
         <v>1.26</v>
       </c>
       <c r="T399">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="U399">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="V399">
         <v>1.57</v>
@@ -65376,34 +65376,34 @@
         <v>1.11</v>
       </c>
       <c r="X399">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y399">
         <v>1.11</v>
       </c>
       <c r="Z399">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA399">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AB399">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC399">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AD399">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE399">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF399">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG399">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AH399" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>1.2</v>
       </c>
       <c r="AK399">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL399">
         <v>0</v>
@@ -65742,7 +65742,7 @@
         </is>
       </c>
       <c r="AJ401">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK401">
         <v>1.92</v>
@@ -66378,7 +66378,7 @@
         <v>1.16</v>
       </c>
       <c r="AF405">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG405">
         <v>2.45</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -641,7 +641,7 @@
         <v>3.9</v>
       </c>
       <c r="P2">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="Q2">
         <v>2.46</v>
@@ -659,7 +659,7 @@
         <v>2.05</v>
       </c>
       <c r="V2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W2">
         <v>1.17</v>
@@ -674,13 +674,13 @@
         <v>6.5</v>
       </c>
       <c r="AA2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB2">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AC2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AD2">
         <v>1.67</v>
@@ -692,7 +692,7 @@
         <v>1.39</v>
       </c>
       <c r="AG2">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
         <v>1.75</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.75</v>
+        <v>2.09</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>1.83</v>
+        <v>2.82</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T6">
-        <v>2.77</v>
+        <v>3.09</v>
       </c>
       <c r="U6">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.07</v>
@@ -1320,31 +1320,31 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="AA6">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB6">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC6">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="U7">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
+        <v>1.23</v>
+      </c>
+      <c r="Z7">
+        <v>3.6</v>
+      </c>
+      <c r="AA7">
+        <v>1.83</v>
+      </c>
+      <c r="AB7">
+        <v>1.91</v>
+      </c>
+      <c r="AC7">
+        <v>3.08</v>
+      </c>
+      <c r="AD7">
+        <v>1.36</v>
+      </c>
+      <c r="AE7">
+        <v>1.13</v>
+      </c>
+      <c r="AF7">
+        <v>1.71</v>
+      </c>
+      <c r="AG7">
+        <v>2.05</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.21</v>
+      </c>
+      <c r="AK7">
         <v>1.25</v>
-      </c>
-      <c r="Z7">
-        <v>3.48</v>
-      </c>
-      <c r="AA7">
-        <v>1.81</v>
-      </c>
-      <c r="AB7">
-        <v>1.9</v>
-      </c>
-      <c r="AC7">
-        <v>3.1</v>
-      </c>
-      <c r="AD7">
-        <v>1.38</v>
-      </c>
-      <c r="AE7">
-        <v>1.1</v>
-      </c>
-      <c r="AF7">
-        <v>1.65</v>
-      </c>
-      <c r="AG7">
-        <v>2.1</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.25</v>
-      </c>
-      <c r="AK7">
-        <v>1.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,61 +1613,61 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.09</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>2.82</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>2.62</v>
+        <v>3.44</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="U8">
         <v>2.6</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>3.73</v>
+        <v>3.48</v>
       </c>
       <c r="AA8">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB8">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC8">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD8">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG8">
         <v>2.1</v>
@@ -1686,7 +1686,7 @@
         <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2603,19 +2603,19 @@
         <v>3</v>
       </c>
       <c r="R14">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S14">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="U14">
         <v>2.6</v>
       </c>
       <c r="V14">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
         <v>1.11</v>
@@ -2664,7 +2664,7 @@
         <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Q23">
-        <v>2.43</v>
+        <v>1.62</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="S23">
         <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="U23">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V23">
         <v>1.57</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA23">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB23">
         <v>2.33</v>
       </c>
       <c r="AC23">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD23">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE23">
         <v>1.15</v>
       </c>
       <c r="AF23">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AG23">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK23">
-        <v>1.79</v>
+        <v>4.16</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.46</v>
+        <v>3.15</v>
       </c>
       <c r="O24">
-        <v>4.51</v>
+        <v>3.65</v>
       </c>
       <c r="P24">
-        <v>7.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q24">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T24">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U24">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="V24">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>4.5</v>
+        <v>6.26</v>
       </c>
       <c r="AA24">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB24">
-        <v>2.33</v>
+        <v>3.25</v>
       </c>
       <c r="AC24">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AD24">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF24">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="AG24">
-        <v>1.64</v>
+        <v>2.99</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AK24">
-        <v>4.16</v>
+        <v>1.32</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q25">
-        <v>2.35</v>
+        <v>3.54</v>
       </c>
       <c r="R25">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>5.5</v>
+        <v>3.56</v>
       </c>
       <c r="U25">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="V25">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
+        <v>1.13</v>
+      </c>
+      <c r="X25">
+        <v>1.02</v>
+      </c>
+      <c r="Y25">
+        <v>1.11</v>
+      </c>
+      <c r="Z25">
+        <v>4.95</v>
+      </c>
+      <c r="AA25">
+        <v>1.44</v>
+      </c>
+      <c r="AB25">
+        <v>2.43</v>
+      </c>
+      <c r="AC25">
+        <v>2.17</v>
+      </c>
+      <c r="AD25">
+        <v>1.65</v>
+      </c>
+      <c r="AE25">
+        <v>1.23</v>
+      </c>
+      <c r="AF25">
+        <v>1.42</v>
+      </c>
+      <c r="AG25">
+        <v>2.66</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.27</v>
       </c>
-      <c r="X25">
-        <v>1.01</v>
-      </c>
-      <c r="Y25">
-        <v>1.01</v>
-      </c>
-      <c r="Z25">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA25">
-        <v>1.28</v>
-      </c>
-      <c r="AB25">
-        <v>3.74</v>
-      </c>
-      <c r="AC25">
-        <v>1.6</v>
-      </c>
-      <c r="AD25">
-        <v>2.15</v>
-      </c>
-      <c r="AE25">
-        <v>1.51</v>
-      </c>
-      <c r="AF25">
-        <v>1.25</v>
-      </c>
-      <c r="AG25">
-        <v>3.5</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.22</v>
-      </c>
       <c r="AK25">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="R26">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T26">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="U26">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="V26">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="W26">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z26">
-        <v>6.26</v>
+        <v>4.4</v>
       </c>
       <c r="AA26">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AB26">
-        <v>3.25</v>
+        <v>2.33</v>
       </c>
       <c r="AC26">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD26">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AE26">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AF26">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AG26">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.54</v>
+        <v>2.35</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="S27">
+        <v>1.15</v>
+      </c>
+      <c r="T27">
+        <v>5.5</v>
+      </c>
+      <c r="U27">
+        <v>1.73</v>
+      </c>
+      <c r="V27">
+        <v>2</v>
+      </c>
+      <c r="W27">
+        <v>1.27</v>
+      </c>
+      <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.01</v>
+      </c>
+      <c r="Z27">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA27">
+        <v>1.28</v>
+      </c>
+      <c r="AB27">
+        <v>3.74</v>
+      </c>
+      <c r="AC27">
+        <v>1.6</v>
+      </c>
+      <c r="AD27">
+        <v>2.15</v>
+      </c>
+      <c r="AE27">
+        <v>1.51</v>
+      </c>
+      <c r="AF27">
+        <v>1.25</v>
+      </c>
+      <c r="AG27">
+        <v>3.5</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.22</v>
       </c>
-      <c r="T27">
-        <v>3.56</v>
-      </c>
-      <c r="U27">
-        <v>2.06</v>
-      </c>
-      <c r="V27">
-        <v>1.6</v>
-      </c>
-      <c r="W27">
-        <v>1.13</v>
-      </c>
-      <c r="X27">
-        <v>1.02</v>
-      </c>
-      <c r="Y27">
-        <v>1.11</v>
-      </c>
-      <c r="Z27">
-        <v>4.95</v>
-      </c>
-      <c r="AA27">
-        <v>1.44</v>
-      </c>
-      <c r="AB27">
-        <v>2.43</v>
-      </c>
-      <c r="AC27">
-        <v>2.17</v>
-      </c>
-      <c r="AD27">
-        <v>1.65</v>
-      </c>
-      <c r="AE27">
-        <v>1.23</v>
-      </c>
-      <c r="AF27">
-        <v>1.42</v>
-      </c>
-      <c r="AG27">
-        <v>2.66</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.27</v>
-      </c>
       <c r="AK27">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5368,13 +5368,13 @@
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="Q31">
         <v>2.8</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S31">
         <v>1.3</v>
@@ -5392,7 +5392,7 @@
         <v>1.09</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
         <v>1.22</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.62</v>
+        <v>5.15</v>
       </c>
       <c r="O32">
         <v>3.95</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="R33">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T33">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="AA33">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AB33">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.14</v>
+        <v>3.82</v>
       </c>
       <c r="AD33">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE33">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF33">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AG33">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q34">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="R34">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U34">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="V34">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="AA34">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AB34">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AC34">
-        <v>3.82</v>
+        <v>3.14</v>
       </c>
       <c r="AD34">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AG34">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>3.08</v>
       </c>
       <c r="AA39">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB39">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
         <v>3.28</v>
@@ -6720,10 +6720,10 @@
         <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG39">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U40">
         <v>2.35</v>
@@ -7650,7 +7650,7 @@
         <v>3.1</v>
       </c>
       <c r="P45">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q45">
         <v>2.86</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O56">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="P56">
-        <v>4.08</v>
+        <v>3.7</v>
       </c>
       <c r="Q56">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R56">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="S56">
+        <v>1.11</v>
+      </c>
+      <c r="T56">
+        <v>5.5</v>
+      </c>
+      <c r="U56">
+        <v>1.8</v>
+      </c>
+      <c r="V56">
+        <v>1.92</v>
+      </c>
+      <c r="W56">
+        <v>1.25</v>
+      </c>
+      <c r="X56">
+        <v>1.01</v>
+      </c>
+      <c r="Y56">
+        <v>1.03</v>
+      </c>
+      <c r="Z56">
+        <v>7.7</v>
+      </c>
+      <c r="AA56">
+        <v>1.25</v>
+      </c>
+      <c r="AB56">
+        <v>3.8</v>
+      </c>
+      <c r="AC56">
+        <v>1.7</v>
+      </c>
+      <c r="AD56">
+        <v>2.13</v>
+      </c>
+      <c r="AE56">
+        <v>1.49</v>
+      </c>
+      <c r="AF56">
+        <v>1.3</v>
+      </c>
+      <c r="AG56">
+        <v>3.14</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
         <v>1.2</v>
       </c>
-      <c r="T56">
-        <v>4</v>
-      </c>
-      <c r="U56">
-        <v>2.16</v>
-      </c>
-      <c r="V56">
-        <v>1.72</v>
-      </c>
-      <c r="W56">
-        <v>1.17</v>
-      </c>
-      <c r="X56">
-        <v>1.02</v>
-      </c>
-      <c r="Y56">
-        <v>1.09</v>
-      </c>
-      <c r="Z56">
-        <v>5.83</v>
-      </c>
-      <c r="AA56">
-        <v>1.44</v>
-      </c>
-      <c r="AB56">
-        <v>2.72</v>
-      </c>
-      <c r="AC56">
-        <v>2.04</v>
-      </c>
-      <c r="AD56">
-        <v>1.7</v>
-      </c>
-      <c r="AE56">
-        <v>1.3</v>
-      </c>
-      <c r="AF56">
-        <v>1.43</v>
-      </c>
-      <c r="AG56">
-        <v>2.63</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.15</v>
-      </c>
       <c r="AK56">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="O57">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P57">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="Q57">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="R57">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="S57">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="U57">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="W57">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>7.7</v>
+        <v>5.2</v>
       </c>
       <c r="AA57">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AB57">
-        <v>3.8</v>
+        <v>2.43</v>
       </c>
       <c r="AC57">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="AD57">
-        <v>2.13</v>
+        <v>1.61</v>
       </c>
       <c r="AE57">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AF57">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG57">
-        <v>3.14</v>
+        <v>2.49</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="O58">
+        <v>4.3</v>
+      </c>
+      <c r="P58">
+        <v>4.08</v>
+      </c>
+      <c r="Q58">
+        <v>2.12</v>
+      </c>
+      <c r="R58">
+        <v>2.5</v>
+      </c>
+      <c r="S58">
+        <v>1.2</v>
+      </c>
+      <c r="T58">
         <v>4</v>
       </c>
-      <c r="P58">
-        <v>3.45</v>
-      </c>
-      <c r="Q58">
-        <v>2.13</v>
-      </c>
-      <c r="R58">
-        <v>2.35</v>
-      </c>
-      <c r="S58">
-        <v>1.22</v>
-      </c>
-      <c r="T58">
-        <v>3.55</v>
-      </c>
       <c r="U58">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V58">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="W58">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z58">
-        <v>5.2</v>
+        <v>5.83</v>
       </c>
       <c r="AA58">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AB58">
-        <v>2.43</v>
+        <v>2.72</v>
       </c>
       <c r="AC58">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="AD58">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AE58">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AF58">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG58">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>1.95</v>
       </c>
       <c r="AB61">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC61">
         <v>3.2</v>
@@ -10584,7 +10584,7 @@
         <v>4.25</v>
       </c>
       <c r="P63">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="Q63">
         <v>4.65</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,65 +10904,65 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.01</v>
+        <v>1.54</v>
       </c>
       <c r="O65">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P65">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="Q65">
-        <v>2.64</v>
+        <v>1.95</v>
       </c>
       <c r="R65">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="S65">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>2.67</v>
+        <v>3.8</v>
       </c>
       <c r="U65">
-        <v>3.21</v>
+        <v>2.25</v>
       </c>
       <c r="V65">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="W65">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>2.97</v>
+        <v>4.57</v>
       </c>
       <c r="AA65">
+        <v>1.61</v>
+      </c>
+      <c r="AB65">
+        <v>2.27</v>
+      </c>
+      <c r="AC65">
+        <v>2.56</v>
+      </c>
+      <c r="AD65">
+        <v>1.48</v>
+      </c>
+      <c r="AE65">
+        <v>1.15</v>
+      </c>
+      <c r="AF65">
+        <v>1.63</v>
+      </c>
+      <c r="AG65">
         <v>2.14</v>
       </c>
-      <c r="AB65">
-        <v>1.65</v>
-      </c>
-      <c r="AC65">
-        <v>3.75</v>
-      </c>
-      <c r="AD65">
-        <v>1.19</v>
-      </c>
-      <c r="AE65">
-        <v>1.03</v>
-      </c>
-      <c r="AF65">
-        <v>1.88</v>
-      </c>
-      <c r="AG65">
-        <v>1.82</v>
-      </c>
       <c r="AH65" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AK65">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.54</v>
+        <v>2.45</v>
       </c>
       <c r="O66">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q66">
-        <v>1.95</v>
+        <v>2.99</v>
       </c>
       <c r="R66">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="S66">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T66">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="U66">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="V66">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z66">
-        <v>4.57</v>
+        <v>3.28</v>
       </c>
       <c r="AA66">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AB66">
-        <v>2.27</v>
+        <v>1.88</v>
       </c>
       <c r="AC66">
-        <v>2.56</v>
+        <v>3.21</v>
       </c>
       <c r="AD66">
+        <v>1.33</v>
+      </c>
+      <c r="AE66">
+        <v>1.12</v>
+      </c>
+      <c r="AF66">
+        <v>1.68</v>
+      </c>
+      <c r="AG66">
+        <v>2.06</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>1.28</v>
+      </c>
+      <c r="AK66">
         <v>1.48</v>
-      </c>
-      <c r="AE66">
-        <v>1.15</v>
-      </c>
-      <c r="AF66">
-        <v>1.63</v>
-      </c>
-      <c r="AG66">
-        <v>2.14</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.18</v>
-      </c>
-      <c r="AK66">
-        <v>2.3</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="O67">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P67">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q67">
-        <v>2.99</v>
+        <v>2.64</v>
       </c>
       <c r="R67">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="S67">
+        <v>1.4</v>
+      </c>
+      <c r="T67">
+        <v>2.67</v>
+      </c>
+      <c r="U67">
+        <v>3.21</v>
+      </c>
+      <c r="V67">
+        <v>1.32</v>
+      </c>
+      <c r="W67">
+        <v>1.05</v>
+      </c>
+      <c r="X67">
+        <v>1.02</v>
+      </c>
+      <c r="Y67">
         <v>1.38</v>
       </c>
-      <c r="T67">
-        <v>2.9</v>
-      </c>
-      <c r="U67">
-        <v>2.81</v>
-      </c>
-      <c r="V67">
-        <v>1.4</v>
-      </c>
-      <c r="W67">
-        <v>1.08</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.28</v>
-      </c>
       <c r="Z67">
-        <v>3.57</v>
+        <v>2.97</v>
       </c>
       <c r="AA67">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AB67">
+        <v>1.65</v>
+      </c>
+      <c r="AC67">
+        <v>3.75</v>
+      </c>
+      <c r="AD67">
+        <v>1.19</v>
+      </c>
+      <c r="AE67">
+        <v>1.03</v>
+      </c>
+      <c r="AF67">
         <v>1.88</v>
       </c>
-      <c r="AC67">
-        <v>3.21</v>
-      </c>
-      <c r="AD67">
-        <v>1.33</v>
-      </c>
-      <c r="AE67">
-        <v>1.12</v>
-      </c>
-      <c r="AF67">
-        <v>1.68</v>
-      </c>
       <c r="AG67">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK67">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="O70">
-        <v>3.75</v>
+        <v>3.37</v>
       </c>
       <c r="P70">
-        <v>3.79</v>
+        <v>2.87</v>
       </c>
       <c r="Q70">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="R70">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
+        <v>1.38</v>
+      </c>
+      <c r="T70">
+        <v>2.9</v>
+      </c>
+      <c r="U70">
+        <v>2.91</v>
+      </c>
+      <c r="V70">
+        <v>1.39</v>
+      </c>
+      <c r="W70">
+        <v>1.08</v>
+      </c>
+      <c r="X70">
+        <v>1.01</v>
+      </c>
+      <c r="Y70">
         <v>1.3</v>
       </c>
-      <c r="T70">
-        <v>2.86</v>
-      </c>
-      <c r="U70">
-        <v>2.48</v>
-      </c>
-      <c r="V70">
-        <v>1.46</v>
-      </c>
-      <c r="W70">
-        <v>1.07</v>
-      </c>
-      <c r="X70">
-        <v>1.02</v>
-      </c>
-      <c r="Y70">
-        <v>1.21</v>
-      </c>
       <c r="Z70">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA70">
+        <v>1.94</v>
+      </c>
+      <c r="AB70">
         <v>1.8</v>
       </c>
-      <c r="AB70">
-        <v>1.98</v>
-      </c>
       <c r="AC70">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="AD70">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE70">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG70">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK70">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,80 +11882,80 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="O71">
-        <v>3.37</v>
+        <v>3.75</v>
       </c>
       <c r="P71">
-        <v>2.87</v>
+        <v>3.79</v>
       </c>
       <c r="Q71">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="R71">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="S71">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="U71">
-        <v>2.91</v>
+        <v>2.48</v>
       </c>
       <c r="V71">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W71">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z71">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA71">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AB71">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AC71">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="AD71">
+        <v>1.33</v>
+      </c>
+      <c r="AE71">
+        <v>1.09</v>
+      </c>
+      <c r="AF71">
+        <v>1.7</v>
+      </c>
+      <c r="AG71">
+        <v>2.03</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
         <v>1.25</v>
       </c>
-      <c r="AE71">
-        <v>1.11</v>
-      </c>
-      <c r="AF71">
-        <v>1.71</v>
-      </c>
-      <c r="AG71">
-        <v>2</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>1.3</v>
-      </c>
       <c r="AK71">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12751,7 +12751,7 @@
         <v>1.16</v>
       </c>
       <c r="AF76">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG76">
         <v>1.95</v>
@@ -13038,7 +13038,7 @@
         <v>2.5</v>
       </c>
       <c r="S78">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T78">
         <v>3.9</v>
@@ -13050,7 +13050,7 @@
         <v>1.67</v>
       </c>
       <c r="W78">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X78">
         <v>1.02</v>
@@ -13071,10 +13071,10 @@
         <v>2.06</v>
       </c>
       <c r="AD78">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE78">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF78">
         <v>1.49</v>
@@ -14185,7 +14185,7 @@
         <v>3.3</v>
       </c>
       <c r="U85">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="V85">
         <v>1.54</v>
@@ -14206,7 +14206,7 @@
         <v>1.6</v>
       </c>
       <c r="AB85">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC85">
         <v>2.33</v>
@@ -15018,7 +15018,7 @@
         <v>4.4</v>
       </c>
       <c r="AA90">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB90">
         <v>2.38</v>
@@ -15347,7 +15347,7 @@
         <v>1.8</v>
       </c>
       <c r="AB92">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC92">
         <v>3.1</v>
@@ -15474,7 +15474,7 @@
         <v>3.11</v>
       </c>
       <c r="P93">
-        <v>3.26</v>
+        <v>3.56</v>
       </c>
       <c r="Q93">
         <v>2.77</v>
@@ -17913,19 +17913,19 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O108">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P108">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q108">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="R108">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S108">
         <v>1.36</v>
@@ -17934,7 +17934,7 @@
         <v>2.73</v>
       </c>
       <c r="U108">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="V108">
         <v>1.36</v>
@@ -17955,7 +17955,7 @@
         <v>2.07</v>
       </c>
       <c r="AB108">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC108">
         <v>3.34</v>
@@ -17964,13 +17964,13 @@
         <v>1.24</v>
       </c>
       <c r="AE108">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF108">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG108">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18085,10 +18085,10 @@
         <v>2.5</v>
       </c>
       <c r="Q109">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R109">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S109">
         <v>1.33</v>
@@ -18106,7 +18106,7 @@
         <v>1.05</v>
       </c>
       <c r="X109">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
         <v>1.26</v>
@@ -18115,10 +18115,10 @@
         <v>3.2</v>
       </c>
       <c r="AA109">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AB109">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC109">
         <v>3.34</v>
@@ -18133,7 +18133,7 @@
         <v>1.71</v>
       </c>
       <c r="AG109">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK109">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18245,7 +18245,7 @@
         <v>3.2</v>
       </c>
       <c r="P110">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q110">
         <v>3.02</v>
@@ -18266,7 +18266,7 @@
         <v>1.46</v>
       </c>
       <c r="W110">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X110">
         <v>1</v>
@@ -18921,7 +18921,7 @@
         <v>1.05</v>
       </c>
       <c r="X114">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y114">
         <v>1.31</v>
@@ -18933,13 +18933,13 @@
         <v>2.15</v>
       </c>
       <c r="AB114">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC114">
         <v>4</v>
       </c>
       <c r="AD114">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE114">
         <v>1.04</v>
@@ -18948,7 +18948,7 @@
         <v>1.79</v>
       </c>
       <c r="AG114">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AK114">
         <v>1.37</v>
@@ -19057,7 +19057,7 @@
         <v>1.78</v>
       </c>
       <c r="O115">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P115">
         <v>4</v>
@@ -19241,7 +19241,7 @@
         <v>2.4</v>
       </c>
       <c r="V116">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W116">
         <v>1.08</v>
@@ -19256,7 +19256,7 @@
         <v>4.1</v>
       </c>
       <c r="AA116">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB116">
         <v>2.12</v>
@@ -19437,7 +19437,7 @@
         <v>1.8</v>
       </c>
       <c r="AG117">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O118">
         <v>3.25</v>
@@ -20883,7 +20883,7 @@
         <v>1.25</v>
       </c>
       <c r="Z126">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA126">
         <v>1.83</v>
@@ -21668,13 +21668,13 @@
         <v>4.75</v>
       </c>
       <c r="P131">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="Q131">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R131">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S131">
         <v>1.21</v>
@@ -21735,7 +21735,7 @@
         <v>1.16</v>
       </c>
       <c r="AK131">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -22061,7 +22061,7 @@
         <v>1.21</v>
       </c>
       <c r="AK133">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22486,10 +22486,10 @@
         <v>7.12</v>
       </c>
       <c r="Q136">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R136">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="S136">
         <v>1.25</v>
@@ -22510,16 +22510,16 @@
         <v>0</v>
       </c>
       <c r="Y136">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z136">
         <v>4.05</v>
       </c>
       <c r="AA136">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB136">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC136">
         <v>2.49</v>
@@ -22531,10 +22531,10 @@
         <v>1.14</v>
       </c>
       <c r="AF136">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG136">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22679,10 +22679,10 @@
         <v>3.28</v>
       </c>
       <c r="AA137">
+        <v>1.83</v>
+      </c>
+      <c r="AB137">
         <v>1.9</v>
-      </c>
-      <c r="AB137">
-        <v>1.83</v>
       </c>
       <c r="AC137">
         <v>3.04</v>
@@ -22815,13 +22815,13 @@
         <v>1.62</v>
       </c>
       <c r="R138">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="S138">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T138">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="U138">
         <v>2.1</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.42</v>
+        <v>2.68</v>
       </c>
       <c r="O139">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="P139">
-        <v>5.2</v>
+        <v>2.31</v>
       </c>
       <c r="Q139">
-        <v>1.9</v>
+        <v>4.05</v>
       </c>
       <c r="R139">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="S139">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T139">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="U139">
-        <v>2.18</v>
+        <v>2.86</v>
       </c>
       <c r="V139">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="W139">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X139">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y139">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="Z139">
-        <v>5.05</v>
+        <v>2.86</v>
       </c>
       <c r="AA139">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="AB139">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC139">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="AD139">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="AE139">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AF139">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AG139">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK139">
-        <v>2.59</v>
+        <v>1.38</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.68</v>
+        <v>1.42</v>
       </c>
       <c r="O140">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="P140">
-        <v>2.31</v>
+        <v>5.2</v>
       </c>
       <c r="Q140">
-        <v>4.05</v>
+        <v>1.9</v>
       </c>
       <c r="R140">
+        <v>2.48</v>
+      </c>
+      <c r="S140">
+        <v>1.25</v>
+      </c>
+      <c r="T140">
+        <v>3.55</v>
+      </c>
+      <c r="U140">
+        <v>2.18</v>
+      </c>
+      <c r="V140">
+        <v>1.67</v>
+      </c>
+      <c r="W140">
+        <v>1.14</v>
+      </c>
+      <c r="X140">
+        <v>1.01</v>
+      </c>
+      <c r="Y140">
+        <v>1.1</v>
+      </c>
+      <c r="Z140">
+        <v>5.05</v>
+      </c>
+      <c r="AA140">
+        <v>1.43</v>
+      </c>
+      <c r="AB140">
+        <v>2.56</v>
+      </c>
+      <c r="AC140">
         <v>2.15</v>
       </c>
-      <c r="S140">
-        <v>1.4</v>
-      </c>
-      <c r="T140">
-        <v>2.75</v>
-      </c>
-      <c r="U140">
-        <v>2.86</v>
-      </c>
-      <c r="V140">
-        <v>1.36</v>
-      </c>
-      <c r="W140">
-        <v>1.06</v>
-      </c>
-      <c r="X140">
-        <v>1.06</v>
-      </c>
-      <c r="Y140">
-        <v>1.35</v>
-      </c>
-      <c r="Z140">
-        <v>2.86</v>
-      </c>
-      <c r="AA140">
-        <v>2.2</v>
-      </c>
-      <c r="AB140">
-        <v>1.65</v>
-      </c>
-      <c r="AC140">
-        <v>3.6</v>
-      </c>
       <c r="AD140">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="AE140">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AF140">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AG140">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK140">
-        <v>1.38</v>
+        <v>2.59</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23666,7 +23666,7 @@
         <v>2.46</v>
       </c>
       <c r="AD143">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE143">
         <v>1.18</v>
@@ -23974,7 +23974,7 @@
         <v>1.11</v>
       </c>
       <c r="X145">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y145">
         <v>1.17</v>
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O146">
         <v>3.5</v>
       </c>
       <c r="P146">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q146">
         <v>2.85</v>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O149">
         <v>3.83</v>
@@ -24653,7 +24653,7 @@
         <v>1.45</v>
       </c>
       <c r="AG149">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK149">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24922,25 +24922,25 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="O151">
         <v>5.5</v>
       </c>
       <c r="P151">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q151">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R151">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="S151">
         <v>1.11</v>
       </c>
       <c r="T151">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="U151">
         <v>1.86</v>
@@ -24949,37 +24949,37 @@
         <v>2</v>
       </c>
       <c r="W151">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X151">
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z151">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="AA151">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AB151">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AC151">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AD151">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AE151">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AF151">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG151">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>1.16</v>
       </c>
       <c r="AK151">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O153">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P153">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="Q153">
         <v>1.92</v>
@@ -25266,10 +25266,10 @@
         <v>1.29</v>
       </c>
       <c r="T153">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="U153">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="V153">
         <v>1.44</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="O154">
         <v>3.5</v>
       </c>
       <c r="P154">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -25426,7 +25426,7 @@
         <v>2.17</v>
       </c>
       <c r="S154">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T154">
         <v>3.12</v>
@@ -25450,7 +25450,7 @@
         <v>4</v>
       </c>
       <c r="AA154">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB154">
         <v>2.05</v>
@@ -25613,10 +25613,10 @@
         <v>2.88</v>
       </c>
       <c r="AA155">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB155">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC155">
         <v>3.82</v>
@@ -26093,7 +26093,7 @@
         <v>1.14</v>
       </c>
       <c r="X158">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y158">
         <v>1.19</v>
@@ -26241,7 +26241,7 @@
         <v>2.39</v>
       </c>
       <c r="S159">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T159">
         <v>3.4</v>
@@ -26256,7 +26256,7 @@
         <v>1.13</v>
       </c>
       <c r="X159">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
         <v>1.2</v>
@@ -26265,7 +26265,7 @@
         <v>4.05</v>
       </c>
       <c r="AA159">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB159">
         <v>2.12</v>
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="O161">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="P161">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Q161">
         <v>7.5</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,16 +27367,16 @@
         </is>
       </c>
       <c r="N166">
-        <v>5.64</v>
+        <v>1.4</v>
       </c>
       <c r="O166">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P166">
-        <v>1.57</v>
+        <v>6</v>
       </c>
       <c r="Q166">
-        <v>5.55</v>
+        <v>1.91</v>
       </c>
       <c r="R166">
         <v>2.3</v>
@@ -27385,7 +27385,7 @@
         <v>1.3</v>
       </c>
       <c r="T166">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U166">
         <v>2.75</v>
@@ -27394,53 +27394,53 @@
         <v>1.4</v>
       </c>
       <c r="W166">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X166">
+        <v>1.02</v>
+      </c>
+      <c r="Y166">
+        <v>1.27</v>
+      </c>
+      <c r="Z166">
+        <v>3.58</v>
+      </c>
+      <c r="AA166">
+        <v>1.79</v>
+      </c>
+      <c r="AB166">
+        <v>1.9</v>
+      </c>
+      <c r="AC166">
+        <v>3.05</v>
+      </c>
+      <c r="AD166">
+        <v>1.35</v>
+      </c>
+      <c r="AE166">
+        <v>1.12</v>
+      </c>
+      <c r="AF166">
+        <v>1.98</v>
+      </c>
+      <c r="AG166">
+        <v>1.72</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ166">
         <v>1.03</v>
       </c>
-      <c r="Y166">
-        <v>1.25</v>
-      </c>
-      <c r="Z166">
-        <v>3.6</v>
-      </c>
-      <c r="AA166">
-        <v>1.82</v>
-      </c>
-      <c r="AB166">
-        <v>1.85</v>
-      </c>
-      <c r="AC166">
-        <v>3.2</v>
-      </c>
-      <c r="AD166">
-        <v>1.32</v>
-      </c>
-      <c r="AE166">
-        <v>1.11</v>
-      </c>
-      <c r="AF166">
-        <v>1.87</v>
-      </c>
-      <c r="AG166">
-        <v>1.85</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ166">
-        <v>1.17</v>
-      </c>
       <c r="AK166">
-        <v>1.14</v>
+        <v>2.75</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,25 +27693,25 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.4</v>
+        <v>5.64</v>
       </c>
       <c r="O168">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P168">
-        <v>6</v>
+        <v>1.57</v>
       </c>
       <c r="Q168">
-        <v>1.91</v>
+        <v>5.55</v>
       </c>
       <c r="R168">
         <v>2.3</v>
       </c>
       <c r="S168">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T168">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U168">
         <v>2.75</v>
@@ -27720,37 +27720,37 @@
         <v>1.4</v>
       </c>
       <c r="W168">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X168">
         <v>1.02</v>
       </c>
       <c r="Y168">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z168">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA168">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB168">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC168">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD168">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE168">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF168">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AG168">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AK168">
-        <v>2.75</v>
+        <v>1.14</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27886,7 +27886,7 @@
         <v>1.11</v>
       </c>
       <c r="X169">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y169">
         <v>1.1</v>
@@ -28037,7 +28037,7 @@
         <v>1.35</v>
       </c>
       <c r="T170">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="U170">
         <v>2.75</v>
@@ -28055,10 +28055,10 @@
         <v>1.28</v>
       </c>
       <c r="Z170">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="AA170">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB170">
         <v>1.8</v>
@@ -28188,13 +28188,13 @@
         <v>3.3</v>
       </c>
       <c r="P171">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q171">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="R171">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S171">
         <v>1.39</v>
@@ -28345,58 +28345,58 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="O172">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P172">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q172">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="R172">
         <v>2.38</v>
       </c>
       <c r="S172">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T172">
         <v>3.3</v>
       </c>
       <c r="U172">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V172">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W172">
         <v>1.11</v>
       </c>
       <c r="X172">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y172">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z172">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA172">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB172">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AC172">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AD172">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE172">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF172">
         <v>1.58</v>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK172">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28517,7 +28517,7 @@
         <v>3.6</v>
       </c>
       <c r="Q173">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="R173">
         <v>2.2</v>
@@ -28529,10 +28529,10 @@
         <v>2.92</v>
       </c>
       <c r="U173">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="V173">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W173">
         <v>1.07</v>
@@ -28544,7 +28544,7 @@
         <v>1.27</v>
       </c>
       <c r="Z173">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="AA173">
         <v>1.87</v>
@@ -28553,7 +28553,7 @@
         <v>1.92</v>
       </c>
       <c r="AC173">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="AD173">
         <v>1.32</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.95</v>
+        <v>1.62</v>
       </c>
       <c r="O174">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P174">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q174">
-        <v>3.5</v>
+        <v>2.13</v>
       </c>
       <c r="R174">
-        <v>2.11</v>
+        <v>2.47</v>
       </c>
       <c r="S174">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T174">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U174">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="V174">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W174">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X174">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y174">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z174">
-        <v>3.91</v>
+        <v>4.53</v>
       </c>
       <c r="AA174">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AB174">
-        <v>2.01</v>
+        <v>2.27</v>
       </c>
       <c r="AC174">
-        <v>2.93</v>
+        <v>2.64</v>
       </c>
       <c r="AD174">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AE174">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF174">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG174">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK174">
-        <v>1.3</v>
+        <v>2.19</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="O175">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P175">
-        <v>4.8</v>
+        <v>2.47</v>
       </c>
       <c r="Q175">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="R175">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S175">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T175">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U175">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="V175">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W175">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X175">
         <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z175">
-        <v>4.53</v>
+        <v>3.78</v>
       </c>
       <c r="AA175">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AB175">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="AC175">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="AD175">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AE175">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF175">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG175">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK175">
-        <v>2.19</v>
+        <v>1.45</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O176">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P176">
         <v>2.75</v>
       </c>
       <c r="Q176">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R176">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S176">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T176">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="U176">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="V176">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W176">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X176">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z176">
-        <v>3.43</v>
+        <v>3.15</v>
       </c>
       <c r="AA176">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AB176">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AC176">
-        <v>3.39</v>
+        <v>3.68</v>
       </c>
       <c r="AD176">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE176">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF176">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG176">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK176">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O177">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P177">
         <v>2.75</v>
       </c>
       <c r="Q177">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R177">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S177">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T177">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="U177">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="V177">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W177">
         <v>1.06</v>
       </c>
       <c r="X177">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z177">
-        <v>3.15</v>
+        <v>3.43</v>
       </c>
       <c r="AA177">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="AB177">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AC177">
-        <v>3.68</v>
+        <v>3.39</v>
       </c>
       <c r="AD177">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE177">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF177">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG177">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK177">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="O178">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P178">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q178">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R178">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S178">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T178">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U178">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="V178">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W178">
+        <v>1.07</v>
+      </c>
+      <c r="X178">
+        <v>1.01</v>
+      </c>
+      <c r="Y178">
+        <v>1.24</v>
+      </c>
+      <c r="Z178">
+        <v>3.91</v>
+      </c>
+      <c r="AA178">
+        <v>1.78</v>
+      </c>
+      <c r="AB178">
+        <v>2.01</v>
+      </c>
+      <c r="AC178">
+        <v>2.93</v>
+      </c>
+      <c r="AD178">
+        <v>1.32</v>
+      </c>
+      <c r="AE178">
         <v>1.08</v>
       </c>
-      <c r="X178">
-        <v>1.02</v>
-      </c>
-      <c r="Y178">
-        <v>1.23</v>
-      </c>
-      <c r="Z178">
-        <v>3.78</v>
-      </c>
-      <c r="AA178">
-        <v>1.76</v>
-      </c>
-      <c r="AB178">
-        <v>2.04</v>
-      </c>
-      <c r="AC178">
-        <v>2.98</v>
-      </c>
-      <c r="AD178">
-        <v>1.35</v>
-      </c>
-      <c r="AE178">
-        <v>1.1</v>
-      </c>
       <c r="AF178">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG178">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK178">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29676,7 +29676,7 @@
         <v>2.21</v>
       </c>
       <c r="W180">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X180">
         <v>1</v>
@@ -30473,22 +30473,22 @@
         <v>8.25</v>
       </c>
       <c r="Q185">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="R185">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="S185">
         <v>1.14</v>
       </c>
       <c r="T185">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="U185">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V185">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W185">
         <v>1.25</v>
@@ -30500,13 +30500,13 @@
         <v>1.04</v>
       </c>
       <c r="Z185">
-        <v>6.95</v>
+        <v>6.85</v>
       </c>
       <c r="AA185">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AB185">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AC185">
         <v>1.73</v>
@@ -30518,10 +30518,10 @@
         <v>1.4</v>
       </c>
       <c r="AF185">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AG185">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>2.7</v>
       </c>
       <c r="Q188">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R188">
         <v>2.4</v>
@@ -30998,16 +30998,16 @@
         <v>2.62</v>
       </c>
       <c r="AC188">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD188">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE188">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF188">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AG188">
         <v>2.8</v>
@@ -31026,7 +31026,7 @@
         <v>1.17</v>
       </c>
       <c r="AK188">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31445,13 +31445,13 @@
         <v>1.49</v>
       </c>
       <c r="O191">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="P191">
         <v>4.5</v>
       </c>
       <c r="Q191">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R191">
         <v>2.88</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="O192">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P192">
-        <v>4.33</v>
+        <v>7.75</v>
       </c>
       <c r="Q192">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="R192">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S192">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T192">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="U192">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V192">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W192">
         <v>1.14</v>
       </c>
       <c r="X192">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y192">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z192">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA192">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AB192">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="AC192">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AD192">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AE192">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AF192">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AG192">
-        <v>2.53</v>
+        <v>1.85</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK192">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.32</v>
+        <v>3.7</v>
       </c>
       <c r="O193">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="P193">
-        <v>7.75</v>
+        <v>1.92</v>
       </c>
       <c r="Q193">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="R193">
-        <v>2.51</v>
+        <v>2.13</v>
       </c>
       <c r="S193">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T193">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U193">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="V193">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W193">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X193">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y193">
+        <v>1.27</v>
+      </c>
+      <c r="Z193">
+        <v>3.48</v>
+      </c>
+      <c r="AA193">
+        <v>1.86</v>
+      </c>
+      <c r="AB193">
+        <v>1.97</v>
+      </c>
+      <c r="AC193">
+        <v>3.05</v>
+      </c>
+      <c r="AD193">
+        <v>1.35</v>
+      </c>
+      <c r="AE193">
         <v>1.13</v>
       </c>
-      <c r="Z193">
-        <v>4.75</v>
-      </c>
-      <c r="AA193">
-        <v>1.6</v>
-      </c>
-      <c r="AB193">
-        <v>2.37</v>
-      </c>
-      <c r="AC193">
-        <v>2.35</v>
-      </c>
-      <c r="AD193">
-        <v>1.54</v>
-      </c>
-      <c r="AE193">
-        <v>1.15</v>
-      </c>
       <c r="AF193">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG193">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="AK193">
-        <v>3.1</v>
+        <v>1.25</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="O195">
-        <v>3.34</v>
+        <v>3.62</v>
       </c>
       <c r="P195">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q195">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R195">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="S195">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="T195">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="U195">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="V195">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W195">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X195">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z195">
-        <v>3.28</v>
+        <v>5.1</v>
       </c>
       <c r="AA195">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AB195">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AC195">
-        <v>3.35</v>
+        <v>2.35</v>
       </c>
       <c r="AD195">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="AE195">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF195">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG195">
-        <v>2.01</v>
+        <v>2.55</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK195">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="O196">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P196">
-        <v>1.92</v>
+        <v>4.2</v>
       </c>
       <c r="Q196">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="R196">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="S196">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T196">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="U196">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="V196">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="W196">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X196">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y196">
+        <v>1.14</v>
+      </c>
+      <c r="Z196">
+        <v>5.5</v>
+      </c>
+      <c r="AA196">
+        <v>1.48</v>
+      </c>
+      <c r="AB196">
+        <v>2.65</v>
+      </c>
+      <c r="AC196">
+        <v>2.15</v>
+      </c>
+      <c r="AD196">
+        <v>1.65</v>
+      </c>
+      <c r="AE196">
         <v>1.27</v>
       </c>
-      <c r="Z196">
-        <v>3.48</v>
-      </c>
-      <c r="AA196">
-        <v>1.86</v>
-      </c>
-      <c r="AB196">
-        <v>1.97</v>
-      </c>
-      <c r="AC196">
-        <v>3.05</v>
-      </c>
-      <c r="AD196">
-        <v>1.35</v>
-      </c>
-      <c r="AE196">
-        <v>1.13</v>
-      </c>
       <c r="AF196">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AG196">
-        <v>2.04</v>
+        <v>2.53</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.8</v>
+        <v>1.19</v>
       </c>
       <c r="AK196">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32426,7 +32426,7 @@
         <v>3.35</v>
       </c>
       <c r="P197">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="Q197">
         <v>2.8</v>
@@ -32468,7 +32468,7 @@
         <v>3.27</v>
       </c>
       <c r="AD197">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE197">
         <v>1.12</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,80 +32583,80 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="O198">
-        <v>3.62</v>
+        <v>3.34</v>
       </c>
       <c r="P198">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="Q198">
+        <v>2.88</v>
+      </c>
+      <c r="R198">
+        <v>2.06</v>
+      </c>
+      <c r="S198">
+        <v>1.37</v>
+      </c>
+      <c r="T198">
         <v>3</v>
       </c>
-      <c r="R198">
-        <v>2.4</v>
-      </c>
-      <c r="S198">
-        <v>1.22</v>
-      </c>
-      <c r="T198">
-        <v>3.5</v>
-      </c>
       <c r="U198">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="V198">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W198">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X198">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y198">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z198">
-        <v>5.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA198">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB198">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AC198">
-        <v>2.35</v>
+        <v>3.35</v>
       </c>
       <c r="AD198">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="AE198">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF198">
+        <v>1.7</v>
+      </c>
+      <c r="AG198">
+        <v>2.01</v>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ198">
+        <v>1.25</v>
+      </c>
+      <c r="AK198">
         <v>1.5</v>
-      </c>
-      <c r="AG198">
-        <v>2.55</v>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ198">
-        <v>1.22</v>
-      </c>
-      <c r="AK198">
-        <v>1.48</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -33241,7 +33241,7 @@
         <v>3.75</v>
       </c>
       <c r="P202">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q202">
         <v>2.38</v>
@@ -33253,7 +33253,7 @@
         <v>1.25</v>
       </c>
       <c r="T202">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U202">
         <v>2.4</v>
@@ -33262,7 +33262,7 @@
         <v>1.5</v>
       </c>
       <c r="W202">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X202">
         <v>1.02</v>
@@ -33428,7 +33428,7 @@
         <v>1.11</v>
       </c>
       <c r="X203">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y203">
         <v>1.15</v>
@@ -33440,7 +33440,7 @@
         <v>1.6</v>
       </c>
       <c r="AB203">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC203">
         <v>2.48</v>
@@ -33754,7 +33754,7 @@
         <v>1.09</v>
       </c>
       <c r="X205">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y205">
         <v>1.17</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G209">
@@ -34379,61 +34379,61 @@
         <v>2.34</v>
       </c>
       <c r="O209">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P209">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="Q209">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="R209">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S209">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="T209">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="U209">
-        <v>2.95</v>
+        <v>2.49</v>
       </c>
       <c r="V209">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="W209">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X209">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z209">
-        <v>2.92</v>
+        <v>4.41</v>
       </c>
       <c r="AA209">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB209">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AC209">
-        <v>3.48</v>
+        <v>2.69</v>
       </c>
       <c r="AD209">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AE209">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF209">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AG209">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK209">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
+        <v>2.7</v>
+      </c>
+      <c r="O210">
+        <v>3.15</v>
+      </c>
+      <c r="P210">
+        <v>2.42</v>
+      </c>
+      <c r="Q210">
+        <v>4.38</v>
+      </c>
+      <c r="R210">
+        <v>2.36</v>
+      </c>
+      <c r="S210">
+        <v>1.33</v>
+      </c>
+      <c r="T210">
+        <v>2.87</v>
+      </c>
+      <c r="U210">
         <v>2.55</v>
       </c>
-      <c r="O210">
-        <v>3.35</v>
-      </c>
-      <c r="P210">
-        <v>2.43</v>
-      </c>
-      <c r="Q210">
+      <c r="V210">
+        <v>1.44</v>
+      </c>
+      <c r="W210">
+        <v>1.07</v>
+      </c>
+      <c r="X210">
+        <v>1</v>
+      </c>
+      <c r="Y210">
+        <v>1.21</v>
+      </c>
+      <c r="Z210">
+        <v>4.02</v>
+      </c>
+      <c r="AA210">
+        <v>1.75</v>
+      </c>
+      <c r="AB210">
+        <v>2.07</v>
+      </c>
+      <c r="AC210">
         <v>2.88</v>
       </c>
-      <c r="R210">
-        <v>2.3</v>
-      </c>
-      <c r="S210">
-        <v>1.28</v>
-      </c>
-      <c r="T210">
-        <v>3.3</v>
-      </c>
-      <c r="U210">
-        <v>2.56</v>
-      </c>
-      <c r="V210">
-        <v>1.5</v>
-      </c>
-      <c r="W210">
-        <v>1.08</v>
-      </c>
-      <c r="X210">
-        <v>1.01</v>
-      </c>
-      <c r="Y210">
-        <v>1.22</v>
-      </c>
-      <c r="Z210">
-        <v>3.7</v>
-      </c>
-      <c r="AA210">
-        <v>1.64</v>
-      </c>
-      <c r="AB210">
-        <v>2.17</v>
-      </c>
-      <c r="AC210">
-        <v>2.52</v>
-      </c>
       <c r="AD210">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE210">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF210">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AG210">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="AK210">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="O211">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="P211">
-        <v>2.57</v>
+        <v>2.94</v>
       </c>
       <c r="Q211">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R211">
         <v>2.1</v>
       </c>
       <c r="S211">
+        <v>1.42</v>
+      </c>
+      <c r="T211">
+        <v>2.6</v>
+      </c>
+      <c r="U211">
+        <v>2.95</v>
+      </c>
+      <c r="V211">
         <v>1.33</v>
       </c>
-      <c r="T211">
-        <v>3</v>
-      </c>
-      <c r="U211">
-        <v>2.88</v>
-      </c>
-      <c r="V211">
-        <v>1.36</v>
-      </c>
       <c r="W211">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X211">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y211">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z211">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA211">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB211">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC211">
-        <v>3.08</v>
+        <v>3.48</v>
       </c>
       <c r="AD211">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE211">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF211">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AG211">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK211">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="O213">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P213">
-        <v>2.7</v>
+        <v>4.14</v>
       </c>
       <c r="Q213">
-        <v>3.2</v>
+        <v>2.06</v>
       </c>
       <c r="R213">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S213">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T213">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="U213">
-        <v>2.49</v>
+        <v>2.01</v>
       </c>
       <c r="V213">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="W213">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X213">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y213">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z213">
-        <v>4.41</v>
+        <v>5.7</v>
       </c>
       <c r="AA213">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AB213">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="AC213">
-        <v>2.69</v>
+        <v>2.04</v>
       </c>
       <c r="AD213">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="AE213">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF213">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG213">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AK213">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,25 +35191,25 @@
         </is>
       </c>
       <c r="N214">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="O214">
+        <v>3.36</v>
+      </c>
+      <c r="P214">
+        <v>2.57</v>
+      </c>
+      <c r="Q214">
         <v>3.1</v>
       </c>
-      <c r="P214">
-        <v>2.65</v>
-      </c>
-      <c r="Q214">
-        <v>3.04</v>
-      </c>
       <c r="R214">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S214">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T214">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U214">
         <v>2.88</v>
@@ -35218,37 +35218,37 @@
         <v>1.36</v>
       </c>
       <c r="W214">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X214">
         <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z214">
-        <v>3.05</v>
+        <v>3.66</v>
       </c>
       <c r="AA214">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB214">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AC214">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD214">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE214">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF214">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG214">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK214">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O215">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P215">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="Q215">
-        <v>4.38</v>
+        <v>3.04</v>
       </c>
       <c r="R215">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="S215">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T215">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="U215">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="V215">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W215">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X215">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y215">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z215">
-        <v>4.02</v>
+        <v>3.05</v>
       </c>
       <c r="AA215">
+        <v>1.96</v>
+      </c>
+      <c r="AB215">
+        <v>1.72</v>
+      </c>
+      <c r="AC215">
+        <v>3.25</v>
+      </c>
+      <c r="AD215">
+        <v>1.28</v>
+      </c>
+      <c r="AE215">
+        <v>1.03</v>
+      </c>
+      <c r="AF215">
         <v>1.75</v>
       </c>
-      <c r="AB215">
-        <v>2.05</v>
-      </c>
-      <c r="AC215">
-        <v>2.88</v>
-      </c>
-      <c r="AD215">
-        <v>1.4</v>
-      </c>
-      <c r="AE215">
-        <v>1.15</v>
-      </c>
-      <c r="AF215">
-        <v>1.66</v>
-      </c>
       <c r="AG215">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.85</v>
+        <v>1.26</v>
       </c>
       <c r="AK215">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.71</v>
+        <v>2.55</v>
       </c>
       <c r="O216">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P216">
-        <v>4.14</v>
+        <v>2.43</v>
       </c>
       <c r="Q216">
-        <v>2.06</v>
+        <v>2.88</v>
       </c>
       <c r="R216">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="S216">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T216">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="U216">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="V216">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="W216">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X216">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="Z216">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="AA216">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AB216">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="AC216">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="AD216">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="AE216">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AF216">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AG216">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK216">
-        <v>2.23</v>
+        <v>1.5</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="O220">
         <v>3.9</v>
       </c>
       <c r="P220">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q220">
         <v>4.33</v>
@@ -36211,7 +36211,7 @@
         <v>1.68</v>
       </c>
       <c r="AB220">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC220">
         <v>2.76</v>
@@ -36495,7 +36495,7 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O222">
         <v>3.73</v>
@@ -37189,7 +37189,7 @@
         <v>1.47</v>
       </c>
       <c r="AB226">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC226">
         <v>2.1</v>
@@ -37512,10 +37512,10 @@
         <v>3.05</v>
       </c>
       <c r="AA228">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB228">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC228">
         <v>3.5</v>
@@ -37645,10 +37645,10 @@
         <v>2.6</v>
       </c>
       <c r="Q229">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R229">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S229">
         <v>1.26</v>
@@ -37657,7 +37657,7 @@
         <v>3.24</v>
       </c>
       <c r="U229">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V229">
         <v>1.53</v>
@@ -37669,31 +37669,31 @@
         <v>1.02</v>
       </c>
       <c r="Y229">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z229">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA229">
         <v>1.65</v>
       </c>
       <c r="AB229">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC229">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AD229">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE229">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF229">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG229">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>1.21</v>
       </c>
       <c r="AK229">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37799,10 +37799,10 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O230">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P230">
         <v>2.2</v>
@@ -38128,31 +38128,31 @@
         <v>2.95</v>
       </c>
       <c r="O232">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P232">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q232">
-        <v>3.09</v>
+        <v>3.45</v>
       </c>
       <c r="R232">
         <v>2.5</v>
       </c>
       <c r="S232">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T232">
         <v>4</v>
       </c>
       <c r="U232">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="V232">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W232">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X232">
         <v>1.02</v>
@@ -38170,13 +38170,13 @@
         <v>2.7</v>
       </c>
       <c r="AC232">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD232">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE232">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF232">
         <v>1.36</v>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK232">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38816,10 +38816,10 @@
         <v>3.28</v>
       </c>
       <c r="AA236">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB236">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC236">
         <v>3.2</v>
@@ -39160,7 +39160,7 @@
         <v>1.4</v>
       </c>
       <c r="AG238">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39269,10 +39269,10 @@
         <v>2.14</v>
       </c>
       <c r="O239">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P239">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q239">
         <v>2.5</v>
@@ -40253,7 +40253,7 @@
         <v>4.25</v>
       </c>
       <c r="Q245">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="R245">
         <v>2.06</v>
@@ -40733,64 +40733,64 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O248">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P248">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S248">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T248">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U248">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V248">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W248">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X248">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y248">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z248">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA248">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB248">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC248">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD248">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG248">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK248">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -40896,64 +40896,64 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O249">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="P249">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S249">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T249">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U249">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V249">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W249">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X249">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y249">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z249">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA249">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB249">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC249">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD249">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE249">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF249">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG249">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK249">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -42076,7 +42076,7 @@
         <v>3.92</v>
       </c>
       <c r="AA256">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB256">
         <v>2.1</v>
@@ -42553,7 +42553,7 @@
         <v>1.5</v>
       </c>
       <c r="W259">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X259">
         <v>1.03</v>
@@ -43039,10 +43039,10 @@
         <v>2.61</v>
       </c>
       <c r="V262">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W262">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X262">
         <v>1.01</v>
@@ -43054,10 +43054,10 @@
         <v>3.28</v>
       </c>
       <c r="AA262">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB262">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC262">
         <v>3.14</v>
@@ -43208,7 +43208,7 @@
         <v>1.04</v>
       </c>
       <c r="X263">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y263">
         <v>1.25</v>
@@ -43347,7 +43347,7 @@
         <v>3.1</v>
       </c>
       <c r="P264">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q264">
         <v>2.88</v>
@@ -43383,7 +43383,7 @@
         <v>2.15</v>
       </c>
       <c r="AB264">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC264">
         <v>3.5</v>
@@ -43860,7 +43860,7 @@
         <v>1.12</v>
       </c>
       <c r="X267">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y267">
         <v>1.17</v>
@@ -44536,7 +44536,7 @@
         <v>1.25</v>
       </c>
       <c r="AF271">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG271">
         <v>2.73</v>
@@ -45028,7 +45028,7 @@
         <v>1.79</v>
       </c>
       <c r="AG274">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="O277">
         <v>3.18</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G279">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="G280">
@@ -46275,64 +46275,64 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q282">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R282">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S282">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T282">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U282">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V282">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X282">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y282">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z282">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC282">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD282">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE282">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF282">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG282">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK282">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46477,10 +46477,10 @@
         <v>0</v>
       </c>
       <c r="AA283">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB283">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC283">
         <v>0</v>
@@ -46610,13 +46610,13 @@
         <v>3.65</v>
       </c>
       <c r="Q284">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="R284">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="S284">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T284">
         <v>3.58</v>
@@ -46628,16 +46628,16 @@
         <v>1.61</v>
       </c>
       <c r="W284">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X284">
         <v>1.02</v>
       </c>
       <c r="Y284">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z284">
-        <v>5.21</v>
+        <v>5.3</v>
       </c>
       <c r="AA284">
         <v>1.49</v>
@@ -46646,13 +46646,13 @@
         <v>2.53</v>
       </c>
       <c r="AC284">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AD284">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE284">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF284">
         <v>1.45</v>
@@ -46674,7 +46674,7 @@
         <v>1.16</v>
       </c>
       <c r="AK284">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>4.33</v>
+        <v>3.02</v>
       </c>
       <c r="O286">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P286">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="Q286">
-        <v>4.5</v>
+        <v>3.13</v>
       </c>
       <c r="R286">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="S286">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T286">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U286">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="V286">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W286">
         <v>1.13</v>
       </c>
       <c r="X286">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y286">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z286">
-        <v>5.13</v>
+        <v>4.3</v>
       </c>
       <c r="AA286">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB286">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC286">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="AD286">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AE286">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF286">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG286">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK286">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,80 +47090,80 @@
         </is>
       </c>
       <c r="N287">
-        <v>3.02</v>
+        <v>4.33</v>
       </c>
       <c r="O287">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P287">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="Q287">
-        <v>3.22</v>
+        <v>4.5</v>
       </c>
       <c r="R287">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="S287">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T287">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U287">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="V287">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W287">
         <v>1.13</v>
       </c>
       <c r="X287">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y287">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z287">
-        <v>4.3</v>
+        <v>5.13</v>
       </c>
       <c r="AA287">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB287">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC287">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="AD287">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AE287">
+        <v>1.2</v>
+      </c>
+      <c r="AF287">
+        <v>1.55</v>
+      </c>
+      <c r="AG287">
+        <v>2.26</v>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ287">
+        <v>1.17</v>
+      </c>
+      <c r="AK287">
         <v>1.13</v>
-      </c>
-      <c r="AF287">
-        <v>1.51</v>
-      </c>
-      <c r="AG287">
-        <v>2.35</v>
-      </c>
-      <c r="AH287" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI287" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ287">
-        <v>1.22</v>
-      </c>
-      <c r="AK287">
-        <v>1.42</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47917,7 +47917,7 @@
         <v>1.75</v>
       </c>
       <c r="R292">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="S292">
         <v>1.2</v>
@@ -47932,13 +47932,13 @@
         <v>1.65</v>
       </c>
       <c r="W292">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X292">
         <v>1.02</v>
       </c>
       <c r="Y292">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z292">
         <v>5.3</v>
@@ -47947,22 +47947,22 @@
         <v>1.39</v>
       </c>
       <c r="AB292">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AC292">
         <v>2.06</v>
       </c>
       <c r="AD292">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE292">
         <v>1.25</v>
       </c>
       <c r="AF292">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG292">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK292">
         <v>3</v>
@@ -48231,7 +48231,7 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O294">
         <v>3.63</v>
@@ -48922,7 +48922,7 @@
         <v>2.75</v>
       </c>
       <c r="AA298">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AB298">
         <v>1.57</v>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O299">
         <v>3</v>
       </c>
       <c r="P299">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="Q299">
         <v>3.16</v>
@@ -49100,10 +49100,10 @@
         <v>1</v>
       </c>
       <c r="AF299">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG299">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="O302">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P302">
-        <v>4.27</v>
+        <v>4.35</v>
       </c>
       <c r="Q302">
         <v>2.41</v>
@@ -49740,7 +49740,7 @@
         <v>1.34</v>
       </c>
       <c r="AB303">
-        <v>3.06</v>
+        <v>2.87</v>
       </c>
       <c r="AC303">
         <v>1.88</v>
@@ -49870,16 +49870,16 @@
         <v>4.7</v>
       </c>
       <c r="Q304">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R304">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S304">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T304">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U304">
         <v>2.75</v>
@@ -49894,31 +49894,31 @@
         <v>1.01</v>
       </c>
       <c r="Y304">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z304">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA304">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AB304">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC304">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD304">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE304">
         <v>1.09</v>
       </c>
       <c r="AF304">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AG304">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK304">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O305">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="P305">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50063,10 +50063,10 @@
         <v>0</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC305">
         <v>0</v>
@@ -50715,7 +50715,7 @@
         <v>2.59</v>
       </c>
       <c r="AA309">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AB309">
         <v>1.53</v>
@@ -50730,10 +50730,10 @@
         <v>1.01</v>
       </c>
       <c r="AF309">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AG309">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>1.12</v>
       </c>
       <c r="X314">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y314">
         <v>1.2</v>
@@ -51533,7 +51533,7 @@
         <v>1.59</v>
       </c>
       <c r="AB314">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC314">
         <v>2.59</v>
@@ -51823,7 +51823,7 @@
         <v>3.35</v>
       </c>
       <c r="P316">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q316">
         <v>2.61</v>
@@ -52031,13 +52031,13 @@
         <v>1.84</v>
       </c>
       <c r="AE317">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF317">
         <v>2.2</v>
       </c>
       <c r="AG317">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52143,13 +52143,13 @@
         </is>
       </c>
       <c r="N318">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O318">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P318">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q318">
         <v>0</v>
@@ -52182,10 +52182,10 @@
         <v>0</v>
       </c>
       <c r="AA318">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB318">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC318">
         <v>0</v>
@@ -53163,7 +53163,7 @@
         <v>1.57</v>
       </c>
       <c r="AB324">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC324">
         <v>2.52</v>
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="N325">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O325">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P325">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q325">
         <v>2.07</v>
@@ -53335,7 +53335,7 @@
         <v>1.21</v>
       </c>
       <c r="AE325">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF325">
         <v>2.19</v>
@@ -53453,10 +53453,10 @@
         <v>3.53</v>
       </c>
       <c r="P326">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q326">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="R326">
         <v>2.2</v>
@@ -53773,13 +53773,13 @@
         </is>
       </c>
       <c r="N328">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O328">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P328">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="Q328">
         <v>2.25</v>
@@ -53818,7 +53818,7 @@
         <v>2.08</v>
       </c>
       <c r="AC328">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="AD328">
         <v>1.37</v>
@@ -53827,10 +53827,10 @@
         <v>1.11</v>
       </c>
       <c r="AF328">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG328">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>1.23</v>
       </c>
       <c r="AK328">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -54120,10 +54120,10 @@
         <v>3.75</v>
       </c>
       <c r="U330">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V330">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W330">
         <v>1.16</v>
@@ -54588,7 +54588,7 @@
         </is>
       </c>
       <c r="N333">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="O333">
         <v>4</v>
@@ -54787,7 +54787,7 @@
         <v>1.69</v>
       </c>
       <c r="Z334">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AA334">
         <v>3.1</v>
@@ -56097,7 +56097,7 @@
         <v>1.44</v>
       </c>
       <c r="AB342">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC342">
         <v>2.23</v>
@@ -56876,7 +56876,7 @@
         <v>3.15</v>
       </c>
       <c r="P347">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q347">
         <v>2.62</v>
@@ -56897,7 +56897,7 @@
         <v>1.3</v>
       </c>
       <c r="W347">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X347">
         <v>1.03</v>
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O348">
         <v>3.6</v>
       </c>
       <c r="P348">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q348">
         <v>2.2</v>
@@ -57706,7 +57706,7 @@
         <v>2.49</v>
       </c>
       <c r="U352">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="V352">
         <v>1.26</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,64 +58011,64 @@
         </is>
       </c>
       <c r="N354">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="O354">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P354">
+        <v>2.5</v>
+      </c>
+      <c r="Q354">
+        <v>2.86</v>
+      </c>
+      <c r="R354">
+        <v>2.04</v>
+      </c>
+      <c r="S354">
+        <v>1.36</v>
+      </c>
+      <c r="T354">
         <v>2.81</v>
       </c>
-      <c r="Q354">
-        <v>2.8</v>
-      </c>
-      <c r="R354">
-        <v>2.1</v>
-      </c>
-      <c r="S354">
-        <v>1.4</v>
-      </c>
-      <c r="T354">
-        <v>2.67</v>
-      </c>
       <c r="U354">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V354">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W354">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X354">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y354">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z354">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AA354">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB354">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC354">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="AD354">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE354">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF354">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG354">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AH354" t="inlineStr">
         <is>
@@ -58081,10 +58081,10 @@
         </is>
       </c>
       <c r="AJ354">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK354">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL354">
         <v>0</v>
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G355">
@@ -58174,80 +58174,80 @@
         </is>
       </c>
       <c r="N355">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O355">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P355">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q355">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="R355">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S355">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T355">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="U355">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V355">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W355">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X355">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y355">
+        <v>1.29</v>
+      </c>
+      <c r="Z355">
+        <v>3.04</v>
+      </c>
+      <c r="AA355">
+        <v>1.95</v>
+      </c>
+      <c r="AB355">
+        <v>1.75</v>
+      </c>
+      <c r="AC355">
+        <v>3.28</v>
+      </c>
+      <c r="AD355">
         <v>1.25</v>
       </c>
-      <c r="Z355">
-        <v>3.28</v>
-      </c>
-      <c r="AA355">
-        <v>1.98</v>
-      </c>
-      <c r="AB355">
-        <v>1.84</v>
-      </c>
-      <c r="AC355">
-        <v>3.27</v>
-      </c>
-      <c r="AD355">
+      <c r="AE355">
+        <v>1.11</v>
+      </c>
+      <c r="AF355">
+        <v>1.77</v>
+      </c>
+      <c r="AG355">
+        <v>1.92</v>
+      </c>
+      <c r="AH355" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI355" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ355">
         <v>1.28</v>
       </c>
-      <c r="AE355">
-        <v>1.07</v>
-      </c>
-      <c r="AF355">
-        <v>1.68</v>
-      </c>
-      <c r="AG355">
-        <v>2.03</v>
-      </c>
-      <c r="AH355" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI355" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ355">
-        <v>1.3</v>
-      </c>
       <c r="AK355">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL355">
         <v>0</v>
@@ -58337,13 +58337,13 @@
         </is>
       </c>
       <c r="N356">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="O356">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="P356">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="Q356">
         <v>2.05</v>
@@ -58358,10 +58358,10 @@
         <v>3.9</v>
       </c>
       <c r="U356">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V356">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W356">
         <v>1.17</v>
@@ -58373,22 +58373,22 @@
         <v>1.14</v>
       </c>
       <c r="Z356">
-        <v>5.67</v>
+        <v>5.81</v>
       </c>
       <c r="AA356">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB356">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC356">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AD356">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE356">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF356">
         <v>1.47</v>
@@ -58407,7 +58407,7 @@
         </is>
       </c>
       <c r="AJ356">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK356">
         <v>2.2</v>
@@ -58539,7 +58539,7 @@
         <v>3.34</v>
       </c>
       <c r="AA357">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB357">
         <v>1.95</v>
@@ -58826,7 +58826,7 @@
         </is>
       </c>
       <c r="N359">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="O359">
         <v>3.25</v>
@@ -59481,7 +59481,7 @@
         <v>1.53</v>
       </c>
       <c r="O363">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P363">
         <v>5.2</v>
@@ -60145,10 +60145,10 @@
         <v>2.5</v>
       </c>
       <c r="S367">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T367">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U367">
         <v>2.2</v>
@@ -60157,37 +60157,37 @@
         <v>1.62</v>
       </c>
       <c r="W367">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X367">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y367">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z367">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA367">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AB367">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AC367">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="AD367">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AE367">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF367">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AG367">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AH367" t="inlineStr">
         <is>
@@ -60203,7 +60203,7 @@
         <v>1.16</v>
       </c>
       <c r="AK367">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AL367">
         <v>0</v>
@@ -60480,13 +60480,13 @@
         <v>2.37</v>
       </c>
       <c r="V369">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W369">
         <v>1.11</v>
       </c>
       <c r="X369">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y369">
         <v>1.23</v>
@@ -60661,7 +60661,7 @@
         <v>1.91</v>
       </c>
       <c r="AB370">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC370">
         <v>3.2</v>
@@ -60948,10 +60948,10 @@
         <v>3.25</v>
       </c>
       <c r="O372">
-        <v>4.28</v>
+        <v>4.34</v>
       </c>
       <c r="P372">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="Q372">
         <v>3.3</v>
@@ -60993,10 +60993,10 @@
         <v>1.68</v>
       </c>
       <c r="AD372">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AE372">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF372">
         <v>1.25</v>
@@ -61015,7 +61015,7 @@
         </is>
       </c>
       <c r="AJ372">
-        <v>1.83</v>
+        <v>1.22</v>
       </c>
       <c r="AK372">
         <v>1.3</v>
@@ -61108,10 +61108,10 @@
         </is>
       </c>
       <c r="N373">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="O373">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P373">
         <v>5.25</v>
@@ -61129,10 +61129,10 @@
         <v>3.5</v>
       </c>
       <c r="U373">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V373">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W373">
         <v>1.12</v>
@@ -61153,7 +61153,7 @@
         <v>2.27</v>
       </c>
       <c r="AC373">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="AD373">
         <v>1.45</v>
@@ -61162,10 +61162,10 @@
         <v>1.14</v>
       </c>
       <c r="AF373">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG373">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH373" t="inlineStr">
         <is>
@@ -61434,19 +61434,19 @@
         </is>
       </c>
       <c r="N375">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="O375">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P375">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="Q375">
         <v>2</v>
       </c>
       <c r="R375">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="S375">
         <v>1.25</v>
@@ -61470,25 +61470,25 @@
         <v>1.17</v>
       </c>
       <c r="Z375">
-        <v>4.11</v>
+        <v>3.99</v>
       </c>
       <c r="AA375">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB375">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC375">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD375">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE375">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF375">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG375">
         <v>2.05</v>
@@ -62258,10 +62258,10 @@
         <v>3.9</v>
       </c>
       <c r="Q380">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="R380">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S380">
         <v>1.36</v>
@@ -62279,28 +62279,28 @@
         <v>1.08</v>
       </c>
       <c r="X380">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y380">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z380">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA380">
         <v>2</v>
       </c>
       <c r="AB380">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC380">
-        <v>3.2</v>
+        <v>3.53</v>
       </c>
       <c r="AD380">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE380">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF380">
         <v>1.8</v>
@@ -62319,7 +62319,7 @@
         </is>
       </c>
       <c r="AJ380">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK380">
         <v>1.91</v>
@@ -63227,13 +63227,13 @@
         </is>
       </c>
       <c r="N386">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O386">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P386">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q386">
         <v>0</v>
@@ -63743,7 +63743,7 @@
         <v>1.73</v>
       </c>
       <c r="W389">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X389">
         <v>0</v>
@@ -63879,13 +63879,13 @@
         </is>
       </c>
       <c r="N390">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O390">
         <v>3.7</v>
       </c>
       <c r="P390">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q390">
         <v>2.44</v>
@@ -63936,7 +63936,7 @@
         <v>1.61</v>
       </c>
       <c r="AG390">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH390" t="inlineStr">
         <is>
@@ -64084,7 +64084,7 @@
         <v>2.97</v>
       </c>
       <c r="AB391">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AC391">
         <v>5.85</v>
@@ -64226,10 +64226,10 @@
         <v>3.2</v>
       </c>
       <c r="U392">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="V392">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W392">
         <v>1.1</v>
@@ -64244,7 +64244,7 @@
         <v>3.72</v>
       </c>
       <c r="AA392">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB392">
         <v>1.95</v>
@@ -64383,10 +64383,10 @@
         <v>2.45</v>
       </c>
       <c r="S393">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T393">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U393">
         <v>2.2</v>
@@ -64395,7 +64395,7 @@
         <v>1.6</v>
       </c>
       <c r="W393">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X393">
         <v>1.01</v>
@@ -65253,7 +65253,7 @@
         </is>
       </c>
       <c r="AJ398">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK398">
         <v>2.38</v>
@@ -65672,19 +65672,19 @@
         </is>
       </c>
       <c r="N401">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O401">
         <v>3.78</v>
       </c>
       <c r="P401">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="Q401">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R401">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="S401">
         <v>1.3</v>
@@ -65696,7 +65696,7 @@
         <v>2.4</v>
       </c>
       <c r="V401">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W401">
         <v>1.09</v>
@@ -65705,16 +65705,16 @@
         <v>1.01</v>
       </c>
       <c r="Y401">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z401">
         <v>3.98</v>
       </c>
       <c r="AA401">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB401">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AC401">
         <v>2.6</v>
@@ -65742,10 +65742,10 @@
         </is>
       </c>
       <c r="AJ401">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK401">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AL401">
         <v>0</v>
@@ -66068,7 +66068,7 @@
         </is>
       </c>
       <c r="AJ403">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK403">
         <v>1.55</v>
@@ -66185,7 +66185,7 @@
         <v>2.75</v>
       </c>
       <c r="V404">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W404">
         <v>1.08</v>
@@ -66381,7 +66381,7 @@
         <v>1.3</v>
       </c>
       <c r="AG405">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AH405" t="inlineStr">
         <is>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -828,16 +828,16 @@
         <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z3">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AA3">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB3">
         <v>1.63</v>
@@ -846,16 +846,16 @@
         <v>4.1</v>
       </c>
       <c r="AD3">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>2.57</v>
       </c>
       <c r="R4">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
         <v>1.3</v>
@@ -1003,22 +1003,22 @@
         <v>1.74</v>
       </c>
       <c r="AB4">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AC4">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE4">
         <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG4">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,10 +1133,10 @@
         <v>4</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="R5">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="S5">
         <v>1.4</v>
@@ -1154,13 +1154,13 @@
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
         <v>2.06</v>
@@ -1169,13 +1169,13 @@
         <v>1.76</v>
       </c>
       <c r="AC5">
-        <v>3.48</v>
+        <v>3.61</v>
       </c>
       <c r="AD5">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
         <v>1.87</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.09</v>
+        <v>3.75</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>2.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>3.09</v>
+        <v>2.74</v>
       </c>
       <c r="U6">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
         <v>1.07</v>
@@ -1320,31 +1320,31 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z6">
-        <v>3.73</v>
+        <v>3.42</v>
       </c>
       <c r="AA6">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB6">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC6">
         <v>2.92</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
         <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AK6">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
         <v>2.77</v>
       </c>
       <c r="U7">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA7">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB7">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC7">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
+        <v>1.25</v>
+      </c>
+      <c r="AK7">
         <v>1.21</v>
-      </c>
-      <c r="AK7">
-        <v>1.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,61 +1613,61 @@
         </is>
       </c>
       <c r="N8">
+        <v>2.09</v>
+      </c>
+      <c r="O8">
         <v>3.4</v>
       </c>
-      <c r="O8">
-        <v>3.25</v>
-      </c>
       <c r="P8">
-        <v>2</v>
+        <v>2.82</v>
       </c>
       <c r="Q8">
-        <v>3.44</v>
+        <v>2.62</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U8">
         <v>2.6</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="AA8">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB8">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC8">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AD8">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
         <v>2.1</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O9">
         <v>3</v>
@@ -1785,10 +1785,10 @@
         <v>2.7</v>
       </c>
       <c r="Q9">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S9">
         <v>1.43</v>
@@ -1797,16 +1797,16 @@
         <v>2.48</v>
       </c>
       <c r="U9">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
         <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
         <v>1.33</v>
@@ -1821,7 +1821,7 @@
         <v>1.64</v>
       </c>
       <c r="AC9">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="AD9">
         <v>1.2</v>
@@ -1830,7 +1830,7 @@
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
         <v>1.87</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q10">
         <v>2.72</v>
@@ -1954,28 +1954,28 @@
         <v>2.28</v>
       </c>
       <c r="S10">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U10">
         <v>2.27</v>
       </c>
       <c r="V10">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>1.12</v>
       </c>
       <c r="Z10">
-        <v>4.75</v>
+        <v>4.83</v>
       </c>
       <c r="AA10">
         <v>1.53</v>
@@ -1990,13 +1990,13 @@
         <v>1.48</v>
       </c>
       <c r="AE10">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF10">
         <v>1.45</v>
       </c>
       <c r="AG10">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
         <v>1.14</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O13">
-        <v>4.84</v>
+        <v>4.6</v>
       </c>
       <c r="P13">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="Q13">
         <v>1.85</v>
       </c>
       <c r="R13">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="S13">
         <v>1.25</v>
@@ -2458,7 +2458,7 @@
         <v>1.11</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.14</v>
@@ -2485,7 +2485,7 @@
         <v>1.76</v>
       </c>
       <c r="AG13">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="O15">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P15">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>4.53</v>
+        <v>3.09</v>
       </c>
       <c r="R15">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="S15">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="T15">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="U15">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="V15">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>2.41</v>
+        <v>2.81</v>
       </c>
       <c r="AA15">
-        <v>2.84</v>
+        <v>2.14</v>
       </c>
       <c r="AB15">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AC15">
-        <v>5.76</v>
+        <v>3.72</v>
       </c>
       <c r="AD15">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE15">
         <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>2.22</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AK15">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="O16">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="Q16">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="R16">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="S16">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>2.68</v>
+        <v>3.22</v>
       </c>
       <c r="U16">
-        <v>3.29</v>
+        <v>2.45</v>
       </c>
       <c r="V16">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
-        <v>2.99</v>
+        <v>3.82</v>
       </c>
       <c r="AA16">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AB16">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="AC16">
-        <v>4.11</v>
+        <v>2.81</v>
       </c>
       <c r="AD16">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK16">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
+        <v>3.1</v>
+      </c>
+      <c r="O17">
+        <v>2.9</v>
+      </c>
+      <c r="P17">
+        <v>2.2</v>
+      </c>
+      <c r="Q17">
+        <v>4.35</v>
+      </c>
+      <c r="R17">
+        <v>1.84</v>
+      </c>
+      <c r="S17">
+        <v>1.58</v>
+      </c>
+      <c r="T17">
         <v>2.25</v>
       </c>
-      <c r="O17">
-        <v>3.64</v>
-      </c>
-      <c r="P17">
-        <v>2.97</v>
-      </c>
-      <c r="Q17">
-        <v>2.78</v>
-      </c>
-      <c r="R17">
-        <v>2.18</v>
-      </c>
-      <c r="S17">
-        <v>1.28</v>
-      </c>
-      <c r="T17">
-        <v>3.22</v>
-      </c>
       <c r="U17">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
+        <v>1.04</v>
+      </c>
+      <c r="X17">
         <v>1.08</v>
       </c>
-      <c r="X17">
+      <c r="Y17">
+        <v>1.56</v>
+      </c>
+      <c r="Z17">
+        <v>2.38</v>
+      </c>
+      <c r="AA17">
+        <v>2.62</v>
+      </c>
+      <c r="AB17">
+        <v>1.38</v>
+      </c>
+      <c r="AC17">
+        <v>5.65</v>
+      </c>
+      <c r="AD17">
+        <v>1.08</v>
+      </c>
+      <c r="AE17">
         <v>1.04</v>
       </c>
-      <c r="Y17">
-        <v>1.19</v>
-      </c>
-      <c r="Z17">
-        <v>3.82</v>
-      </c>
-      <c r="AA17">
-        <v>1.79</v>
-      </c>
-      <c r="AB17">
-        <v>2.05</v>
-      </c>
-      <c r="AC17">
-        <v>2.81</v>
-      </c>
-      <c r="AD17">
-        <v>1.33</v>
-      </c>
-      <c r="AE17">
-        <v>1.09</v>
-      </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AG17">
-        <v>2.19</v>
+        <v>1.59</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AK17">
-        <v>1.64</v>
+        <v>1.3</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,10 +3246,10 @@
         <v>1.94</v>
       </c>
       <c r="O18">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q18">
         <v>2.39</v>
@@ -3273,25 +3273,25 @@
         <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>4.61</v>
+        <v>4.2</v>
       </c>
       <c r="AA18">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB18">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AC18">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AD18">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
         <v>1.15</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
         <v>1.85</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="Q20">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="U20">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="V20">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>4.75</v>
+        <v>3.74</v>
       </c>
       <c r="AA20">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AB20">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AC20">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="AD20">
-        <v>1.59</v>
+        <v>1.41</v>
       </c>
       <c r="AE20">
+        <v>1.15</v>
+      </c>
+      <c r="AF20">
+        <v>1.6</v>
+      </c>
+      <c r="AG20">
+        <v>2.21</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.18</v>
       </c>
-      <c r="AF20">
-        <v>1.44</v>
-      </c>
-      <c r="AG20">
-        <v>2.6</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.16</v>
-      </c>
       <c r="AK20">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q21">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="R21">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="S21">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T21">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U21">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="V21">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z21">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AA21">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AB21">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AC21">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AD21">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AE21">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF21">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AG21">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="P22">
-        <v>2.23</v>
+        <v>2.79</v>
       </c>
       <c r="Q22">
-        <v>3.23</v>
+        <v>3.54</v>
       </c>
       <c r="R22">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="S22">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.02</v>
+        <v>3.56</v>
       </c>
       <c r="U22">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="V22">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>3.74</v>
+        <v>4.95</v>
       </c>
       <c r="AA22">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AC22">
-        <v>2.77</v>
+        <v>2.17</v>
       </c>
       <c r="AD22">
+        <v>1.65</v>
+      </c>
+      <c r="AE22">
+        <v>1.23</v>
+      </c>
+      <c r="AF22">
+        <v>1.42</v>
+      </c>
+      <c r="AG22">
+        <v>2.66</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.25</v>
+      </c>
+      <c r="AK22">
         <v>1.36</v>
-      </c>
-      <c r="AE22">
-        <v>1.15</v>
-      </c>
-      <c r="AF22">
-        <v>1.6</v>
-      </c>
-      <c r="AG22">
-        <v>2.21</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.18</v>
-      </c>
-      <c r="AK22">
-        <v>1.25</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>7.05</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="R23">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T23">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="U23">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="V23">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="Z23">
-        <v>4.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA23">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AB23">
+        <v>4.2</v>
+      </c>
+      <c r="AC23">
+        <v>1.58</v>
+      </c>
+      <c r="AD23">
         <v>2.33</v>
       </c>
-      <c r="AC23">
-        <v>2.35</v>
-      </c>
-      <c r="AD23">
-        <v>1.46</v>
-      </c>
       <c r="AE23">
-        <v>1.15</v>
+        <v>1.56</v>
       </c>
       <c r="AF23">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AG23">
-        <v>1.64</v>
+        <v>3.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>4.16</v>
+        <v>1.77</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.15</v>
+        <v>1.46</v>
       </c>
       <c r="O24">
-        <v>3.65</v>
+        <v>4.51</v>
       </c>
       <c r="P24">
-        <v>1.91</v>
+        <v>7.05</v>
       </c>
       <c r="Q24">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="R24">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="S24">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U24">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="V24">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="W24">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
+        <v>1.18</v>
+      </c>
+      <c r="Z24">
+        <v>4.8</v>
+      </c>
+      <c r="AA24">
+        <v>1.57</v>
+      </c>
+      <c r="AB24">
+        <v>2.38</v>
+      </c>
+      <c r="AC24">
+        <v>2.34</v>
+      </c>
+      <c r="AD24">
+        <v>1.46</v>
+      </c>
+      <c r="AE24">
+        <v>1.15</v>
+      </c>
+      <c r="AF24">
+        <v>2.11</v>
+      </c>
+      <c r="AG24">
+        <v>1.65</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.1</v>
       </c>
-      <c r="Z24">
-        <v>6.26</v>
-      </c>
-      <c r="AA24">
-        <v>1.36</v>
-      </c>
-      <c r="AB24">
-        <v>3.25</v>
-      </c>
-      <c r="AC24">
-        <v>1.88</v>
-      </c>
-      <c r="AD24">
-        <v>1.85</v>
-      </c>
-      <c r="AE24">
-        <v>1.33</v>
-      </c>
-      <c r="AF24">
-        <v>1.34</v>
-      </c>
-      <c r="AG24">
-        <v>2.99</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.24</v>
-      </c>
       <c r="AK24">
-        <v>1.32</v>
+        <v>3.86</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T25">
-        <v>3.56</v>
+        <v>4.5</v>
       </c>
       <c r="U25">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="AA25">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB25">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AC25">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AD25">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF25">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG25">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q26">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T26">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="U26">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W26">
         <v>1.13</v>
@@ -4580,31 +4580,31 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z26">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA26">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AB26">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AC26">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AD26">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AE26">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF26">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK26">
-        <v>1.79</v>
+        <v>1.37</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G27">
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="R27">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="V27">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="W27">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>8.300000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AA27">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>3.74</v>
+        <v>2.33</v>
       </c>
       <c r="AC27">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD27">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AE27">
-        <v>1.51</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,10 +4882,10 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="R28">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
         <v>1.4</v>
@@ -4909,10 +4909,10 @@
         <v>1.26</v>
       </c>
       <c r="Z28">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA28">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AB28">
         <v>1.75</v>
@@ -4924,7 +4924,7 @@
         <v>1.29</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
         <v>1.84</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="O36">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P36">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q36">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R36">
         <v>2.46</v>
@@ -6216,10 +6216,10 @@
         <v>4.95</v>
       </c>
       <c r="AA36">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB36">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AC36">
         <v>2.2</v>
@@ -6231,10 +6231,10 @@
         <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG36">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O56">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P56">
-        <v>3.7</v>
+        <v>4.08</v>
       </c>
       <c r="Q56">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R56">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="S56">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T56">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="U56">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="V56">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="W56">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Z56">
-        <v>7.7</v>
+        <v>5.83</v>
       </c>
       <c r="AA56">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AB56">
-        <v>3.8</v>
+        <v>2.72</v>
       </c>
       <c r="AC56">
+        <v>2.04</v>
+      </c>
+      <c r="AD56">
         <v>1.7</v>
       </c>
-      <c r="AD56">
-        <v>2.13</v>
-      </c>
       <c r="AE56">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AF56">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AG56">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK56">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="O57">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P57">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="Q57">
+        <v>2</v>
+      </c>
+      <c r="R57">
+        <v>2.64</v>
+      </c>
+      <c r="S57">
+        <v>1.11</v>
+      </c>
+      <c r="T57">
+        <v>5.5</v>
+      </c>
+      <c r="U57">
+        <v>1.8</v>
+      </c>
+      <c r="V57">
+        <v>1.92</v>
+      </c>
+      <c r="W57">
+        <v>1.25</v>
+      </c>
+      <c r="X57">
+        <v>1.01</v>
+      </c>
+      <c r="Y57">
+        <v>1.03</v>
+      </c>
+      <c r="Z57">
+        <v>7.7</v>
+      </c>
+      <c r="AA57">
+        <v>1.25</v>
+      </c>
+      <c r="AB57">
+        <v>3.8</v>
+      </c>
+      <c r="AC57">
+        <v>1.7</v>
+      </c>
+      <c r="AD57">
         <v>2.13</v>
       </c>
-      <c r="R57">
-        <v>2.35</v>
-      </c>
-      <c r="S57">
-        <v>1.22</v>
-      </c>
-      <c r="T57">
-        <v>3.55</v>
-      </c>
-      <c r="U57">
-        <v>2.2</v>
-      </c>
-      <c r="V57">
-        <v>1.6</v>
-      </c>
-      <c r="W57">
-        <v>1.12</v>
-      </c>
-      <c r="X57">
-        <v>1.02</v>
-      </c>
-      <c r="Y57">
-        <v>1.1</v>
-      </c>
-      <c r="Z57">
-        <v>5.2</v>
-      </c>
-      <c r="AA57">
-        <v>1.56</v>
-      </c>
-      <c r="AB57">
-        <v>2.43</v>
-      </c>
-      <c r="AC57">
-        <v>2.36</v>
-      </c>
-      <c r="AD57">
-        <v>1.61</v>
-      </c>
       <c r="AE57">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="AF57">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG57">
-        <v>2.49</v>
+        <v>3.14</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="O58">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P58">
-        <v>4.08</v>
+        <v>3.45</v>
       </c>
       <c r="Q58">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="R58">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="S58">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T58">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U58">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V58">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="W58">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z58">
-        <v>5.83</v>
+        <v>5.2</v>
       </c>
       <c r="AA58">
+        <v>1.56</v>
+      </c>
+      <c r="AB58">
+        <v>2.43</v>
+      </c>
+      <c r="AC58">
+        <v>2.36</v>
+      </c>
+      <c r="AD58">
+        <v>1.61</v>
+      </c>
+      <c r="AE58">
+        <v>1.21</v>
+      </c>
+      <c r="AF58">
         <v>1.44</v>
       </c>
-      <c r="AB58">
-        <v>2.72</v>
-      </c>
-      <c r="AC58">
-        <v>2.04</v>
-      </c>
-      <c r="AD58">
-        <v>1.7</v>
-      </c>
-      <c r="AE58">
-        <v>1.3</v>
-      </c>
-      <c r="AF58">
-        <v>1.43</v>
-      </c>
       <c r="AG58">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O90">
         <v>3.5</v>
       </c>
       <c r="P90">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q90">
-        <v>2.41</v>
+        <v>2.26</v>
       </c>
       <c r="R90">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S90">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U90">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V90">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W90">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z90">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="AA90">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB90">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC90">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AD90">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE90">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF90">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG90">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK90">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O91">
         <v>3.5</v>
       </c>
       <c r="P91">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q91">
-        <v>2.26</v>
+        <v>2.41</v>
       </c>
       <c r="R91">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U91">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V91">
+        <v>1.44</v>
+      </c>
+      <c r="W91">
+        <v>1.13</v>
+      </c>
+      <c r="X91">
+        <v>1.01</v>
+      </c>
+      <c r="Y91">
+        <v>1.14</v>
+      </c>
+      <c r="Z91">
+        <v>4.4</v>
+      </c>
+      <c r="AA91">
         <v>1.57</v>
       </c>
-      <c r="W91">
-        <v>1.14</v>
-      </c>
-      <c r="X91">
-        <v>1.02</v>
-      </c>
-      <c r="Y91">
-        <v>1.1</v>
-      </c>
-      <c r="Z91">
-        <v>4.95</v>
-      </c>
-      <c r="AA91">
-        <v>1.47</v>
-      </c>
       <c r="AB91">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC91">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AD91">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE91">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AF91">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG91">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16781,22 +16781,22 @@
         <v>1.62</v>
       </c>
       <c r="Q101">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R101">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S101">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T101">
         <v>4.55</v>
       </c>
       <c r="U101">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V101">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W101">
         <v>1.25</v>
@@ -16805,10 +16805,10 @@
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z101">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AA101">
         <v>1.29</v>
@@ -16817,19 +16817,19 @@
         <v>3.5</v>
       </c>
       <c r="AC101">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD101">
         <v>2.01</v>
       </c>
       <c r="AE101">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF101">
         <v>1.33</v>
       </c>
       <c r="AG101">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK101">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="O151">
+        <v>4.2</v>
+      </c>
+      <c r="P151">
+        <v>4.15</v>
+      </c>
+      <c r="Q151">
+        <v>2.24</v>
+      </c>
+      <c r="R151">
+        <v>2.44</v>
+      </c>
+      <c r="S151">
+        <v>1.22</v>
+      </c>
+      <c r="T151">
+        <v>3.75</v>
+      </c>
+      <c r="U151">
+        <v>2.3</v>
+      </c>
+      <c r="V151">
+        <v>1.66</v>
+      </c>
+      <c r="W151">
+        <v>1.17</v>
+      </c>
+      <c r="X151">
+        <v>1.03</v>
+      </c>
+      <c r="Y151">
+        <v>1.14</v>
+      </c>
+      <c r="Z151">
         <v>5.5</v>
       </c>
-      <c r="P151">
-        <v>5.4</v>
-      </c>
-      <c r="Q151">
-        <v>1.79</v>
-      </c>
-      <c r="R151">
-        <v>2.92</v>
-      </c>
-      <c r="S151">
-        <v>1.11</v>
-      </c>
-      <c r="T151">
-        <v>5.3</v>
-      </c>
-      <c r="U151">
-        <v>1.86</v>
-      </c>
-      <c r="V151">
-        <v>2</v>
-      </c>
-      <c r="W151">
-        <v>1.31</v>
-      </c>
-      <c r="X151">
-        <v>1.01</v>
-      </c>
-      <c r="Y151">
-        <v>1.03</v>
-      </c>
-      <c r="Z151">
-        <v>7.3</v>
-      </c>
       <c r="AA151">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AB151">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC151">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="AD151">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="AE151">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="AF151">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG151">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK151">
-        <v>3.02</v>
+        <v>2.13</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="O152">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="P152">
-        <v>4.15</v>
+        <v>5.4</v>
       </c>
       <c r="Q152">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="R152">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="S152">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="T152">
+        <v>5.3</v>
+      </c>
+      <c r="U152">
+        <v>1.86</v>
+      </c>
+      <c r="V152">
+        <v>2</v>
+      </c>
+      <c r="W152">
+        <v>1.31</v>
+      </c>
+      <c r="X152">
+        <v>1.01</v>
+      </c>
+      <c r="Y152">
+        <v>1.03</v>
+      </c>
+      <c r="Z152">
+        <v>7.3</v>
+      </c>
+      <c r="AA152">
+        <v>1.28</v>
+      </c>
+      <c r="AB152">
         <v>3.75</v>
       </c>
-      <c r="U152">
-        <v>2.3</v>
-      </c>
-      <c r="V152">
-        <v>1.66</v>
-      </c>
-      <c r="W152">
-        <v>1.17</v>
-      </c>
-      <c r="X152">
-        <v>1.03</v>
-      </c>
-      <c r="Y152">
-        <v>1.14</v>
-      </c>
-      <c r="Z152">
-        <v>5.5</v>
-      </c>
-      <c r="AA152">
-        <v>1.5</v>
-      </c>
-      <c r="AB152">
-        <v>2.55</v>
-      </c>
       <c r="AC152">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="AD152">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="AE152">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="AF152">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG152">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK152">
-        <v>2.13</v>
+        <v>3.02</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.34</v>
+        <v>5.64</v>
       </c>
       <c r="O167">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P167">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="Q167">
-        <v>2.88</v>
+        <v>5.55</v>
       </c>
       <c r="R167">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S167">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T167">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U167">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="V167">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W167">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X167">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y167">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z167">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AA167">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AB167">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AC167">
-        <v>3.78</v>
+        <v>2.92</v>
       </c>
       <c r="AD167">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE167">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF167">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG167">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK167">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,80 +27693,80 @@
         </is>
       </c>
       <c r="N168">
-        <v>5.64</v>
+        <v>2.34</v>
       </c>
       <c r="O168">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P168">
+        <v>2.7</v>
+      </c>
+      <c r="Q168">
+        <v>2.88</v>
+      </c>
+      <c r="R168">
+        <v>2.1</v>
+      </c>
+      <c r="S168">
+        <v>1.37</v>
+      </c>
+      <c r="T168">
+        <v>2.69</v>
+      </c>
+      <c r="U168">
+        <v>2.86</v>
+      </c>
+      <c r="V168">
+        <v>1.33</v>
+      </c>
+      <c r="W168">
+        <v>1.04</v>
+      </c>
+      <c r="X168">
+        <v>1.01</v>
+      </c>
+      <c r="Y168">
+        <v>1.33</v>
+      </c>
+      <c r="Z168">
+        <v>3</v>
+      </c>
+      <c r="AA168">
+        <v>2.13</v>
+      </c>
+      <c r="AB168">
+        <v>1.69</v>
+      </c>
+      <c r="AC168">
+        <v>3.78</v>
+      </c>
+      <c r="AD168">
+        <v>1.22</v>
+      </c>
+      <c r="AE168">
+        <v>1.02</v>
+      </c>
+      <c r="AF168">
+        <v>1.8</v>
+      </c>
+      <c r="AG168">
+        <v>1.9</v>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ168">
+        <v>1.3</v>
+      </c>
+      <c r="AK168">
         <v>1.57</v>
-      </c>
-      <c r="Q168">
-        <v>5.55</v>
-      </c>
-      <c r="R168">
-        <v>2.3</v>
-      </c>
-      <c r="S168">
-        <v>1.3</v>
-      </c>
-      <c r="T168">
-        <v>3.2</v>
-      </c>
-      <c r="U168">
-        <v>2.75</v>
-      </c>
-      <c r="V168">
-        <v>1.4</v>
-      </c>
-      <c r="W168">
-        <v>1.07</v>
-      </c>
-      <c r="X168">
-        <v>1.02</v>
-      </c>
-      <c r="Y168">
-        <v>1.25</v>
-      </c>
-      <c r="Z168">
-        <v>3.6</v>
-      </c>
-      <c r="AA168">
-        <v>1.8</v>
-      </c>
-      <c r="AB168">
-        <v>1.87</v>
-      </c>
-      <c r="AC168">
-        <v>2.92</v>
-      </c>
-      <c r="AD168">
-        <v>1.32</v>
-      </c>
-      <c r="AE168">
-        <v>1.11</v>
-      </c>
-      <c r="AF168">
-        <v>1.85</v>
-      </c>
-      <c r="AG168">
-        <v>1.85</v>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ168">
-        <v>1.17</v>
-      </c>
-      <c r="AK168">
-        <v>1.14</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="O174">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P174">
-        <v>4.8</v>
+        <v>2.47</v>
       </c>
       <c r="Q174">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="R174">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S174">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T174">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U174">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="V174">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W174">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X174">
         <v>1.02</v>
       </c>
       <c r="Y174">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z174">
-        <v>4.53</v>
+        <v>3.78</v>
       </c>
       <c r="AA174">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AB174">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="AC174">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="AD174">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE174">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF174">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG174">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK174">
-        <v>2.19</v>
+        <v>1.45</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="O175">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P175">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="Q175">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R175">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S175">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T175">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U175">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="V175">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W175">
+        <v>1.07</v>
+      </c>
+      <c r="X175">
+        <v>1.01</v>
+      </c>
+      <c r="Y175">
+        <v>1.24</v>
+      </c>
+      <c r="Z175">
+        <v>3.91</v>
+      </c>
+      <c r="AA175">
+        <v>1.78</v>
+      </c>
+      <c r="AB175">
+        <v>2.01</v>
+      </c>
+      <c r="AC175">
+        <v>2.93</v>
+      </c>
+      <c r="AD175">
+        <v>1.32</v>
+      </c>
+      <c r="AE175">
         <v>1.08</v>
       </c>
-      <c r="X175">
-        <v>1.02</v>
-      </c>
-      <c r="Y175">
-        <v>1.23</v>
-      </c>
-      <c r="Z175">
-        <v>3.78</v>
-      </c>
-      <c r="AA175">
-        <v>1.76</v>
-      </c>
-      <c r="AB175">
-        <v>2.04</v>
-      </c>
-      <c r="AC175">
-        <v>2.98</v>
-      </c>
-      <c r="AD175">
-        <v>1.35</v>
-      </c>
-      <c r="AE175">
-        <v>1.1</v>
-      </c>
       <c r="AF175">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG175">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.37</v>
+        <v>1.62</v>
       </c>
       <c r="O176">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P176">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q176">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="R176">
-        <v>2.03</v>
+        <v>2.47</v>
       </c>
       <c r="S176">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T176">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="U176">
-        <v>3.07</v>
+        <v>2.47</v>
       </c>
       <c r="V176">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="W176">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X176">
         <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="Z176">
-        <v>3.15</v>
+        <v>4.53</v>
       </c>
       <c r="AA176">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="AB176">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="AC176">
-        <v>3.68</v>
+        <v>2.64</v>
       </c>
       <c r="AD176">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AE176">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF176">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AG176">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK176">
-        <v>1.53</v>
+        <v>2.19</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O177">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P177">
         <v>2.75</v>
       </c>
       <c r="Q177">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R177">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S177">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T177">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="U177">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="V177">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W177">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y177">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z177">
-        <v>3.43</v>
+        <v>3.15</v>
       </c>
       <c r="AA177">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AB177">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AC177">
-        <v>3.39</v>
+        <v>3.68</v>
       </c>
       <c r="AD177">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE177">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF177">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG177">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK177">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="O178">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P178">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="Q178">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="R178">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S178">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T178">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="U178">
-        <v>2.57</v>
+        <v>2.97</v>
       </c>
       <c r="V178">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W178">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X178">
         <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z178">
-        <v>3.91</v>
+        <v>3.43</v>
       </c>
       <c r="AA178">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AB178">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AC178">
-        <v>2.93</v>
+        <v>3.39</v>
       </c>
       <c r="AD178">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE178">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF178">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG178">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK178">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="O192">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="P192">
-        <v>7.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q192">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="R192">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="S192">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T192">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="U192">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V192">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W192">
         <v>1.14</v>
       </c>
       <c r="X192">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y192">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z192">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA192">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AB192">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="AC192">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AD192">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AE192">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AF192">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AG192">
-        <v>1.85</v>
+        <v>2.53</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK192">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="O193">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="P193">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="Q193">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="R193">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="S193">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T193">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U193">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="V193">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W193">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X193">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z193">
-        <v>3.48</v>
+        <v>3.12</v>
       </c>
       <c r="AA193">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AB193">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AC193">
-        <v>3.05</v>
+        <v>3.89</v>
       </c>
       <c r="AD193">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AE193">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF193">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG193">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AK193">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,80 +31931,80 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.88</v>
+        <v>1.32</v>
       </c>
       <c r="O194">
-        <v>3.43</v>
+        <v>5.25</v>
       </c>
       <c r="P194">
-        <v>2.21</v>
+        <v>7.75</v>
       </c>
       <c r="Q194">
-        <v>3.4</v>
+        <v>1.73</v>
       </c>
       <c r="R194">
-        <v>2.08</v>
+        <v>2.51</v>
       </c>
       <c r="S194">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T194">
-        <v>3.09</v>
+        <v>3.6</v>
       </c>
       <c r="U194">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="V194">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W194">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X194">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y194">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="Z194">
-        <v>3.42</v>
+        <v>4.75</v>
       </c>
       <c r="AA194">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AB194">
-        <v>1.94</v>
+        <v>2.36</v>
       </c>
       <c r="AC194">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="AD194">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AE194">
+        <v>1.15</v>
+      </c>
+      <c r="AF194">
+        <v>1.85</v>
+      </c>
+      <c r="AG194">
+        <v>1.85</v>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ194">
         <v>1.13</v>
       </c>
-      <c r="AF194">
-        <v>1.66</v>
-      </c>
-      <c r="AG194">
-        <v>2.1</v>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ194">
-        <v>1.25</v>
-      </c>
       <c r="AK194">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
+        <v>3.7</v>
+      </c>
+      <c r="O196">
+        <v>3.5</v>
+      </c>
+      <c r="P196">
+        <v>1.92</v>
+      </c>
+      <c r="Q196">
+        <v>4</v>
+      </c>
+      <c r="R196">
+        <v>2.13</v>
+      </c>
+      <c r="S196">
+        <v>1.35</v>
+      </c>
+      <c r="T196">
+        <v>3.1</v>
+      </c>
+      <c r="U196">
+        <v>2.75</v>
+      </c>
+      <c r="V196">
+        <v>1.43</v>
+      </c>
+      <c r="W196">
+        <v>1.07</v>
+      </c>
+      <c r="X196">
+        <v>1</v>
+      </c>
+      <c r="Y196">
+        <v>1.27</v>
+      </c>
+      <c r="Z196">
+        <v>3.48</v>
+      </c>
+      <c r="AA196">
+        <v>1.86</v>
+      </c>
+      <c r="AB196">
+        <v>1.97</v>
+      </c>
+      <c r="AC196">
+        <v>3.05</v>
+      </c>
+      <c r="AD196">
+        <v>1.35</v>
+      </c>
+      <c r="AE196">
+        <v>1.13</v>
+      </c>
+      <c r="AF196">
         <v>1.7</v>
       </c>
-      <c r="O196">
-        <v>4</v>
-      </c>
-      <c r="P196">
-        <v>4.2</v>
-      </c>
-      <c r="Q196">
-        <v>2.1</v>
-      </c>
-      <c r="R196">
-        <v>2.5</v>
-      </c>
-      <c r="S196">
-        <v>1.22</v>
-      </c>
-      <c r="T196">
-        <v>3.78</v>
-      </c>
-      <c r="U196">
-        <v>2.1</v>
-      </c>
-      <c r="V196">
-        <v>1.65</v>
-      </c>
-      <c r="W196">
-        <v>1.14</v>
-      </c>
-      <c r="X196">
-        <v>1.02</v>
-      </c>
-      <c r="Y196">
-        <v>1.14</v>
-      </c>
-      <c r="Z196">
-        <v>5.5</v>
-      </c>
-      <c r="AA196">
-        <v>1.48</v>
-      </c>
-      <c r="AB196">
-        <v>2.65</v>
-      </c>
-      <c r="AC196">
-        <v>2.15</v>
-      </c>
-      <c r="AD196">
-        <v>1.65</v>
-      </c>
-      <c r="AE196">
-        <v>1.27</v>
-      </c>
-      <c r="AF196">
-        <v>1.45</v>
-      </c>
       <c r="AG196">
-        <v>2.53</v>
+        <v>2.04</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="AK196">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,80 +32420,80 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="O197">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="P197">
-        <v>2.65</v>
+        <v>2.21</v>
       </c>
       <c r="Q197">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R197">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S197">
+        <v>1.33</v>
+      </c>
+      <c r="T197">
+        <v>3.09</v>
+      </c>
+      <c r="U197">
+        <v>2.67</v>
+      </c>
+      <c r="V197">
+        <v>1.4</v>
+      </c>
+      <c r="W197">
+        <v>1.05</v>
+      </c>
+      <c r="X197">
+        <v>1.03</v>
+      </c>
+      <c r="Y197">
+        <v>1.23</v>
+      </c>
+      <c r="Z197">
+        <v>3.42</v>
+      </c>
+      <c r="AA197">
+        <v>1.84</v>
+      </c>
+      <c r="AB197">
+        <v>1.94</v>
+      </c>
+      <c r="AC197">
+        <v>2.97</v>
+      </c>
+      <c r="AD197">
+        <v>1.35</v>
+      </c>
+      <c r="AE197">
+        <v>1.13</v>
+      </c>
+      <c r="AF197">
+        <v>1.66</v>
+      </c>
+      <c r="AG197">
+        <v>2.1</v>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ197">
+        <v>1.25</v>
+      </c>
+      <c r="AK197">
         <v>1.36</v>
-      </c>
-      <c r="T197">
-        <v>3.03</v>
-      </c>
-      <c r="U197">
-        <v>2.88</v>
-      </c>
-      <c r="V197">
-        <v>1.36</v>
-      </c>
-      <c r="W197">
-        <v>1.06</v>
-      </c>
-      <c r="X197">
-        <v>1</v>
-      </c>
-      <c r="Y197">
-        <v>1.3</v>
-      </c>
-      <c r="Z197">
-        <v>3.1</v>
-      </c>
-      <c r="AA197">
-        <v>1.96</v>
-      </c>
-      <c r="AB197">
-        <v>1.81</v>
-      </c>
-      <c r="AC197">
-        <v>3.27</v>
-      </c>
-      <c r="AD197">
-        <v>1.34</v>
-      </c>
-      <c r="AE197">
-        <v>1.12</v>
-      </c>
-      <c r="AF197">
-        <v>1.73</v>
-      </c>
-      <c r="AG197">
-        <v>2.05</v>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ197">
-        <v>1.3</v>
-      </c>
-      <c r="AK197">
-        <v>1.59</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O198">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="P198">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="Q198">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R198">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S198">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T198">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="U198">
         <v>2.88</v>
       </c>
       <c r="V198">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W198">
         <v>1.06</v>
       </c>
       <c r="X198">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y198">
         <v>1.3</v>
       </c>
       <c r="Z198">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AA198">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB198">
         <v>1.81</v>
       </c>
       <c r="AC198">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="AD198">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE198">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF198">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG198">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK198">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="O199">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="P199">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="Q199">
-        <v>3.44</v>
+        <v>2.88</v>
       </c>
       <c r="R199">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="S199">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T199">
+        <v>3</v>
+      </c>
+      <c r="U199">
         <v>2.88</v>
       </c>
-      <c r="U199">
-        <v>3</v>
-      </c>
       <c r="V199">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W199">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X199">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y199">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z199">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="AA199">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AB199">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AC199">
-        <v>3.89</v>
+        <v>3.35</v>
       </c>
       <c r="AD199">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE199">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF199">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AG199">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK199">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G209">
@@ -34379,77 +34379,77 @@
         <v>2.34</v>
       </c>
       <c r="O209">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P209">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="Q209">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="R209">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S209">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="T209">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="U209">
-        <v>2.49</v>
+        <v>2.95</v>
       </c>
       <c r="V209">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="W209">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X209">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y209">
+        <v>1.31</v>
+      </c>
+      <c r="Z209">
+        <v>2.92</v>
+      </c>
+      <c r="AA209">
+        <v>2.05</v>
+      </c>
+      <c r="AB209">
+        <v>1.7</v>
+      </c>
+      <c r="AC209">
+        <v>3.48</v>
+      </c>
+      <c r="AD209">
+        <v>1.22</v>
+      </c>
+      <c r="AE209">
+        <v>1.05</v>
+      </c>
+      <c r="AF209">
+        <v>1.84</v>
+      </c>
+      <c r="AG209">
+        <v>1.84</v>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ209">
         <v>1.2</v>
       </c>
-      <c r="Z209">
-        <v>4.41</v>
-      </c>
-      <c r="AA209">
-        <v>1.65</v>
-      </c>
-      <c r="AB209">
-        <v>2.2</v>
-      </c>
-      <c r="AC209">
-        <v>2.69</v>
-      </c>
-      <c r="AD209">
-        <v>1.45</v>
-      </c>
-      <c r="AE209">
-        <v>1.17</v>
-      </c>
-      <c r="AF209">
-        <v>1.53</v>
-      </c>
-      <c r="AG209">
-        <v>2.3</v>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ209">
-        <v>1.29</v>
-      </c>
       <c r="AK209">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O210">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="P210">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="Q210">
-        <v>4.38</v>
+        <v>3.1</v>
       </c>
       <c r="R210">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="S210">
         <v>1.33</v>
       </c>
       <c r="T210">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="U210">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="V210">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W210">
         <v>1.07</v>
       </c>
       <c r="X210">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z210">
-        <v>4.02</v>
+        <v>3.66</v>
       </c>
       <c r="AA210">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB210">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="AC210">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD210">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE210">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF210">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG210">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AK210">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="O211">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P211">
-        <v>2.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q211">
-        <v>2.5</v>
+        <v>4.79</v>
       </c>
       <c r="R211">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S211">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T211">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="U211">
-        <v>2.95</v>
+        <v>2.57</v>
       </c>
       <c r="V211">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W211">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X211">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="Z211">
-        <v>2.92</v>
+        <v>3.58</v>
       </c>
       <c r="AA211">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AB211">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AC211">
-        <v>3.48</v>
+        <v>2.78</v>
       </c>
       <c r="AD211">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AE211">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF211">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AG211">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK211">
-        <v>1.8</v>
+        <v>1.08</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O212">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P212">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="Q212">
-        <v>4.79</v>
+        <v>3.04</v>
       </c>
       <c r="R212">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S212">
+        <v>1.41</v>
+      </c>
+      <c r="T212">
+        <v>2.63</v>
+      </c>
+      <c r="U212">
+        <v>2.88</v>
+      </c>
+      <c r="V212">
         <v>1.36</v>
       </c>
-      <c r="T212">
-        <v>2.82</v>
-      </c>
-      <c r="U212">
-        <v>2.57</v>
-      </c>
-      <c r="V212">
-        <v>1.43</v>
-      </c>
       <c r="W212">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X212">
         <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z212">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AA212">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AB212">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="AC212">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="AD212">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE212">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF212">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG212">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK212">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,80 +35028,80 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="O213">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P213">
-        <v>4.14</v>
+        <v>2.7</v>
       </c>
       <c r="Q213">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="R213">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="S213">
+        <v>1.25</v>
+      </c>
+      <c r="T213">
+        <v>3.3</v>
+      </c>
+      <c r="U213">
+        <v>2.49</v>
+      </c>
+      <c r="V213">
+        <v>1.51</v>
+      </c>
+      <c r="W213">
+        <v>1.08</v>
+      </c>
+      <c r="X213">
+        <v>1.01</v>
+      </c>
+      <c r="Y213">
         <v>1.2</v>
       </c>
-      <c r="T213">
-        <v>4.1</v>
-      </c>
-      <c r="U213">
-        <v>2.01</v>
-      </c>
-      <c r="V213">
-        <v>1.69</v>
-      </c>
-      <c r="W213">
+      <c r="Z213">
+        <v>4.41</v>
+      </c>
+      <c r="AA213">
+        <v>1.65</v>
+      </c>
+      <c r="AB213">
+        <v>2.2</v>
+      </c>
+      <c r="AC213">
+        <v>2.69</v>
+      </c>
+      <c r="AD213">
+        <v>1.45</v>
+      </c>
+      <c r="AE213">
         <v>1.17</v>
       </c>
-      <c r="X213">
-        <v>1.02</v>
-      </c>
-      <c r="Y213">
-        <v>1.1</v>
-      </c>
-      <c r="Z213">
-        <v>5.7</v>
-      </c>
-      <c r="AA213">
-        <v>1.44</v>
-      </c>
-      <c r="AB213">
-        <v>2.53</v>
-      </c>
-      <c r="AC213">
-        <v>2.04</v>
-      </c>
-      <c r="AD213">
-        <v>1.68</v>
-      </c>
-      <c r="AE213">
+      <c r="AF213">
+        <v>1.53</v>
+      </c>
+      <c r="AG213">
+        <v>2.3</v>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ213">
         <v>1.29</v>
       </c>
-      <c r="AF213">
-        <v>1.48</v>
-      </c>
-      <c r="AG213">
-        <v>2.47</v>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ213">
-        <v>1.13</v>
-      </c>
       <c r="AK213">
-        <v>2.23</v>
+        <v>1.4</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="O214">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P214">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="Q214">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R214">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S214">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T214">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U214">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="V214">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W214">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X214">
         <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z214">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="AA214">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AB214">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AC214">
-        <v>3.14</v>
+        <v>2.52</v>
       </c>
       <c r="AD214">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE214">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF214">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG214">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK214">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O215">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P215">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="Q215">
-        <v>3.04</v>
+        <v>4.38</v>
       </c>
       <c r="R215">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="S215">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T215">
-        <v>2.63</v>
+        <v>2.87</v>
       </c>
       <c r="U215">
+        <v>2.55</v>
+      </c>
+      <c r="V215">
+        <v>1.44</v>
+      </c>
+      <c r="W215">
+        <v>1.07</v>
+      </c>
+      <c r="X215">
+        <v>1</v>
+      </c>
+      <c r="Y215">
+        <v>1.21</v>
+      </c>
+      <c r="Z215">
+        <v>4.02</v>
+      </c>
+      <c r="AA215">
+        <v>1.75</v>
+      </c>
+      <c r="AB215">
+        <v>2.07</v>
+      </c>
+      <c r="AC215">
         <v>2.88</v>
       </c>
-      <c r="V215">
-        <v>1.36</v>
-      </c>
-      <c r="W215">
-        <v>1.08</v>
-      </c>
-      <c r="X215">
-        <v>1.01</v>
-      </c>
-      <c r="Y215">
-        <v>1.28</v>
-      </c>
-      <c r="Z215">
-        <v>3.05</v>
-      </c>
-      <c r="AA215">
-        <v>1.96</v>
-      </c>
-      <c r="AB215">
-        <v>1.72</v>
-      </c>
-      <c r="AC215">
-        <v>3.25</v>
-      </c>
       <c r="AD215">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE215">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AF215">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG215">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="AK215">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>2.55</v>
+        <v>1.71</v>
       </c>
       <c r="O216">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P216">
-        <v>2.43</v>
+        <v>4.14</v>
       </c>
       <c r="Q216">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="R216">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S216">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T216">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="U216">
-        <v>2.56</v>
+        <v>2.01</v>
       </c>
       <c r="V216">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="W216">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X216">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y216">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Z216">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="AA216">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AB216">
-        <v>2.17</v>
+        <v>2.53</v>
       </c>
       <c r="AC216">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="AD216">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AE216">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AF216">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG216">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK216">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -36984,7 +36984,7 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O225">
         <v>5.25</v>
@@ -36996,7 +36996,7 @@
         <v>1.65</v>
       </c>
       <c r="R225">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="S225">
         <v>1.25</v>
@@ -37005,10 +37005,10 @@
         <v>3.3</v>
       </c>
       <c r="U225">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="V225">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W225">
         <v>1.14</v>
@@ -37026,7 +37026,7 @@
         <v>1.53</v>
       </c>
       <c r="AB225">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AC225">
         <v>2.33</v>
@@ -41554,7 +41554,7 @@
         <v>3.5</v>
       </c>
       <c r="P253">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q253">
         <v>3.1</v>
@@ -41566,7 +41566,7 @@
         <v>1.29</v>
       </c>
       <c r="T253">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U253">
         <v>2.25</v>
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.15</v>
+        <v>5.75</v>
       </c>
       <c r="O266">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="P266">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="Q266">
-        <v>2.9</v>
+        <v>5.95</v>
       </c>
       <c r="R266">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="S266">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T266">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U266">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="V266">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="W266">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X266">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y266">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z266">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA266">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AB266">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="AC266">
-        <v>4.1</v>
+        <v>2.62</v>
       </c>
       <c r="AD266">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AE266">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF266">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG266">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK266">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,64 +43830,64 @@
         </is>
       </c>
       <c r="N267">
-        <v>5.75</v>
+        <v>2.15</v>
       </c>
       <c r="O267">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="P267">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="Q267">
-        <v>5.95</v>
+        <v>2.9</v>
       </c>
       <c r="R267">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="S267">
+        <v>1.4</v>
+      </c>
+      <c r="T267">
+        <v>2.75</v>
+      </c>
+      <c r="U267">
+        <v>3.2</v>
+      </c>
+      <c r="V267">
+        <v>1.3</v>
+      </c>
+      <c r="W267">
+        <v>1.06</v>
+      </c>
+      <c r="X267">
+        <v>1.03</v>
+      </c>
+      <c r="Y267">
         <v>1.33</v>
       </c>
-      <c r="T267">
-        <v>3.25</v>
-      </c>
-      <c r="U267">
-        <v>2.35</v>
-      </c>
-      <c r="V267">
-        <v>1.51</v>
-      </c>
-      <c r="W267">
-        <v>1.12</v>
-      </c>
-      <c r="X267">
-        <v>1.01</v>
-      </c>
-      <c r="Y267">
-        <v>1.17</v>
-      </c>
       <c r="Z267">
+        <v>2.9</v>
+      </c>
+      <c r="AA267">
+        <v>2.15</v>
+      </c>
+      <c r="AB267">
+        <v>1.67</v>
+      </c>
+      <c r="AC267">
         <v>4.1</v>
       </c>
-      <c r="AA267">
-        <v>1.68</v>
-      </c>
-      <c r="AB267">
-        <v>2.09</v>
-      </c>
-      <c r="AC267">
-        <v>2.62</v>
-      </c>
       <c r="AD267">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AE267">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF267">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG267">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK267">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,64 +46275,64 @@
         </is>
       </c>
       <c r="N282">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="O282">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P282">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q282">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R282">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S282">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T282">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U282">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="V282">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W282">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X282">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y282">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z282">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA282">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AB282">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AC282">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD282">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE282">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF282">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG282">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK282">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,64 +46438,64 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="O283">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P283">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="Q283">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R283">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S283">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T283">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U283">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V283">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W283">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X283">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y283">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z283">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA283">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AB283">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AC283">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD283">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE283">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF283">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG283">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK283">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -55412,10 +55412,10 @@
         <v>0</v>
       </c>
       <c r="Q338">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="R338">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="S338">
         <v>1.22</v>
@@ -55424,43 +55424,43 @@
         <v>3.75</v>
       </c>
       <c r="U338">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V338">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W338">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X338">
         <v>1.01</v>
       </c>
       <c r="Y338">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z338">
-        <v>5.01</v>
+        <v>4.9</v>
       </c>
       <c r="AA338">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB338">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AC338">
         <v>2.29</v>
       </c>
       <c r="AD338">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AE338">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AF338">
         <v>1.43</v>
       </c>
       <c r="AG338">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK338">
         <v>1.44</v>
@@ -55753,10 +55753,10 @@
         <v>2.25</v>
       </c>
       <c r="V340">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W340">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X340">
         <v>1.02</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,80 +58011,80 @@
         </is>
       </c>
       <c r="N354">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O354">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P354">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q354">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="R354">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S354">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T354">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="U354">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V354">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W354">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X354">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y354">
+        <v>1.29</v>
+      </c>
+      <c r="Z354">
+        <v>3.04</v>
+      </c>
+      <c r="AA354">
+        <v>1.95</v>
+      </c>
+      <c r="AB354">
+        <v>1.75</v>
+      </c>
+      <c r="AC354">
+        <v>3.28</v>
+      </c>
+      <c r="AD354">
         <v>1.25</v>
       </c>
-      <c r="Z354">
-        <v>3.28</v>
-      </c>
-      <c r="AA354">
-        <v>1.98</v>
-      </c>
-      <c r="AB354">
-        <v>1.84</v>
-      </c>
-      <c r="AC354">
-        <v>3.27</v>
-      </c>
-      <c r="AD354">
+      <c r="AE354">
+        <v>1.11</v>
+      </c>
+      <c r="AF354">
+        <v>1.77</v>
+      </c>
+      <c r="AG354">
+        <v>1.92</v>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI354" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ354">
         <v>1.28</v>
       </c>
-      <c r="AE354">
-        <v>1.07</v>
-      </c>
-      <c r="AF354">
-        <v>1.68</v>
-      </c>
-      <c r="AG354">
-        <v>2.03</v>
-      </c>
-      <c r="AH354" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI354" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ354">
-        <v>1.3</v>
-      </c>
       <c r="AK354">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL354">
         <v>0</v>
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G355">
@@ -58174,64 +58174,64 @@
         </is>
       </c>
       <c r="N355">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="O355">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P355">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q355">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="R355">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S355">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T355">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="U355">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V355">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W355">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X355">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y355">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z355">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AA355">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB355">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC355">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="AD355">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE355">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF355">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG355">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AH355" t="inlineStr">
         <is>
@@ -58244,10 +58244,10 @@
         </is>
       </c>
       <c r="AJ355">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK355">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL355">
         <v>0</v>
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G362">
@@ -59315,61 +59315,61 @@
         </is>
       </c>
       <c r="N362">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="O362">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P362">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="Q362">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="R362">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="S362">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="T362">
-        <v>2.84</v>
+        <v>3.24</v>
       </c>
       <c r="U362">
-        <v>2.61</v>
+        <v>2.32</v>
       </c>
       <c r="V362">
+        <v>1.49</v>
+      </c>
+      <c r="W362">
+        <v>1.11</v>
+      </c>
+      <c r="X362">
+        <v>1.02</v>
+      </c>
+      <c r="Y362">
+        <v>1.17</v>
+      </c>
+      <c r="Z362">
+        <v>4</v>
+      </c>
+      <c r="AA362">
+        <v>1.65</v>
+      </c>
+      <c r="AB362">
+        <v>2.06</v>
+      </c>
+      <c r="AC362">
+        <v>2.59</v>
+      </c>
+      <c r="AD362">
         <v>1.39</v>
       </c>
-      <c r="W362">
-        <v>1.06</v>
-      </c>
-      <c r="X362">
-        <v>1.01</v>
-      </c>
-      <c r="Y362">
-        <v>1.26</v>
-      </c>
-      <c r="Z362">
-        <v>3.2</v>
-      </c>
-      <c r="AA362">
-        <v>1.88</v>
-      </c>
-      <c r="AB362">
-        <v>1.79</v>
-      </c>
-      <c r="AC362">
-        <v>3.14</v>
-      </c>
-      <c r="AD362">
-        <v>1.27</v>
-      </c>
       <c r="AE362">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF362">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG362">
         <v>1.98</v>
@@ -59385,10 +59385,10 @@
         </is>
       </c>
       <c r="AJ362">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK362">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="AL362">
         <v>0</v>
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G363">
@@ -59478,64 +59478,64 @@
         </is>
       </c>
       <c r="N363">
-        <v>1.53</v>
+        <v>2.42</v>
       </c>
       <c r="O363">
-        <v>3.9</v>
+        <v>3.24</v>
       </c>
       <c r="P363">
-        <v>5.2</v>
+        <v>2.52</v>
       </c>
       <c r="Q363">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R363">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S363">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T363">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U363">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V363">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W363">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X363">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y363">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z363">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA363">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB363">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC363">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD363">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE363">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF363">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG363">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH363" t="inlineStr">
         <is>
@@ -59548,10 +59548,10 @@
         </is>
       </c>
       <c r="AJ363">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK363">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL363">
         <v>0</v>
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G364">
@@ -59641,64 +59641,64 @@
         </is>
       </c>
       <c r="N364">
-        <v>2.42</v>
+        <v>1.99</v>
       </c>
       <c r="O364">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P364">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="Q364">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R364">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S364">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T364">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U364">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V364">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W364">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X364">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y364">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z364">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA364">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB364">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC364">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD364">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE364">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF364">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG364">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH364" t="inlineStr">
         <is>
@@ -59711,10 +59711,10 @@
         </is>
       </c>
       <c r="AJ364">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK364">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL364">
         <v>0</v>
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G365">
@@ -59804,80 +59804,80 @@
         </is>
       </c>
       <c r="N365">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O365">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P365">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q365">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="R365">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="S365">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T365">
-        <v>2.69</v>
+        <v>3.12</v>
       </c>
       <c r="U365">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="V365">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="W365">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X365">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y365">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z365">
-        <v>2.97</v>
+        <v>4.1</v>
       </c>
       <c r="AA365">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AB365">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AC365">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="AD365">
+        <v>1.41</v>
+      </c>
+      <c r="AE365">
+        <v>1.13</v>
+      </c>
+      <c r="AF365">
+        <v>1.56</v>
+      </c>
+      <c r="AG365">
+        <v>2.25</v>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ365">
         <v>1.22</v>
       </c>
-      <c r="AE365">
-        <v>1.04</v>
-      </c>
-      <c r="AF365">
-        <v>1.82</v>
-      </c>
-      <c r="AG365">
-        <v>1.87</v>
-      </c>
-      <c r="AH365" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI365" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ365">
-        <v>1.25</v>
-      </c>
       <c r="AK365">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AL365">
         <v>0</v>
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G366">
@@ -59967,64 +59967,64 @@
         </is>
       </c>
       <c r="N366">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O366">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P366">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q366">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="R366">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="S366">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T366">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
       <c r="U366">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="V366">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W366">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X366">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y366">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z366">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA366">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AB366">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AC366">
-        <v>2.52</v>
+        <v>3.14</v>
       </c>
       <c r="AD366">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AE366">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF366">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AG366">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AH366" t="inlineStr">
         <is>
@@ -60037,10 +60037,10 @@
         </is>
       </c>
       <c r="AJ366">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK366">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AL366">
         <v>0</v>
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G369">
@@ -60456,64 +60456,64 @@
         </is>
       </c>
       <c r="N369">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="O369">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="P369">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q369">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="R369">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="S369">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T369">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="U369">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="V369">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W369">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X369">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y369">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z369">
-        <v>3.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA369">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AB369">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC369">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AD369">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AE369">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF369">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AG369">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AH369" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>1.14</v>
       </c>
       <c r="AK369">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AL369">
         <v>0</v>
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G370">
@@ -60619,64 +60619,64 @@
         </is>
       </c>
       <c r="N370">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="O370">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="P370">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q370">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="R370">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="S370">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T370">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U370">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="V370">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W370">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X370">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y370">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z370">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="AA370">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AB370">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC370">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AD370">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AE370">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF370">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG370">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AH370" t="inlineStr">
         <is>
@@ -60692,7 +60692,7 @@
         <v>1.14</v>
       </c>
       <c r="AK370">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AL370">
         <v>0</v>
@@ -61938,19 +61938,19 @@
         <v>2.7</v>
       </c>
       <c r="S378">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T378">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U378">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="V378">
         <v>1.74</v>
       </c>
       <c r="W378">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X378">
         <v>1.01</v>
@@ -61996,7 +61996,7 @@
         <v>1.03</v>
       </c>
       <c r="AK378">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AL378">
         <v>0</v>
@@ -62421,55 +62421,55 @@
         <v>0</v>
       </c>
       <c r="Q381">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R381">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S381">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T381">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U381">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V381">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W381">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X381">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y381">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z381">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA381">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB381">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC381">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AD381">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE381">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF381">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG381">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH381" t="inlineStr">
         <is>
@@ -62482,10 +62482,10 @@
         </is>
       </c>
       <c r="AJ381">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK381">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL381">
         <v>0</v>
@@ -62910,55 +62910,55 @@
         <v>0</v>
       </c>
       <c r="Q384">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R384">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S384">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T384">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U384">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V384">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W384">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X384">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y384">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z384">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA384">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB384">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC384">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD384">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE384">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF384">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG384">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH384" t="inlineStr">
         <is>
@@ -62971,10 +62971,10 @@
         </is>
       </c>
       <c r="AJ384">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK384">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL384">
         <v>0</v>
@@ -65065,7 +65065,7 @@
         <v>1.95</v>
       </c>
       <c r="AC397">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="AD397">
         <v>1.51</v>
@@ -65090,7 +65090,7 @@
         </is>
       </c>
       <c r="AJ397">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK397">
         <v>2.1</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -804,7 +804,7 @@
         <v>3.2</v>
       </c>
       <c r="P3">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q3">
         <v>2.8</v>
@@ -819,7 +819,7 @@
         <v>2.45</v>
       </c>
       <c r="U3">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="V3">
         <v>1.33</v>
@@ -855,7 +855,7 @@
         <v>1.87</v>
       </c>
       <c r="AG3">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O4">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>3.44</v>
+        <v>3.08</v>
       </c>
       <c r="Q4">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="R4">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S4">
         <v>1.3</v>
@@ -994,31 +994,31 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z4">
-        <v>3.99</v>
+        <v>4.06</v>
       </c>
       <c r="AA4">
         <v>1.74</v>
       </c>
       <c r="AB4">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC4">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG4">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>2.44</v>
       </c>
       <c r="R5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
         <v>1.4</v>
@@ -1181,7 +1181,7 @@
         <v>1.87</v>
       </c>
       <c r="AG5">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
         <v>1.91</v>
@@ -1308,13 +1308,13 @@
         <v>2.82</v>
       </c>
       <c r="U6">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1360,7 +1360,7 @@
         <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
+        <v>1.38</v>
+      </c>
+      <c r="T7">
+        <v>2.74</v>
+      </c>
+      <c r="U7">
+        <v>2.56</v>
+      </c>
+      <c r="V7">
+        <v>1.43</v>
+      </c>
+      <c r="W7">
+        <v>1.07</v>
+      </c>
+      <c r="X7">
+        <v>1.03</v>
+      </c>
+      <c r="Y7">
+        <v>1.23</v>
+      </c>
+      <c r="Z7">
+        <v>3.42</v>
+      </c>
+      <c r="AA7">
+        <v>1.83</v>
+      </c>
+      <c r="AB7">
+        <v>1.91</v>
+      </c>
+      <c r="AC7">
+        <v>3.2</v>
+      </c>
+      <c r="AD7">
         <v>1.3</v>
       </c>
-      <c r="T7">
-        <v>2.77</v>
-      </c>
-      <c r="U7">
-        <v>2.6</v>
-      </c>
-      <c r="V7">
-        <v>1.44</v>
-      </c>
-      <c r="W7">
-        <v>1.06</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>1.22</v>
-      </c>
-      <c r="Z7">
-        <v>3.7</v>
-      </c>
-      <c r="AA7">
-        <v>1.81</v>
-      </c>
-      <c r="AB7">
-        <v>1.9</v>
-      </c>
-      <c r="AC7">
-        <v>2.83</v>
-      </c>
-      <c r="AD7">
-        <v>1.33</v>
-      </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG7">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AK7">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,43 +1613,43 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T8">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="U8">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AA8">
         <v>1.81</v>
@@ -1658,19 +1658,19 @@
         <v>1.91</v>
       </c>
       <c r="AC8">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O11">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P11">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="Q11">
-        <v>4.76</v>
+        <v>4.83</v>
       </c>
       <c r="R11">
         <v>2.56</v>
@@ -2132,7 +2132,7 @@
         <v>1.15</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
         <v>1.12</v>
@@ -2150,16 +2150,16 @@
         <v>2.27</v>
       </c>
       <c r="AD11">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AE11">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF11">
         <v>1.53</v>
       </c>
       <c r="AG11">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.18</v>
+        <v>3.02</v>
       </c>
       <c r="O15">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="P15">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="Q15">
-        <v>2.63</v>
+        <v>3.93</v>
       </c>
       <c r="R15">
-        <v>2.17</v>
+        <v>1.82</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="T15">
-        <v>3.22</v>
+        <v>2.27</v>
       </c>
       <c r="U15">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="V15">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
+        <v>1.07</v>
+      </c>
+      <c r="Y15">
+        <v>1.56</v>
+      </c>
+      <c r="Z15">
+        <v>2.43</v>
+      </c>
+      <c r="AA15">
+        <v>2.69</v>
+      </c>
+      <c r="AB15">
+        <v>1.44</v>
+      </c>
+      <c r="AC15">
+        <v>5.5</v>
+      </c>
+      <c r="AD15">
+        <v>1.12</v>
+      </c>
+      <c r="AE15">
         <v>1.02</v>
       </c>
-      <c r="Y15">
-        <v>1.22</v>
-      </c>
-      <c r="Z15">
-        <v>3.94</v>
-      </c>
-      <c r="AA15">
-        <v>1.78</v>
-      </c>
-      <c r="AB15">
-        <v>2.05</v>
-      </c>
-      <c r="AC15">
-        <v>2.92</v>
-      </c>
-      <c r="AD15">
-        <v>1.39</v>
-      </c>
-      <c r="AE15">
-        <v>1.15</v>
-      </c>
       <c r="AF15">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AG15">
-        <v>2.19</v>
+        <v>1.62</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK15">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="O16">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="P16">
-        <v>2.23</v>
+        <v>2.73</v>
       </c>
       <c r="Q16">
-        <v>3.93</v>
+        <v>2.83</v>
       </c>
       <c r="R16">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="S16">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>2.27</v>
+        <v>2.57</v>
       </c>
       <c r="U16">
-        <v>3.7</v>
+        <v>2.91</v>
       </c>
       <c r="V16">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="W16">
+        <v>1.03</v>
+      </c>
+      <c r="X16">
+        <v>1.05</v>
+      </c>
+      <c r="Y16">
+        <v>1.33</v>
+      </c>
+      <c r="Z16">
+        <v>2.9</v>
+      </c>
+      <c r="AA16">
+        <v>2.14</v>
+      </c>
+      <c r="AB16">
+        <v>1.64</v>
+      </c>
+      <c r="AC16">
+        <v>3.72</v>
+      </c>
+      <c r="AD16">
+        <v>1.2</v>
+      </c>
+      <c r="AE16">
         <v>1.04</v>
       </c>
-      <c r="X16">
-        <v>1.07</v>
-      </c>
-      <c r="Y16">
-        <v>1.56</v>
-      </c>
-      <c r="Z16">
-        <v>2.43</v>
-      </c>
-      <c r="AA16">
-        <v>2.69</v>
-      </c>
-      <c r="AB16">
-        <v>1.44</v>
-      </c>
-      <c r="AC16">
-        <v>5.5</v>
-      </c>
-      <c r="AD16">
-        <v>1.12</v>
-      </c>
-      <c r="AE16">
-        <v>1.02</v>
-      </c>
       <c r="AF16">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O17">
-        <v>3.23</v>
+        <v>3.58</v>
       </c>
       <c r="P17">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="Q17">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="R17">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="U17">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>2.9</v>
+        <v>3.94</v>
       </c>
       <c r="AA17">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="AB17">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AC17">
-        <v>3.72</v>
+        <v>2.92</v>
       </c>
       <c r="AD17">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>1.86</v>
+        <v>2.19</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK17">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q20">
-        <v>2.35</v>
+        <v>3.23</v>
       </c>
       <c r="R20">
-        <v>2.61</v>
+        <v>2.14</v>
       </c>
       <c r="S20">
+        <v>1.29</v>
+      </c>
+      <c r="T20">
+        <v>3.02</v>
+      </c>
+      <c r="U20">
+        <v>2.55</v>
+      </c>
+      <c r="V20">
+        <v>1.46</v>
+      </c>
+      <c r="W20">
+        <v>1.08</v>
+      </c>
+      <c r="X20">
+        <v>1.02</v>
+      </c>
+      <c r="Y20">
+        <v>1.22</v>
+      </c>
+      <c r="Z20">
+        <v>3.74</v>
+      </c>
+      <c r="AA20">
+        <v>1.73</v>
+      </c>
+      <c r="AB20">
+        <v>2.07</v>
+      </c>
+      <c r="AC20">
+        <v>2.69</v>
+      </c>
+      <c r="AD20">
+        <v>1.41</v>
+      </c>
+      <c r="AE20">
         <v>1.15</v>
       </c>
-      <c r="T20">
-        <v>5.5</v>
-      </c>
-      <c r="U20">
-        <v>1.73</v>
-      </c>
-      <c r="V20">
-        <v>2</v>
-      </c>
-      <c r="W20">
-        <v>1.27</v>
-      </c>
-      <c r="X20">
-        <v>1.01</v>
-      </c>
-      <c r="Y20">
-        <v>1.01</v>
-      </c>
-      <c r="Z20">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA20">
-        <v>1.22</v>
-      </c>
-      <c r="AB20">
-        <v>4.2</v>
-      </c>
-      <c r="AC20">
-        <v>1.58</v>
-      </c>
-      <c r="AD20">
-        <v>2.33</v>
-      </c>
-      <c r="AE20">
-        <v>1.56</v>
-      </c>
       <c r="AF20">
+        <v>1.57</v>
+      </c>
+      <c r="AG20">
+        <v>2.21</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.18</v>
+      </c>
+      <c r="AK20">
         <v>1.25</v>
-      </c>
-      <c r="AG20">
-        <v>3.5</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.22</v>
-      </c>
-      <c r="AK20">
-        <v>1.77</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.2</v>
+        <v>1.09</v>
       </c>
       <c r="O21">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="P21">
-        <v>1.91</v>
+        <v>9.5</v>
       </c>
       <c r="Q21">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="R21">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="S21">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>4.8</v>
+        <v>3.46</v>
       </c>
       <c r="U21">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="V21">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AA21">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="AC21">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="AD21">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AE21">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>1.34</v>
+        <v>2.11</v>
       </c>
       <c r="AG21">
-        <v>2.99</v>
+        <v>1.65</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK21">
-        <v>1.33</v>
+        <v>3.86</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="P22">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="Q22">
-        <v>3.23</v>
+        <v>2.43</v>
       </c>
       <c r="R22">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="U22">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="V22">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z22">
-        <v>3.74</v>
+        <v>4.54</v>
       </c>
       <c r="AA22">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AB22">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="AC22">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AD22">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AE22">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF22">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG22">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P23">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="Q23">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="R23">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="U23">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V23">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z23">
-        <v>4.75</v>
+        <v>5.07</v>
       </c>
       <c r="AA23">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB23">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="AC23">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="AD23">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AE23">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AF23">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG23">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="S24">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T24">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U24">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="V24">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="W24">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z24">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AA24">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB24">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AC24">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AD24">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AE24">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF24">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AG24">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.46</v>
+        <v>1.93</v>
       </c>
       <c r="O25">
-        <v>4.51</v>
+        <v>4.1</v>
       </c>
       <c r="P25">
-        <v>7.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q25">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="R25">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="S25">
+        <v>1.15</v>
+      </c>
+      <c r="T25">
+        <v>5</v>
+      </c>
+      <c r="U25">
+        <v>1.73</v>
+      </c>
+      <c r="V25">
+        <v>2</v>
+      </c>
+      <c r="W25">
+        <v>1.27</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1.04</v>
+      </c>
+      <c r="Z25">
+        <v>8.5</v>
+      </c>
+      <c r="AA25">
+        <v>1.25</v>
+      </c>
+      <c r="AB25">
+        <v>4.2</v>
+      </c>
+      <c r="AC25">
+        <v>1.58</v>
+      </c>
+      <c r="AD25">
+        <v>2.33</v>
+      </c>
+      <c r="AE25">
+        <v>1.56</v>
+      </c>
+      <c r="AF25">
+        <v>1.25</v>
+      </c>
+      <c r="AG25">
+        <v>3.5</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.22</v>
       </c>
-      <c r="T25">
-        <v>3.8</v>
-      </c>
-      <c r="U25">
-        <v>2.25</v>
-      </c>
-      <c r="V25">
-        <v>1.57</v>
-      </c>
-      <c r="W25">
-        <v>1.11</v>
-      </c>
-      <c r="X25">
-        <v>1.01</v>
-      </c>
-      <c r="Y25">
-        <v>1.18</v>
-      </c>
-      <c r="Z25">
-        <v>4.8</v>
-      </c>
-      <c r="AA25">
-        <v>1.57</v>
-      </c>
-      <c r="AB25">
-        <v>2.38</v>
-      </c>
-      <c r="AC25">
-        <v>2.34</v>
-      </c>
-      <c r="AD25">
-        <v>1.46</v>
-      </c>
-      <c r="AE25">
-        <v>1.15</v>
-      </c>
-      <c r="AF25">
-        <v>2.11</v>
-      </c>
-      <c r="AG25">
-        <v>1.65</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.1</v>
-      </c>
       <c r="AK25">
-        <v>3.86</v>
+        <v>1.77</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O26">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>2.79</v>
+        <v>2.54</v>
       </c>
       <c r="Q26">
-        <v>3.54</v>
+        <v>2.99</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T26">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="U26">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W26">
         <v>1.13</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>4.95</v>
+        <v>4.69</v>
       </c>
       <c r="AA26">
+        <v>1.5</v>
+      </c>
+      <c r="AB26">
+        <v>2.28</v>
+      </c>
+      <c r="AC26">
+        <v>2.29</v>
+      </c>
+      <c r="AD26">
+        <v>1.53</v>
+      </c>
+      <c r="AE26">
+        <v>1.2</v>
+      </c>
+      <c r="AF26">
         <v>1.44</v>
       </c>
-      <c r="AB26">
-        <v>2.43</v>
-      </c>
-      <c r="AC26">
-        <v>2.17</v>
-      </c>
-      <c r="AD26">
-        <v>1.65</v>
-      </c>
-      <c r="AE26">
-        <v>1.23</v>
-      </c>
-      <c r="AF26">
-        <v>1.42</v>
-      </c>
       <c r="AG26">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q27">
-        <v>2.43</v>
+        <v>3.58</v>
       </c>
       <c r="R27">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="S27">
+        <v>1.17</v>
+      </c>
+      <c r="T27">
+        <v>4.5</v>
+      </c>
+      <c r="U27">
+        <v>2.05</v>
+      </c>
+      <c r="V27">
+        <v>1.72</v>
+      </c>
+      <c r="W27">
+        <v>1.2</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27">
+        <v>1.12</v>
+      </c>
+      <c r="Z27">
+        <v>5.54</v>
+      </c>
+      <c r="AA27">
+        <v>1.4</v>
+      </c>
+      <c r="AB27">
+        <v>2.7</v>
+      </c>
+      <c r="AC27">
+        <v>2.02</v>
+      </c>
+      <c r="AD27">
+        <v>1.76</v>
+      </c>
+      <c r="AE27">
+        <v>1.32</v>
+      </c>
+      <c r="AF27">
+        <v>1.4</v>
+      </c>
+      <c r="AG27">
+        <v>2.7</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.22</v>
       </c>
-      <c r="T27">
-        <v>3.8</v>
-      </c>
-      <c r="U27">
-        <v>2.23</v>
-      </c>
-      <c r="V27">
-        <v>1.57</v>
-      </c>
-      <c r="W27">
-        <v>1.13</v>
-      </c>
-      <c r="X27">
-        <v>1.01</v>
-      </c>
-      <c r="Y27">
-        <v>1.14</v>
-      </c>
-      <c r="Z27">
-        <v>4.4</v>
-      </c>
-      <c r="AA27">
-        <v>1.62</v>
-      </c>
-      <c r="AB27">
-        <v>2.33</v>
-      </c>
-      <c r="AC27">
-        <v>2.5</v>
-      </c>
-      <c r="AD27">
-        <v>1.45</v>
-      </c>
-      <c r="AE27">
-        <v>1.15</v>
-      </c>
-      <c r="AF27">
-        <v>1.53</v>
-      </c>
-      <c r="AG27">
-        <v>2.37</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.2</v>
-      </c>
       <c r="AK27">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q28">
         <v>2.32</v>
@@ -4888,13 +4888,13 @@
         <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T28">
         <v>2.88</v>
       </c>
       <c r="U28">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="V28">
         <v>1.4</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="R33">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T33">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="AA33">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AB33">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.14</v>
+        <v>3.82</v>
       </c>
       <c r="AD33">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE33">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF33">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AG33">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q34">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="R34">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="U34">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="V34">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="AA34">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AB34">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
-        <v>3.82</v>
+        <v>3.14</v>
       </c>
       <c r="AD34">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AG34">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6186,22 +6186,22 @@
         <v>4.8</v>
       </c>
       <c r="Q36">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R36">
         <v>2.46</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T36">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U36">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="V36">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
         <v>1.17</v>
@@ -6210,31 +6210,31 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="AA36">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AC36">
         <v>2.2</v>
       </c>
       <c r="AD36">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF36">
         <v>1.57</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.12</v>
       </c>
       <c r="AK36">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S46">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T46">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA46">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB46">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AC46">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD46">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG46">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="O56">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P56">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="Q56">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="R56">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="S56">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="U56">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="V56">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA56">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AB56">
-        <v>3.8</v>
+        <v>2.43</v>
       </c>
       <c r="AC56">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="AD56">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AE56">
+        <v>1.22</v>
+      </c>
+      <c r="AF56">
         <v>1.5</v>
       </c>
-      <c r="AF56">
-        <v>1.3</v>
-      </c>
       <c r="AG56">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="O57">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P57">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="Q57">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="R57">
-        <v>2.35</v>
+        <v>2.64</v>
       </c>
       <c r="S57">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="T57">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="U57">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="V57">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="W57">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="X57">
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Z57">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA57">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="AB57">
-        <v>2.43</v>
+        <v>3.8</v>
       </c>
       <c r="AC57">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="AD57">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AE57">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AF57">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AG57">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9956,13 +9956,13 @@
         <v>1.06</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y59">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z59">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AA59">
         <v>2.05</v>
@@ -9971,19 +9971,19 @@
         <v>1.75</v>
       </c>
       <c r="AC59">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD59">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE59">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF59">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG59">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10291,10 +10291,10 @@
         <v>3.2</v>
       </c>
       <c r="AA61">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB61">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC61">
         <v>3.2</v>
@@ -11396,7 +11396,7 @@
         <v>4</v>
       </c>
       <c r="O68">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
         <v>1.65</v>
@@ -11432,7 +11432,7 @@
         <v>4.15</v>
       </c>
       <c r="AA68">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB68">
         <v>2.13</v>
@@ -11450,7 +11450,7 @@
         <v>1.57</v>
       </c>
       <c r="AG68">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
+        <v>1.62</v>
+      </c>
+      <c r="O88">
+        <v>4.2</v>
+      </c>
+      <c r="P88">
+        <v>4.4</v>
+      </c>
+      <c r="Q88">
+        <v>2</v>
+      </c>
+      <c r="R88">
+        <v>2.61</v>
+      </c>
+      <c r="S88">
+        <v>1.17</v>
+      </c>
+      <c r="T88">
+        <v>4.15</v>
+      </c>
+      <c r="U88">
+        <v>1.91</v>
+      </c>
+      <c r="V88">
+        <v>1.8</v>
+      </c>
+      <c r="W88">
+        <v>1.22</v>
+      </c>
+      <c r="X88">
+        <v>1.01</v>
+      </c>
+      <c r="Y88">
+        <v>1.06</v>
+      </c>
+      <c r="Z88">
+        <v>6.3</v>
+      </c>
+      <c r="AA88">
+        <v>1.29</v>
+      </c>
+      <c r="AB88">
+        <v>3.04</v>
+      </c>
+      <c r="AC88">
+        <v>1.81</v>
+      </c>
+      <c r="AD88">
         <v>1.93</v>
       </c>
-      <c r="O88">
-        <v>3.75</v>
-      </c>
-      <c r="P88">
-        <v>3.15</v>
-      </c>
-      <c r="Q88">
-        <v>2.26</v>
-      </c>
-      <c r="R88">
-        <v>2.28</v>
-      </c>
-      <c r="S88">
-        <v>1.23</v>
-      </c>
-      <c r="T88">
-        <v>3.7</v>
-      </c>
-      <c r="U88">
-        <v>2.25</v>
-      </c>
-      <c r="V88">
-        <v>1.57</v>
-      </c>
-      <c r="W88">
-        <v>1.09</v>
-      </c>
-      <c r="X88">
-        <v>1.02</v>
-      </c>
-      <c r="Y88">
-        <v>1.1</v>
-      </c>
-      <c r="Z88">
-        <v>4.95</v>
-      </c>
-      <c r="AA88">
-        <v>1.47</v>
-      </c>
-      <c r="AB88">
-        <v>2.35</v>
-      </c>
-      <c r="AC88">
-        <v>2.24</v>
-      </c>
-      <c r="AD88">
-        <v>1.55</v>
-      </c>
       <c r="AE88">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AF88">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AG88">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK88">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="O89">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P89">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q89">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="R89">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="S89">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="U89">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="V89">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="W89">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z89">
-        <v>6.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA89">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AB89">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="AC89">
-        <v>1.81</v>
+        <v>2.41</v>
       </c>
       <c r="AD89">
-        <v>1.93</v>
+        <v>1.41</v>
       </c>
       <c r="AE89">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AF89">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG89">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK89">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,25 +14979,25 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O90">
+        <v>3.75</v>
+      </c>
+      <c r="P90">
+        <v>3.15</v>
+      </c>
+      <c r="Q90">
+        <v>2.26</v>
+      </c>
+      <c r="R90">
+        <v>2.28</v>
+      </c>
+      <c r="S90">
+        <v>1.23</v>
+      </c>
+      <c r="T90">
         <v>3.7</v>
-      </c>
-      <c r="P90">
-        <v>3.1</v>
-      </c>
-      <c r="Q90">
-        <v>2.45</v>
-      </c>
-      <c r="R90">
-        <v>2.38</v>
-      </c>
-      <c r="S90">
-        <v>1.25</v>
-      </c>
-      <c r="T90">
-        <v>3.5</v>
       </c>
       <c r="U90">
         <v>2.25</v>
@@ -15006,37 +15006,37 @@
         <v>1.57</v>
       </c>
       <c r="W90">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z90">
-        <v>4.33</v>
+        <v>4.95</v>
       </c>
       <c r="AA90">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB90">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC90">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="AD90">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AE90">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AF90">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG90">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK90">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15797,10 +15797,10 @@
         <v>2.75</v>
       </c>
       <c r="O95">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P95">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -16298,13 +16298,13 @@
         <v>2.23</v>
       </c>
       <c r="S98">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T98">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U98">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V98">
         <v>1.5</v>
@@ -16313,28 +16313,28 @@
         <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z98">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA98">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB98">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC98">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD98">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE98">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF98">
         <v>1.57</v>
@@ -16449,10 +16449,10 @@
         <v>2.64</v>
       </c>
       <c r="O99">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="P99">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB99">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O103">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P103">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Q103">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="R103">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="S103">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T103">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="U103">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="V103">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="W103">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
+        <v>1</v>
+      </c>
+      <c r="Y103">
+        <v>1.28</v>
+      </c>
+      <c r="Z103">
+        <v>3.05</v>
+      </c>
+      <c r="AA103">
+        <v>2</v>
+      </c>
+      <c r="AB103">
+        <v>1.8</v>
+      </c>
+      <c r="AC103">
+        <v>3.5</v>
+      </c>
+      <c r="AD103">
+        <v>1.22</v>
+      </c>
+      <c r="AE103">
         <v>1.03</v>
       </c>
-      <c r="Y103">
-        <v>1.19</v>
-      </c>
-      <c r="Z103">
-        <v>3.8</v>
-      </c>
-      <c r="AA103">
-        <v>1.75</v>
-      </c>
-      <c r="AB103">
-        <v>2.05</v>
-      </c>
-      <c r="AC103">
-        <v>2.74</v>
-      </c>
-      <c r="AD103">
-        <v>1.35</v>
-      </c>
-      <c r="AE103">
-        <v>1.1</v>
-      </c>
       <c r="AF103">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AG103">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
+        <v>2.3</v>
+      </c>
+      <c r="O104">
+        <v>3.25</v>
+      </c>
+      <c r="P104">
         <v>2.62</v>
       </c>
-      <c r="O104">
-        <v>3.1</v>
-      </c>
-      <c r="P104">
-        <v>2.45</v>
-      </c>
       <c r="Q104">
-        <v>3.24</v>
+        <v>2.88</v>
       </c>
       <c r="R104">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="S104">
+        <v>1.3</v>
+      </c>
+      <c r="T104">
+        <v>2.99</v>
+      </c>
+      <c r="U104">
+        <v>2.52</v>
+      </c>
+      <c r="V104">
+        <v>1.48</v>
+      </c>
+      <c r="W104">
+        <v>1.07</v>
+      </c>
+      <c r="X104">
+        <v>1.03</v>
+      </c>
+      <c r="Y104">
+        <v>1.19</v>
+      </c>
+      <c r="Z104">
+        <v>3.8</v>
+      </c>
+      <c r="AA104">
+        <v>1.75</v>
+      </c>
+      <c r="AB104">
+        <v>2.05</v>
+      </c>
+      <c r="AC104">
+        <v>2.74</v>
+      </c>
+      <c r="AD104">
         <v>1.35</v>
       </c>
-      <c r="T104">
-        <v>2.77</v>
-      </c>
-      <c r="U104">
-        <v>2.8</v>
-      </c>
-      <c r="V104">
-        <v>1.34</v>
-      </c>
-      <c r="W104">
-        <v>1.04</v>
-      </c>
-      <c r="X104">
-        <v>1</v>
-      </c>
-      <c r="Y104">
-        <v>1.28</v>
-      </c>
-      <c r="Z104">
-        <v>3.05</v>
-      </c>
-      <c r="AA104">
-        <v>2</v>
-      </c>
-      <c r="AB104">
-        <v>1.8</v>
-      </c>
-      <c r="AC104">
-        <v>3.5</v>
-      </c>
-      <c r="AD104">
+      <c r="AE104">
+        <v>1.1</v>
+      </c>
+      <c r="AF104">
+        <v>1.57</v>
+      </c>
+      <c r="AG104">
+        <v>2.2</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
         <v>1.22</v>
       </c>
-      <c r="AE104">
-        <v>1.03</v>
-      </c>
-      <c r="AF104">
-        <v>1.76</v>
-      </c>
-      <c r="AG104">
-        <v>1.91</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.25</v>
-      </c>
       <c r="AK104">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -18245,7 +18245,7 @@
         <v>3.2</v>
       </c>
       <c r="P110">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q110">
         <v>3.02</v>
@@ -18269,13 +18269,13 @@
         <v>1.11</v>
       </c>
       <c r="X110">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y110">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z110">
-        <v>4.01</v>
+        <v>4.1</v>
       </c>
       <c r="AA110">
         <v>1.85</v>
@@ -18284,19 +18284,19 @@
         <v>1.95</v>
       </c>
       <c r="AC110">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD110">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF110">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG110">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="O111">
         <v>3.3</v>
       </c>
       <c r="P111">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q111">
         <v>2.9</v>
@@ -18444,7 +18444,7 @@
         <v>1.66</v>
       </c>
       <c r="AB111">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AC111">
         <v>2.7</v>
@@ -18571,55 +18571,55 @@
         <v>3.5</v>
       </c>
       <c r="P112">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q112">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="R112">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S112">
+        <v>1.43</v>
+      </c>
+      <c r="T112">
+        <v>2.56</v>
+      </c>
+      <c r="U112">
+        <v>2.79</v>
+      </c>
+      <c r="V112">
         <v>1.37</v>
-      </c>
-      <c r="T112">
-        <v>2.69</v>
-      </c>
-      <c r="U112">
-        <v>2.86</v>
-      </c>
-      <c r="V112">
-        <v>1.33</v>
       </c>
       <c r="W112">
         <v>1.05</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y112">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z112">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA112">
+        <v>2.04</v>
+      </c>
+      <c r="AB112">
+        <v>1.67</v>
+      </c>
+      <c r="AC112">
+        <v>3.9</v>
+      </c>
+      <c r="AD112">
+        <v>1.22</v>
+      </c>
+      <c r="AE112">
+        <v>1.05</v>
+      </c>
+      <c r="AF112">
         <v>2.1</v>
-      </c>
-      <c r="AB112">
-        <v>1.73</v>
-      </c>
-      <c r="AC112">
-        <v>3.68</v>
-      </c>
-      <c r="AD112">
-        <v>1.2</v>
-      </c>
-      <c r="AE112">
-        <v>1.03</v>
-      </c>
-      <c r="AF112">
-        <v>2.06</v>
       </c>
       <c r="AG112">
         <v>1.65</v>
@@ -18638,7 +18638,7 @@
         <v>1.18</v>
       </c>
       <c r="AK112">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.55</v>
+        <v>2.58</v>
       </c>
       <c r="O114">
-        <v>4.2</v>
+        <v>3.23</v>
       </c>
       <c r="P114">
-        <v>5.15</v>
+        <v>2.33</v>
       </c>
       <c r="Q114">
-        <v>2</v>
+        <v>3.68</v>
       </c>
       <c r="R114">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="S114">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="T114">
-        <v>3.29</v>
+        <v>2.5</v>
       </c>
       <c r="U114">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V114">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="W114">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X114">
+        <v>1.03</v>
+      </c>
+      <c r="Y114">
+        <v>1.31</v>
+      </c>
+      <c r="Z114">
+        <v>2.92</v>
+      </c>
+      <c r="AA114">
+        <v>2.15</v>
+      </c>
+      <c r="AB114">
+        <v>1.65</v>
+      </c>
+      <c r="AC114">
+        <v>4.1</v>
+      </c>
+      <c r="AD114">
+        <v>1.22</v>
+      </c>
+      <c r="AE114">
         <v>1.04</v>
       </c>
-      <c r="Y114">
-        <v>1.2</v>
-      </c>
-      <c r="Z114">
-        <v>4.1</v>
-      </c>
-      <c r="AA114">
-        <v>1.72</v>
-      </c>
-      <c r="AB114">
-        <v>2.12</v>
-      </c>
-      <c r="AC114">
-        <v>2.56</v>
-      </c>
-      <c r="AD114">
-        <v>1.4</v>
-      </c>
-      <c r="AE114">
-        <v>1.12</v>
-      </c>
       <c r="AF114">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AG114">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AK114">
-        <v>2.33</v>
+        <v>1.37</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,61 +19054,61 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="O115">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P115">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="Q115">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R115">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S115">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T115">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U115">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V115">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W115">
         <v>1.06</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z115">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA115">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AB115">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC115">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD115">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE115">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG115">
         <v>1.87</v>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,80 +19380,80 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.58</v>
+        <v>1.55</v>
       </c>
       <c r="O117">
-        <v>3.23</v>
+        <v>4.2</v>
       </c>
       <c r="P117">
+        <v>5.15</v>
+      </c>
+      <c r="Q117">
+        <v>2</v>
+      </c>
+      <c r="R117">
+        <v>2.32</v>
+      </c>
+      <c r="S117">
+        <v>1.32</v>
+      </c>
+      <c r="T117">
+        <v>3.29</v>
+      </c>
+      <c r="U117">
+        <v>2.4</v>
+      </c>
+      <c r="V117">
+        <v>1.48</v>
+      </c>
+      <c r="W117">
+        <v>1.08</v>
+      </c>
+      <c r="X117">
+        <v>1.04</v>
+      </c>
+      <c r="Y117">
+        <v>1.2</v>
+      </c>
+      <c r="Z117">
+        <v>4.1</v>
+      </c>
+      <c r="AA117">
+        <v>1.72</v>
+      </c>
+      <c r="AB117">
+        <v>2.12</v>
+      </c>
+      <c r="AC117">
+        <v>2.56</v>
+      </c>
+      <c r="AD117">
+        <v>1.4</v>
+      </c>
+      <c r="AE117">
+        <v>1.12</v>
+      </c>
+      <c r="AF117">
+        <v>1.74</v>
+      </c>
+      <c r="AG117">
+        <v>1.98</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ117">
+        <v>1.2</v>
+      </c>
+      <c r="AK117">
         <v>2.33</v>
-      </c>
-      <c r="Q117">
-        <v>3.68</v>
-      </c>
-      <c r="R117">
-        <v>1.9</v>
-      </c>
-      <c r="S117">
-        <v>1.45</v>
-      </c>
-      <c r="T117">
-        <v>2.5</v>
-      </c>
-      <c r="U117">
-        <v>2.88</v>
-      </c>
-      <c r="V117">
-        <v>1.35</v>
-      </c>
-      <c r="W117">
-        <v>1.05</v>
-      </c>
-      <c r="X117">
-        <v>1.03</v>
-      </c>
-      <c r="Y117">
-        <v>1.31</v>
-      </c>
-      <c r="Z117">
-        <v>2.92</v>
-      </c>
-      <c r="AA117">
-        <v>2.15</v>
-      </c>
-      <c r="AB117">
-        <v>1.65</v>
-      </c>
-      <c r="AC117">
-        <v>4.1</v>
-      </c>
-      <c r="AD117">
-        <v>1.22</v>
-      </c>
-      <c r="AE117">
-        <v>1.04</v>
-      </c>
-      <c r="AF117">
-        <v>1.79</v>
-      </c>
-      <c r="AG117">
-        <v>1.89</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ117">
-        <v>1.45</v>
-      </c>
-      <c r="AK117">
-        <v>1.37</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,61 +19543,61 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="O118">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P118">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="Q118">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R118">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S118">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T118">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U118">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V118">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W118">
         <v>1.06</v>
       </c>
       <c r="X118">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z118">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AA118">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AB118">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC118">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD118">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE118">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF118">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG118">
         <v>1.87</v>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK118">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -21182,55 +21182,55 @@
         <v>1.79</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="O129">
-        <v>5.4</v>
+        <v>6.06</v>
       </c>
       <c r="P129">
-        <v>8.300000000000001</v>
+        <v>10.19</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -22815,7 +22815,7 @@
         <v>1.62</v>
       </c>
       <c r="R138">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="S138">
         <v>1.25</v>
@@ -22981,10 +22981,10 @@
         <v>1.92</v>
       </c>
       <c r="S139">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T139">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U139">
         <v>2.86</v>
@@ -23008,7 +23008,7 @@
         <v>2.15</v>
       </c>
       <c r="AB139">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC139">
         <v>3.72</v>
@@ -23132,13 +23132,13 @@
         <v>1.53</v>
       </c>
       <c r="O140">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="P140">
         <v>5.2</v>
       </c>
       <c r="Q140">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R140">
         <v>2.48</v>
@@ -23455,10 +23455,10 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O142">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P142">
         <v>2.6</v>
@@ -23509,7 +23509,7 @@
         <v>1.1</v>
       </c>
       <c r="AF142">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG142">
         <v>2.25</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="O143">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P143">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="Q143">
         <v>2.75</v>
@@ -23660,7 +23660,7 @@
         <v>1.65</v>
       </c>
       <c r="AB143">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC143">
         <v>2.46</v>
@@ -24433,7 +24433,7 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O148">
         <v>3.83</v>
@@ -24457,7 +24457,7 @@
         <v>2.1</v>
       </c>
       <c r="V148">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W148">
         <v>1.15</v>
@@ -24472,7 +24472,7 @@
         <v>5.25</v>
       </c>
       <c r="AA148">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB148">
         <v>2.55</v>
@@ -24487,10 +24487,10 @@
         <v>1.25</v>
       </c>
       <c r="AF148">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG148">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>2.18</v>
       </c>
       <c r="O149">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P149">
         <v>2.6</v>
@@ -24635,7 +24635,7 @@
         <v>5.5</v>
       </c>
       <c r="AA149">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB149">
         <v>2.47</v>
@@ -24647,7 +24647,7 @@
         <v>1.56</v>
       </c>
       <c r="AE149">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF149">
         <v>1.48</v>
@@ -24786,7 +24786,7 @@
         <v>1.66</v>
       </c>
       <c r="W150">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X150">
         <v>1</v>
@@ -24922,7 +24922,7 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="O151">
         <v>5.25</v>
@@ -24970,7 +24970,7 @@
         <v>1.73</v>
       </c>
       <c r="AD151">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AE151">
         <v>1.48</v>
@@ -26751,19 +26751,19 @@
         <v>1.18</v>
       </c>
       <c r="Z162">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="AA162">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB162">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC162">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="AD162">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE162">
         <v>1.14</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.95</v>
+        <v>2.37</v>
       </c>
       <c r="O175">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P175">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q175">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="R175">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="S175">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="T175">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U175">
-        <v>2.57</v>
+        <v>3.07</v>
       </c>
       <c r="V175">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W175">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X175">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Z175">
-        <v>3.91</v>
+        <v>3.15</v>
       </c>
       <c r="AA175">
+        <v>2.07</v>
+      </c>
+      <c r="AB175">
+        <v>1.73</v>
+      </c>
+      <c r="AC175">
+        <v>3.68</v>
+      </c>
+      <c r="AD175">
+        <v>1.26</v>
+      </c>
+      <c r="AE175">
+        <v>1.05</v>
+      </c>
+      <c r="AF175">
         <v>1.78</v>
       </c>
-      <c r="AB175">
-        <v>2.01</v>
-      </c>
-      <c r="AC175">
-        <v>2.93</v>
-      </c>
-      <c r="AD175">
-        <v>1.32</v>
-      </c>
-      <c r="AE175">
-        <v>1.08</v>
-      </c>
-      <c r="AF175">
-        <v>1.62</v>
-      </c>
       <c r="AG175">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.37</v>
+        <v>1.62</v>
       </c>
       <c r="O176">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P176">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q176">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="R176">
-        <v>2.03</v>
+        <v>2.47</v>
       </c>
       <c r="S176">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T176">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="U176">
-        <v>3.07</v>
+        <v>2.47</v>
       </c>
       <c r="V176">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="W176">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X176">
         <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="Z176">
-        <v>3.15</v>
+        <v>4.53</v>
       </c>
       <c r="AA176">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="AB176">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="AC176">
-        <v>3.68</v>
+        <v>2.64</v>
       </c>
       <c r="AD176">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AE176">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF176">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AG176">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK176">
-        <v>1.57</v>
+        <v>2.19</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="O177">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P177">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q177">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="R177">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S177">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T177">
-        <v>3.32</v>
+        <v>2.87</v>
       </c>
       <c r="U177">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="V177">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W177">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X177">
         <v>1.02</v>
       </c>
       <c r="Y177">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z177">
-        <v>4.53</v>
+        <v>3.78</v>
       </c>
       <c r="AA177">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AB177">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="AC177">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="AD177">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE177">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF177">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG177">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK177">
-        <v>2.19</v>
+        <v>1.45</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="O178">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P178">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q178">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R178">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S178">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T178">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="U178">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="V178">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W178">
+        <v>1.07</v>
+      </c>
+      <c r="X178">
+        <v>1.01</v>
+      </c>
+      <c r="Y178">
+        <v>1.24</v>
+      </c>
+      <c r="Z178">
+        <v>3.91</v>
+      </c>
+      <c r="AA178">
+        <v>1.78</v>
+      </c>
+      <c r="AB178">
+        <v>2.01</v>
+      </c>
+      <c r="AC178">
+        <v>2.93</v>
+      </c>
+      <c r="AD178">
+        <v>1.32</v>
+      </c>
+      <c r="AE178">
         <v>1.08</v>
       </c>
-      <c r="X178">
-        <v>1.02</v>
-      </c>
-      <c r="Y178">
-        <v>1.23</v>
-      </c>
-      <c r="Z178">
-        <v>3.78</v>
-      </c>
-      <c r="AA178">
-        <v>1.76</v>
-      </c>
-      <c r="AB178">
-        <v>2.04</v>
-      </c>
-      <c r="AC178">
-        <v>2.98</v>
-      </c>
-      <c r="AD178">
-        <v>1.35</v>
-      </c>
-      <c r="AE178">
-        <v>1.1</v>
-      </c>
       <c r="AF178">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG178">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK178">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29682,10 +29682,10 @@
         <v>1</v>
       </c>
       <c r="Y180">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z180">
-        <v>9.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="AA180">
         <v>1.16</v>
@@ -29821,55 +29821,55 @@
         <v>0</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="S181">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T181">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U181">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V181">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W181">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X181">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z181">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA181">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB181">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC181">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD181">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE181">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF181">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG181">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK181">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29984,55 +29984,55 @@
         <v>0</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T182">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U182">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V182">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W182">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X182">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y182">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z182">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA182">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB182">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC182">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD182">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE182">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG182">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK182">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="O185">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="P185">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="Q185">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="R185">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="S185">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T185">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="U185">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="V185">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="W185">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X185">
         <v>1.01</v>
       </c>
       <c r="Y185">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z185">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="AA185">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AB185">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AC185">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AD185">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AE185">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF185">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG185">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK185">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="O189">
-        <v>4.05</v>
+        <v>4.35</v>
       </c>
       <c r="P189">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="Q189">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="R189">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="S189">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T189">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="U189">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="V189">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="W189">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="X189">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y189">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z189">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="AA189">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AB189">
-        <v>4.67</v>
+        <v>3.5</v>
       </c>
       <c r="AC189">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AD189">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="AE189">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AF189">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AG189">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK189">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="O190">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="P190">
-        <v>4.45</v>
+        <v>2.9</v>
       </c>
       <c r="Q190">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="R190">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="S190">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T190">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="U190">
+        <v>1.55</v>
+      </c>
+      <c r="V190">
+        <v>2.25</v>
+      </c>
+      <c r="W190">
+        <v>1.38</v>
+      </c>
+      <c r="X190">
+        <v>0</v>
+      </c>
+      <c r="Y190">
+        <v>1.04</v>
+      </c>
+      <c r="Z190">
+        <v>11</v>
+      </c>
+      <c r="AA190">
+        <v>1.11</v>
+      </c>
+      <c r="AB190">
+        <v>4.67</v>
+      </c>
+      <c r="AC190">
+        <v>1.38</v>
+      </c>
+      <c r="AD190">
+        <v>2.66</v>
+      </c>
+      <c r="AE190">
         <v>1.76</v>
       </c>
-      <c r="V190">
-        <v>1.97</v>
-      </c>
-      <c r="W190">
-        <v>1.3</v>
-      </c>
-      <c r="X190">
-        <v>1.01</v>
-      </c>
-      <c r="Y190">
-        <v>1.03</v>
-      </c>
-      <c r="Z190">
-        <v>7.4</v>
-      </c>
-      <c r="AA190">
-        <v>1.28</v>
-      </c>
-      <c r="AB190">
-        <v>3.5</v>
-      </c>
-      <c r="AC190">
-        <v>1.66</v>
-      </c>
-      <c r="AD190">
-        <v>2.15</v>
-      </c>
-      <c r="AE190">
-        <v>1.5</v>
-      </c>
       <c r="AF190">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AG190">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK190">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.32</v>
+        <v>2.7</v>
       </c>
       <c r="O193">
-        <v>5.25</v>
+        <v>3.12</v>
       </c>
       <c r="P193">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="Q193">
-        <v>1.73</v>
+        <v>3.44</v>
       </c>
       <c r="R193">
-        <v>2.51</v>
+        <v>1.96</v>
       </c>
       <c r="S193">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T193">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="U193">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="V193">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="W193">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X193">
         <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="Z193">
-        <v>4.75</v>
+        <v>3.12</v>
       </c>
       <c r="AA193">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="AB193">
-        <v>2.36</v>
+        <v>1.66</v>
       </c>
       <c r="AC193">
-        <v>2.35</v>
+        <v>3.89</v>
       </c>
       <c r="AD193">
-        <v>1.54</v>
+        <v>1.2</v>
       </c>
       <c r="AE193">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF193">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG193">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK193">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="O194">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="P194">
-        <v>1.92</v>
+        <v>4.1</v>
       </c>
       <c r="Q194">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="R194">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="S194">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T194">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="U194">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="V194">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="W194">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X194">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y194">
+        <v>1.14</v>
+      </c>
+      <c r="Z194">
+        <v>5.5</v>
+      </c>
+      <c r="AA194">
+        <v>1.48</v>
+      </c>
+      <c r="AB194">
+        <v>2.62</v>
+      </c>
+      <c r="AC194">
+        <v>2.15</v>
+      </c>
+      <c r="AD194">
+        <v>1.65</v>
+      </c>
+      <c r="AE194">
         <v>1.27</v>
       </c>
-      <c r="Z194">
-        <v>3.48</v>
-      </c>
-      <c r="AA194">
-        <v>1.86</v>
-      </c>
-      <c r="AB194">
-        <v>1.97</v>
-      </c>
-      <c r="AC194">
-        <v>3.05</v>
-      </c>
-      <c r="AD194">
-        <v>1.35</v>
-      </c>
-      <c r="AE194">
-        <v>1.13</v>
-      </c>
       <c r="AF194">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AG194">
-        <v>2.04</v>
+        <v>2.53</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.8</v>
+        <v>1.19</v>
       </c>
       <c r="AK194">
-        <v>1.19</v>
+        <v>2.12</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="O195">
-        <v>3.12</v>
+        <v>5.25</v>
       </c>
       <c r="P195">
-        <v>2.6</v>
+        <v>8</v>
       </c>
       <c r="Q195">
-        <v>3.44</v>
+        <v>1.73</v>
       </c>
       <c r="R195">
-        <v>1.96</v>
+        <v>2.51</v>
       </c>
       <c r="S195">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T195">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="U195">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="V195">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="W195">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X195">
         <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="Z195">
-        <v>3.12</v>
+        <v>4.75</v>
       </c>
       <c r="AA195">
-        <v>2.09</v>
+        <v>1.6</v>
       </c>
       <c r="AB195">
-        <v>1.66</v>
+        <v>2.36</v>
       </c>
       <c r="AC195">
-        <v>3.89</v>
+        <v>2.35</v>
       </c>
       <c r="AD195">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="AE195">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF195">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG195">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK195">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
+        <v>3.7</v>
+      </c>
+      <c r="O196">
+        <v>3.5</v>
+      </c>
+      <c r="P196">
+        <v>1.92</v>
+      </c>
+      <c r="Q196">
+        <v>4</v>
+      </c>
+      <c r="R196">
+        <v>2.13</v>
+      </c>
+      <c r="S196">
+        <v>1.35</v>
+      </c>
+      <c r="T196">
+        <v>3.1</v>
+      </c>
+      <c r="U196">
+        <v>2.75</v>
+      </c>
+      <c r="V196">
+        <v>1.43</v>
+      </c>
+      <c r="W196">
+        <v>1.07</v>
+      </c>
+      <c r="X196">
+        <v>1</v>
+      </c>
+      <c r="Y196">
+        <v>1.27</v>
+      </c>
+      <c r="Z196">
+        <v>3.48</v>
+      </c>
+      <c r="AA196">
+        <v>1.86</v>
+      </c>
+      <c r="AB196">
+        <v>1.97</v>
+      </c>
+      <c r="AC196">
+        <v>3.05</v>
+      </c>
+      <c r="AD196">
+        <v>1.35</v>
+      </c>
+      <c r="AE196">
+        <v>1.13</v>
+      </c>
+      <c r="AF196">
         <v>1.7</v>
       </c>
-      <c r="O196">
-        <v>4.25</v>
-      </c>
-      <c r="P196">
-        <v>4.1</v>
-      </c>
-      <c r="Q196">
-        <v>2.1</v>
-      </c>
-      <c r="R196">
-        <v>2.5</v>
-      </c>
-      <c r="S196">
-        <v>1.2</v>
-      </c>
-      <c r="T196">
-        <v>3.78</v>
-      </c>
-      <c r="U196">
-        <v>2.14</v>
-      </c>
-      <c r="V196">
-        <v>1.64</v>
-      </c>
-      <c r="W196">
-        <v>1.18</v>
-      </c>
-      <c r="X196">
-        <v>1.02</v>
-      </c>
-      <c r="Y196">
-        <v>1.14</v>
-      </c>
-      <c r="Z196">
-        <v>5.5</v>
-      </c>
-      <c r="AA196">
-        <v>1.48</v>
-      </c>
-      <c r="AB196">
-        <v>2.62</v>
-      </c>
-      <c r="AC196">
-        <v>2.15</v>
-      </c>
-      <c r="AD196">
-        <v>1.65</v>
-      </c>
-      <c r="AE196">
-        <v>1.27</v>
-      </c>
-      <c r="AF196">
-        <v>1.45</v>
-      </c>
       <c r="AG196">
-        <v>2.53</v>
+        <v>2.04</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
+        <v>1.8</v>
+      </c>
+      <c r="AK196">
         <v>1.19</v>
-      </c>
-      <c r="AK196">
-        <v>2.12</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="O199">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P199">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="O209">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="P209">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="Q209">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R209">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S209">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T209">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U209">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="V209">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="W209">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X209">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="Z209">
-        <v>5.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA209">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="AB209">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC209">
-        <v>2.19</v>
+        <v>3.14</v>
       </c>
       <c r="AD209">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AE209">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AF209">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AG209">
-        <v>2.61</v>
+        <v>2.05</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK209">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,25 +34539,25 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="O210">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="P210">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="Q210">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="R210">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S210">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T210">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U210">
         <v>2.88</v>
@@ -34566,37 +34566,37 @@
         <v>1.36</v>
       </c>
       <c r="W210">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X210">
         <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z210">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA210">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB210">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC210">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD210">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE210">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF210">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG210">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK210">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="O211">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P211">
-        <v>2.65</v>
+        <v>4.14</v>
       </c>
       <c r="Q211">
-        <v>3.04</v>
+        <v>2.05</v>
       </c>
       <c r="R211">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="S211">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="T211">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="U211">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="V211">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="W211">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X211">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y211">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="Z211">
-        <v>2.92</v>
+        <v>5.7</v>
       </c>
       <c r="AA211">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="AB211">
-        <v>1.73</v>
+        <v>2.53</v>
       </c>
       <c r="AC211">
-        <v>3.25</v>
+        <v>2.04</v>
       </c>
       <c r="AD211">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AE211">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AF211">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AG211">
-        <v>1.95</v>
+        <v>2.47</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK211">
-        <v>1.37</v>
+        <v>2.23</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O213">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P213">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="Q213">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R213">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S213">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T213">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U213">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="V213">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W213">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X213">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y213">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z213">
-        <v>3.65</v>
+        <v>5.05</v>
       </c>
       <c r="AA213">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AB213">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="AC213">
-        <v>2.53</v>
+        <v>2.19</v>
       </c>
       <c r="AD213">
+        <v>1.65</v>
+      </c>
+      <c r="AE213">
+        <v>1.27</v>
+      </c>
+      <c r="AF213">
         <v>1.42</v>
       </c>
-      <c r="AE213">
-        <v>1.11</v>
-      </c>
-      <c r="AF213">
-        <v>1.55</v>
-      </c>
       <c r="AG213">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK213">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O214">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P214">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="Q214">
-        <v>4.7</v>
+        <v>2.88</v>
       </c>
       <c r="R214">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S214">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T214">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="U214">
         <v>2.55</v>
       </c>
       <c r="V214">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W214">
         <v>1.07</v>
       </c>
       <c r="X214">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z214">
-        <v>3.92</v>
+        <v>3.65</v>
       </c>
       <c r="AA214">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB214">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC214">
-        <v>2.95</v>
+        <v>2.53</v>
       </c>
       <c r="AD214">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE214">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF214">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AG214">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.87</v>
+        <v>1.26</v>
       </c>
       <c r="AK214">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="O215">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="P215">
-        <v>4.14</v>
+        <v>2.42</v>
       </c>
       <c r="Q215">
+        <v>4.7</v>
+      </c>
+      <c r="R215">
+        <v>2.36</v>
+      </c>
+      <c r="S215">
+        <v>1.33</v>
+      </c>
+      <c r="T215">
+        <v>2.86</v>
+      </c>
+      <c r="U215">
+        <v>2.55</v>
+      </c>
+      <c r="V215">
+        <v>1.44</v>
+      </c>
+      <c r="W215">
+        <v>1.07</v>
+      </c>
+      <c r="X215">
+        <v>1</v>
+      </c>
+      <c r="Y215">
+        <v>1.21</v>
+      </c>
+      <c r="Z215">
+        <v>3.92</v>
+      </c>
+      <c r="AA215">
+        <v>1.75</v>
+      </c>
+      <c r="AB215">
         <v>2.05</v>
       </c>
-      <c r="R215">
-        <v>2.47</v>
-      </c>
-      <c r="S215">
-        <v>1.2</v>
-      </c>
-      <c r="T215">
-        <v>4.2</v>
-      </c>
-      <c r="U215">
-        <v>1.99</v>
-      </c>
-      <c r="V215">
-        <v>1.7</v>
-      </c>
-      <c r="W215">
-        <v>1.18</v>
-      </c>
-      <c r="X215">
-        <v>1.02</v>
-      </c>
-      <c r="Y215">
-        <v>1.1</v>
-      </c>
-      <c r="Z215">
-        <v>5.7</v>
-      </c>
-      <c r="AA215">
-        <v>1.44</v>
-      </c>
-      <c r="AB215">
-        <v>2.53</v>
-      </c>
       <c r="AC215">
-        <v>2.04</v>
+        <v>2.95</v>
       </c>
       <c r="AD215">
+        <v>1.39</v>
+      </c>
+      <c r="AE215">
+        <v>1.15</v>
+      </c>
+      <c r="AF215">
         <v>1.68</v>
       </c>
-      <c r="AE215">
-        <v>1.29</v>
-      </c>
-      <c r="AF215">
-        <v>1.48</v>
-      </c>
       <c r="AG215">
-        <v>2.47</v>
+        <v>2.03</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.13</v>
+        <v>1.87</v>
       </c>
       <c r="AK215">
-        <v>2.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35855,43 +35855,43 @@
         <v>2.82</v>
       </c>
       <c r="R218">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S218">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T218">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="U218">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="V218">
         <v>1.3</v>
       </c>
       <c r="W218">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X218">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y218">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z218">
         <v>2.88</v>
       </c>
       <c r="AA218">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB218">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC218">
         <v>4.5</v>
       </c>
       <c r="AD218">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE218">
         <v>0</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="O219">
         <v>3.9</v>
       </c>
       <c r="P219">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q219">
         <v>4.1</v>
@@ -36021,7 +36021,7 @@
         <v>2.36</v>
       </c>
       <c r="S219">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T219">
         <v>3.4</v>
@@ -36033,13 +36033,13 @@
         <v>1.53</v>
       </c>
       <c r="W219">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X219">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y219">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z219">
         <v>4.43</v>
@@ -36054,7 +36054,7 @@
         <v>2.76</v>
       </c>
       <c r="AD219">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE219">
         <v>1.18</v>
@@ -36821,19 +36821,19 @@
         </is>
       </c>
       <c r="N224">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O224">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P224">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Q224">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="R224">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="S224">
         <v>1.25</v>
@@ -36842,43 +36842,43 @@
         <v>3.3</v>
       </c>
       <c r="U224">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="V224">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W224">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X224">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y224">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z224">
-        <v>4.55</v>
+        <v>5.2</v>
       </c>
       <c r="AA224">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AB224">
-        <v>2.28</v>
+        <v>2.69</v>
       </c>
       <c r="AC224">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AD224">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AE224">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF224">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AG224">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK224">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O227">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P227">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q227">
         <v>3.5</v>
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O228">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P228">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q228">
         <v>3.05</v>
@@ -37512,7 +37512,7 @@
         <v>4.4</v>
       </c>
       <c r="AA228">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB228">
         <v>2.17</v>
@@ -37636,10 +37636,10 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="O229">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P229">
         <v>2.2</v>
@@ -37802,10 +37802,10 @@
         <v>1.67</v>
       </c>
       <c r="O230">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="P230">
-        <v>3.93</v>
+        <v>4.64</v>
       </c>
       <c r="Q230">
         <v>2.12</v>
@@ -37829,13 +37829,13 @@
         <v>1.17</v>
       </c>
       <c r="X230">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y230">
         <v>1.12</v>
       </c>
       <c r="Z230">
-        <v>5.48</v>
+        <v>6</v>
       </c>
       <c r="AA230">
         <v>1.4</v>
@@ -38297,34 +38297,34 @@
         <v>5.44</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA233">
         <v>1.72</v>
@@ -38333,19 +38333,19 @@
         <v>2.07</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G242">
@@ -39755,64 +39755,64 @@
         </is>
       </c>
       <c r="N242">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="O242">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P242">
-        <v>2.65</v>
+        <v>3.13</v>
       </c>
       <c r="Q242">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="R242">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="S242">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T242">
-        <v>2.97</v>
+        <v>3.32</v>
       </c>
       <c r="U242">
-        <v>2.53</v>
+        <v>2.29</v>
       </c>
       <c r="V242">
+        <v>1.55</v>
+      </c>
+      <c r="W242">
+        <v>1.11</v>
+      </c>
+      <c r="X242">
+        <v>1.01</v>
+      </c>
+      <c r="Y242">
+        <v>1.16</v>
+      </c>
+      <c r="Z242">
+        <v>4.15</v>
+      </c>
+      <c r="AA242">
+        <v>1.64</v>
+      </c>
+      <c r="AB242">
+        <v>2.17</v>
+      </c>
+      <c r="AC242">
+        <v>2.46</v>
+      </c>
+      <c r="AD242">
         <v>1.44</v>
       </c>
-      <c r="W242">
-        <v>1.08</v>
-      </c>
-      <c r="X242">
-        <v>1.03</v>
-      </c>
-      <c r="Y242">
-        <v>1.23</v>
-      </c>
-      <c r="Z242">
-        <v>3.42</v>
-      </c>
-      <c r="AA242">
-        <v>1.88</v>
-      </c>
-      <c r="AB242">
-        <v>1.95</v>
-      </c>
-      <c r="AC242">
-        <v>3.38</v>
-      </c>
-      <c r="AD242">
-        <v>1.32</v>
-      </c>
       <c r="AE242">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF242">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG242">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK242">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,64 +39918,64 @@
         </is>
       </c>
       <c r="N243">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="O243">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P243">
-        <v>3.13</v>
+        <v>2.65</v>
       </c>
       <c r="Q243">
-        <v>2.63</v>
+        <v>2.87</v>
       </c>
       <c r="R243">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="S243">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T243">
-        <v>3.32</v>
+        <v>2.97</v>
       </c>
       <c r="U243">
-        <v>2.29</v>
+        <v>2.53</v>
       </c>
       <c r="V243">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W243">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X243">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y243">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z243">
-        <v>4.15</v>
+        <v>3.42</v>
       </c>
       <c r="AA243">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="AB243">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AC243">
-        <v>2.46</v>
+        <v>3.38</v>
       </c>
       <c r="AD243">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AE243">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF243">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG243">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK243">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="O244">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="P244">
-        <v>4.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q244">
         <v>2.92</v>
@@ -40096,10 +40096,10 @@
         <v>2</v>
       </c>
       <c r="S244">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T244">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U244">
         <v>3</v>
@@ -40138,7 +40138,7 @@
         <v>1.88</v>
       </c>
       <c r="AG244">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40244,16 +40244,16 @@
         </is>
       </c>
       <c r="N245">
+        <v>2.6</v>
+      </c>
+      <c r="O245">
+        <v>3</v>
+      </c>
+      <c r="P245">
         <v>2.5</v>
       </c>
-      <c r="O245">
-        <v>3.3</v>
-      </c>
-      <c r="P245">
-        <v>2.41</v>
-      </c>
       <c r="Q245">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="R245">
         <v>2.01</v>
@@ -40262,7 +40262,7 @@
         <v>1.37</v>
       </c>
       <c r="T245">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U245">
         <v>2.88</v>
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="O246">
         <v>3.1</v>
       </c>
       <c r="P246">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q246">
         <v>3.27</v>
@@ -40437,7 +40437,7 @@
         <v>1.05</v>
       </c>
       <c r="X246">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y246">
         <v>1.4</v>
@@ -40464,7 +40464,7 @@
         <v>1.9</v>
       </c>
       <c r="AG246">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>3.5</v>
       </c>
       <c r="P247">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q247">
         <v>2.33</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O248">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P248">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q248">
         <v>2.7</v>
@@ -40754,7 +40754,7 @@
         <v>2.48</v>
       </c>
       <c r="U248">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V248">
         <v>1.3</v>
@@ -40775,7 +40775,7 @@
         <v>2.2</v>
       </c>
       <c r="AB248">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC248">
         <v>4.05</v>
@@ -40938,7 +40938,7 @@
         <v>1.9</v>
       </c>
       <c r="AB249">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC249">
         <v>3.04</v>
@@ -41113,10 +41113,10 @@
         <v>1.06</v>
       </c>
       <c r="AF250">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG250">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41222,10 +41222,10 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="O251">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P251">
         <v>4</v>
@@ -41261,10 +41261,10 @@
         <v>0</v>
       </c>
       <c r="AA251">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB251">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC251">
         <v>0</v>
@@ -41391,13 +41391,13 @@
         <v>3.5</v>
       </c>
       <c r="P252">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q252">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R252">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S252">
         <v>1.29</v>
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.88</v>
+        <v>1.12</v>
       </c>
       <c r="O259">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="P259">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="Q259">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="R259">
-        <v>2.25</v>
+        <v>3.09</v>
       </c>
       <c r="S259">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T259">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="U259">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="V259">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="W259">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X259">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y259">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="Z259">
-        <v>4</v>
+        <v>6.55</v>
       </c>
       <c r="AA259">
-        <v>1.71</v>
+        <v>1.27</v>
       </c>
       <c r="AB259">
-        <v>2.08</v>
+        <v>3.14</v>
       </c>
       <c r="AC259">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="AD259">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AE259">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AF259">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG259">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK259">
-        <v>1.88</v>
+        <v>5.35</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>1.12</v>
+        <v>1.88</v>
       </c>
       <c r="O260">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="P260">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="Q260">
+        <v>2.38</v>
+      </c>
+      <c r="R260">
+        <v>2.25</v>
+      </c>
+      <c r="S260">
+        <v>1.3</v>
+      </c>
+      <c r="T260">
+        <v>3.25</v>
+      </c>
+      <c r="U260">
+        <v>2.5</v>
+      </c>
+      <c r="V260">
+        <v>1.5</v>
+      </c>
+      <c r="W260">
+        <v>1.06</v>
+      </c>
+      <c r="X260">
+        <v>1.03</v>
+      </c>
+      <c r="Y260">
+        <v>1.17</v>
+      </c>
+      <c r="Z260">
+        <v>4</v>
+      </c>
+      <c r="AA260">
+        <v>1.71</v>
+      </c>
+      <c r="AB260">
+        <v>2.08</v>
+      </c>
+      <c r="AC260">
+        <v>2.66</v>
+      </c>
+      <c r="AD260">
         <v>1.44</v>
       </c>
-      <c r="R260">
-        <v>3.09</v>
-      </c>
-      <c r="S260">
-        <v>1.18</v>
-      </c>
-      <c r="T260">
-        <v>4.5</v>
-      </c>
-      <c r="U260">
-        <v>1.86</v>
-      </c>
-      <c r="V260">
-        <v>1.9</v>
-      </c>
-      <c r="W260">
-        <v>1.22</v>
-      </c>
-      <c r="X260">
-        <v>1.01</v>
-      </c>
-      <c r="Y260">
-        <v>1.05</v>
-      </c>
-      <c r="Z260">
-        <v>6.55</v>
-      </c>
-      <c r="AA260">
-        <v>1.27</v>
-      </c>
-      <c r="AB260">
-        <v>3.14</v>
-      </c>
-      <c r="AC260">
-        <v>1.81</v>
-      </c>
-      <c r="AD260">
-        <v>1.93</v>
-      </c>
       <c r="AE260">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AF260">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG260">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK260">
-        <v>5.35</v>
+        <v>1.88</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -43024,55 +43024,55 @@
         <v>0</v>
       </c>
       <c r="Q262">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R262">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S262">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T262">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="U262">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="V262">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W262">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X262">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y262">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z262">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA262">
         <v>1.9</v>
       </c>
       <c r="AB262">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC262">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD262">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE262">
         <v>1.06</v>
       </c>
       <c r="AF262">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG262">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK262">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43187,55 +43187,55 @@
         <v>3.3</v>
       </c>
       <c r="Q263">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R263">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S263">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T263">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U263">
-        <v>2.99</v>
+        <v>2.78</v>
       </c>
       <c r="V263">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W263">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X263">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y263">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z263">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA263">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AB263">
         <v>1.7</v>
       </c>
       <c r="AC263">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD263">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE263">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF263">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG263">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK263">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43341,10 +43341,10 @@
         </is>
       </c>
       <c r="N264">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="O264">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P264">
         <v>2.26</v>
@@ -43356,10 +43356,10 @@
         <v>2.3</v>
       </c>
       <c r="S264">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T264">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U264">
         <v>2.27</v>
@@ -43371,34 +43371,34 @@
         <v>1.11</v>
       </c>
       <c r="X264">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y264">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z264">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA264">
         <v>1.58</v>
       </c>
       <c r="AB264">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AC264">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="AD264">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE264">
         <v>1.18</v>
       </c>
       <c r="AF264">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG264">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G265">
@@ -43504,64 +43504,64 @@
         </is>
       </c>
       <c r="N265">
-        <v>5.75</v>
+        <v>2.15</v>
       </c>
       <c r="O265">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="P265">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="Q265">
-        <v>5.95</v>
+        <v>2.84</v>
       </c>
       <c r="R265">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="S265">
+        <v>1.4</v>
+      </c>
+      <c r="T265">
+        <v>2.75</v>
+      </c>
+      <c r="U265">
+        <v>3.2</v>
+      </c>
+      <c r="V265">
+        <v>1.3</v>
+      </c>
+      <c r="W265">
+        <v>1.06</v>
+      </c>
+      <c r="X265">
+        <v>1.03</v>
+      </c>
+      <c r="Y265">
         <v>1.33</v>
       </c>
-      <c r="T265">
-        <v>3.25</v>
-      </c>
-      <c r="U265">
-        <v>2.35</v>
-      </c>
-      <c r="V265">
-        <v>1.51</v>
-      </c>
-      <c r="W265">
-        <v>1.12</v>
-      </c>
-      <c r="X265">
-        <v>1.01</v>
-      </c>
-      <c r="Y265">
-        <v>1.17</v>
-      </c>
       <c r="Z265">
+        <v>2.9</v>
+      </c>
+      <c r="AA265">
+        <v>2.15</v>
+      </c>
+      <c r="AB265">
+        <v>1.67</v>
+      </c>
+      <c r="AC265">
         <v>4.1</v>
       </c>
-      <c r="AA265">
-        <v>1.68</v>
-      </c>
-      <c r="AB265">
-        <v>2.09</v>
-      </c>
-      <c r="AC265">
-        <v>2.62</v>
-      </c>
       <c r="AD265">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AE265">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF265">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG265">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK265">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.15</v>
+        <v>5.75</v>
       </c>
       <c r="O266">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="P266">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="Q266">
-        <v>2.84</v>
+        <v>5.95</v>
       </c>
       <c r="R266">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="S266">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T266">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U266">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="V266">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="W266">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X266">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y266">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z266">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA266">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AB266">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="AC266">
-        <v>4.1</v>
+        <v>2.62</v>
       </c>
       <c r="AD266">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AE266">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF266">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG266">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK266">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -45137,7 +45137,7 @@
         <v>4.33</v>
       </c>
       <c r="O275">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P275">
         <v>1.61</v>
@@ -45164,13 +45164,13 @@
         <v>1.13</v>
       </c>
       <c r="X275">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y275">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z275">
-        <v>4.71</v>
+        <v>5.5</v>
       </c>
       <c r="AA275">
         <v>1.54</v>
@@ -45182,16 +45182,16 @@
         <v>2.36</v>
       </c>
       <c r="AD275">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE275">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF275">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG275">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -47099,43 +47099,43 @@
         <v>0</v>
       </c>
       <c r="Q287">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="R287">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S287">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T287">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="U287">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="V287">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W287">
         <v>1.05</v>
       </c>
       <c r="X287">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y287">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z287">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA287">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AB287">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC287">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AD287">
         <v>1.22</v>
@@ -47144,7 +47144,7 @@
         <v>1.05</v>
       </c>
       <c r="AF287">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG287">
         <v>1.85</v>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK287">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47416,19 +47416,19 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O289">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="P289">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="Q289">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="R289">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S289">
         <v>1.33</v>
@@ -47437,7 +47437,7 @@
         <v>2.92</v>
       </c>
       <c r="U289">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V289">
         <v>1.47</v>
@@ -47446,13 +47446,13 @@
         <v>1.1</v>
       </c>
       <c r="X289">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y289">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z289">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA289">
         <v>1.82</v>
@@ -47470,10 +47470,10 @@
         <v>1.09</v>
       </c>
       <c r="AF289">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG289">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK289">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47594,10 +47594,10 @@
         <v>2.12</v>
       </c>
       <c r="S290">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T290">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U290">
         <v>2.75</v>
@@ -47606,7 +47606,7 @@
         <v>1.45</v>
       </c>
       <c r="W290">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X290">
         <v>1</v>
@@ -47630,7 +47630,7 @@
         <v>1.36</v>
       </c>
       <c r="AE290">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF290">
         <v>1.66</v>
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="O294">
         <v>3.63</v>
       </c>
       <c r="P294">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="Q294">
         <v>2.38</v>
@@ -48261,13 +48261,13 @@
         <v>1.14</v>
       </c>
       <c r="X294">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y294">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z294">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA294">
         <v>1.6</v>
@@ -48276,7 +48276,7 @@
         <v>2.3</v>
       </c>
       <c r="AC294">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AD294">
         <v>1.5</v>
@@ -48285,7 +48285,7 @@
         <v>1.2</v>
       </c>
       <c r="AF294">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG294">
         <v>2.38</v>
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="O304">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P304">
-        <v>4.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q304">
         <v>1.95</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O305">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P305">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50226,7 +50226,7 @@
         <v>7.16</v>
       </c>
       <c r="AA306">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB306">
         <v>2.91</v>
@@ -50257,7 +50257,7 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK306">
         <v>2.63</v>
@@ -53453,7 +53453,7 @@
         <v>3.45</v>
       </c>
       <c r="P326">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q326">
         <v>3.62</v>
@@ -53486,10 +53486,10 @@
         <v>3.5</v>
       </c>
       <c r="AA326">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB326">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC326">
         <v>2.88</v>
@@ -54262,7 +54262,7 @@
         </is>
       </c>
       <c r="N331">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O331">
         <v>3.3</v>
@@ -55460,7 +55460,7 @@
         <v>1.43</v>
       </c>
       <c r="AG338">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>0</v>
       </c>
       <c r="Q340">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R340">
         <v>2.38</v>
@@ -55768,16 +55768,16 @@
         <v>4.45</v>
       </c>
       <c r="AA340">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB340">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AC340">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="AD340">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE340">
         <v>1.14</v>
@@ -55799,10 +55799,10 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK340">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL340">
         <v>0</v>
@@ -55892,13 +55892,13 @@
         </is>
       </c>
       <c r="N341">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="O341">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="P341">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="Q341">
         <v>1.89</v>
@@ -55913,7 +55913,7 @@
         <v>3.15</v>
       </c>
       <c r="U341">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V341">
         <v>1.43</v>
@@ -55928,7 +55928,7 @@
         <v>1.28</v>
       </c>
       <c r="Z341">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="AA341">
         <v>1.87</v>
@@ -55937,13 +55937,13 @@
         <v>1.95</v>
       </c>
       <c r="AC341">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="AD341">
         <v>1.36</v>
       </c>
       <c r="AE341">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF341">
         <v>2.09</v>
@@ -55965,7 +55965,7 @@
         <v>1.11</v>
       </c>
       <c r="AK341">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AL341">
         <v>0</v>
@@ -56055,10 +56055,10 @@
         </is>
       </c>
       <c r="N342">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="O342">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="P342">
         <v>3.1</v>
@@ -56088,13 +56088,13 @@
         <v>1</v>
       </c>
       <c r="Y342">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z342">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA342">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB342">
         <v>2.6</v>
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="O343">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P343">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q343">
         <v>3.3</v>
@@ -56260,7 +56260,7 @@
         <v>1.9</v>
       </c>
       <c r="AB343">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC343">
         <v>3.19</v>
@@ -56275,7 +56275,7 @@
         <v>1.66</v>
       </c>
       <c r="AG343">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH343" t="inlineStr">
         <is>
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G362">
@@ -59315,64 +59315,64 @@
         </is>
       </c>
       <c r="N362">
-        <v>1.53</v>
+        <v>2.55</v>
       </c>
       <c r="O362">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P362">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q362">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R362">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S362">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T362">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U362">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V362">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W362">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X362">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y362">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z362">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA362">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB362">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC362">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD362">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE362">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF362">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG362">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH362" t="inlineStr">
         <is>
@@ -59385,10 +59385,10 @@
         </is>
       </c>
       <c r="AJ362">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK362">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL362">
         <v>0</v>
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G363">
@@ -59478,64 +59478,64 @@
         </is>
       </c>
       <c r="N363">
-        <v>2.55</v>
+        <v>1.99</v>
       </c>
       <c r="O363">
         <v>3.2</v>
       </c>
       <c r="P363">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q363">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R363">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S363">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T363">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U363">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V363">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W363">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X363">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y363">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z363">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA363">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB363">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC363">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD363">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE363">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF363">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG363">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH363" t="inlineStr">
         <is>
@@ -59548,10 +59548,10 @@
         </is>
       </c>
       <c r="AJ363">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK363">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL363">
         <v>0</v>
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G364">
@@ -59641,64 +59641,64 @@
         </is>
       </c>
       <c r="N364">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="O364">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="P364">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="Q364">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="R364">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="S364">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T364">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="U364">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="V364">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W364">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X364">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y364">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z364">
-        <v>2.97</v>
+        <v>3.92</v>
       </c>
       <c r="AA364">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AB364">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC364">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="AD364">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AE364">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF364">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AG364">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="AH364" t="inlineStr">
         <is>
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G366">
@@ -59967,31 +59967,31 @@
         </is>
       </c>
       <c r="N366">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="O366">
-        <v>3.52</v>
+        <v>3.9</v>
       </c>
       <c r="P366">
-        <v>3.51</v>
+        <v>5.4</v>
       </c>
       <c r="Q366">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="R366">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="S366">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T366">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="U366">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="V366">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W366">
         <v>1.11</v>
@@ -60000,31 +60000,31 @@
         <v>1.02</v>
       </c>
       <c r="Y366">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z366">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AA366">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB366">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC366">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD366">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE366">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF366">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG366">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="AH366" t="inlineStr">
         <is>
@@ -60037,10 +60037,10 @@
         </is>
       </c>
       <c r="AJ366">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK366">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="AL366">
         <v>0</v>
@@ -61923,13 +61923,13 @@
         </is>
       </c>
       <c r="N378">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="O378">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="P378">
-        <v>5.36</v>
+        <v>6.1</v>
       </c>
       <c r="Q378">
         <v>1.73</v>
@@ -61950,7 +61950,7 @@
         <v>1.74</v>
       </c>
       <c r="W378">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X378">
         <v>1.01</v>
@@ -65090,7 +65090,7 @@
         </is>
       </c>
       <c r="AJ397">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK397">
         <v>2.1</v>

--- a/jogos_2026-10-24.xlsx
+++ b/jogos_2026-10-24.xlsx
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
         <v>3.08</v>
       </c>
       <c r="Q3">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="R3">
         <v>2.19</v>
@@ -834,7 +834,7 @@
         <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="AA3">
         <v>1.74</v>
@@ -970,16 +970,16 @@
         <v>4</v>
       </c>
       <c r="Q4">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
         <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="U4">
         <v>2.88</v>
@@ -997,25 +997,25 @@
         <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA4">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB4">
         <v>1.76</v>
       </c>
       <c r="AC4">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="AD4">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
         <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG4">
         <v>1.9</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="Q5">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R5">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S5">
+        <v>1.44</v>
+      </c>
+      <c r="T5">
+        <v>2.45</v>
+      </c>
+      <c r="U5">
+        <v>2.94</v>
+      </c>
+      <c r="V5">
+        <v>1.33</v>
+      </c>
+      <c r="W5">
+        <v>1.06</v>
+      </c>
+      <c r="X5">
+        <v>1.04</v>
+      </c>
+      <c r="Y5">
         <v>1.36</v>
       </c>
-      <c r="T5">
-        <v>2.82</v>
-      </c>
-      <c r="U5">
-        <v>2.75</v>
-      </c>
-      <c r="V5">
-        <v>1.4</v>
-      </c>
-      <c r="W5">
-        <v>1.1</v>
-      </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
-      <c r="Y5">
-        <v>1.26</v>
-      </c>
       <c r="Z5">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="AA5">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AB5">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AC5">
-        <v>3.12</v>
+        <v>4.1</v>
       </c>
       <c r="AD5">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AE5">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK5">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
-        <v>3.44</v>
+        <v>4.46</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S6">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="U6">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z6">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AA6">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB6">
         <v>1.91</v>
       </c>
       <c r="AC6">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AD6">
         <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AK6">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S7">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="U7">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AA7">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB7">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AK7">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="Q8">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R8">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>2.45</v>
+        <v>2.82</v>
       </c>
       <c r="U8">
-        <v>2.93</v>
+        <v>2.76</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
+        <v>1.27</v>
+      </c>
+      <c r="Z8">
+        <v>3.6</v>
+      </c>
+      <c r="AA8">
+        <v>1.79</v>
+      </c>
+      <c r="AB8">
+        <v>1.88</v>
+      </c>
+      <c r="AC8">
+        <v>3.14</v>
+      </c>
+      <c r="AD8">
         <v>1.36</v>
       </c>
-      <c r="Z8">
-        <v>2.7</v>
-      </c>
-      <c r="AA8">
-        <v>2.19</v>
-      </c>
-      <c r="AB8">
-        <v>1.63</v>
-      </c>
-      <c r="AC8">
-        <v>4.1</v>
-      </c>
-      <c r="AD8">
-        <v>1.18</v>
-      </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O11">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="P11">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="Q11">
         <v>4.83</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.3</v>
+        <v>3.01</v>
       </c>
       <c r="O16">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="Q16">
-        <v>2.83</v>
+        <v>3.83</v>
       </c>
       <c r="R16">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="S16">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="T16">
-        <v>2.57</v>
+        <v>2.29</v>
       </c>
       <c r="U16">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
+        <v>1.04</v>
+      </c>
+      <c r="X16">
         <v>1.07</v>
       </c>
-      <c r="X16">
-        <v>1.05</v>
-      </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="Z16">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="AA16">
-        <v>2.14</v>
+        <v>2.61</v>
       </c>
       <c r="AB16">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AC16">
-        <v>3.72</v>
+        <v>5.5</v>
       </c>
       <c r="AD16">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF16">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG16">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.01</v>
+        <v>2.3</v>
       </c>
       <c r="O17">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="P17">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="Q17">
-        <v>3.83</v>
+        <v>2.83</v>
       </c>
       <c r="R17">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="S17">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.29</v>
+        <v>2.57</v>
       </c>
       <c r="U17">
-        <v>3.6</v>
+        <v>2.86</v>
       </c>
       <c r="V17">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
+        <v>1.07</v>
+      </c>
+      <c r="X17">
+        <v>1.05</v>
+      </c>
+      <c r="Y17">
+        <v>1.33</v>
+      </c>
+      <c r="Z17">
+        <v>2.9</v>
+      </c>
+      <c r="AA17">
+        <v>2.14</v>
+      </c>
+      <c r="AB17">
+        <v>1.66</v>
+      </c>
+      <c r="AC17">
+        <v>3.72</v>
+      </c>
+      <c r="AD17">
+        <v>1.2</v>
+      </c>
+      <c r="AE17">
         <v>1.04</v>
       </c>
-      <c r="X17">
-        <v>1.07</v>
-      </c>
-      <c r="Y17">
-        <v>1.55</v>
-      </c>
-      <c r="Z17">
-        <v>2.48</v>
-      </c>
-      <c r="AA17">
-        <v>2.61</v>
-      </c>
-      <c r="AB17">
-        <v>1.46</v>
-      </c>
-      <c r="AC17">
-        <v>5.5</v>
-      </c>
-      <c r="AD17">
-        <v>1.12</v>
-      </c>
-      <c r="AE17">
-        <v>1.02</v>
-      </c>
       <c r="AF17">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK17">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3415,34 +3415,34 @@
         <v>1.85</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA19">
         <v>1.88</v>
@@ -3451,19 +3451,19 @@
         <v>1.85</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O20">
         <v>3.5</v>
       </c>
       <c r="P20">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
         <v>3.23</v>
       </c>
       <c r="R20">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
         <v>1.29</v>
@@ -3605,22 +3605,22 @@
         <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.74</v>
+        <v>4.33</v>
       </c>
       <c r="AA20">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB20">
         <v>2.07</v>
       </c>
       <c r="AC20">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD20">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
         <v>1.57</v>
@@ -3642,7 +3642,7 @@
         <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.4</v>
+        <v>1.09</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="P21">
-        <v>2.54</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>2.99</v>
+        <v>1.62</v>
       </c>
       <c r="R21">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="S21">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="U21">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="V21">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>4.69</v>
+        <v>4.8</v>
       </c>
       <c r="AA21">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AC21">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AD21">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>2.11</v>
       </c>
       <c r="AG21">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK21">
-        <v>1.37</v>
+        <v>3.86</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.09</v>
+        <v>2.45</v>
       </c>
       <c r="O22">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>9.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q22">
+        <v>2.97</v>
+      </c>
+      <c r="R22">
+        <v>2.2</v>
+      </c>
+      <c r="S22">
+        <v>1.24</v>
+      </c>
+      <c r="T22">
+        <v>3.75</v>
+      </c>
+      <c r="U22">
+        <v>2.18</v>
+      </c>
+      <c r="V22">
         <v>1.62</v>
       </c>
-      <c r="R22">
-        <v>2.57</v>
-      </c>
-      <c r="S22">
-        <v>1.22</v>
-      </c>
-      <c r="T22">
-        <v>3.46</v>
-      </c>
-      <c r="U22">
-        <v>2.25</v>
-      </c>
-      <c r="V22">
-        <v>1.57</v>
-      </c>
       <c r="W22">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z22">
-        <v>4.8</v>
+        <v>4.98</v>
       </c>
       <c r="AA22">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB22">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AC22">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AD22">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AE22">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>2.11</v>
+        <v>1.44</v>
       </c>
       <c r="AG22">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK22">
-        <v>3.86</v>
+        <v>1.37</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O23">
         <v>3.9</v>
       </c>
       <c r="P23">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q23">
         <v>3.58</v>
@@ -4079,13 +4079,13 @@
         <v>4.5</v>
       </c>
       <c r="U23">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="V23">
         <v>1.72</v>
       </c>
       <c r="W23">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X23">
         <v>1</v>
@@ -4103,7 +4103,7 @@
         <v>2.7</v>
       </c>
       <c r="AC23">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AD23">
         <v>1.76</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O24">
-        <v>3.47</v>
+        <v>4.2</v>
       </c>
       <c r="P24">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q24">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="S24">
+        <v>1.15</v>
+      </c>
+      <c r="T24">
+        <v>5</v>
+      </c>
+      <c r="U24">
+        <v>1.73</v>
+      </c>
+      <c r="V24">
+        <v>2</v>
+      </c>
+      <c r="W24">
+        <v>1.27</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1.04</v>
+      </c>
+      <c r="Z24">
+        <v>8.5</v>
+      </c>
+      <c r="AA24">
         <v>1.22</v>
       </c>
-      <c r="T24">
-        <v>3.6</v>
-      </c>
-      <c r="U24">
-        <v>2.23</v>
-      </c>
-      <c r="V24">
-        <v>1.57</v>
-      </c>
-      <c r="W24">
-        <v>1.13</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>1.17</v>
-      </c>
-      <c r="Z24">
-        <v>4.54</v>
-      </c>
-      <c r="AA24">
-        <v>1.62</v>
-      </c>
       <c r="AB24">
-        <v>2.33</v>
+        <v>4.2</v>
       </c>
       <c r="AC24">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AD24">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="AE24">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AG24">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O25">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="Q25">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="R25">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="S25">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="U25">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="V25">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>8.5</v>
+        <v>4.54</v>
       </c>
       <c r="AA25">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AB25">
-        <v>4.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC25">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="AD25">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE25">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AF25">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>2.8</v>
       </c>
       <c r="O26">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q26">
         <v>3.54</v>
@@ -4592,7 +4592,7 @@
         <v>2.52</v>
       </c>
       <c r="AC26">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AD26">
         <v>1.65</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O27">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -4755,10 +4755,10 @@
         <v>3.25</v>
       </c>
       <c r="AC27">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AD27">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE27">
         <v>1.33</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="O28">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
         <v>4.2</v>
       </c>
       <c r="Q28">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S28">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
         <v>2.88</v>
       </c>
       <c r="U28">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V28">
         <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA28">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AB28">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC28">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD28">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>4.3</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="R33">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T33">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>3.71</v>
+        <v>2.88</v>
       </c>
       <c r="AA33">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB33">
+        <v>1.66</v>
+      </c>
+      <c r="AC33">
+        <v>3.82</v>
+      </c>
+      <c r="AD33">
+        <v>1.18</v>
+      </c>
+      <c r="AE33">
+        <v>1.02</v>
+      </c>
+      <c r="AF33">
         <v>1.85</v>
       </c>
-      <c r="AC33">
-        <v>3.14</v>
-      </c>
-      <c r="AD33">
-        <v>1.27</v>
-      </c>
-      <c r="AE33">
-        <v>1.07</v>
-      </c>
-      <c r="AF33">
-        <v>1.75</v>
-      </c>
       <c r="AG33">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q34">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="R34">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U34">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="V34">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>2.88</v>
+        <v>3.71</v>
       </c>
       <c r="AA34">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AB34">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
-        <v>3.82</v>
+        <v>3.14</v>
       </c>
       <c r="AD34">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7007,16 +7007,16 @@
         <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
         <v>3.2</v>
       </c>
       <c r="U41">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W41">
         <v>1.1</v>
@@ -7025,10 +7025,10 @@
         <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA41">
         <v>1.81</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="O56">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P56">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="Q56">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="R56">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="S56">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U56">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V56">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
-        <v>5.94</v>
+        <v>5.5</v>
       </c>
       <c r="AA56">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB56">
-        <v>2.76</v>
+        <v>2.43</v>
       </c>
       <c r="AC56">
-        <v>2.04</v>
+        <v>2.37</v>
       </c>
       <c r="AD56">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE56">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF56">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG56">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="O58">
+        <v>4.2</v>
+      </c>
+      <c r="P58">
+        <v>3.47</v>
+      </c>
+      <c r="Q58">
+        <v>2.12</v>
+      </c>
+      <c r="R58">
+        <v>2.5</v>
+      </c>
+      <c r="S58">
+        <v>1.18</v>
+      </c>
+      <c r="T58">
         <v>4</v>
       </c>
-      <c r="P58">
-        <v>3.43</v>
-      </c>
-      <c r="Q58">
-        <v>2.13</v>
-      </c>
-      <c r="R58">
-        <v>2.35</v>
-      </c>
-      <c r="S58">
-        <v>1.22</v>
-      </c>
-      <c r="T58">
-        <v>3.55</v>
-      </c>
       <c r="U58">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V58">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="W58">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z58">
-        <v>5.5</v>
+        <v>5.94</v>
       </c>
       <c r="AA58">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AB58">
-        <v>2.43</v>
+        <v>2.76</v>
       </c>
       <c r="AC58">
-        <v>2.37</v>
+        <v>2.04</v>
       </c>
       <c r="AD58">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AE58">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF58">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG58">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK58">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9956,7 +9956,7 @@
         <v>1.06</v>
       </c>
       <c r="X59">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
         <v>1.33</v>
@@ -9968,22 +9968,22 @@
         <v>2.05</v>
       </c>
       <c r="AB59">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC59">
         <v>3.5</v>
       </c>
       <c r="AD59">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE59">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF59">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG59">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,65 +11067,65 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="O66">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P66">
-        <v>3.32</v>
+        <v>4.9</v>
       </c>
       <c r="Q66">
-        <v>2.64</v>
+        <v>1.95</v>
       </c>
       <c r="R66">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="S66">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="T66">
-        <v>2.71</v>
+        <v>3.6</v>
       </c>
       <c r="U66">
-        <v>3.22</v>
+        <v>2.43</v>
       </c>
       <c r="V66">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="W66">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X66">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z66">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA66">
+        <v>1.61</v>
+      </c>
+      <c r="AB66">
+        <v>2.3</v>
+      </c>
+      <c r="AC66">
+        <v>2.58</v>
+      </c>
+      <c r="AD66">
+        <v>1.5</v>
+      </c>
+      <c r="AE66">
+        <v>1.15</v>
+      </c>
+      <c r="AF66">
+        <v>1.67</v>
+      </c>
+      <c r="AG66">
         <v>2.14</v>
       </c>
-      <c r="AB66">
-        <v>1.65</v>
-      </c>
-      <c r="AC66">
-        <v>4.2</v>
-      </c>
-      <c r="AD66">
-        <v>1.22</v>
-      </c>
-      <c r="AE66">
-        <v>1.07</v>
-      </c>
-      <c r="AF66">
-        <v>1.9</v>
-      </c>
-      <c r="AG66">
-        <v>1.87</v>
-      </c>
       <c r="AH66" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK66">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="O67">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>4.9</v>
+        <v>3.32</v>
       </c>
       <c r="Q67">
-        <v>1.95</v>
+        <v>2.64</v>
       </c>
       <c r="R67">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="S67">
+        <v>1.44</v>
+      </c>
+      <c r="T67">
+        <v>2.71</v>
+      </c>
+      <c r="U67">
+        <v>3.22</v>
+      </c>
+      <c r="V67">
+        <v>1.33</v>
+      </c>
+      <c r="W67">
+        <v>1.05</v>
+      </c>
+      <c r="X67">
+        <v>1.06</v>
+      </c>
+      <c r="Y67">
+        <v>1.36</v>
+      </c>
+      <c r="Z67">
+        <v>3.1</v>
+      </c>
+      <c r="AA67">
+        <v>2.14</v>
+      </c>
+      <c r="AB67">
+        <v>1.65</v>
+      </c>
+      <c r="AC67">
+        <v>4.2</v>
+      </c>
+      <c r="AD67">
         <v>1.22</v>
       </c>
-      <c r="T67">
-        <v>3.6</v>
-      </c>
-      <c r="U67">
-        <v>2.43</v>
-      </c>
-      <c r="V67">
-        <v>1.6</v>
-      </c>
-      <c r="W67">
-        <v>1.12</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.2</v>
-      </c>
-      <c r="Z67">
-        <v>4.5</v>
-      </c>
-      <c r="AA67">
-        <v>1.61</v>
-      </c>
-      <c r="AB67">
-        <v>2.3</v>
-      </c>
-      <c r="AC67">
-        <v>2.58</v>
-      </c>
-      <c r="AD67">
-        <v>1.5</v>
-      </c>
       <c r="AE67">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF67">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG67">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK67">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q72">
-        <v>2.94</v>
+        <v>5.02</v>
       </c>
       <c r="R72">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="S72">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="T72">
-        <v>2.31</v>
+        <v>2.76</v>
       </c>
       <c r="U72">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="V72">
+        <v>1.41</v>
+      </c>
+      <c r="W72">
+        <v>1.05</v>
+      </c>
+      <c r="X72">
+        <v>1.01</v>
+      </c>
+      <c r="Y72">
         <v>1.26</v>
       </c>
-      <c r="W72">
-        <v>1.03</v>
-      </c>
-      <c r="X72">
-        <v>1.07</v>
-      </c>
-      <c r="Y72">
-        <v>1.47</v>
-      </c>
       <c r="Z72">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="AA72">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="AB72">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC72">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD72">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AE72">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF72">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="AG72">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK72">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.99</v>
+        <v>1.88</v>
       </c>
       <c r="O73">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="P73">
-        <v>1.78</v>
+        <v>3.58</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA73">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AB73">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA74">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AB74">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -16458,7 +16458,7 @@
         <v>3.38</v>
       </c>
       <c r="R99">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S99">
         <v>1.36</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="O101">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P101">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="Q101">
         <v>3.8</v>
@@ -16793,13 +16793,13 @@
         <v>4.55</v>
       </c>
       <c r="U101">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V101">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="W101">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X101">
         <v>1.01</v>
@@ -16823,7 +16823,7 @@
         <v>2.1</v>
       </c>
       <c r="AE101">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF101">
         <v>1.3</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,25 +19217,25 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.85</v>
+        <v>2.91</v>
       </c>
       <c r="O116">
-        <v>3.54</v>
+        <v>2.9</v>
       </c>
       <c r="P116">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="Q116">
-        <v>2.5</v>
+        <v>3.68</v>
       </c>
       <c r="R116">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="S116">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T116">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U116">
         <v>2.88</v>
@@ -19244,37 +19244,37 @@
         <v>1.36</v>
       </c>
       <c r="W116">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z116">
-        <v>3.38</v>
+        <v>2.92</v>
       </c>
       <c r="AA116">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AB116">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC116">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AD116">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE116">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG116">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AK116">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.91</v>
+        <v>2.17</v>
       </c>
       <c r="O117">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P117">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="Q117">
-        <v>3.68</v>
+        <v>2.75</v>
       </c>
       <c r="R117">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="S117">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T117">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="U117">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V117">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W117">
+        <v>1.06</v>
+      </c>
+      <c r="X117">
+        <v>1.01</v>
+      </c>
+      <c r="Y117">
+        <v>1.35</v>
+      </c>
+      <c r="Z117">
+        <v>3.08</v>
+      </c>
+      <c r="AA117">
+        <v>2.08</v>
+      </c>
+      <c r="AB117">
+        <v>1.77</v>
+      </c>
+      <c r="AC117">
+        <v>3.34</v>
+      </c>
+      <c r="AD117">
+        <v>1.24</v>
+      </c>
+      <c r="AE117">
         <v>1.05</v>
       </c>
-      <c r="X117">
-        <v>1.03</v>
-      </c>
-      <c r="Y117">
-        <v>1.31</v>
-      </c>
-      <c r="Z117">
-        <v>2.92</v>
-      </c>
-      <c r="AA117">
-        <v>2.15</v>
-      </c>
-      <c r="AB117">
-        <v>1.65</v>
-      </c>
-      <c r="AC117">
-        <v>4.1</v>
-      </c>
-      <c r="AD117">
-        <v>1.22</v>
-      </c>
-      <c r="AE117">
-        <v>1.04</v>
-      </c>
       <c r="AF117">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG117">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AK117">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="O118">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P118">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="Q118">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R118">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S118">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T118">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U118">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V118">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W118">
         <v>1.06</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y118">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z118">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="AA118">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AB118">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC118">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD118">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE118">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF118">
         <v>1.8</v>
       </c>
       <c r="AG118">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK118">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,80 +20847,80 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="O126">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="P126">
-        <v>3.1</v>
+        <v>4.35</v>
       </c>
       <c r="Q126">
+        <v>2.2</v>
+      </c>
+      <c r="R126">
+        <v>2.3</v>
+      </c>
+      <c r="S126">
+        <v>1.31</v>
+      </c>
+      <c r="T126">
+        <v>2.82</v>
+      </c>
+      <c r="U126">
+        <v>2.62</v>
+      </c>
+      <c r="V126">
+        <v>1.44</v>
+      </c>
+      <c r="W126">
+        <v>1.08</v>
+      </c>
+      <c r="X126">
+        <v>1.03</v>
+      </c>
+      <c r="Y126">
+        <v>1.2</v>
+      </c>
+      <c r="Z126">
+        <v>3.71</v>
+      </c>
+      <c r="AA126">
+        <v>1.78</v>
+      </c>
+      <c r="AB126">
+        <v>1.98</v>
+      </c>
+      <c r="AC126">
         <v>2.7</v>
       </c>
-      <c r="R126">
-        <v>2.08</v>
-      </c>
-      <c r="S126">
-        <v>1.33</v>
-      </c>
-      <c r="T126">
-        <v>3.1</v>
-      </c>
-      <c r="U126">
-        <v>2.75</v>
-      </c>
-      <c r="V126">
-        <v>1.4</v>
-      </c>
-      <c r="W126">
-        <v>1.07</v>
-      </c>
-      <c r="X126">
-        <v>1.02</v>
-      </c>
-      <c r="Y126">
-        <v>1.25</v>
-      </c>
-      <c r="Z126">
-        <v>3.6</v>
-      </c>
-      <c r="AA126">
-        <v>1.83</v>
-      </c>
-      <c r="AB126">
-        <v>1.93</v>
-      </c>
-      <c r="AC126">
-        <v>2.66</v>
-      </c>
       <c r="AD126">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE126">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF126">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AG126">
+        <v>2.05</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126">
+        <v>1.13</v>
+      </c>
+      <c r="AK126">
         <v>2.1</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>1.33</v>
-      </c>
-      <c r="AK126">
-        <v>1.63</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="O127">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="P127">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q127">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="R127">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S127">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T127">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="U127">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V127">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W127">
+        <v>1.07</v>
+      </c>
+      <c r="X127">
+        <v>1.02</v>
+      </c>
+      <c r="Y127">
+        <v>1.25</v>
+      </c>
+      <c r="Z127">
+        <v>3.6</v>
+      </c>
+      <c r="AA127">
+        <v>1.83</v>
+      </c>
+      <c r="AB127">
+        <v>1.93</v>
+      </c>
+      <c r="AC127">
+        <v>2.66</v>
+      </c>
+      <c r="AD127">
+        <v>1.35</v>
+      </c>
+      <c r="AE127">
         <v>1.08</v>
       </c>
-      <c r="X127">
-        <v>1.03</v>
-      </c>
-      <c r="Y127">
-        <v>1.2</v>
-      </c>
-      <c r="Z127">
-        <v>3.71</v>
-      </c>
-      <c r="AA127">
-        <v>1.78</v>
-      </c>
-      <c r="AB127">
-        <v>1.98</v>
-      </c>
-      <c r="AC127">
-        <v>2.7</v>
-      </c>
-      <c r="AD127">
-        <v>1.36</v>
-      </c>
-      <c r="AE127">
-        <v>1.11</v>
-      </c>
       <c r="AF127">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG127">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AK127">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21182,10 +21182,10 @@
         <v>1.79</v>
       </c>
       <c r="Q128">
-        <v>4.22</v>
+        <v>4.25</v>
       </c>
       <c r="R128">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S128">
         <v>1.25</v>
@@ -21194,34 +21194,34 @@
         <v>3.3</v>
       </c>
       <c r="U128">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V128">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W128">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X128">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z128">
         <v>4.1</v>
       </c>
       <c r="AA128">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB128">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC128">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AD128">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE128">
         <v>1.14</v>
@@ -21230,7 +21230,7 @@
         <v>1.53</v>
       </c>
       <c r="AG128">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK128">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21345,55 +21345,55 @@
         <v>10.19</v>
       </c>
       <c r="Q129">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="R129">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="S129">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T129">
         <v>3.9</v>
       </c>
       <c r="U129">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V129">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W129">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X129">
         <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z129">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA129">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB129">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC129">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AD129">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE129">
         <v>1.27</v>
       </c>
       <c r="AF129">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AG129">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK129">
-        <v>3.32</v>
+        <v>3.84</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -22332,10 +22332,10 @@
         <v>1.38</v>
       </c>
       <c r="T135">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="U135">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="V135">
         <v>1.32</v>
@@ -22510,7 +22510,7 @@
         <v>1.02</v>
       </c>
       <c r="Y136">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z136">
         <v>4.05</v>
@@ -22815,7 +22815,7 @@
         <v>1.62</v>
       </c>
       <c r="R138">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="S138">
         <v>1.23</v>
@@ -22860,7 +22860,7 @@
         <v>1.85</v>
       </c>
       <c r="AG138">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>2.1</v>
       </c>
       <c r="AD140">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE140">
         <v>1.3</v>
@@ -23458,10 +23458,10 @@
         <v>2.25</v>
       </c>
       <c r="O142">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P142">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q142">
         <v>2.8</v>
@@ -23491,10 +23491,10 @@
         <v>1.2</v>
       </c>
       <c r="Z142">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="AA142">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB142">
         <v>2.02</v>
@@ -23503,7 +23503,7 @@
         <v>2.75</v>
       </c>
       <c r="AD142">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE142">
         <v>1.1</v>
@@ -23787,7 +23787,7 @@
         <v>3.35</v>
       </c>
       <c r="P144">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q144">
         <v>3</v>
@@ -23826,10 +23826,10 @@
         <v>2.18</v>
       </c>
       <c r="AC144">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AD144">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE144">
         <v>1.22</v>
@@ -24270,7 +24270,7 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O147">
         <v>3.3</v>
@@ -24279,10 +24279,10 @@
         <v>3.6</v>
       </c>
       <c r="Q147">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R147">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S147">
         <v>1.35</v>
@@ -24306,10 +24306,10 @@
         <v>1.26</v>
       </c>
       <c r="Z147">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="AA147">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB147">
         <v>1.9</v>
@@ -24327,7 +24327,7 @@
         <v>1.77</v>
       </c>
       <c r="AG147">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>3.7</v>
       </c>
       <c r="P148">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q148">
         <v>2.52</v>
@@ -24457,7 +24457,7 @@
         <v>2.25</v>
       </c>
       <c r="V148">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W148">
         <v>1.17</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,64 +24596,64 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="O149">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P149">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="Q149">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="R149">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="S149">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T149">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="U149">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="V149">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="W149">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X149">
         <v>1</v>
       </c>
       <c r="Y149">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z149">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA149">
+        <v>1.61</v>
+      </c>
+      <c r="AB149">
+        <v>2.46</v>
+      </c>
+      <c r="AC149">
+        <v>2.33</v>
+      </c>
+      <c r="AD149">
+        <v>1.52</v>
+      </c>
+      <c r="AE149">
+        <v>1.22</v>
+      </c>
+      <c r="AF149">
         <v>1.5</v>
       </c>
-      <c r="AB149">
-        <v>2.55</v>
-      </c>
-      <c r="AC149">
+      <c r="AG149">
         <v>2.45</v>
-      </c>
-      <c r="AD149">
-        <v>1.65</v>
-      </c>
-      <c r="AE149">
-        <v>1.2</v>
-      </c>
-      <c r="AF149">
-        <v>1.53</v>
-      </c>
-      <c r="AG149">
-        <v>2.5</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>1.25</v>
       </c>
       <c r="AK149">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,80 +24759,80 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="O150">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="P150">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q150">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="R150">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="S150">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="T150">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="U150">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="V150">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="W150">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="X150">
         <v>1</v>
       </c>
       <c r="Y150">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Z150">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA150">
+        <v>1.5</v>
+      </c>
+      <c r="AB150">
+        <v>2.55</v>
+      </c>
+      <c r="AC150">
+        <v>2.45</v>
+      </c>
+      <c r="AD150">
+        <v>1.65</v>
+      </c>
+      <c r="AE150">
+        <v>1.2</v>
+      </c>
+      <c r="AF150">
+        <v>1.5</v>
+      </c>
+      <c r="AG150">
+        <v>2.5</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ150">
         <v>1.25</v>
       </c>
-      <c r="AB150">
-        <v>3.75</v>
-      </c>
-      <c r="AC150">
-        <v>1.73</v>
-      </c>
-      <c r="AD150">
-        <v>2.19</v>
-      </c>
-      <c r="AE150">
-        <v>1.49</v>
-      </c>
-      <c r="AF150">
-        <v>1.4</v>
-      </c>
-      <c r="AG150">
-        <v>2.8</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ150">
-        <v>1.17</v>
-      </c>
       <c r="AK150">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK151">
         <v>1.87</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="O152">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="P152">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q152">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="R152">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="S152">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="T152">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="U152">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="V152">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="W152">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="X152">
         <v>1</v>
       </c>
       <c r="Y152">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="Z152">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AA152">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AB152">
-        <v>2.46</v>
+        <v>3.75</v>
       </c>
       <c r="AC152">
-        <v>2.33</v>
+        <v>1.73</v>
       </c>
       <c r="AD152">
-        <v>1.52</v>
+        <v>2.19</v>
       </c>
       <c r="AE152">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AF152">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG152">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK152">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,80 +25248,80 @@
         </is>
       </c>
       <c r="N153">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="O153">
-        <v>3.61</v>
+        <v>4.6</v>
       </c>
       <c r="P153">
-        <v>2.13</v>
+        <v>7.25</v>
       </c>
       <c r="Q153">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="R153">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="S153">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T153">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U153">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="V153">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W153">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X153">
         <v>1.02</v>
       </c>
       <c r="Y153">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z153">
-        <v>4.09</v>
+        <v>3.75</v>
       </c>
       <c r="AA153">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AB153">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC153">
+        <v>3.08</v>
+      </c>
+      <c r="AD153">
+        <v>1.38</v>
+      </c>
+      <c r="AE153">
+        <v>1.08</v>
+      </c>
+      <c r="AF153">
+        <v>2</v>
+      </c>
+      <c r="AG153">
+        <v>1.74</v>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ153">
+        <v>1.11</v>
+      </c>
+      <c r="AK153">
         <v>2.8</v>
-      </c>
-      <c r="AD153">
-        <v>1.4</v>
-      </c>
-      <c r="AE153">
-        <v>1.1</v>
-      </c>
-      <c r="AF153">
-        <v>1.6</v>
-      </c>
-      <c r="AG153">
-        <v>2.3</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ153">
-        <v>1.68</v>
-      </c>
-      <c r="AK153">
-        <v>1.39</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="O154">
-        <v>4.6</v>
+        <v>3.61</v>
       </c>
       <c r="P154">
-        <v>7.25</v>
+        <v>2.13</v>
       </c>
       <c r="Q154">
-        <v>1.98</v>
+        <v>3.3</v>
       </c>
       <c r="R154">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="S154">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T154">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="U154">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="V154">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W154">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X154">
         <v>1.02</v>
       </c>
       <c r="Y154">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z154">
-        <v>3.75</v>
+        <v>4.09</v>
       </c>
       <c r="AA154">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AB154">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC154">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AD154">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE154">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF154">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AG154">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="AK154">
-        <v>2.8</v>
+        <v>1.39</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -26751,19 +26751,19 @@
         <v>1.18</v>
       </c>
       <c r="Z162">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="AA162">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB162">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC162">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AD162">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE162">
         <v>1.14</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,25 +27530,25 @@
         </is>
       </c>
       <c r="N167">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="O167">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="P167">
-        <v>1.57</v>
+        <v>6</v>
       </c>
       <c r="Q167">
-        <v>5.55</v>
+        <v>1.91</v>
       </c>
       <c r="R167">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S167">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T167">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U167">
         <v>2.6</v>
@@ -27557,38 +27557,38 @@
         <v>1.44</v>
       </c>
       <c r="W167">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X167">
         <v>1.02</v>
       </c>
       <c r="Y167">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z167">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AA167">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB167">
+        <v>2.05</v>
+      </c>
+      <c r="AC167">
+        <v>3</v>
+      </c>
+      <c r="AD167">
+        <v>1.4</v>
+      </c>
+      <c r="AE167">
+        <v>1.13</v>
+      </c>
+      <c r="AF167">
+        <v>1.93</v>
+      </c>
+      <c r="AG167">
         <v>1.87</v>
       </c>
-      <c r="AC167">
-        <v>2.92</v>
-      </c>
-      <c r="AD167">
-        <v>1.32</v>
-      </c>
-      <c r="AE167">
-        <v>1.11</v>
-      </c>
-      <c r="AF167">
-        <v>1.85</v>
-      </c>
-      <c r="AG167">
-        <v>1.85</v>
-      </c>
       <c r="AH167" t="inlineStr">
         <is>
           <t>[]</t>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK167">
-        <v>1.14</v>
+        <v>2.8</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,25 +27693,25 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="O168">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="P168">
-        <v>6</v>
+        <v>1.57</v>
       </c>
       <c r="Q168">
-        <v>1.91</v>
+        <v>5.55</v>
       </c>
       <c r="R168">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S168">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T168">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U168">
         <v>2.6</v>
@@ -27720,37 +27720,37 @@
         <v>1.44</v>
       </c>
       <c r="W168">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X168">
         <v>1.02</v>
       </c>
       <c r="Y168">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z168">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AA168">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB168">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AC168">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AD168">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AE168">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF168">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG168">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK168">
-        <v>2.8</v>
+        <v>1.14</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,58 +28997,58 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.95</v>
+        <v>1.61</v>
       </c>
       <c r="O176">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P176">
-        <v>2.15</v>
+        <v>4.72</v>
       </c>
       <c r="Q176">
-        <v>3.5</v>
+        <v>2.13</v>
       </c>
       <c r="R176">
-        <v>2.11</v>
+        <v>2.47</v>
       </c>
       <c r="S176">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T176">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U176">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="V176">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W176">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X176">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z176">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA176">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AB176">
-        <v>2.01</v>
+        <v>2.27</v>
       </c>
       <c r="AC176">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="AD176">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE176">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF176">
         <v>1.67</v>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK176">
-        <v>1.3</v>
+        <v>2.19</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,58 +29160,58 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.61</v>
+        <v>2.95</v>
       </c>
       <c r="O177">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P177">
-        <v>4.72</v>
+        <v>2.15</v>
       </c>
       <c r="Q177">
-        <v>2.13</v>
+        <v>3.5</v>
       </c>
       <c r="R177">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="S177">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T177">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="U177">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="V177">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W177">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y177">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z177">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA177">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AB177">
-        <v>2.27</v>
+        <v>2.01</v>
       </c>
       <c r="AC177">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="AD177">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AE177">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF177">
         <v>1.67</v>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK177">
-        <v>2.19</v>
+        <v>1.3</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29652,7 +29652,7 @@
         <v>1.15</v>
       </c>
       <c r="O180">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="P180">
         <v>10</v>
@@ -29691,7 +29691,7 @@
         <v>1.16</v>
       </c>
       <c r="AB180">
-        <v>5.17</v>
+        <v>5.2</v>
       </c>
       <c r="AC180">
         <v>1.45</v>
@@ -29722,7 +29722,7 @@
         <v>1.04</v>
       </c>
       <c r="AK180">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29827,10 +29827,10 @@
         <v>3.34</v>
       </c>
       <c r="S181">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T181">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="U181">
         <v>1.91</v>
@@ -29839,7 +29839,7 @@
         <v>1.85</v>
       </c>
       <c r="W181">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X181">
         <v>1.01</v>
@@ -29866,10 +29866,10 @@
         <v>1.36</v>
       </c>
       <c r="AF181">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG181">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK181">
         <v>6.55</v>
@@ -29984,16 +29984,16 @@
         <v>0</v>
       </c>
       <c r="Q182">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R182">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S182">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T182">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="U182">
         <v>2.53</v>
@@ -30011,19 +30011,19 @@
         <v>1.18</v>
       </c>
       <c r="Z182">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="AA182">
         <v>1.7</v>
       </c>
       <c r="AB182">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC182">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD182">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE182">
         <v>1.09</v>
@@ -30048,7 +30048,7 @@
         <v>1.22</v>
       </c>
       <c r="AK182">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="O186">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="P186">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q186">
         <v>1.95</v>
       </c>
       <c r="R186">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="S186">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="T186">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U186">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="V186">
-        <v>1.75</v>
+        <v>2.54</v>
       </c>
       <c r="W186">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="X186">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y186">
+        <v>1.01</v>
+      </c>
+      <c r="Z186">
+        <v>15</v>
+      </c>
+      <c r="AA186">
         <v>1.1</v>
       </c>
-      <c r="Z186">
-        <v>5.14</v>
-      </c>
-      <c r="AA186">
-        <v>1.39</v>
-      </c>
       <c r="AB186">
-        <v>2.59</v>
+        <v>6.5</v>
       </c>
       <c r="AC186">
-        <v>2.06</v>
+        <v>1.29</v>
       </c>
       <c r="AD186">
-        <v>1.7</v>
+        <v>3.04</v>
       </c>
       <c r="AE186">
-        <v>1.26</v>
+        <v>1.98</v>
       </c>
       <c r="AF186">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="AG186">
-        <v>2.3</v>
+        <v>4.65</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>1.13</v>
       </c>
       <c r="AK186">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
+        <v>1.51</v>
+      </c>
+      <c r="O187">
+        <v>4.35</v>
+      </c>
+      <c r="P187">
+        <v>4.4</v>
+      </c>
+      <c r="Q187">
+        <v>1.92</v>
+      </c>
+      <c r="R187">
+        <v>2.97</v>
+      </c>
+      <c r="S187">
+        <v>1.14</v>
+      </c>
+      <c r="T187">
+        <v>5</v>
+      </c>
+      <c r="U187">
+        <v>1.76</v>
+      </c>
+      <c r="V187">
+        <v>1.98</v>
+      </c>
+      <c r="W187">
+        <v>1.3</v>
+      </c>
+      <c r="X187">
+        <v>1.01</v>
+      </c>
+      <c r="Y187">
+        <v>1.03</v>
+      </c>
+      <c r="Z187">
+        <v>7.4</v>
+      </c>
+      <c r="AA187">
+        <v>1.25</v>
+      </c>
+      <c r="AB187">
+        <v>3.5</v>
+      </c>
+      <c r="AC187">
         <v>1.66</v>
       </c>
-      <c r="O187">
-        <v>4.4</v>
-      </c>
-      <c r="P187">
-        <v>3.35</v>
-      </c>
-      <c r="Q187">
-        <v>1.95</v>
-      </c>
-      <c r="R187">
-        <v>3.1</v>
-      </c>
-      <c r="S187">
-        <v>1.07</v>
-      </c>
-      <c r="T187">
-        <v>7</v>
-      </c>
-      <c r="U187">
-        <v>1.44</v>
-      </c>
-      <c r="V187">
-        <v>2.54</v>
-      </c>
-      <c r="W187">
+      <c r="AD187">
+        <v>2.14</v>
+      </c>
+      <c r="AE187">
         <v>1.5</v>
       </c>
-      <c r="X187">
-        <v>0</v>
-      </c>
-      <c r="Y187">
-        <v>1.01</v>
-      </c>
-      <c r="Z187">
-        <v>15</v>
-      </c>
-      <c r="AA187">
-        <v>1.1</v>
-      </c>
-      <c r="AB187">
-        <v>6.5</v>
-      </c>
-      <c r="AC187">
-        <v>1.29</v>
-      </c>
-      <c r="AD187">
-        <v>3.04</v>
-      </c>
-      <c r="AE187">
-        <v>1.98</v>
-      </c>
       <c r="AF187">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AG187">
-        <v>4.65</v>
+        <v>3</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK187">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="O188">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="P188">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q188">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R188">
-        <v>2.97</v>
+        <v>2.43</v>
       </c>
       <c r="S188">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T188">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U188">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="V188">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="W188">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X188">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y188">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z188">
-        <v>7.4</v>
+        <v>5.14</v>
       </c>
       <c r="AA188">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AB188">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="AC188">
-        <v>1.66</v>
+        <v>2.06</v>
       </c>
       <c r="AD188">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="AE188">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AF188">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AG188">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK188">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="O193">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P193">
-        <v>2.63</v>
+        <v>4.16</v>
       </c>
       <c r="Q193">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="R193">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S193">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T193">
-        <v>2.97</v>
+        <v>3.78</v>
       </c>
       <c r="U193">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="V193">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="W193">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X193">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y193">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z193">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA193">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="AB193">
-        <v>1.79</v>
+        <v>2.64</v>
       </c>
       <c r="AC193">
-        <v>3.37</v>
+        <v>2.15</v>
       </c>
       <c r="AD193">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AE193">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AF193">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AG193">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK193">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>3.62</v>
+        <v>1.37</v>
       </c>
       <c r="O194">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="P194">
-        <v>1.92</v>
+        <v>7.75</v>
       </c>
       <c r="Q194">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="R194">
-        <v>2.13</v>
+        <v>2.51</v>
       </c>
       <c r="S194">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T194">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="U194">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="V194">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="W194">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X194">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y194">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z194">
-        <v>3.48</v>
+        <v>4.75</v>
       </c>
       <c r="AA194">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AB194">
-        <v>1.97</v>
+        <v>2.36</v>
       </c>
       <c r="AC194">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AD194">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AE194">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF194">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG194">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.8</v>
+        <v>1.14</v>
       </c>
       <c r="AK194">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.34</v>
+        <v>3.62</v>
       </c>
       <c r="O195">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="P195">
-        <v>2.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R195">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S195">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T195">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U195">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V195">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W195">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X195">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y195">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z195">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="AA195">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AB195">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AC195">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AD195">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE195">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF195">
         <v>1.7</v>
       </c>
       <c r="AG195">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
+        <v>1.8</v>
+      </c>
+      <c r="AK195">
         <v>1.25</v>
-      </c>
-      <c r="AK195">
-        <v>1.5</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,80 +32257,80 @@
         </is>
       </c>
       <c r="N196">
+        <v>2.34</v>
+      </c>
+      <c r="O196">
+        <v>3.34</v>
+      </c>
+      <c r="P196">
+        <v>2.91</v>
+      </c>
+      <c r="Q196">
+        <v>3</v>
+      </c>
+      <c r="R196">
+        <v>2.1</v>
+      </c>
+      <c r="S196">
         <v>1.37</v>
       </c>
-      <c r="O196">
-        <v>5</v>
-      </c>
-      <c r="P196">
-        <v>7.75</v>
-      </c>
-      <c r="Q196">
-        <v>1.73</v>
-      </c>
-      <c r="R196">
-        <v>2.51</v>
-      </c>
-      <c r="S196">
+      <c r="T196">
+        <v>3</v>
+      </c>
+      <c r="U196">
+        <v>2.88</v>
+      </c>
+      <c r="V196">
+        <v>1.36</v>
+      </c>
+      <c r="W196">
+        <v>1.06</v>
+      </c>
+      <c r="X196">
+        <v>1.03</v>
+      </c>
+      <c r="Y196">
+        <v>1.3</v>
+      </c>
+      <c r="Z196">
+        <v>3.28</v>
+      </c>
+      <c r="AA196">
+        <v>1.87</v>
+      </c>
+      <c r="AB196">
+        <v>1.81</v>
+      </c>
+      <c r="AC196">
+        <v>3.35</v>
+      </c>
+      <c r="AD196">
+        <v>1.27</v>
+      </c>
+      <c r="AE196">
+        <v>1.06</v>
+      </c>
+      <c r="AF196">
+        <v>1.7</v>
+      </c>
+      <c r="AG196">
+        <v>2.01</v>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ196">
         <v>1.25</v>
       </c>
-      <c r="T196">
-        <v>3.7</v>
-      </c>
-      <c r="U196">
-        <v>2.21</v>
-      </c>
-      <c r="V196">
-        <v>1.56</v>
-      </c>
-      <c r="W196">
-        <v>1.14</v>
-      </c>
-      <c r="X196">
-        <v>1.01</v>
-      </c>
-      <c r="Y196">
-        <v>1.13</v>
-      </c>
-      <c r="Z196">
-        <v>4.75</v>
-      </c>
-      <c r="AA196">
-        <v>1.6</v>
-      </c>
-      <c r="AB196">
-        <v>2.36</v>
-      </c>
-      <c r="AC196">
-        <v>2.35</v>
-      </c>
-      <c r="AD196">
-        <v>1.54</v>
-      </c>
-      <c r="AE196">
-        <v>1.15</v>
-      </c>
-      <c r="AF196">
-        <v>1.85</v>
-      </c>
-      <c r="AG196">
-        <v>1.85<